--- a/Precios_Metales_COP.xlsx
+++ b/Precios_Metales_COP.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Precios Diarios" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Precios Diarios'!$A$1:$H$485</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Precios Diarios'!$A$1:$H$486</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -321,12 +321,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard y Gráficos'!$P$2:$P$485</f>
+              <f>'Dashboard y Gráficos'!$P$2:$P$486</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$Q$2:$Q$485</f>
+              <f>'Dashboard y Gráficos'!$Q$2:$Q$486</f>
             </numRef>
           </val>
         </ser>
@@ -446,12 +446,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard y Gráficos'!$P$2:$P$485</f>
+              <f>'Dashboard y Gráficos'!$P$2:$P$486</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$R$2:$R$485</f>
+              <f>'Dashboard y Gráficos'!$R$2:$R$486</f>
             </numRef>
           </val>
         </ser>
@@ -570,12 +570,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard y Gráficos'!$P$2:$P$485</f>
+              <f>'Dashboard y Gráficos'!$P$2:$P$486</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$Q$2:$Q$485</f>
+              <f>'Dashboard y Gráficos'!$Q$2:$Q$486</f>
             </numRef>
           </val>
         </ser>
@@ -610,7 +610,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$R$2:$R$485</f>
+              <f>'Dashboard y Gráficos'!$R$2:$R$486</f>
             </numRef>
           </val>
         </ser>
@@ -1074,7 +1074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R485"/>
+  <dimension ref="A1:R486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1118,15 +1118,15 @@
     </row>
     <row r="2">
       <c r="P2" s="2">
-        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 1 - 1), NA())</f>
+        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 1 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q2">
-        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 1 - 1), NA())</f>
+        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 1 - 1), NA())</f>
         <v/>
       </c>
       <c r="R2">
-        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 1 - 1), NA())</f>
+        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 1 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1166,58 +1166,58 @@
       </c>
       <c r="N3" s="4" t="n"/>
       <c r="P3" s="2">
-        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 2 - 1), NA())</f>
+        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 2 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q3">
-        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 2 - 1), NA())</f>
+        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 2 - 1), NA())</f>
         <v/>
       </c>
       <c r="R3">
-        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 2 - 1), NA())</f>
+        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 2 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5">
-        <f>'Precios Diarios'!A485</f>
+        <f>'Precios Diarios'!A486</f>
         <v/>
       </c>
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="6">
-        <f>'Precios Diarios'!E485</f>
+        <f>'Precios Diarios'!E486</f>
         <v/>
       </c>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="6">
-        <f>'Precios Diarios'!F485</f>
+        <f>'Precios Diarios'!F486</f>
         <v/>
       </c>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="6">
-        <f>'Precios Diarios'!D485</f>
+        <f>'Precios Diarios'!D486</f>
         <v/>
       </c>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="7">
-        <f>'Precios Diarios'!G485</f>
+        <f>'Precios Diarios'!G486</f>
         <v/>
       </c>
       <c r="N4" s="4" t="n"/>
       <c r="P4" s="2">
-        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 3 - 1), NA())</f>
+        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 3 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q4">
-        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 3 - 1), NA())</f>
+        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 3 - 1), NA())</f>
         <v/>
       </c>
       <c r="R4">
-        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 3 - 1), NA())</f>
+        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 3 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1237,29 +1237,29 @@
       <c r="M5" s="4" t="n"/>
       <c r="N5" s="4" t="n"/>
       <c r="P5" s="2">
-        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 4 - 1), NA())</f>
+        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 4 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q5">
-        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 4 - 1), NA())</f>
+        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 4 - 1), NA())</f>
         <v/>
       </c>
       <c r="R5">
-        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 4 - 1), NA())</f>
+        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 4 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="P6" s="2">
-        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 5 - 1), NA())</f>
+        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 5 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q6">
-        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 5 - 1), NA())</f>
+        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 5 - 1), NA())</f>
         <v/>
       </c>
       <c r="R6">
-        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 5 - 1), NA())</f>
+        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 5 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1270,15 +1270,15 @@
         </is>
       </c>
       <c r="P7" s="2">
-        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 6 - 1), NA())</f>
+        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 6 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q7">
-        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 6 - 1), NA())</f>
+        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 6 - 1), NA())</f>
         <v/>
       </c>
       <c r="R7">
-        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 6 - 1), NA())</f>
+        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 6 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1297,11 +1297,11 @@
         <v/>
       </c>
       <c r="G8" s="11">
-        <f>IFERROR(MATCH(E8, 'Precios Diarios'!$A$2:$A$485, 1), 1) + 1</f>
+        <f>IFERROR(MATCH(E8, 'Precios Diarios'!$A$2:$A$486, 1), 1) + 1</f>
         <v/>
       </c>
       <c r="H8" s="11">
-        <f>IFERROR(MATCH(F8, 'Precios Diarios'!$A$2:$A$485, 1), 484) + 1</f>
+        <f>IFERROR(MATCH(F8, 'Precios Diarios'!$A$2:$A$486, 1), 485) + 1</f>
         <v/>
       </c>
       <c r="I8" s="11">
@@ -1309,15 +1309,15 @@
         <v/>
       </c>
       <c r="P8" s="2">
-        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 7 - 1), NA())</f>
+        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 7 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q8">
-        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 7 - 1), NA())</f>
+        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 7 - 1), NA())</f>
         <v/>
       </c>
       <c r="R8">
-        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 7 - 1), NA())</f>
+        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 7 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1328,6679 +1328,6693 @@
         </is>
       </c>
       <c r="P9" s="2">
-        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 8 - 1), NA())</f>
+        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 8 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q9">
-        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 8 - 1), NA())</f>
+        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 8 - 1), NA())</f>
         <v/>
       </c>
       <c r="R9">
-        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 8 - 1), NA())</f>
+        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 8 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="P10" s="2">
-        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 9 - 1), NA())</f>
+        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 9 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q10">
-        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 9 - 1), NA())</f>
+        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 9 - 1), NA())</f>
         <v/>
       </c>
       <c r="R10">
-        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 9 - 1), NA())</f>
+        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 9 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="P11" s="2">
-        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 10 - 1), NA())</f>
+        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 10 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q11">
-        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 10 - 1), NA())</f>
+        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 10 - 1), NA())</f>
         <v/>
       </c>
       <c r="R11">
-        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 10 - 1), NA())</f>
+        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 10 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="P12" s="2">
-        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 11 - 1), NA())</f>
+        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 11 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q12">
-        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 11 - 1), NA())</f>
+        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 11 - 1), NA())</f>
         <v/>
       </c>
       <c r="R12">
-        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 11 - 1), NA())</f>
+        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 11 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="P13" s="2">
-        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 12 - 1), NA())</f>
+        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 12 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q13">
-        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 12 - 1), NA())</f>
+        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 12 - 1), NA())</f>
         <v/>
       </c>
       <c r="R13">
-        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 12 - 1), NA())</f>
+        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 12 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="P14" s="2">
-        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 13 - 1), NA())</f>
+        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 13 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q14">
-        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 13 - 1), NA())</f>
+        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 13 - 1), NA())</f>
         <v/>
       </c>
       <c r="R14">
-        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 13 - 1), NA())</f>
+        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 13 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="P15" s="2">
-        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 14 - 1), NA())</f>
+        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 14 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q15">
-        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 14 - 1), NA())</f>
+        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 14 - 1), NA())</f>
         <v/>
       </c>
       <c r="R15">
-        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 14 - 1), NA())</f>
+        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 14 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="P16" s="2">
-        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 15 - 1), NA())</f>
+        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 15 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q16">
-        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 15 - 1), NA())</f>
+        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 15 - 1), NA())</f>
         <v/>
       </c>
       <c r="R16">
-        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 15 - 1), NA())</f>
+        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 15 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="P17" s="2">
-        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 16 - 1), NA())</f>
+        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 16 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q17">
-        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 16 - 1), NA())</f>
+        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 16 - 1), NA())</f>
         <v/>
       </c>
       <c r="R17">
-        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 16 - 1), NA())</f>
+        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 16 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="P18" s="2">
-        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 17 - 1), NA())</f>
+        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 17 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q18">
-        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 17 - 1), NA())</f>
+        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 17 - 1), NA())</f>
         <v/>
       </c>
       <c r="R18">
-        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 17 - 1), NA())</f>
+        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 17 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="P19" s="2">
-        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 18 - 1), NA())</f>
+        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 18 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q19">
-        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 18 - 1), NA())</f>
+        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 18 - 1), NA())</f>
         <v/>
       </c>
       <c r="R19">
-        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 18 - 1), NA())</f>
+        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 18 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="P20" s="2">
-        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 19 - 1), NA())</f>
+        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 19 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q20">
-        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 19 - 1), NA())</f>
+        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 19 - 1), NA())</f>
         <v/>
       </c>
       <c r="R20">
-        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 19 - 1), NA())</f>
+        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 19 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="P21" s="2">
-        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 20 - 1), NA())</f>
+        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 20 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q21">
-        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 20 - 1), NA())</f>
+        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 20 - 1), NA())</f>
         <v/>
       </c>
       <c r="R21">
-        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 20 - 1), NA())</f>
+        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 20 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="P22" s="2">
-        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 21 - 1), NA())</f>
+        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 21 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q22">
-        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 21 - 1), NA())</f>
+        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 21 - 1), NA())</f>
         <v/>
       </c>
       <c r="R22">
-        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 21 - 1), NA())</f>
+        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 21 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="P23" s="2">
-        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 22 - 1), NA())</f>
+        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 22 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q23">
-        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 22 - 1), NA())</f>
+        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 22 - 1), NA())</f>
         <v/>
       </c>
       <c r="R23">
-        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 22 - 1), NA())</f>
+        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 22 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="P24" s="2">
-        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 23 - 1), NA())</f>
+        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 23 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q24">
-        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 23 - 1), NA())</f>
+        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 23 - 1), NA())</f>
         <v/>
       </c>
       <c r="R24">
-        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 23 - 1), NA())</f>
+        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 23 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="P25" s="2">
-        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 24 - 1), NA())</f>
+        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 24 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q25">
-        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 24 - 1), NA())</f>
+        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 24 - 1), NA())</f>
         <v/>
       </c>
       <c r="R25">
-        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 24 - 1), NA())</f>
+        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 24 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="P26" s="2">
-        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 25 - 1), NA())</f>
+        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 25 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q26">
-        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 25 - 1), NA())</f>
+        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 25 - 1), NA())</f>
         <v/>
       </c>
       <c r="R26">
-        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 25 - 1), NA())</f>
+        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 25 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="P27" s="2">
-        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 26 - 1), NA())</f>
+        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 26 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q27">
-        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 26 - 1), NA())</f>
+        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 26 - 1), NA())</f>
         <v/>
       </c>
       <c r="R27">
-        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 26 - 1), NA())</f>
+        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 26 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="P28" s="2">
-        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 27 - 1), NA())</f>
+        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 27 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q28">
-        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 27 - 1), NA())</f>
+        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 27 - 1), NA())</f>
         <v/>
       </c>
       <c r="R28">
-        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 27 - 1), NA())</f>
+        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 27 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="P29" s="2">
-        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 28 - 1), NA())</f>
+        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 28 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q29">
-        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 28 - 1), NA())</f>
+        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 28 - 1), NA())</f>
         <v/>
       </c>
       <c r="R29">
-        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 28 - 1), NA())</f>
+        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 28 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="P30" s="2">
-        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 29 - 1), NA())</f>
+        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 29 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q30">
-        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 29 - 1), NA())</f>
+        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 29 - 1), NA())</f>
         <v/>
       </c>
       <c r="R30">
-        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 29 - 1), NA())</f>
+        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 29 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="P31" s="2">
-        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 30 - 1), NA())</f>
+        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 30 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q31">
-        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 30 - 1), NA())</f>
+        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 30 - 1), NA())</f>
         <v/>
       </c>
       <c r="R31">
-        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 30 - 1), NA())</f>
+        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 30 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="P32" s="2">
-        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 31 - 1), NA())</f>
+        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 31 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q32">
-        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 31 - 1), NA())</f>
+        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 31 - 1), NA())</f>
         <v/>
       </c>
       <c r="R32">
-        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 31 - 1), NA())</f>
+        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 31 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="P33" s="2">
-        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 32 - 1), NA())</f>
+        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 32 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q33">
-        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 32 - 1), NA())</f>
+        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 32 - 1), NA())</f>
         <v/>
       </c>
       <c r="R33">
-        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 32 - 1), NA())</f>
+        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 32 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="P34" s="2">
-        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 33 - 1), NA())</f>
+        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 33 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q34">
-        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 33 - 1), NA())</f>
+        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 33 - 1), NA())</f>
         <v/>
       </c>
       <c r="R34">
-        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 33 - 1), NA())</f>
+        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 33 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="P35" s="2">
-        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 34 - 1), NA())</f>
+        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 34 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q35">
-        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 34 - 1), NA())</f>
+        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 34 - 1), NA())</f>
         <v/>
       </c>
       <c r="R35">
-        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 34 - 1), NA())</f>
+        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 34 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="P36" s="2">
-        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 35 - 1), NA())</f>
+        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 35 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q36">
-        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 35 - 1), NA())</f>
+        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 35 - 1), NA())</f>
         <v/>
       </c>
       <c r="R36">
-        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 35 - 1), NA())</f>
+        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 35 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="P37" s="2">
-        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 36 - 1), NA())</f>
+        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 36 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q37">
-        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 36 - 1), NA())</f>
+        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 36 - 1), NA())</f>
         <v/>
       </c>
       <c r="R37">
-        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 36 - 1), NA())</f>
+        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 36 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="P38" s="2">
-        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 37 - 1), NA())</f>
+        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 37 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q38">
-        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 37 - 1), NA())</f>
+        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 37 - 1), NA())</f>
         <v/>
       </c>
       <c r="R38">
-        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 37 - 1), NA())</f>
+        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 37 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="P39" s="2">
-        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 38 - 1), NA())</f>
+        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 38 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q39">
-        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 38 - 1), NA())</f>
+        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 38 - 1), NA())</f>
         <v/>
       </c>
       <c r="R39">
-        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 38 - 1), NA())</f>
+        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 38 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="P40" s="2">
-        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 39 - 1), NA())</f>
+        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 39 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q40">
-        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 39 - 1), NA())</f>
+        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 39 - 1), NA())</f>
         <v/>
       </c>
       <c r="R40">
-        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 39 - 1), NA())</f>
+        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 39 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="P41" s="2">
-        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 40 - 1), NA())</f>
+        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 40 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q41">
-        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 40 - 1), NA())</f>
+        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 40 - 1), NA())</f>
         <v/>
       </c>
       <c r="R41">
-        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 40 - 1), NA())</f>
+        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 40 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="P42" s="2">
-        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 41 - 1), NA())</f>
+        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 41 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q42">
-        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 41 - 1), NA())</f>
+        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 41 - 1), NA())</f>
         <v/>
       </c>
       <c r="R42">
-        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 41 - 1), NA())</f>
+        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 41 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="P43" s="2">
-        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 42 - 1), NA())</f>
+        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 42 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q43">
-        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 42 - 1), NA())</f>
+        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 42 - 1), NA())</f>
         <v/>
       </c>
       <c r="R43">
-        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 42 - 1), NA())</f>
+        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 42 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="P44" s="2">
-        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 43 - 1), NA())</f>
+        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 43 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q44">
-        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 43 - 1), NA())</f>
+        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 43 - 1), NA())</f>
         <v/>
       </c>
       <c r="R44">
-        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 43 - 1), NA())</f>
+        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 43 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="P45" s="2">
-        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 44 - 1), NA())</f>
+        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 44 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q45">
-        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 44 - 1), NA())</f>
+        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 44 - 1), NA())</f>
         <v/>
       </c>
       <c r="R45">
-        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 44 - 1), NA())</f>
+        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 44 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="P46" s="2">
-        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 45 - 1), NA())</f>
+        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 45 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q46">
-        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 45 - 1), NA())</f>
+        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 45 - 1), NA())</f>
         <v/>
       </c>
       <c r="R46">
-        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 45 - 1), NA())</f>
+        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 45 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="P47" s="2">
-        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 46 - 1), NA())</f>
+        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 46 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q47">
-        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 46 - 1), NA())</f>
+        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 46 - 1), NA())</f>
         <v/>
       </c>
       <c r="R47">
-        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 46 - 1), NA())</f>
+        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 46 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="P48" s="2">
-        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 47 - 1), NA())</f>
+        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 47 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q48">
-        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 47 - 1), NA())</f>
+        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 47 - 1), NA())</f>
         <v/>
       </c>
       <c r="R48">
-        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 47 - 1), NA())</f>
+        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 47 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="P49" s="2">
-        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 48 - 1), NA())</f>
+        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 48 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q49">
-        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 48 - 1), NA())</f>
+        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 48 - 1), NA())</f>
         <v/>
       </c>
       <c r="R49">
-        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 48 - 1), NA())</f>
+        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 48 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="P50" s="2">
-        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 49 - 1), NA())</f>
+        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 49 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q50">
-        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 49 - 1), NA())</f>
+        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 49 - 1), NA())</f>
         <v/>
       </c>
       <c r="R50">
-        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 49 - 1), NA())</f>
+        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 49 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="P51" s="2">
-        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 50 - 1), NA())</f>
+        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 50 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q51">
-        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 50 - 1), NA())</f>
+        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 50 - 1), NA())</f>
         <v/>
       </c>
       <c r="R51">
-        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 50 - 1), NA())</f>
+        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 50 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="P52" s="2">
-        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 51 - 1), NA())</f>
+        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 51 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q52">
-        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 51 - 1), NA())</f>
+        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 51 - 1), NA())</f>
         <v/>
       </c>
       <c r="R52">
-        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 51 - 1), NA())</f>
+        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 51 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="P53" s="2">
-        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 52 - 1), NA())</f>
+        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 52 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q53">
-        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 52 - 1), NA())</f>
+        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 52 - 1), NA())</f>
         <v/>
       </c>
       <c r="R53">
-        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 52 - 1), NA())</f>
+        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 52 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="P54" s="2">
-        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 53 - 1), NA())</f>
+        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 53 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q54">
-        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 53 - 1), NA())</f>
+        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 53 - 1), NA())</f>
         <v/>
       </c>
       <c r="R54">
-        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 53 - 1), NA())</f>
+        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 53 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="P55" s="2">
-        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 54 - 1), NA())</f>
+        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 54 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q55">
-        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 54 - 1), NA())</f>
+        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 54 - 1), NA())</f>
         <v/>
       </c>
       <c r="R55">
-        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 54 - 1), NA())</f>
+        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 54 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="P56" s="2">
-        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 55 - 1), NA())</f>
+        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 55 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q56">
-        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 55 - 1), NA())</f>
+        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 55 - 1), NA())</f>
         <v/>
       </c>
       <c r="R56">
-        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 55 - 1), NA())</f>
+        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 55 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="P57" s="2">
-        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 56 - 1), NA())</f>
+        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 56 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q57">
-        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 56 - 1), NA())</f>
+        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 56 - 1), NA())</f>
         <v/>
       </c>
       <c r="R57">
-        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 56 - 1), NA())</f>
+        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 56 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="P58" s="2">
-        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 57 - 1), NA())</f>
+        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 57 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q58">
-        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 57 - 1), NA())</f>
+        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 57 - 1), NA())</f>
         <v/>
       </c>
       <c r="R58">
-        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 57 - 1), NA())</f>
+        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 57 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="P59" s="2">
-        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 58 - 1), NA())</f>
+        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 58 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q59">
-        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 58 - 1), NA())</f>
+        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 58 - 1), NA())</f>
         <v/>
       </c>
       <c r="R59">
-        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 58 - 1), NA())</f>
+        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 58 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="P60" s="2">
-        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 59 - 1), NA())</f>
+        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 59 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q60">
-        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 59 - 1), NA())</f>
+        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 59 - 1), NA())</f>
         <v/>
       </c>
       <c r="R60">
-        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 59 - 1), NA())</f>
+        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 59 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="P61" s="2">
-        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 60 - 1), NA())</f>
+        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 60 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q61">
-        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 60 - 1), NA())</f>
+        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 60 - 1), NA())</f>
         <v/>
       </c>
       <c r="R61">
-        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 60 - 1), NA())</f>
+        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 60 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="P62" s="2">
-        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 61 - 1), NA())</f>
+        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 61 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q62">
-        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 61 - 1), NA())</f>
+        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 61 - 1), NA())</f>
         <v/>
       </c>
       <c r="R62">
-        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 61 - 1), NA())</f>
+        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 61 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="P63" s="2">
-        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 62 - 1), NA())</f>
+        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 62 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q63">
-        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 62 - 1), NA())</f>
+        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 62 - 1), NA())</f>
         <v/>
       </c>
       <c r="R63">
-        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 62 - 1), NA())</f>
+        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 62 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="P64" s="2">
-        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 63 - 1), NA())</f>
+        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 63 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q64">
-        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 63 - 1), NA())</f>
+        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 63 - 1), NA())</f>
         <v/>
       </c>
       <c r="R64">
-        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 63 - 1), NA())</f>
+        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 63 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="P65" s="2">
-        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 64 - 1), NA())</f>
+        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 64 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q65">
-        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 64 - 1), NA())</f>
+        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 64 - 1), NA())</f>
         <v/>
       </c>
       <c r="R65">
-        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 64 - 1), NA())</f>
+        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 64 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="P66" s="2">
-        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 65 - 1), NA())</f>
+        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 65 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q66">
-        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 65 - 1), NA())</f>
+        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 65 - 1), NA())</f>
         <v/>
       </c>
       <c r="R66">
-        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 65 - 1), NA())</f>
+        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 65 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="P67" s="2">
-        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 66 - 1), NA())</f>
+        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 66 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q67">
-        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 66 - 1), NA())</f>
+        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 66 - 1), NA())</f>
         <v/>
       </c>
       <c r="R67">
-        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 66 - 1), NA())</f>
+        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 66 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="P68" s="2">
-        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 67 - 1), NA())</f>
+        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 67 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q68">
-        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 67 - 1), NA())</f>
+        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 67 - 1), NA())</f>
         <v/>
       </c>
       <c r="R68">
-        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 67 - 1), NA())</f>
+        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 67 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="P69" s="2">
-        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 68 - 1), NA())</f>
+        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 68 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q69">
-        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 68 - 1), NA())</f>
+        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 68 - 1), NA())</f>
         <v/>
       </c>
       <c r="R69">
-        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 68 - 1), NA())</f>
+        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 68 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="P70" s="2">
-        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 69 - 1), NA())</f>
+        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 69 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q70">
-        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 69 - 1), NA())</f>
+        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 69 - 1), NA())</f>
         <v/>
       </c>
       <c r="R70">
-        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 69 - 1), NA())</f>
+        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 69 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="P71" s="2">
-        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 70 - 1), NA())</f>
+        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 70 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q71">
-        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 70 - 1), NA())</f>
+        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 70 - 1), NA())</f>
         <v/>
       </c>
       <c r="R71">
-        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 70 - 1), NA())</f>
+        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 70 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="P72" s="2">
-        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 71 - 1), NA())</f>
+        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 71 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q72">
-        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 71 - 1), NA())</f>
+        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 71 - 1), NA())</f>
         <v/>
       </c>
       <c r="R72">
-        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 71 - 1), NA())</f>
+        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 71 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="P73" s="2">
-        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 72 - 1), NA())</f>
+        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 72 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q73">
-        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 72 - 1), NA())</f>
+        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 72 - 1), NA())</f>
         <v/>
       </c>
       <c r="R73">
-        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 72 - 1), NA())</f>
+        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 72 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="P74" s="2">
-        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 73 - 1), NA())</f>
+        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 73 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q74">
-        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 73 - 1), NA())</f>
+        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 73 - 1), NA())</f>
         <v/>
       </c>
       <c r="R74">
-        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 73 - 1), NA())</f>
+        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 73 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="P75" s="2">
-        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 74 - 1), NA())</f>
+        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 74 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q75">
-        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 74 - 1), NA())</f>
+        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 74 - 1), NA())</f>
         <v/>
       </c>
       <c r="R75">
-        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 74 - 1), NA())</f>
+        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 74 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="P76" s="2">
-        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 75 - 1), NA())</f>
+        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 75 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q76">
-        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 75 - 1), NA())</f>
+        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 75 - 1), NA())</f>
         <v/>
       </c>
       <c r="R76">
-        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 75 - 1), NA())</f>
+        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 75 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="P77" s="2">
-        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 76 - 1), NA())</f>
+        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 76 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q77">
-        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 76 - 1), NA())</f>
+        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 76 - 1), NA())</f>
         <v/>
       </c>
       <c r="R77">
-        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 76 - 1), NA())</f>
+        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 76 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="P78" s="2">
-        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 77 - 1), NA())</f>
+        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 77 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q78">
-        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 77 - 1), NA())</f>
+        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 77 - 1), NA())</f>
         <v/>
       </c>
       <c r="R78">
-        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 77 - 1), NA())</f>
+        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 77 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="P79" s="2">
-        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 78 - 1), NA())</f>
+        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 78 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q79">
-        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 78 - 1), NA())</f>
+        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 78 - 1), NA())</f>
         <v/>
       </c>
       <c r="R79">
-        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 78 - 1), NA())</f>
+        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 78 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="P80" s="2">
-        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 79 - 1), NA())</f>
+        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 79 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q80">
-        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 79 - 1), NA())</f>
+        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 79 - 1), NA())</f>
         <v/>
       </c>
       <c r="R80">
-        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 79 - 1), NA())</f>
+        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 79 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="P81" s="2">
-        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 80 - 1), NA())</f>
+        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 80 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q81">
-        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 80 - 1), NA())</f>
+        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 80 - 1), NA())</f>
         <v/>
       </c>
       <c r="R81">
-        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 80 - 1), NA())</f>
+        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 80 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="P82" s="2">
-        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 81 - 1), NA())</f>
+        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 81 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q82">
-        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 81 - 1), NA())</f>
+        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 81 - 1), NA())</f>
         <v/>
       </c>
       <c r="R82">
-        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 81 - 1), NA())</f>
+        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 81 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="P83" s="2">
-        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 82 - 1), NA())</f>
+        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 82 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q83">
-        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 82 - 1), NA())</f>
+        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 82 - 1), NA())</f>
         <v/>
       </c>
       <c r="R83">
-        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 82 - 1), NA())</f>
+        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 82 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="P84" s="2">
-        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 83 - 1), NA())</f>
+        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 83 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q84">
-        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 83 - 1), NA())</f>
+        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 83 - 1), NA())</f>
         <v/>
       </c>
       <c r="R84">
-        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 83 - 1), NA())</f>
+        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 83 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="P85" s="2">
-        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 84 - 1), NA())</f>
+        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 84 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q85">
-        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 84 - 1), NA())</f>
+        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 84 - 1), NA())</f>
         <v/>
       </c>
       <c r="R85">
-        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 84 - 1), NA())</f>
+        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 84 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="P86" s="2">
-        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 85 - 1), NA())</f>
+        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 85 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q86">
-        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 85 - 1), NA())</f>
+        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 85 - 1), NA())</f>
         <v/>
       </c>
       <c r="R86">
-        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 85 - 1), NA())</f>
+        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 85 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="P87" s="2">
-        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 86 - 1), NA())</f>
+        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 86 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q87">
-        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 86 - 1), NA())</f>
+        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 86 - 1), NA())</f>
         <v/>
       </c>
       <c r="R87">
-        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 86 - 1), NA())</f>
+        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 86 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="P88" s="2">
-        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 87 - 1), NA())</f>
+        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 87 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q88">
-        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 87 - 1), NA())</f>
+        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 87 - 1), NA())</f>
         <v/>
       </c>
       <c r="R88">
-        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 87 - 1), NA())</f>
+        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 87 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="P89" s="2">
-        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 88 - 1), NA())</f>
+        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 88 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q89">
-        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 88 - 1), NA())</f>
+        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 88 - 1), NA())</f>
         <v/>
       </c>
       <c r="R89">
-        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 88 - 1), NA())</f>
+        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 88 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="P90" s="2">
-        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 89 - 1), NA())</f>
+        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 89 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q90">
-        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 89 - 1), NA())</f>
+        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 89 - 1), NA())</f>
         <v/>
       </c>
       <c r="R90">
-        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 89 - 1), NA())</f>
+        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 89 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="P91" s="2">
-        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 90 - 1), NA())</f>
+        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 90 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q91">
-        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 90 - 1), NA())</f>
+        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 90 - 1), NA())</f>
         <v/>
       </c>
       <c r="R91">
-        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 90 - 1), NA())</f>
+        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 90 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="P92" s="2">
-        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 91 - 1), NA())</f>
+        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 91 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q92">
-        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 91 - 1), NA())</f>
+        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 91 - 1), NA())</f>
         <v/>
       </c>
       <c r="R92">
-        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 91 - 1), NA())</f>
+        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 91 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="P93" s="2">
-        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 92 - 1), NA())</f>
+        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 92 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q93">
-        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 92 - 1), NA())</f>
+        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 92 - 1), NA())</f>
         <v/>
       </c>
       <c r="R93">
-        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 92 - 1), NA())</f>
+        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 92 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="P94" s="2">
-        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 93 - 1), NA())</f>
+        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 93 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q94">
-        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 93 - 1), NA())</f>
+        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 93 - 1), NA())</f>
         <v/>
       </c>
       <c r="R94">
-        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 93 - 1), NA())</f>
+        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 93 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="P95" s="2">
-        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 94 - 1), NA())</f>
+        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 94 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q95">
-        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 94 - 1), NA())</f>
+        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 94 - 1), NA())</f>
         <v/>
       </c>
       <c r="R95">
-        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 94 - 1), NA())</f>
+        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 94 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="P96" s="2">
-        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 95 - 1), NA())</f>
+        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 95 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q96">
-        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 95 - 1), NA())</f>
+        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 95 - 1), NA())</f>
         <v/>
       </c>
       <c r="R96">
-        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 95 - 1), NA())</f>
+        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 95 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="P97" s="2">
-        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 96 - 1), NA())</f>
+        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 96 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q97">
-        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 96 - 1), NA())</f>
+        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 96 - 1), NA())</f>
         <v/>
       </c>
       <c r="R97">
-        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 96 - 1), NA())</f>
+        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 96 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="P98" s="2">
-        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 97 - 1), NA())</f>
+        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 97 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q98">
-        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 97 - 1), NA())</f>
+        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 97 - 1), NA())</f>
         <v/>
       </c>
       <c r="R98">
-        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 97 - 1), NA())</f>
+        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 97 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="P99" s="2">
-        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 98 - 1), NA())</f>
+        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 98 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q99">
-        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 98 - 1), NA())</f>
+        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 98 - 1), NA())</f>
         <v/>
       </c>
       <c r="R99">
-        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 98 - 1), NA())</f>
+        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 98 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="P100" s="2">
-        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 99 - 1), NA())</f>
+        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 99 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q100">
-        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 99 - 1), NA())</f>
+        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 99 - 1), NA())</f>
         <v/>
       </c>
       <c r="R100">
-        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 99 - 1), NA())</f>
+        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 99 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="P101" s="2">
-        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 100 - 1), NA())</f>
+        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 100 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q101">
-        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 100 - 1), NA())</f>
+        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 100 - 1), NA())</f>
         <v/>
       </c>
       <c r="R101">
-        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 100 - 1), NA())</f>
+        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 100 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="P102" s="2">
-        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 101 - 1), NA())</f>
+        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 101 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q102">
-        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 101 - 1), NA())</f>
+        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 101 - 1), NA())</f>
         <v/>
       </c>
       <c r="R102">
-        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 101 - 1), NA())</f>
+        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 101 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="P103" s="2">
-        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 102 - 1), NA())</f>
+        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 102 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q103">
-        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 102 - 1), NA())</f>
+        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 102 - 1), NA())</f>
         <v/>
       </c>
       <c r="R103">
-        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 102 - 1), NA())</f>
+        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 102 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="P104" s="2">
-        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 103 - 1), NA())</f>
+        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 103 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q104">
-        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 103 - 1), NA())</f>
+        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 103 - 1), NA())</f>
         <v/>
       </c>
       <c r="R104">
-        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 103 - 1), NA())</f>
+        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 103 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="P105" s="2">
-        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 104 - 1), NA())</f>
+        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 104 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q105">
-        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 104 - 1), NA())</f>
+        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 104 - 1), NA())</f>
         <v/>
       </c>
       <c r="R105">
-        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 104 - 1), NA())</f>
+        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 104 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="P106" s="2">
-        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 105 - 1), NA())</f>
+        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 105 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q106">
-        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 105 - 1), NA())</f>
+        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 105 - 1), NA())</f>
         <v/>
       </c>
       <c r="R106">
-        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 105 - 1), NA())</f>
+        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 105 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="P107" s="2">
-        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 106 - 1), NA())</f>
+        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 106 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q107">
-        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 106 - 1), NA())</f>
+        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 106 - 1), NA())</f>
         <v/>
       </c>
       <c r="R107">
-        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 106 - 1), NA())</f>
+        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 106 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="P108" s="2">
-        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 107 - 1), NA())</f>
+        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 107 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q108">
-        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 107 - 1), NA())</f>
+        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 107 - 1), NA())</f>
         <v/>
       </c>
       <c r="R108">
-        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 107 - 1), NA())</f>
+        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 107 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="P109" s="2">
-        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 108 - 1), NA())</f>
+        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 108 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q109">
-        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 108 - 1), NA())</f>
+        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 108 - 1), NA())</f>
         <v/>
       </c>
       <c r="R109">
-        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 108 - 1), NA())</f>
+        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 108 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="P110" s="2">
-        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 109 - 1), NA())</f>
+        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 109 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q110">
-        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 109 - 1), NA())</f>
+        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 109 - 1), NA())</f>
         <v/>
       </c>
       <c r="R110">
-        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 109 - 1), NA())</f>
+        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 109 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="P111" s="2">
-        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 110 - 1), NA())</f>
+        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 110 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q111">
-        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 110 - 1), NA())</f>
+        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 110 - 1), NA())</f>
         <v/>
       </c>
       <c r="R111">
-        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 110 - 1), NA())</f>
+        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 110 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="P112" s="2">
-        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 111 - 1), NA())</f>
+        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 111 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q112">
-        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 111 - 1), NA())</f>
+        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 111 - 1), NA())</f>
         <v/>
       </c>
       <c r="R112">
-        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 111 - 1), NA())</f>
+        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 111 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="P113" s="2">
-        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 112 - 1), NA())</f>
+        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 112 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q113">
-        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 112 - 1), NA())</f>
+        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 112 - 1), NA())</f>
         <v/>
       </c>
       <c r="R113">
-        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 112 - 1), NA())</f>
+        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 112 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="P114" s="2">
-        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 113 - 1), NA())</f>
+        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 113 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q114">
-        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 113 - 1), NA())</f>
+        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 113 - 1), NA())</f>
         <v/>
       </c>
       <c r="R114">
-        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 113 - 1), NA())</f>
+        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 113 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="P115" s="2">
-        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 114 - 1), NA())</f>
+        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 114 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q115">
-        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 114 - 1), NA())</f>
+        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 114 - 1), NA())</f>
         <v/>
       </c>
       <c r="R115">
-        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 114 - 1), NA())</f>
+        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 114 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="P116" s="2">
-        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 115 - 1), NA())</f>
+        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 115 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q116">
-        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 115 - 1), NA())</f>
+        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 115 - 1), NA())</f>
         <v/>
       </c>
       <c r="R116">
-        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 115 - 1), NA())</f>
+        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 115 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="P117" s="2">
-        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 116 - 1), NA())</f>
+        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 116 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q117">
-        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 116 - 1), NA())</f>
+        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 116 - 1), NA())</f>
         <v/>
       </c>
       <c r="R117">
-        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 116 - 1), NA())</f>
+        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 116 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="P118" s="2">
-        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 117 - 1), NA())</f>
+        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 117 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q118">
-        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 117 - 1), NA())</f>
+        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 117 - 1), NA())</f>
         <v/>
       </c>
       <c r="R118">
-        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 117 - 1), NA())</f>
+        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 117 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="P119" s="2">
-        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 118 - 1), NA())</f>
+        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 118 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q119">
-        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 118 - 1), NA())</f>
+        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 118 - 1), NA())</f>
         <v/>
       </c>
       <c r="R119">
-        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 118 - 1), NA())</f>
+        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 118 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="P120" s="2">
-        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 119 - 1), NA())</f>
+        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 119 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q120">
-        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 119 - 1), NA())</f>
+        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 119 - 1), NA())</f>
         <v/>
       </c>
       <c r="R120">
-        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 119 - 1), NA())</f>
+        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 119 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="P121" s="2">
-        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 120 - 1), NA())</f>
+        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 120 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q121">
-        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 120 - 1), NA())</f>
+        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 120 - 1), NA())</f>
         <v/>
       </c>
       <c r="R121">
-        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 120 - 1), NA())</f>
+        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 120 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="P122" s="2">
-        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 121 - 1), NA())</f>
+        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 121 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q122">
-        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 121 - 1), NA())</f>
+        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 121 - 1), NA())</f>
         <v/>
       </c>
       <c r="R122">
-        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 121 - 1), NA())</f>
+        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 121 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="123">
       <c r="P123" s="2">
-        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 122 - 1), NA())</f>
+        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 122 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q123">
-        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 122 - 1), NA())</f>
+        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 122 - 1), NA())</f>
         <v/>
       </c>
       <c r="R123">
-        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 122 - 1), NA())</f>
+        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 122 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="124">
       <c r="P124" s="2">
-        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 123 - 1), NA())</f>
+        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 123 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q124">
-        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 123 - 1), NA())</f>
+        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 123 - 1), NA())</f>
         <v/>
       </c>
       <c r="R124">
-        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 123 - 1), NA())</f>
+        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 123 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="125">
       <c r="P125" s="2">
-        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 124 - 1), NA())</f>
+        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 124 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q125">
-        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 124 - 1), NA())</f>
+        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 124 - 1), NA())</f>
         <v/>
       </c>
       <c r="R125">
-        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 124 - 1), NA())</f>
+        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 124 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="126">
       <c r="P126" s="2">
-        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 125 - 1), NA())</f>
+        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 125 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q126">
-        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 125 - 1), NA())</f>
+        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 125 - 1), NA())</f>
         <v/>
       </c>
       <c r="R126">
-        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 125 - 1), NA())</f>
+        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 125 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="127">
       <c r="P127" s="2">
-        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 126 - 1), NA())</f>
+        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 126 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q127">
-        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 126 - 1), NA())</f>
+        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 126 - 1), NA())</f>
         <v/>
       </c>
       <c r="R127">
-        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 126 - 1), NA())</f>
+        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 126 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="P128" s="2">
-        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 127 - 1), NA())</f>
+        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 127 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q128">
-        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 127 - 1), NA())</f>
+        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 127 - 1), NA())</f>
         <v/>
       </c>
       <c r="R128">
-        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 127 - 1), NA())</f>
+        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 127 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="129">
       <c r="P129" s="2">
-        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 128 - 1), NA())</f>
+        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 128 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q129">
-        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 128 - 1), NA())</f>
+        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 128 - 1), NA())</f>
         <v/>
       </c>
       <c r="R129">
-        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 128 - 1), NA())</f>
+        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 128 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="130">
       <c r="P130" s="2">
-        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 129 - 1), NA())</f>
+        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 129 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q130">
-        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 129 - 1), NA())</f>
+        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 129 - 1), NA())</f>
         <v/>
       </c>
       <c r="R130">
-        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 129 - 1), NA())</f>
+        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 129 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="131">
       <c r="P131" s="2">
-        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 130 - 1), NA())</f>
+        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 130 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q131">
-        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 130 - 1), NA())</f>
+        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 130 - 1), NA())</f>
         <v/>
       </c>
       <c r="R131">
-        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 130 - 1), NA())</f>
+        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 130 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="132">
       <c r="P132" s="2">
-        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 131 - 1), NA())</f>
+        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 131 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q132">
-        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 131 - 1), NA())</f>
+        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 131 - 1), NA())</f>
         <v/>
       </c>
       <c r="R132">
-        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 131 - 1), NA())</f>
+        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 131 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="133">
       <c r="P133" s="2">
-        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 132 - 1), NA())</f>
+        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 132 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q133">
-        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 132 - 1), NA())</f>
+        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 132 - 1), NA())</f>
         <v/>
       </c>
       <c r="R133">
-        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 132 - 1), NA())</f>
+        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 132 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="134">
       <c r="P134" s="2">
-        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 133 - 1), NA())</f>
+        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 133 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q134">
-        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 133 - 1), NA())</f>
+        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 133 - 1), NA())</f>
         <v/>
       </c>
       <c r="R134">
-        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 133 - 1), NA())</f>
+        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 133 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="135">
       <c r="P135" s="2">
-        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 134 - 1), NA())</f>
+        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 134 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q135">
-        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 134 - 1), NA())</f>
+        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 134 - 1), NA())</f>
         <v/>
       </c>
       <c r="R135">
-        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 134 - 1), NA())</f>
+        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 134 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="136">
       <c r="P136" s="2">
-        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 135 - 1), NA())</f>
+        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 135 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q136">
-        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 135 - 1), NA())</f>
+        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 135 - 1), NA())</f>
         <v/>
       </c>
       <c r="R136">
-        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 135 - 1), NA())</f>
+        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 135 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="137">
       <c r="P137" s="2">
-        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 136 - 1), NA())</f>
+        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 136 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q137">
-        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 136 - 1), NA())</f>
+        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 136 - 1), NA())</f>
         <v/>
       </c>
       <c r="R137">
-        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 136 - 1), NA())</f>
+        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 136 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="138">
       <c r="P138" s="2">
-        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 137 - 1), NA())</f>
+        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 137 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q138">
-        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 137 - 1), NA())</f>
+        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 137 - 1), NA())</f>
         <v/>
       </c>
       <c r="R138">
-        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 137 - 1), NA())</f>
+        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 137 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="139">
       <c r="P139" s="2">
-        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 138 - 1), NA())</f>
+        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 138 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q139">
-        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 138 - 1), NA())</f>
+        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 138 - 1), NA())</f>
         <v/>
       </c>
       <c r="R139">
-        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 138 - 1), NA())</f>
+        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 138 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="140">
       <c r="P140" s="2">
-        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 139 - 1), NA())</f>
+        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 139 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q140">
-        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 139 - 1), NA())</f>
+        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 139 - 1), NA())</f>
         <v/>
       </c>
       <c r="R140">
-        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 139 - 1), NA())</f>
+        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 139 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="141">
       <c r="P141" s="2">
-        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 140 - 1), NA())</f>
+        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 140 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q141">
-        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 140 - 1), NA())</f>
+        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 140 - 1), NA())</f>
         <v/>
       </c>
       <c r="R141">
-        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 140 - 1), NA())</f>
+        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 140 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="142">
       <c r="P142" s="2">
-        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 141 - 1), NA())</f>
+        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 141 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q142">
-        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 141 - 1), NA())</f>
+        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 141 - 1), NA())</f>
         <v/>
       </c>
       <c r="R142">
-        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 141 - 1), NA())</f>
+        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 141 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="143">
       <c r="P143" s="2">
-        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 142 - 1), NA())</f>
+        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 142 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q143">
-        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 142 - 1), NA())</f>
+        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 142 - 1), NA())</f>
         <v/>
       </c>
       <c r="R143">
-        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 142 - 1), NA())</f>
+        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 142 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="144">
       <c r="P144" s="2">
-        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 143 - 1), NA())</f>
+        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 143 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q144">
-        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 143 - 1), NA())</f>
+        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 143 - 1), NA())</f>
         <v/>
       </c>
       <c r="R144">
-        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 143 - 1), NA())</f>
+        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 143 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="145">
       <c r="P145" s="2">
-        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 144 - 1), NA())</f>
+        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 144 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q145">
-        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 144 - 1), NA())</f>
+        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 144 - 1), NA())</f>
         <v/>
       </c>
       <c r="R145">
-        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 144 - 1), NA())</f>
+        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 144 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="146">
       <c r="P146" s="2">
-        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 145 - 1), NA())</f>
+        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 145 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q146">
-        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 145 - 1), NA())</f>
+        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 145 - 1), NA())</f>
         <v/>
       </c>
       <c r="R146">
-        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 145 - 1), NA())</f>
+        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 145 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="147">
       <c r="P147" s="2">
-        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 146 - 1), NA())</f>
+        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 146 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q147">
-        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 146 - 1), NA())</f>
+        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 146 - 1), NA())</f>
         <v/>
       </c>
       <c r="R147">
-        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 146 - 1), NA())</f>
+        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 146 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="148">
       <c r="P148" s="2">
-        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 147 - 1), NA())</f>
+        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 147 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q148">
-        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 147 - 1), NA())</f>
+        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 147 - 1), NA())</f>
         <v/>
       </c>
       <c r="R148">
-        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 147 - 1), NA())</f>
+        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 147 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="149">
       <c r="P149" s="2">
-        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 148 - 1), NA())</f>
+        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 148 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q149">
-        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 148 - 1), NA())</f>
+        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 148 - 1), NA())</f>
         <v/>
       </c>
       <c r="R149">
-        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 148 - 1), NA())</f>
+        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 148 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="150">
       <c r="P150" s="2">
-        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 149 - 1), NA())</f>
+        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 149 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q150">
-        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 149 - 1), NA())</f>
+        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 149 - 1), NA())</f>
         <v/>
       </c>
       <c r="R150">
-        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 149 - 1), NA())</f>
+        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 149 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="151">
       <c r="P151" s="2">
-        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 150 - 1), NA())</f>
+        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 150 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q151">
-        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 150 - 1), NA())</f>
+        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 150 - 1), NA())</f>
         <v/>
       </c>
       <c r="R151">
-        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 150 - 1), NA())</f>
+        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 150 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="152">
       <c r="P152" s="2">
-        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 151 - 1), NA())</f>
+        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 151 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q152">
-        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 151 - 1), NA())</f>
+        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 151 - 1), NA())</f>
         <v/>
       </c>
       <c r="R152">
-        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 151 - 1), NA())</f>
+        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 151 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="153">
       <c r="P153" s="2">
-        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 152 - 1), NA())</f>
+        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 152 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q153">
-        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 152 - 1), NA())</f>
+        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 152 - 1), NA())</f>
         <v/>
       </c>
       <c r="R153">
-        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 152 - 1), NA())</f>
+        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 152 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="154">
       <c r="P154" s="2">
-        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 153 - 1), NA())</f>
+        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 153 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q154">
-        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 153 - 1), NA())</f>
+        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 153 - 1), NA())</f>
         <v/>
       </c>
       <c r="R154">
-        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 153 - 1), NA())</f>
+        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 153 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="155">
       <c r="P155" s="2">
-        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 154 - 1), NA())</f>
+        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 154 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q155">
-        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 154 - 1), NA())</f>
+        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 154 - 1), NA())</f>
         <v/>
       </c>
       <c r="R155">
-        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 154 - 1), NA())</f>
+        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 154 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="156">
       <c r="P156" s="2">
-        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 155 - 1), NA())</f>
+        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 155 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q156">
-        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 155 - 1), NA())</f>
+        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 155 - 1), NA())</f>
         <v/>
       </c>
       <c r="R156">
-        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 155 - 1), NA())</f>
+        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 155 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="157">
       <c r="P157" s="2">
-        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 156 - 1), NA())</f>
+        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 156 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q157">
-        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 156 - 1), NA())</f>
+        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 156 - 1), NA())</f>
         <v/>
       </c>
       <c r="R157">
-        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 156 - 1), NA())</f>
+        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 156 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="158">
       <c r="P158" s="2">
-        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 157 - 1), NA())</f>
+        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 157 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q158">
-        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 157 - 1), NA())</f>
+        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 157 - 1), NA())</f>
         <v/>
       </c>
       <c r="R158">
-        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 157 - 1), NA())</f>
+        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 157 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="159">
       <c r="P159" s="2">
-        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 158 - 1), NA())</f>
+        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 158 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q159">
-        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 158 - 1), NA())</f>
+        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 158 - 1), NA())</f>
         <v/>
       </c>
       <c r="R159">
-        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 158 - 1), NA())</f>
+        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 158 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="160">
       <c r="P160" s="2">
-        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 159 - 1), NA())</f>
+        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 159 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q160">
-        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 159 - 1), NA())</f>
+        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 159 - 1), NA())</f>
         <v/>
       </c>
       <c r="R160">
-        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 159 - 1), NA())</f>
+        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 159 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="161">
       <c r="P161" s="2">
-        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 160 - 1), NA())</f>
+        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 160 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q161">
-        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 160 - 1), NA())</f>
+        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 160 - 1), NA())</f>
         <v/>
       </c>
       <c r="R161">
-        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 160 - 1), NA())</f>
+        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 160 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="162">
       <c r="P162" s="2">
-        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 161 - 1), NA())</f>
+        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 161 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q162">
-        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 161 - 1), NA())</f>
+        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 161 - 1), NA())</f>
         <v/>
       </c>
       <c r="R162">
-        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 161 - 1), NA())</f>
+        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 161 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="163">
       <c r="P163" s="2">
-        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 162 - 1), NA())</f>
+        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 162 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q163">
-        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 162 - 1), NA())</f>
+        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 162 - 1), NA())</f>
         <v/>
       </c>
       <c r="R163">
-        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 162 - 1), NA())</f>
+        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 162 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="164">
       <c r="P164" s="2">
-        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 163 - 1), NA())</f>
+        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 163 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q164">
-        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 163 - 1), NA())</f>
+        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 163 - 1), NA())</f>
         <v/>
       </c>
       <c r="R164">
-        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 163 - 1), NA())</f>
+        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 163 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="165">
       <c r="P165" s="2">
-        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 164 - 1), NA())</f>
+        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 164 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q165">
-        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 164 - 1), NA())</f>
+        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 164 - 1), NA())</f>
         <v/>
       </c>
       <c r="R165">
-        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 164 - 1), NA())</f>
+        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 164 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="166">
       <c r="P166" s="2">
-        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 165 - 1), NA())</f>
+        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 165 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q166">
-        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 165 - 1), NA())</f>
+        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 165 - 1), NA())</f>
         <v/>
       </c>
       <c r="R166">
-        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 165 - 1), NA())</f>
+        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 165 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="167">
       <c r="P167" s="2">
-        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 166 - 1), NA())</f>
+        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 166 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q167">
-        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 166 - 1), NA())</f>
+        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 166 - 1), NA())</f>
         <v/>
       </c>
       <c r="R167">
-        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 166 - 1), NA())</f>
+        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 166 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="168">
       <c r="P168" s="2">
-        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 167 - 1), NA())</f>
+        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 167 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q168">
-        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 167 - 1), NA())</f>
+        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 167 - 1), NA())</f>
         <v/>
       </c>
       <c r="R168">
-        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 167 - 1), NA())</f>
+        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 167 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="169">
       <c r="P169" s="2">
-        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 168 - 1), NA())</f>
+        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 168 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q169">
-        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 168 - 1), NA())</f>
+        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 168 - 1), NA())</f>
         <v/>
       </c>
       <c r="R169">
-        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 168 - 1), NA())</f>
+        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 168 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="170">
       <c r="P170" s="2">
-        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 169 - 1), NA())</f>
+        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 169 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q170">
-        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 169 - 1), NA())</f>
+        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 169 - 1), NA())</f>
         <v/>
       </c>
       <c r="R170">
-        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 169 - 1), NA())</f>
+        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 169 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="171">
       <c r="P171" s="2">
-        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 170 - 1), NA())</f>
+        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 170 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q171">
-        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 170 - 1), NA())</f>
+        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 170 - 1), NA())</f>
         <v/>
       </c>
       <c r="R171">
-        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 170 - 1), NA())</f>
+        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 170 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="172">
       <c r="P172" s="2">
-        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 171 - 1), NA())</f>
+        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 171 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q172">
-        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 171 - 1), NA())</f>
+        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 171 - 1), NA())</f>
         <v/>
       </c>
       <c r="R172">
-        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 171 - 1), NA())</f>
+        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 171 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="173">
       <c r="P173" s="2">
-        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 172 - 1), NA())</f>
+        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 172 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q173">
-        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 172 - 1), NA())</f>
+        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 172 - 1), NA())</f>
         <v/>
       </c>
       <c r="R173">
-        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 172 - 1), NA())</f>
+        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 172 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="174">
       <c r="P174" s="2">
-        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 173 - 1), NA())</f>
+        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 173 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q174">
-        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 173 - 1), NA())</f>
+        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 173 - 1), NA())</f>
         <v/>
       </c>
       <c r="R174">
-        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 173 - 1), NA())</f>
+        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 173 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="175">
       <c r="P175" s="2">
-        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 174 - 1), NA())</f>
+        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 174 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q175">
-        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 174 - 1), NA())</f>
+        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 174 - 1), NA())</f>
         <v/>
       </c>
       <c r="R175">
-        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 174 - 1), NA())</f>
+        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 174 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="176">
       <c r="P176" s="2">
-        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 175 - 1), NA())</f>
+        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 175 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q176">
-        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 175 - 1), NA())</f>
+        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 175 - 1), NA())</f>
         <v/>
       </c>
       <c r="R176">
-        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 175 - 1), NA())</f>
+        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 175 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="177">
       <c r="P177" s="2">
-        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 176 - 1), NA())</f>
+        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 176 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q177">
-        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 176 - 1), NA())</f>
+        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 176 - 1), NA())</f>
         <v/>
       </c>
       <c r="R177">
-        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 176 - 1), NA())</f>
+        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 176 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="178">
       <c r="P178" s="2">
-        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 177 - 1), NA())</f>
+        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 177 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q178">
-        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 177 - 1), NA())</f>
+        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 177 - 1), NA())</f>
         <v/>
       </c>
       <c r="R178">
-        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 177 - 1), NA())</f>
+        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 177 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="179">
       <c r="P179" s="2">
-        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 178 - 1), NA())</f>
+        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 178 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q179">
-        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 178 - 1), NA())</f>
+        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 178 - 1), NA())</f>
         <v/>
       </c>
       <c r="R179">
-        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 178 - 1), NA())</f>
+        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 178 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="180">
       <c r="P180" s="2">
-        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 179 - 1), NA())</f>
+        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 179 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q180">
-        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 179 - 1), NA())</f>
+        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 179 - 1), NA())</f>
         <v/>
       </c>
       <c r="R180">
-        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 179 - 1), NA())</f>
+        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 179 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="181">
       <c r="P181" s="2">
-        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 180 - 1), NA())</f>
+        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 180 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q181">
-        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 180 - 1), NA())</f>
+        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 180 - 1), NA())</f>
         <v/>
       </c>
       <c r="R181">
-        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 180 - 1), NA())</f>
+        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 180 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="182">
       <c r="P182" s="2">
-        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 181 - 1), NA())</f>
+        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 181 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q182">
-        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 181 - 1), NA())</f>
+        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 181 - 1), NA())</f>
         <v/>
       </c>
       <c r="R182">
-        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 181 - 1), NA())</f>
+        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 181 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="183">
       <c r="P183" s="2">
-        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 182 - 1), NA())</f>
+        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 182 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q183">
-        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 182 - 1), NA())</f>
+        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 182 - 1), NA())</f>
         <v/>
       </c>
       <c r="R183">
-        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 182 - 1), NA())</f>
+        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 182 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="184">
       <c r="P184" s="2">
-        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 183 - 1), NA())</f>
+        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 183 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q184">
-        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 183 - 1), NA())</f>
+        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 183 - 1), NA())</f>
         <v/>
       </c>
       <c r="R184">
-        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 183 - 1), NA())</f>
+        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 183 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="185">
       <c r="P185" s="2">
-        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 184 - 1), NA())</f>
+        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 184 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q185">
-        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 184 - 1), NA())</f>
+        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 184 - 1), NA())</f>
         <v/>
       </c>
       <c r="R185">
-        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 184 - 1), NA())</f>
+        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 184 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="186">
       <c r="P186" s="2">
-        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 185 - 1), NA())</f>
+        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 185 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q186">
-        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 185 - 1), NA())</f>
+        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 185 - 1), NA())</f>
         <v/>
       </c>
       <c r="R186">
-        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 185 - 1), NA())</f>
+        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 185 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="187">
       <c r="P187" s="2">
-        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 186 - 1), NA())</f>
+        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 186 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q187">
-        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 186 - 1), NA())</f>
+        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 186 - 1), NA())</f>
         <v/>
       </c>
       <c r="R187">
-        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 186 - 1), NA())</f>
+        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 186 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="188">
       <c r="P188" s="2">
-        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 187 - 1), NA())</f>
+        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 187 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q188">
-        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 187 - 1), NA())</f>
+        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 187 - 1), NA())</f>
         <v/>
       </c>
       <c r="R188">
-        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 187 - 1), NA())</f>
+        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 187 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="189">
       <c r="P189" s="2">
-        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 188 - 1), NA())</f>
+        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 188 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q189">
-        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 188 - 1), NA())</f>
+        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 188 - 1), NA())</f>
         <v/>
       </c>
       <c r="R189">
-        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 188 - 1), NA())</f>
+        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 188 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="190">
       <c r="P190" s="2">
-        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 189 - 1), NA())</f>
+        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 189 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q190">
-        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 189 - 1), NA())</f>
+        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 189 - 1), NA())</f>
         <v/>
       </c>
       <c r="R190">
-        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 189 - 1), NA())</f>
+        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 189 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="191">
       <c r="P191" s="2">
-        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 190 - 1), NA())</f>
+        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 190 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q191">
-        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 190 - 1), NA())</f>
+        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 190 - 1), NA())</f>
         <v/>
       </c>
       <c r="R191">
-        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 190 - 1), NA())</f>
+        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 190 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="192">
       <c r="P192" s="2">
-        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 191 - 1), NA())</f>
+        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 191 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q192">
-        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 191 - 1), NA())</f>
+        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 191 - 1), NA())</f>
         <v/>
       </c>
       <c r="R192">
-        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 191 - 1), NA())</f>
+        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 191 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="193">
       <c r="P193" s="2">
-        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 192 - 1), NA())</f>
+        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 192 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q193">
-        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 192 - 1), NA())</f>
+        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 192 - 1), NA())</f>
         <v/>
       </c>
       <c r="R193">
-        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 192 - 1), NA())</f>
+        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 192 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="194">
       <c r="P194" s="2">
-        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 193 - 1), NA())</f>
+        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 193 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q194">
-        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 193 - 1), NA())</f>
+        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 193 - 1), NA())</f>
         <v/>
       </c>
       <c r="R194">
-        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 193 - 1), NA())</f>
+        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 193 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="195">
       <c r="P195" s="2">
-        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 194 - 1), NA())</f>
+        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 194 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q195">
-        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 194 - 1), NA())</f>
+        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 194 - 1), NA())</f>
         <v/>
       </c>
       <c r="R195">
-        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 194 - 1), NA())</f>
+        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 194 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="196">
       <c r="P196" s="2">
-        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 195 - 1), NA())</f>
+        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 195 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q196">
-        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 195 - 1), NA())</f>
+        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 195 - 1), NA())</f>
         <v/>
       </c>
       <c r="R196">
-        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 195 - 1), NA())</f>
+        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 195 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="197">
       <c r="P197" s="2">
-        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 196 - 1), NA())</f>
+        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 196 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q197">
-        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 196 - 1), NA())</f>
+        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 196 - 1), NA())</f>
         <v/>
       </c>
       <c r="R197">
-        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 196 - 1), NA())</f>
+        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 196 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="198">
       <c r="P198" s="2">
-        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 197 - 1), NA())</f>
+        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 197 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q198">
-        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 197 - 1), NA())</f>
+        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 197 - 1), NA())</f>
         <v/>
       </c>
       <c r="R198">
-        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 197 - 1), NA())</f>
+        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 197 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="199">
       <c r="P199" s="2">
-        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 198 - 1), NA())</f>
+        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 198 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q199">
-        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 198 - 1), NA())</f>
+        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 198 - 1), NA())</f>
         <v/>
       </c>
       <c r="R199">
-        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 198 - 1), NA())</f>
+        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 198 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="200">
       <c r="P200" s="2">
-        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 199 - 1), NA())</f>
+        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 199 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q200">
-        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 199 - 1), NA())</f>
+        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 199 - 1), NA())</f>
         <v/>
       </c>
       <c r="R200">
-        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 199 - 1), NA())</f>
+        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 199 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="201">
       <c r="P201" s="2">
-        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 200 - 1), NA())</f>
+        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 200 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q201">
-        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 200 - 1), NA())</f>
+        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 200 - 1), NA())</f>
         <v/>
       </c>
       <c r="R201">
-        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 200 - 1), NA())</f>
+        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 200 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="202">
       <c r="P202" s="2">
-        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 201 - 1), NA())</f>
+        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 201 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q202">
-        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 201 - 1), NA())</f>
+        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 201 - 1), NA())</f>
         <v/>
       </c>
       <c r="R202">
-        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 201 - 1), NA())</f>
+        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 201 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="203">
       <c r="P203" s="2">
-        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 202 - 1), NA())</f>
+        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 202 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q203">
-        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 202 - 1), NA())</f>
+        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 202 - 1), NA())</f>
         <v/>
       </c>
       <c r="R203">
-        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 202 - 1), NA())</f>
+        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 202 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="204">
       <c r="P204" s="2">
-        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 203 - 1), NA())</f>
+        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 203 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q204">
-        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 203 - 1), NA())</f>
+        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 203 - 1), NA())</f>
         <v/>
       </c>
       <c r="R204">
-        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 203 - 1), NA())</f>
+        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 203 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="205">
       <c r="P205" s="2">
-        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 204 - 1), NA())</f>
+        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 204 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q205">
-        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 204 - 1), NA())</f>
+        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 204 - 1), NA())</f>
         <v/>
       </c>
       <c r="R205">
-        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 204 - 1), NA())</f>
+        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 204 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="206">
       <c r="P206" s="2">
-        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 205 - 1), NA())</f>
+        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 205 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q206">
-        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 205 - 1), NA())</f>
+        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 205 - 1), NA())</f>
         <v/>
       </c>
       <c r="R206">
-        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 205 - 1), NA())</f>
+        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 205 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="207">
       <c r="P207" s="2">
-        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 206 - 1), NA())</f>
+        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 206 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q207">
-        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 206 - 1), NA())</f>
+        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 206 - 1), NA())</f>
         <v/>
       </c>
       <c r="R207">
-        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 206 - 1), NA())</f>
+        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 206 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="208">
       <c r="P208" s="2">
-        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 207 - 1), NA())</f>
+        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 207 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q208">
-        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 207 - 1), NA())</f>
+        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 207 - 1), NA())</f>
         <v/>
       </c>
       <c r="R208">
-        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 207 - 1), NA())</f>
+        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 207 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="209">
       <c r="P209" s="2">
-        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 208 - 1), NA())</f>
+        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 208 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q209">
-        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 208 - 1), NA())</f>
+        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 208 - 1), NA())</f>
         <v/>
       </c>
       <c r="R209">
-        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 208 - 1), NA())</f>
+        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 208 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="210">
       <c r="P210" s="2">
-        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 209 - 1), NA())</f>
+        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 209 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q210">
-        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 209 - 1), NA())</f>
+        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 209 - 1), NA())</f>
         <v/>
       </c>
       <c r="R210">
-        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 209 - 1), NA())</f>
+        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 209 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="211">
       <c r="P211" s="2">
-        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 210 - 1), NA())</f>
+        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 210 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q211">
-        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 210 - 1), NA())</f>
+        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 210 - 1), NA())</f>
         <v/>
       </c>
       <c r="R211">
-        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 210 - 1), NA())</f>
+        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 210 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="212">
       <c r="P212" s="2">
-        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 211 - 1), NA())</f>
+        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 211 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q212">
-        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 211 - 1), NA())</f>
+        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 211 - 1), NA())</f>
         <v/>
       </c>
       <c r="R212">
-        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 211 - 1), NA())</f>
+        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 211 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="213">
       <c r="P213" s="2">
-        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 212 - 1), NA())</f>
+        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 212 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q213">
-        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 212 - 1), NA())</f>
+        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 212 - 1), NA())</f>
         <v/>
       </c>
       <c r="R213">
-        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 212 - 1), NA())</f>
+        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 212 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="214">
       <c r="P214" s="2">
-        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 213 - 1), NA())</f>
+        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 213 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q214">
-        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 213 - 1), NA())</f>
+        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 213 - 1), NA())</f>
         <v/>
       </c>
       <c r="R214">
-        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 213 - 1), NA())</f>
+        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 213 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="215">
       <c r="P215" s="2">
-        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 214 - 1), NA())</f>
+        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 214 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q215">
-        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 214 - 1), NA())</f>
+        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 214 - 1), NA())</f>
         <v/>
       </c>
       <c r="R215">
-        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 214 - 1), NA())</f>
+        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 214 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="216">
       <c r="P216" s="2">
-        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 215 - 1), NA())</f>
+        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 215 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q216">
-        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 215 - 1), NA())</f>
+        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 215 - 1), NA())</f>
         <v/>
       </c>
       <c r="R216">
-        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 215 - 1), NA())</f>
+        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 215 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="217">
       <c r="P217" s="2">
-        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 216 - 1), NA())</f>
+        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 216 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q217">
-        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 216 - 1), NA())</f>
+        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 216 - 1), NA())</f>
         <v/>
       </c>
       <c r="R217">
-        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 216 - 1), NA())</f>
+        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 216 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="218">
       <c r="P218" s="2">
-        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 217 - 1), NA())</f>
+        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 217 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q218">
-        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 217 - 1), NA())</f>
+        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 217 - 1), NA())</f>
         <v/>
       </c>
       <c r="R218">
-        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 217 - 1), NA())</f>
+        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 217 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="219">
       <c r="P219" s="2">
-        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 218 - 1), NA())</f>
+        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 218 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q219">
-        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 218 - 1), NA())</f>
+        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 218 - 1), NA())</f>
         <v/>
       </c>
       <c r="R219">
-        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 218 - 1), NA())</f>
+        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 218 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="220">
       <c r="P220" s="2">
-        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 219 - 1), NA())</f>
+        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 219 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q220">
-        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 219 - 1), NA())</f>
+        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 219 - 1), NA())</f>
         <v/>
       </c>
       <c r="R220">
-        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 219 - 1), NA())</f>
+        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 219 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="221">
       <c r="P221" s="2">
-        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 220 - 1), NA())</f>
+        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 220 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q221">
-        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 220 - 1), NA())</f>
+        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 220 - 1), NA())</f>
         <v/>
       </c>
       <c r="R221">
-        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 220 - 1), NA())</f>
+        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 220 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="222">
       <c r="P222" s="2">
-        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 221 - 1), NA())</f>
+        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 221 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q222">
-        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 221 - 1), NA())</f>
+        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 221 - 1), NA())</f>
         <v/>
       </c>
       <c r="R222">
-        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 221 - 1), NA())</f>
+        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 221 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="223">
       <c r="P223" s="2">
-        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 222 - 1), NA())</f>
+        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 222 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q223">
-        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 222 - 1), NA())</f>
+        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 222 - 1), NA())</f>
         <v/>
       </c>
       <c r="R223">
-        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 222 - 1), NA())</f>
+        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 222 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="224">
       <c r="P224" s="2">
-        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 223 - 1), NA())</f>
+        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 223 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q224">
-        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 223 - 1), NA())</f>
+        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 223 - 1), NA())</f>
         <v/>
       </c>
       <c r="R224">
-        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 223 - 1), NA())</f>
+        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 223 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="225">
       <c r="P225" s="2">
-        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 224 - 1), NA())</f>
+        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 224 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q225">
-        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 224 - 1), NA())</f>
+        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 224 - 1), NA())</f>
         <v/>
       </c>
       <c r="R225">
-        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 224 - 1), NA())</f>
+        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 224 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="226">
       <c r="P226" s="2">
-        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 225 - 1), NA())</f>
+        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 225 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q226">
-        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 225 - 1), NA())</f>
+        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 225 - 1), NA())</f>
         <v/>
       </c>
       <c r="R226">
-        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 225 - 1), NA())</f>
+        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 225 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="227">
       <c r="P227" s="2">
-        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 226 - 1), NA())</f>
+        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 226 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q227">
-        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 226 - 1), NA())</f>
+        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 226 - 1), NA())</f>
         <v/>
       </c>
       <c r="R227">
-        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 226 - 1), NA())</f>
+        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 226 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="228">
       <c r="P228" s="2">
-        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 227 - 1), NA())</f>
+        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 227 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q228">
-        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 227 - 1), NA())</f>
+        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 227 - 1), NA())</f>
         <v/>
       </c>
       <c r="R228">
-        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 227 - 1), NA())</f>
+        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 227 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="229">
       <c r="P229" s="2">
-        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 228 - 1), NA())</f>
+        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 228 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q229">
-        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 228 - 1), NA())</f>
+        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 228 - 1), NA())</f>
         <v/>
       </c>
       <c r="R229">
-        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 228 - 1), NA())</f>
+        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 228 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="230">
       <c r="P230" s="2">
-        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 229 - 1), NA())</f>
+        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 229 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q230">
-        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 229 - 1), NA())</f>
+        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 229 - 1), NA())</f>
         <v/>
       </c>
       <c r="R230">
-        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 229 - 1), NA())</f>
+        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 229 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="231">
       <c r="P231" s="2">
-        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 230 - 1), NA())</f>
+        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 230 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q231">
-        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 230 - 1), NA())</f>
+        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 230 - 1), NA())</f>
         <v/>
       </c>
       <c r="R231">
-        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 230 - 1), NA())</f>
+        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 230 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="232">
       <c r="P232" s="2">
-        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 231 - 1), NA())</f>
+        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 231 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q232">
-        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 231 - 1), NA())</f>
+        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 231 - 1), NA())</f>
         <v/>
       </c>
       <c r="R232">
-        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 231 - 1), NA())</f>
+        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 231 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="233">
       <c r="P233" s="2">
-        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 232 - 1), NA())</f>
+        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 232 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q233">
-        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 232 - 1), NA())</f>
+        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 232 - 1), NA())</f>
         <v/>
       </c>
       <c r="R233">
-        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 232 - 1), NA())</f>
+        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 232 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="234">
       <c r="P234" s="2">
-        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 233 - 1), NA())</f>
+        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 233 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q234">
-        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 233 - 1), NA())</f>
+        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 233 - 1), NA())</f>
         <v/>
       </c>
       <c r="R234">
-        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 233 - 1), NA())</f>
+        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 233 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="235">
       <c r="P235" s="2">
-        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 234 - 1), NA())</f>
+        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 234 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q235">
-        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 234 - 1), NA())</f>
+        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 234 - 1), NA())</f>
         <v/>
       </c>
       <c r="R235">
-        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 234 - 1), NA())</f>
+        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 234 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="236">
       <c r="P236" s="2">
-        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 235 - 1), NA())</f>
+        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 235 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q236">
-        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 235 - 1), NA())</f>
+        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 235 - 1), NA())</f>
         <v/>
       </c>
       <c r="R236">
-        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 235 - 1), NA())</f>
+        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 235 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="237">
       <c r="P237" s="2">
-        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 236 - 1), NA())</f>
+        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 236 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q237">
-        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 236 - 1), NA())</f>
+        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 236 - 1), NA())</f>
         <v/>
       </c>
       <c r="R237">
-        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 236 - 1), NA())</f>
+        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 236 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="238">
       <c r="P238" s="2">
-        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 237 - 1), NA())</f>
+        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 237 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q238">
-        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 237 - 1), NA())</f>
+        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 237 - 1), NA())</f>
         <v/>
       </c>
       <c r="R238">
-        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 237 - 1), NA())</f>
+        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 237 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="239">
       <c r="P239" s="2">
-        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 238 - 1), NA())</f>
+        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 238 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q239">
-        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 238 - 1), NA())</f>
+        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 238 - 1), NA())</f>
         <v/>
       </c>
       <c r="R239">
-        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 238 - 1), NA())</f>
+        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 238 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="240">
       <c r="P240" s="2">
-        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 239 - 1), NA())</f>
+        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 239 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q240">
-        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 239 - 1), NA())</f>
+        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 239 - 1), NA())</f>
         <v/>
       </c>
       <c r="R240">
-        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 239 - 1), NA())</f>
+        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 239 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="241">
       <c r="P241" s="2">
-        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 240 - 1), NA())</f>
+        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 240 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q241">
-        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 240 - 1), NA())</f>
+        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 240 - 1), NA())</f>
         <v/>
       </c>
       <c r="R241">
-        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 240 - 1), NA())</f>
+        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 240 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="242">
       <c r="P242" s="2">
-        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 241 - 1), NA())</f>
+        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 241 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q242">
-        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 241 - 1), NA())</f>
+        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 241 - 1), NA())</f>
         <v/>
       </c>
       <c r="R242">
-        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 241 - 1), NA())</f>
+        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 241 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="243">
       <c r="P243" s="2">
-        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 242 - 1), NA())</f>
+        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 242 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q243">
-        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 242 - 1), NA())</f>
+        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 242 - 1), NA())</f>
         <v/>
       </c>
       <c r="R243">
-        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 242 - 1), NA())</f>
+        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 242 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="244">
       <c r="P244" s="2">
-        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 243 - 1), NA())</f>
+        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 243 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q244">
-        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 243 - 1), NA())</f>
+        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 243 - 1), NA())</f>
         <v/>
       </c>
       <c r="R244">
-        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 243 - 1), NA())</f>
+        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 243 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="245">
       <c r="P245" s="2">
-        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 244 - 1), NA())</f>
+        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 244 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q245">
-        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 244 - 1), NA())</f>
+        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 244 - 1), NA())</f>
         <v/>
       </c>
       <c r="R245">
-        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 244 - 1), NA())</f>
+        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 244 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="246">
       <c r="P246" s="2">
-        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 245 - 1), NA())</f>
+        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 245 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q246">
-        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 245 - 1), NA())</f>
+        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 245 - 1), NA())</f>
         <v/>
       </c>
       <c r="R246">
-        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 245 - 1), NA())</f>
+        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 245 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="247">
       <c r="P247" s="2">
-        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 246 - 1), NA())</f>
+        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 246 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q247">
-        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 246 - 1), NA())</f>
+        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 246 - 1), NA())</f>
         <v/>
       </c>
       <c r="R247">
-        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 246 - 1), NA())</f>
+        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 246 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="248">
       <c r="P248" s="2">
-        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 247 - 1), NA())</f>
+        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 247 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q248">
-        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 247 - 1), NA())</f>
+        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 247 - 1), NA())</f>
         <v/>
       </c>
       <c r="R248">
-        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 247 - 1), NA())</f>
+        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 247 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="249">
       <c r="P249" s="2">
-        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 248 - 1), NA())</f>
+        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 248 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q249">
-        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 248 - 1), NA())</f>
+        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 248 - 1), NA())</f>
         <v/>
       </c>
       <c r="R249">
-        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 248 - 1), NA())</f>
+        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 248 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="250">
       <c r="P250" s="2">
-        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 249 - 1), NA())</f>
+        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 249 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q250">
-        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 249 - 1), NA())</f>
+        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 249 - 1), NA())</f>
         <v/>
       </c>
       <c r="R250">
-        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 249 - 1), NA())</f>
+        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 249 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="251">
       <c r="P251" s="2">
-        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 250 - 1), NA())</f>
+        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 250 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q251">
-        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 250 - 1), NA())</f>
+        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 250 - 1), NA())</f>
         <v/>
       </c>
       <c r="R251">
-        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 250 - 1), NA())</f>
+        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 250 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="252">
       <c r="P252" s="2">
-        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 251 - 1), NA())</f>
+        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 251 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q252">
-        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 251 - 1), NA())</f>
+        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 251 - 1), NA())</f>
         <v/>
       </c>
       <c r="R252">
-        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 251 - 1), NA())</f>
+        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 251 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="253">
       <c r="P253" s="2">
-        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 252 - 1), NA())</f>
+        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 252 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q253">
-        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 252 - 1), NA())</f>
+        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 252 - 1), NA())</f>
         <v/>
       </c>
       <c r="R253">
-        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 252 - 1), NA())</f>
+        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 252 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="254">
       <c r="P254" s="2">
-        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 253 - 1), NA())</f>
+        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 253 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q254">
-        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 253 - 1), NA())</f>
+        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 253 - 1), NA())</f>
         <v/>
       </c>
       <c r="R254">
-        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 253 - 1), NA())</f>
+        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 253 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="255">
       <c r="P255" s="2">
-        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 254 - 1), NA())</f>
+        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 254 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q255">
-        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 254 - 1), NA())</f>
+        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 254 - 1), NA())</f>
         <v/>
       </c>
       <c r="R255">
-        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 254 - 1), NA())</f>
+        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 254 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="256">
       <c r="P256" s="2">
-        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 255 - 1), NA())</f>
+        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 255 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q256">
-        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 255 - 1), NA())</f>
+        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 255 - 1), NA())</f>
         <v/>
       </c>
       <c r="R256">
-        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 255 - 1), NA())</f>
+        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 255 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="257">
       <c r="P257" s="2">
-        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 256 - 1), NA())</f>
+        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 256 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q257">
-        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 256 - 1), NA())</f>
+        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 256 - 1), NA())</f>
         <v/>
       </c>
       <c r="R257">
-        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 256 - 1), NA())</f>
+        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 256 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="258">
       <c r="P258" s="2">
-        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 257 - 1), NA())</f>
+        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 257 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q258">
-        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 257 - 1), NA())</f>
+        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 257 - 1), NA())</f>
         <v/>
       </c>
       <c r="R258">
-        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 257 - 1), NA())</f>
+        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 257 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="259">
       <c r="P259" s="2">
-        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 258 - 1), NA())</f>
+        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 258 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q259">
-        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 258 - 1), NA())</f>
+        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 258 - 1), NA())</f>
         <v/>
       </c>
       <c r="R259">
-        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 258 - 1), NA())</f>
+        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 258 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="260">
       <c r="P260" s="2">
-        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 259 - 1), NA())</f>
+        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 259 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q260">
-        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 259 - 1), NA())</f>
+        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 259 - 1), NA())</f>
         <v/>
       </c>
       <c r="R260">
-        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 259 - 1), NA())</f>
+        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 259 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="261">
       <c r="P261" s="2">
-        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 260 - 1), NA())</f>
+        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 260 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q261">
-        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 260 - 1), NA())</f>
+        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 260 - 1), NA())</f>
         <v/>
       </c>
       <c r="R261">
-        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 260 - 1), NA())</f>
+        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 260 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="262">
       <c r="P262" s="2">
-        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 261 - 1), NA())</f>
+        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 261 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q262">
-        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 261 - 1), NA())</f>
+        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 261 - 1), NA())</f>
         <v/>
       </c>
       <c r="R262">
-        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 261 - 1), NA())</f>
+        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 261 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="263">
       <c r="P263" s="2">
-        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 262 - 1), NA())</f>
+        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 262 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q263">
-        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 262 - 1), NA())</f>
+        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 262 - 1), NA())</f>
         <v/>
       </c>
       <c r="R263">
-        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 262 - 1), NA())</f>
+        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 262 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="264">
       <c r="P264" s="2">
-        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 263 - 1), NA())</f>
+        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 263 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q264">
-        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 263 - 1), NA())</f>
+        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 263 - 1), NA())</f>
         <v/>
       </c>
       <c r="R264">
-        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 263 - 1), NA())</f>
+        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 263 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="265">
       <c r="P265" s="2">
-        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 264 - 1), NA())</f>
+        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 264 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q265">
-        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 264 - 1), NA())</f>
+        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 264 - 1), NA())</f>
         <v/>
       </c>
       <c r="R265">
-        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 264 - 1), NA())</f>
+        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 264 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="266">
       <c r="P266" s="2">
-        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 265 - 1), NA())</f>
+        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 265 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q266">
-        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 265 - 1), NA())</f>
+        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 265 - 1), NA())</f>
         <v/>
       </c>
       <c r="R266">
-        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 265 - 1), NA())</f>
+        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 265 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="267">
       <c r="P267" s="2">
-        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 266 - 1), NA())</f>
+        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 266 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q267">
-        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 266 - 1), NA())</f>
+        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 266 - 1), NA())</f>
         <v/>
       </c>
       <c r="R267">
-        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 266 - 1), NA())</f>
+        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 266 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="268">
       <c r="P268" s="2">
-        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 267 - 1), NA())</f>
+        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 267 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q268">
-        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 267 - 1), NA())</f>
+        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 267 - 1), NA())</f>
         <v/>
       </c>
       <c r="R268">
-        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 267 - 1), NA())</f>
+        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 267 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="269">
       <c r="P269" s="2">
-        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 268 - 1), NA())</f>
+        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 268 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q269">
-        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 268 - 1), NA())</f>
+        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 268 - 1), NA())</f>
         <v/>
       </c>
       <c r="R269">
-        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 268 - 1), NA())</f>
+        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 268 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="270">
       <c r="P270" s="2">
-        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 269 - 1), NA())</f>
+        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 269 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q270">
-        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 269 - 1), NA())</f>
+        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 269 - 1), NA())</f>
         <v/>
       </c>
       <c r="R270">
-        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 269 - 1), NA())</f>
+        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 269 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="271">
       <c r="P271" s="2">
-        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 270 - 1), NA())</f>
+        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 270 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q271">
-        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 270 - 1), NA())</f>
+        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 270 - 1), NA())</f>
         <v/>
       </c>
       <c r="R271">
-        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 270 - 1), NA())</f>
+        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 270 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="272">
       <c r="P272" s="2">
-        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 271 - 1), NA())</f>
+        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 271 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q272">
-        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 271 - 1), NA())</f>
+        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 271 - 1), NA())</f>
         <v/>
       </c>
       <c r="R272">
-        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 271 - 1), NA())</f>
+        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 271 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="273">
       <c r="P273" s="2">
-        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 272 - 1), NA())</f>
+        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 272 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q273">
-        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 272 - 1), NA())</f>
+        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 272 - 1), NA())</f>
         <v/>
       </c>
       <c r="R273">
-        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 272 - 1), NA())</f>
+        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 272 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="274">
       <c r="P274" s="2">
-        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 273 - 1), NA())</f>
+        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 273 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q274">
-        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 273 - 1), NA())</f>
+        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 273 - 1), NA())</f>
         <v/>
       </c>
       <c r="R274">
-        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 273 - 1), NA())</f>
+        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 273 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="275">
       <c r="P275" s="2">
-        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 274 - 1), NA())</f>
+        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 274 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q275">
-        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 274 - 1), NA())</f>
+        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 274 - 1), NA())</f>
         <v/>
       </c>
       <c r="R275">
-        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 274 - 1), NA())</f>
+        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 274 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="276">
       <c r="P276" s="2">
-        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 275 - 1), NA())</f>
+        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 275 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q276">
-        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 275 - 1), NA())</f>
+        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 275 - 1), NA())</f>
         <v/>
       </c>
       <c r="R276">
-        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 275 - 1), NA())</f>
+        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 275 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="277">
       <c r="P277" s="2">
-        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 276 - 1), NA())</f>
+        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 276 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q277">
-        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 276 - 1), NA())</f>
+        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 276 - 1), NA())</f>
         <v/>
       </c>
       <c r="R277">
-        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 276 - 1), NA())</f>
+        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 276 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="278">
       <c r="P278" s="2">
-        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 277 - 1), NA())</f>
+        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 277 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q278">
-        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 277 - 1), NA())</f>
+        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 277 - 1), NA())</f>
         <v/>
       </c>
       <c r="R278">
-        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 277 - 1), NA())</f>
+        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 277 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="279">
       <c r="P279" s="2">
-        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 278 - 1), NA())</f>
+        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 278 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q279">
-        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 278 - 1), NA())</f>
+        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 278 - 1), NA())</f>
         <v/>
       </c>
       <c r="R279">
-        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 278 - 1), NA())</f>
+        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 278 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="280">
       <c r="P280" s="2">
-        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 279 - 1), NA())</f>
+        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 279 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q280">
-        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 279 - 1), NA())</f>
+        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 279 - 1), NA())</f>
         <v/>
       </c>
       <c r="R280">
-        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 279 - 1), NA())</f>
+        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 279 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="281">
       <c r="P281" s="2">
-        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 280 - 1), NA())</f>
+        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 280 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q281">
-        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 280 - 1), NA())</f>
+        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 280 - 1), NA())</f>
         <v/>
       </c>
       <c r="R281">
-        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 280 - 1), NA())</f>
+        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 280 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="282">
       <c r="P282" s="2">
-        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 281 - 1), NA())</f>
+        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 281 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q282">
-        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 281 - 1), NA())</f>
+        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 281 - 1), NA())</f>
         <v/>
       </c>
       <c r="R282">
-        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 281 - 1), NA())</f>
+        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 281 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="283">
       <c r="P283" s="2">
-        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 282 - 1), NA())</f>
+        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 282 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q283">
-        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 282 - 1), NA())</f>
+        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 282 - 1), NA())</f>
         <v/>
       </c>
       <c r="R283">
-        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 282 - 1), NA())</f>
+        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 282 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="284">
       <c r="P284" s="2">
-        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 283 - 1), NA())</f>
+        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 283 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q284">
-        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 283 - 1), NA())</f>
+        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 283 - 1), NA())</f>
         <v/>
       </c>
       <c r="R284">
-        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 283 - 1), NA())</f>
+        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 283 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="285">
       <c r="P285" s="2">
-        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 284 - 1), NA())</f>
+        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 284 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q285">
-        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 284 - 1), NA())</f>
+        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 284 - 1), NA())</f>
         <v/>
       </c>
       <c r="R285">
-        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 284 - 1), NA())</f>
+        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 284 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="286">
       <c r="P286" s="2">
-        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 285 - 1), NA())</f>
+        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 285 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q286">
-        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 285 - 1), NA())</f>
+        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 285 - 1), NA())</f>
         <v/>
       </c>
       <c r="R286">
-        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 285 - 1), NA())</f>
+        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 285 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="287">
       <c r="P287" s="2">
-        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 286 - 1), NA())</f>
+        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 286 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q287">
-        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 286 - 1), NA())</f>
+        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 286 - 1), NA())</f>
         <v/>
       </c>
       <c r="R287">
-        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 286 - 1), NA())</f>
+        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 286 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="288">
       <c r="P288" s="2">
-        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 287 - 1), NA())</f>
+        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 287 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q288">
-        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 287 - 1), NA())</f>
+        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 287 - 1), NA())</f>
         <v/>
       </c>
       <c r="R288">
-        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 287 - 1), NA())</f>
+        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 287 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="289">
       <c r="P289" s="2">
-        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 288 - 1), NA())</f>
+        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 288 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q289">
-        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 288 - 1), NA())</f>
+        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 288 - 1), NA())</f>
         <v/>
       </c>
       <c r="R289">
-        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 288 - 1), NA())</f>
+        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 288 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="290">
       <c r="P290" s="2">
-        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 289 - 1), NA())</f>
+        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 289 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q290">
-        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 289 - 1), NA())</f>
+        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 289 - 1), NA())</f>
         <v/>
       </c>
       <c r="R290">
-        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 289 - 1), NA())</f>
+        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 289 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="291">
       <c r="P291" s="2">
-        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 290 - 1), NA())</f>
+        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 290 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q291">
-        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 290 - 1), NA())</f>
+        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 290 - 1), NA())</f>
         <v/>
       </c>
       <c r="R291">
-        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 290 - 1), NA())</f>
+        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 290 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="292">
       <c r="P292" s="2">
-        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 291 - 1), NA())</f>
+        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 291 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q292">
-        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 291 - 1), NA())</f>
+        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 291 - 1), NA())</f>
         <v/>
       </c>
       <c r="R292">
-        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 291 - 1), NA())</f>
+        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 291 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="293">
       <c r="P293" s="2">
-        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 292 - 1), NA())</f>
+        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 292 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q293">
-        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 292 - 1), NA())</f>
+        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 292 - 1), NA())</f>
         <v/>
       </c>
       <c r="R293">
-        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 292 - 1), NA())</f>
+        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 292 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="294">
       <c r="P294" s="2">
-        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 293 - 1), NA())</f>
+        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 293 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q294">
-        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 293 - 1), NA())</f>
+        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 293 - 1), NA())</f>
         <v/>
       </c>
       <c r="R294">
-        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 293 - 1), NA())</f>
+        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 293 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="295">
       <c r="P295" s="2">
-        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 294 - 1), NA())</f>
+        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 294 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q295">
-        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 294 - 1), NA())</f>
+        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 294 - 1), NA())</f>
         <v/>
       </c>
       <c r="R295">
-        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 294 - 1), NA())</f>
+        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 294 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="296">
       <c r="P296" s="2">
-        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 295 - 1), NA())</f>
+        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 295 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q296">
-        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 295 - 1), NA())</f>
+        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 295 - 1), NA())</f>
         <v/>
       </c>
       <c r="R296">
-        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 295 - 1), NA())</f>
+        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 295 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="297">
       <c r="P297" s="2">
-        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 296 - 1), NA())</f>
+        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 296 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q297">
-        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 296 - 1), NA())</f>
+        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 296 - 1), NA())</f>
         <v/>
       </c>
       <c r="R297">
-        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 296 - 1), NA())</f>
+        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 296 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="298">
       <c r="P298" s="2">
-        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 297 - 1), NA())</f>
+        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 297 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q298">
-        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 297 - 1), NA())</f>
+        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 297 - 1), NA())</f>
         <v/>
       </c>
       <c r="R298">
-        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 297 - 1), NA())</f>
+        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 297 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="299">
       <c r="P299" s="2">
-        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 298 - 1), NA())</f>
+        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 298 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q299">
-        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 298 - 1), NA())</f>
+        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 298 - 1), NA())</f>
         <v/>
       </c>
       <c r="R299">
-        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 298 - 1), NA())</f>
+        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 298 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="300">
       <c r="P300" s="2">
-        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 299 - 1), NA())</f>
+        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 299 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q300">
-        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 299 - 1), NA())</f>
+        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 299 - 1), NA())</f>
         <v/>
       </c>
       <c r="R300">
-        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 299 - 1), NA())</f>
+        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 299 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="301">
       <c r="P301" s="2">
-        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 300 - 1), NA())</f>
+        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 300 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q301">
-        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 300 - 1), NA())</f>
+        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 300 - 1), NA())</f>
         <v/>
       </c>
       <c r="R301">
-        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 300 - 1), NA())</f>
+        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 300 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="302">
       <c r="P302" s="2">
-        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 301 - 1), NA())</f>
+        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 301 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q302">
-        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 301 - 1), NA())</f>
+        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 301 - 1), NA())</f>
         <v/>
       </c>
       <c r="R302">
-        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 301 - 1), NA())</f>
+        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 301 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="303">
       <c r="P303" s="2">
-        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 302 - 1), NA())</f>
+        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 302 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q303">
-        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 302 - 1), NA())</f>
+        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 302 - 1), NA())</f>
         <v/>
       </c>
       <c r="R303">
-        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 302 - 1), NA())</f>
+        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 302 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="304">
       <c r="P304" s="2">
-        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 303 - 1), NA())</f>
+        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 303 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q304">
-        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 303 - 1), NA())</f>
+        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 303 - 1), NA())</f>
         <v/>
       </c>
       <c r="R304">
-        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 303 - 1), NA())</f>
+        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 303 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="305">
       <c r="P305" s="2">
-        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 304 - 1), NA())</f>
+        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 304 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q305">
-        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 304 - 1), NA())</f>
+        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 304 - 1), NA())</f>
         <v/>
       </c>
       <c r="R305">
-        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 304 - 1), NA())</f>
+        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 304 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="306">
       <c r="P306" s="2">
-        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 305 - 1), NA())</f>
+        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 305 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q306">
-        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 305 - 1), NA())</f>
+        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 305 - 1), NA())</f>
         <v/>
       </c>
       <c r="R306">
-        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 305 - 1), NA())</f>
+        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 305 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="307">
       <c r="P307" s="2">
-        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 306 - 1), NA())</f>
+        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 306 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q307">
-        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 306 - 1), NA())</f>
+        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 306 - 1), NA())</f>
         <v/>
       </c>
       <c r="R307">
-        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 306 - 1), NA())</f>
+        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 306 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="308">
       <c r="P308" s="2">
-        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 307 - 1), NA())</f>
+        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 307 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q308">
-        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 307 - 1), NA())</f>
+        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 307 - 1), NA())</f>
         <v/>
       </c>
       <c r="R308">
-        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 307 - 1), NA())</f>
+        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 307 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="309">
       <c r="P309" s="2">
-        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 308 - 1), NA())</f>
+        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 308 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q309">
-        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 308 - 1), NA())</f>
+        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 308 - 1), NA())</f>
         <v/>
       </c>
       <c r="R309">
-        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 308 - 1), NA())</f>
+        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 308 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="310">
       <c r="P310" s="2">
-        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 309 - 1), NA())</f>
+        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 309 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q310">
-        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 309 - 1), NA())</f>
+        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 309 - 1), NA())</f>
         <v/>
       </c>
       <c r="R310">
-        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 309 - 1), NA())</f>
+        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 309 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="311">
       <c r="P311" s="2">
-        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 310 - 1), NA())</f>
+        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 310 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q311">
-        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 310 - 1), NA())</f>
+        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 310 - 1), NA())</f>
         <v/>
       </c>
       <c r="R311">
-        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 310 - 1), NA())</f>
+        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 310 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="312">
       <c r="P312" s="2">
-        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 311 - 1), NA())</f>
+        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 311 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q312">
-        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 311 - 1), NA())</f>
+        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 311 - 1), NA())</f>
         <v/>
       </c>
       <c r="R312">
-        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 311 - 1), NA())</f>
+        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 311 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="313">
       <c r="P313" s="2">
-        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 312 - 1), NA())</f>
+        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 312 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q313">
-        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 312 - 1), NA())</f>
+        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 312 - 1), NA())</f>
         <v/>
       </c>
       <c r="R313">
-        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 312 - 1), NA())</f>
+        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 312 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="314">
       <c r="P314" s="2">
-        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 313 - 1), NA())</f>
+        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 313 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q314">
-        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 313 - 1), NA())</f>
+        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 313 - 1), NA())</f>
         <v/>
       </c>
       <c r="R314">
-        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 313 - 1), NA())</f>
+        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 313 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="315">
       <c r="P315" s="2">
-        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 314 - 1), NA())</f>
+        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 314 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q315">
-        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 314 - 1), NA())</f>
+        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 314 - 1), NA())</f>
         <v/>
       </c>
       <c r="R315">
-        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 314 - 1), NA())</f>
+        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 314 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="316">
       <c r="P316" s="2">
-        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 315 - 1), NA())</f>
+        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 315 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q316">
-        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 315 - 1), NA())</f>
+        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 315 - 1), NA())</f>
         <v/>
       </c>
       <c r="R316">
-        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 315 - 1), NA())</f>
+        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 315 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="317">
       <c r="P317" s="2">
-        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 316 - 1), NA())</f>
+        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 316 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q317">
-        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 316 - 1), NA())</f>
+        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 316 - 1), NA())</f>
         <v/>
       </c>
       <c r="R317">
-        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 316 - 1), NA())</f>
+        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 316 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="318">
       <c r="P318" s="2">
-        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 317 - 1), NA())</f>
+        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 317 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q318">
-        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 317 - 1), NA())</f>
+        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 317 - 1), NA())</f>
         <v/>
       </c>
       <c r="R318">
-        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 317 - 1), NA())</f>
+        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 317 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="319">
       <c r="P319" s="2">
-        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 318 - 1), NA())</f>
+        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 318 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q319">
-        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 318 - 1), NA())</f>
+        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 318 - 1), NA())</f>
         <v/>
       </c>
       <c r="R319">
-        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 318 - 1), NA())</f>
+        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 318 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="320">
       <c r="P320" s="2">
-        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 319 - 1), NA())</f>
+        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 319 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q320">
-        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 319 - 1), NA())</f>
+        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 319 - 1), NA())</f>
         <v/>
       </c>
       <c r="R320">
-        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 319 - 1), NA())</f>
+        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 319 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="321">
       <c r="P321" s="2">
-        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 320 - 1), NA())</f>
+        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 320 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q321">
-        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 320 - 1), NA())</f>
+        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 320 - 1), NA())</f>
         <v/>
       </c>
       <c r="R321">
-        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 320 - 1), NA())</f>
+        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 320 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="322">
       <c r="P322" s="2">
-        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 321 - 1), NA())</f>
+        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 321 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q322">
-        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 321 - 1), NA())</f>
+        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 321 - 1), NA())</f>
         <v/>
       </c>
       <c r="R322">
-        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 321 - 1), NA())</f>
+        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 321 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="323">
       <c r="P323" s="2">
-        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 322 - 1), NA())</f>
+        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 322 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q323">
-        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 322 - 1), NA())</f>
+        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 322 - 1), NA())</f>
         <v/>
       </c>
       <c r="R323">
-        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 322 - 1), NA())</f>
+        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 322 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="324">
       <c r="P324" s="2">
-        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 323 - 1), NA())</f>
+        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 323 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q324">
-        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 323 - 1), NA())</f>
+        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 323 - 1), NA())</f>
         <v/>
       </c>
       <c r="R324">
-        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 323 - 1), NA())</f>
+        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 323 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="325">
       <c r="P325" s="2">
-        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 324 - 1), NA())</f>
+        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 324 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q325">
-        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 324 - 1), NA())</f>
+        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 324 - 1), NA())</f>
         <v/>
       </c>
       <c r="R325">
-        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 324 - 1), NA())</f>
+        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 324 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="326">
       <c r="P326" s="2">
-        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 325 - 1), NA())</f>
+        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 325 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q326">
-        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 325 - 1), NA())</f>
+        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 325 - 1), NA())</f>
         <v/>
       </c>
       <c r="R326">
-        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 325 - 1), NA())</f>
+        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 325 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="327">
       <c r="P327" s="2">
-        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 326 - 1), NA())</f>
+        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 326 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q327">
-        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 326 - 1), NA())</f>
+        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 326 - 1), NA())</f>
         <v/>
       </c>
       <c r="R327">
-        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 326 - 1), NA())</f>
+        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 326 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="328">
       <c r="P328" s="2">
-        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 327 - 1), NA())</f>
+        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 327 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q328">
-        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 327 - 1), NA())</f>
+        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 327 - 1), NA())</f>
         <v/>
       </c>
       <c r="R328">
-        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 327 - 1), NA())</f>
+        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 327 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="329">
       <c r="P329" s="2">
-        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 328 - 1), NA())</f>
+        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 328 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q329">
-        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 328 - 1), NA())</f>
+        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 328 - 1), NA())</f>
         <v/>
       </c>
       <c r="R329">
-        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 328 - 1), NA())</f>
+        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 328 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="330">
       <c r="P330" s="2">
-        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 329 - 1), NA())</f>
+        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 329 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q330">
-        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 329 - 1), NA())</f>
+        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 329 - 1), NA())</f>
         <v/>
       </c>
       <c r="R330">
-        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 329 - 1), NA())</f>
+        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 329 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="331">
       <c r="P331" s="2">
-        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 330 - 1), NA())</f>
+        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 330 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q331">
-        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 330 - 1), NA())</f>
+        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 330 - 1), NA())</f>
         <v/>
       </c>
       <c r="R331">
-        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 330 - 1), NA())</f>
+        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 330 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="332">
       <c r="P332" s="2">
-        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 331 - 1), NA())</f>
+        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 331 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q332">
-        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 331 - 1), NA())</f>
+        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 331 - 1), NA())</f>
         <v/>
       </c>
       <c r="R332">
-        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 331 - 1), NA())</f>
+        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 331 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="333">
       <c r="P333" s="2">
-        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 332 - 1), NA())</f>
+        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 332 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q333">
-        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 332 - 1), NA())</f>
+        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 332 - 1), NA())</f>
         <v/>
       </c>
       <c r="R333">
-        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 332 - 1), NA())</f>
+        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 332 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="334">
       <c r="P334" s="2">
-        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 333 - 1), NA())</f>
+        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 333 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q334">
-        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 333 - 1), NA())</f>
+        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 333 - 1), NA())</f>
         <v/>
       </c>
       <c r="R334">
-        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 333 - 1), NA())</f>
+        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 333 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="335">
       <c r="P335" s="2">
-        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 334 - 1), NA())</f>
+        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 334 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q335">
-        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 334 - 1), NA())</f>
+        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 334 - 1), NA())</f>
         <v/>
       </c>
       <c r="R335">
-        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 334 - 1), NA())</f>
+        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 334 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="336">
       <c r="P336" s="2">
-        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 335 - 1), NA())</f>
+        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 335 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q336">
-        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 335 - 1), NA())</f>
+        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 335 - 1), NA())</f>
         <v/>
       </c>
       <c r="R336">
-        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 335 - 1), NA())</f>
+        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 335 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="337">
       <c r="P337" s="2">
-        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 336 - 1), NA())</f>
+        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 336 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q337">
-        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 336 - 1), NA())</f>
+        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 336 - 1), NA())</f>
         <v/>
       </c>
       <c r="R337">
-        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 336 - 1), NA())</f>
+        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 336 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="338">
       <c r="P338" s="2">
-        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 337 - 1), NA())</f>
+        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 337 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q338">
-        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 337 - 1), NA())</f>
+        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 337 - 1), NA())</f>
         <v/>
       </c>
       <c r="R338">
-        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 337 - 1), NA())</f>
+        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 337 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="339">
       <c r="P339" s="2">
-        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 338 - 1), NA())</f>
+        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 338 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q339">
-        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 338 - 1), NA())</f>
+        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 338 - 1), NA())</f>
         <v/>
       </c>
       <c r="R339">
-        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 338 - 1), NA())</f>
+        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 338 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="340">
       <c r="P340" s="2">
-        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 339 - 1), NA())</f>
+        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 339 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q340">
-        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 339 - 1), NA())</f>
+        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 339 - 1), NA())</f>
         <v/>
       </c>
       <c r="R340">
-        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 339 - 1), NA())</f>
+        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 339 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="341">
       <c r="P341" s="2">
-        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 340 - 1), NA())</f>
+        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 340 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q341">
-        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 340 - 1), NA())</f>
+        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 340 - 1), NA())</f>
         <v/>
       </c>
       <c r="R341">
-        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 340 - 1), NA())</f>
+        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 340 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="342">
       <c r="P342" s="2">
-        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 341 - 1), NA())</f>
+        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 341 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q342">
-        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 341 - 1), NA())</f>
+        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 341 - 1), NA())</f>
         <v/>
       </c>
       <c r="R342">
-        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 341 - 1), NA())</f>
+        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 341 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="343">
       <c r="P343" s="2">
-        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 342 - 1), NA())</f>
+        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 342 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q343">
-        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 342 - 1), NA())</f>
+        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 342 - 1), NA())</f>
         <v/>
       </c>
       <c r="R343">
-        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 342 - 1), NA())</f>
+        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 342 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="344">
       <c r="P344" s="2">
-        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 343 - 1), NA())</f>
+        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 343 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q344">
-        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 343 - 1), NA())</f>
+        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 343 - 1), NA())</f>
         <v/>
       </c>
       <c r="R344">
-        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 343 - 1), NA())</f>
+        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 343 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="345">
       <c r="P345" s="2">
-        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 344 - 1), NA())</f>
+        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 344 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q345">
-        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 344 - 1), NA())</f>
+        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 344 - 1), NA())</f>
         <v/>
       </c>
       <c r="R345">
-        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 344 - 1), NA())</f>
+        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 344 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="346">
       <c r="P346" s="2">
-        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 345 - 1), NA())</f>
+        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 345 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q346">
-        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 345 - 1), NA())</f>
+        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 345 - 1), NA())</f>
         <v/>
       </c>
       <c r="R346">
-        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 345 - 1), NA())</f>
+        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 345 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="347">
       <c r="P347" s="2">
-        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 346 - 1), NA())</f>
+        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 346 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q347">
-        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 346 - 1), NA())</f>
+        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 346 - 1), NA())</f>
         <v/>
       </c>
       <c r="R347">
-        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 346 - 1), NA())</f>
+        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 346 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="348">
       <c r="P348" s="2">
-        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 347 - 1), NA())</f>
+        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 347 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q348">
-        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 347 - 1), NA())</f>
+        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 347 - 1), NA())</f>
         <v/>
       </c>
       <c r="R348">
-        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 347 - 1), NA())</f>
+        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 347 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="349">
       <c r="P349" s="2">
-        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 348 - 1), NA())</f>
+        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 348 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q349">
-        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 348 - 1), NA())</f>
+        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 348 - 1), NA())</f>
         <v/>
       </c>
       <c r="R349">
-        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 348 - 1), NA())</f>
+        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 348 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="350">
       <c r="P350" s="2">
-        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 349 - 1), NA())</f>
+        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 349 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q350">
-        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 349 - 1), NA())</f>
+        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 349 - 1), NA())</f>
         <v/>
       </c>
       <c r="R350">
-        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 349 - 1), NA())</f>
+        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 349 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="351">
       <c r="P351" s="2">
-        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 350 - 1), NA())</f>
+        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 350 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q351">
-        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 350 - 1), NA())</f>
+        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 350 - 1), NA())</f>
         <v/>
       </c>
       <c r="R351">
-        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 350 - 1), NA())</f>
+        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 350 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="352">
       <c r="P352" s="2">
-        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 351 - 1), NA())</f>
+        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 351 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q352">
-        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 351 - 1), NA())</f>
+        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 351 - 1), NA())</f>
         <v/>
       </c>
       <c r="R352">
-        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 351 - 1), NA())</f>
+        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 351 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="353">
       <c r="P353" s="2">
-        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 352 - 1), NA())</f>
+        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 352 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q353">
-        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 352 - 1), NA())</f>
+        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 352 - 1), NA())</f>
         <v/>
       </c>
       <c r="R353">
-        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 352 - 1), NA())</f>
+        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 352 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="354">
       <c r="P354" s="2">
-        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 353 - 1), NA())</f>
+        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 353 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q354">
-        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 353 - 1), NA())</f>
+        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 353 - 1), NA())</f>
         <v/>
       </c>
       <c r="R354">
-        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 353 - 1), NA())</f>
+        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 353 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="355">
       <c r="P355" s="2">
-        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 354 - 1), NA())</f>
+        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 354 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q355">
-        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 354 - 1), NA())</f>
+        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 354 - 1), NA())</f>
         <v/>
       </c>
       <c r="R355">
-        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 354 - 1), NA())</f>
+        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 354 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="356">
       <c r="P356" s="2">
-        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 355 - 1), NA())</f>
+        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 355 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q356">
-        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 355 - 1), NA())</f>
+        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 355 - 1), NA())</f>
         <v/>
       </c>
       <c r="R356">
-        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 355 - 1), NA())</f>
+        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 355 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="357">
       <c r="P357" s="2">
-        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 356 - 1), NA())</f>
+        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 356 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q357">
-        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 356 - 1), NA())</f>
+        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 356 - 1), NA())</f>
         <v/>
       </c>
       <c r="R357">
-        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 356 - 1), NA())</f>
+        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 356 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="358">
       <c r="P358" s="2">
-        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 357 - 1), NA())</f>
+        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 357 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q358">
-        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 357 - 1), NA())</f>
+        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 357 - 1), NA())</f>
         <v/>
       </c>
       <c r="R358">
-        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 357 - 1), NA())</f>
+        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 357 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="359">
       <c r="P359" s="2">
-        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 358 - 1), NA())</f>
+        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 358 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q359">
-        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 358 - 1), NA())</f>
+        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 358 - 1), NA())</f>
         <v/>
       </c>
       <c r="R359">
-        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 358 - 1), NA())</f>
+        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 358 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="360">
       <c r="P360" s="2">
-        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 359 - 1), NA())</f>
+        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 359 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q360">
-        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 359 - 1), NA())</f>
+        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 359 - 1), NA())</f>
         <v/>
       </c>
       <c r="R360">
-        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 359 - 1), NA())</f>
+        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 359 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="361">
       <c r="P361" s="2">
-        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 360 - 1), NA())</f>
+        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 360 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q361">
-        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 360 - 1), NA())</f>
+        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 360 - 1), NA())</f>
         <v/>
       </c>
       <c r="R361">
-        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 360 - 1), NA())</f>
+        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 360 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="362">
       <c r="P362" s="2">
-        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 361 - 1), NA())</f>
+        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 361 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q362">
-        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 361 - 1), NA())</f>
+        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 361 - 1), NA())</f>
         <v/>
       </c>
       <c r="R362">
-        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 361 - 1), NA())</f>
+        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 361 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="363">
       <c r="P363" s="2">
-        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 362 - 1), NA())</f>
+        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 362 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q363">
-        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 362 - 1), NA())</f>
+        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 362 - 1), NA())</f>
         <v/>
       </c>
       <c r="R363">
-        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 362 - 1), NA())</f>
+        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 362 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="364">
       <c r="P364" s="2">
-        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 363 - 1), NA())</f>
+        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 363 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q364">
-        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 363 - 1), NA())</f>
+        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 363 - 1), NA())</f>
         <v/>
       </c>
       <c r="R364">
-        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 363 - 1), NA())</f>
+        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 363 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="365">
       <c r="P365" s="2">
-        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 364 - 1), NA())</f>
+        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 364 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q365">
-        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 364 - 1), NA())</f>
+        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 364 - 1), NA())</f>
         <v/>
       </c>
       <c r="R365">
-        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 364 - 1), NA())</f>
+        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 364 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="366">
       <c r="P366" s="2">
-        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 365 - 1), NA())</f>
+        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 365 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q366">
-        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 365 - 1), NA())</f>
+        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 365 - 1), NA())</f>
         <v/>
       </c>
       <c r="R366">
-        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 365 - 1), NA())</f>
+        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 365 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="367">
       <c r="P367" s="2">
-        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 366 - 1), NA())</f>
+        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 366 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q367">
-        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 366 - 1), NA())</f>
+        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 366 - 1), NA())</f>
         <v/>
       </c>
       <c r="R367">
-        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 366 - 1), NA())</f>
+        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 366 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="368">
       <c r="P368" s="2">
-        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 367 - 1), NA())</f>
+        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 367 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q368">
-        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 367 - 1), NA())</f>
+        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 367 - 1), NA())</f>
         <v/>
       </c>
       <c r="R368">
-        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 367 - 1), NA())</f>
+        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 367 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="369">
       <c r="P369" s="2">
-        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 368 - 1), NA())</f>
+        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 368 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q369">
-        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 368 - 1), NA())</f>
+        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 368 - 1), NA())</f>
         <v/>
       </c>
       <c r="R369">
-        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 368 - 1), NA())</f>
+        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 368 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="370">
       <c r="P370" s="2">
-        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 369 - 1), NA())</f>
+        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 369 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q370">
-        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 369 - 1), NA())</f>
+        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 369 - 1), NA())</f>
         <v/>
       </c>
       <c r="R370">
-        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 369 - 1), NA())</f>
+        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 369 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="371">
       <c r="P371" s="2">
-        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 370 - 1), NA())</f>
+        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 370 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q371">
-        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 370 - 1), NA())</f>
+        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 370 - 1), NA())</f>
         <v/>
       </c>
       <c r="R371">
-        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 370 - 1), NA())</f>
+        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 370 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="372">
       <c r="P372" s="2">
-        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 371 - 1), NA())</f>
+        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 371 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q372">
-        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 371 - 1), NA())</f>
+        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 371 - 1), NA())</f>
         <v/>
       </c>
       <c r="R372">
-        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 371 - 1), NA())</f>
+        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 371 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="373">
       <c r="P373" s="2">
-        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 372 - 1), NA())</f>
+        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 372 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q373">
-        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 372 - 1), NA())</f>
+        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 372 - 1), NA())</f>
         <v/>
       </c>
       <c r="R373">
-        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 372 - 1), NA())</f>
+        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 372 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="374">
       <c r="P374" s="2">
-        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 373 - 1), NA())</f>
+        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 373 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q374">
-        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 373 - 1), NA())</f>
+        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 373 - 1), NA())</f>
         <v/>
       </c>
       <c r="R374">
-        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 373 - 1), NA())</f>
+        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 373 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="375">
       <c r="P375" s="2">
-        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 374 - 1), NA())</f>
+        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 374 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q375">
-        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 374 - 1), NA())</f>
+        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 374 - 1), NA())</f>
         <v/>
       </c>
       <c r="R375">
-        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 374 - 1), NA())</f>
+        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 374 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="376">
       <c r="P376" s="2">
-        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 375 - 1), NA())</f>
+        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 375 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q376">
-        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 375 - 1), NA())</f>
+        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 375 - 1), NA())</f>
         <v/>
       </c>
       <c r="R376">
-        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 375 - 1), NA())</f>
+        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 375 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="377">
       <c r="P377" s="2">
-        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 376 - 1), NA())</f>
+        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 376 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q377">
-        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 376 - 1), NA())</f>
+        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 376 - 1), NA())</f>
         <v/>
       </c>
       <c r="R377">
-        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 376 - 1), NA())</f>
+        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 376 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="378">
       <c r="P378" s="2">
-        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 377 - 1), NA())</f>
+        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 377 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q378">
-        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 377 - 1), NA())</f>
+        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 377 - 1), NA())</f>
         <v/>
       </c>
       <c r="R378">
-        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 377 - 1), NA())</f>
+        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 377 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="379">
       <c r="P379" s="2">
-        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 378 - 1), NA())</f>
+        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 378 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q379">
-        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 378 - 1), NA())</f>
+        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 378 - 1), NA())</f>
         <v/>
       </c>
       <c r="R379">
-        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 378 - 1), NA())</f>
+        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 378 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="380">
       <c r="P380" s="2">
-        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 379 - 1), NA())</f>
+        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 379 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q380">
-        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 379 - 1), NA())</f>
+        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 379 - 1), NA())</f>
         <v/>
       </c>
       <c r="R380">
-        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 379 - 1), NA())</f>
+        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 379 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="381">
       <c r="P381" s="2">
-        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 380 - 1), NA())</f>
+        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 380 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q381">
-        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 380 - 1), NA())</f>
+        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 380 - 1), NA())</f>
         <v/>
       </c>
       <c r="R381">
-        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 380 - 1), NA())</f>
+        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 380 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="382">
       <c r="P382" s="2">
-        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 381 - 1), NA())</f>
+        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 381 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q382">
-        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 381 - 1), NA())</f>
+        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 381 - 1), NA())</f>
         <v/>
       </c>
       <c r="R382">
-        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 381 - 1), NA())</f>
+        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 381 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="383">
       <c r="P383" s="2">
-        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 382 - 1), NA())</f>
+        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 382 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q383">
-        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 382 - 1), NA())</f>
+        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 382 - 1), NA())</f>
         <v/>
       </c>
       <c r="R383">
-        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 382 - 1), NA())</f>
+        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 382 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="384">
       <c r="P384" s="2">
-        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 383 - 1), NA())</f>
+        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 383 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q384">
-        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 383 - 1), NA())</f>
+        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 383 - 1), NA())</f>
         <v/>
       </c>
       <c r="R384">
-        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 383 - 1), NA())</f>
+        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 383 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="385">
       <c r="P385" s="2">
-        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 384 - 1), NA())</f>
+        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 384 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q385">
-        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 384 - 1), NA())</f>
+        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 384 - 1), NA())</f>
         <v/>
       </c>
       <c r="R385">
-        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 384 - 1), NA())</f>
+        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 384 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="386">
       <c r="P386" s="2">
-        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 385 - 1), NA())</f>
+        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 385 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q386">
-        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 385 - 1), NA())</f>
+        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 385 - 1), NA())</f>
         <v/>
       </c>
       <c r="R386">
-        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 385 - 1), NA())</f>
+        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 385 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="387">
       <c r="P387" s="2">
-        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 386 - 1), NA())</f>
+        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 386 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q387">
-        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 386 - 1), NA())</f>
+        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 386 - 1), NA())</f>
         <v/>
       </c>
       <c r="R387">
-        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 386 - 1), NA())</f>
+        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 386 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="388">
       <c r="P388" s="2">
-        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 387 - 1), NA())</f>
+        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 387 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q388">
-        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 387 - 1), NA())</f>
+        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 387 - 1), NA())</f>
         <v/>
       </c>
       <c r="R388">
-        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 387 - 1), NA())</f>
+        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 387 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="389">
       <c r="P389" s="2">
-        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 388 - 1), NA())</f>
+        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 388 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q389">
-        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 388 - 1), NA())</f>
+        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 388 - 1), NA())</f>
         <v/>
       </c>
       <c r="R389">
-        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 388 - 1), NA())</f>
+        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 388 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="390">
       <c r="P390" s="2">
-        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 389 - 1), NA())</f>
+        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 389 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q390">
-        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 389 - 1), NA())</f>
+        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 389 - 1), NA())</f>
         <v/>
       </c>
       <c r="R390">
-        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 389 - 1), NA())</f>
+        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 389 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="391">
       <c r="P391" s="2">
-        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 390 - 1), NA())</f>
+        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 390 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q391">
-        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 390 - 1), NA())</f>
+        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 390 - 1), NA())</f>
         <v/>
       </c>
       <c r="R391">
-        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 390 - 1), NA())</f>
+        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 390 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="392">
       <c r="P392" s="2">
-        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 391 - 1), NA())</f>
+        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 391 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q392">
-        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 391 - 1), NA())</f>
+        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 391 - 1), NA())</f>
         <v/>
       </c>
       <c r="R392">
-        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 391 - 1), NA())</f>
+        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 391 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="393">
       <c r="P393" s="2">
-        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 392 - 1), NA())</f>
+        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 392 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q393">
-        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 392 - 1), NA())</f>
+        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 392 - 1), NA())</f>
         <v/>
       </c>
       <c r="R393">
-        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 392 - 1), NA())</f>
+        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 392 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="394">
       <c r="P394" s="2">
-        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 393 - 1), NA())</f>
+        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 393 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q394">
-        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 393 - 1), NA())</f>
+        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 393 - 1), NA())</f>
         <v/>
       </c>
       <c r="R394">
-        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 393 - 1), NA())</f>
+        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 393 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="395">
       <c r="P395" s="2">
-        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 394 - 1), NA())</f>
+        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 394 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q395">
-        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 394 - 1), NA())</f>
+        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 394 - 1), NA())</f>
         <v/>
       </c>
       <c r="R395">
-        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 394 - 1), NA())</f>
+        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 394 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="396">
       <c r="P396" s="2">
-        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 395 - 1), NA())</f>
+        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 395 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q396">
-        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 395 - 1), NA())</f>
+        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 395 - 1), NA())</f>
         <v/>
       </c>
       <c r="R396">
-        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 395 - 1), NA())</f>
+        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 395 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="397">
       <c r="P397" s="2">
-        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 396 - 1), NA())</f>
+        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 396 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q397">
-        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 396 - 1), NA())</f>
+        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 396 - 1), NA())</f>
         <v/>
       </c>
       <c r="R397">
-        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 396 - 1), NA())</f>
+        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 396 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="398">
       <c r="P398" s="2">
-        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 397 - 1), NA())</f>
+        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 397 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q398">
-        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 397 - 1), NA())</f>
+        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 397 - 1), NA())</f>
         <v/>
       </c>
       <c r="R398">
-        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 397 - 1), NA())</f>
+        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 397 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="399">
       <c r="P399" s="2">
-        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 398 - 1), NA())</f>
+        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 398 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q399">
-        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 398 - 1), NA())</f>
+        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 398 - 1), NA())</f>
         <v/>
       </c>
       <c r="R399">
-        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 398 - 1), NA())</f>
+        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 398 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="400">
       <c r="P400" s="2">
-        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 399 - 1), NA())</f>
+        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 399 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q400">
-        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 399 - 1), NA())</f>
+        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 399 - 1), NA())</f>
         <v/>
       </c>
       <c r="R400">
-        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 399 - 1), NA())</f>
+        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 399 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="401">
       <c r="P401" s="2">
-        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 400 - 1), NA())</f>
+        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 400 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q401">
-        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 400 - 1), NA())</f>
+        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 400 - 1), NA())</f>
         <v/>
       </c>
       <c r="R401">
-        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 400 - 1), NA())</f>
+        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 400 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="402">
       <c r="P402" s="2">
-        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 401 - 1), NA())</f>
+        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 401 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q402">
-        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 401 - 1), NA())</f>
+        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 401 - 1), NA())</f>
         <v/>
       </c>
       <c r="R402">
-        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 401 - 1), NA())</f>
+        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 401 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="403">
       <c r="P403" s="2">
-        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 402 - 1), NA())</f>
+        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 402 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q403">
-        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 402 - 1), NA())</f>
+        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 402 - 1), NA())</f>
         <v/>
       </c>
       <c r="R403">
-        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 402 - 1), NA())</f>
+        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 402 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="404">
       <c r="P404" s="2">
-        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 403 - 1), NA())</f>
+        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 403 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q404">
-        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 403 - 1), NA())</f>
+        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 403 - 1), NA())</f>
         <v/>
       </c>
       <c r="R404">
-        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 403 - 1), NA())</f>
+        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 403 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="405">
       <c r="P405" s="2">
-        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 404 - 1), NA())</f>
+        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 404 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q405">
-        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 404 - 1), NA())</f>
+        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 404 - 1), NA())</f>
         <v/>
       </c>
       <c r="R405">
-        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 404 - 1), NA())</f>
+        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 404 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="406">
       <c r="P406" s="2">
-        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 405 - 1), NA())</f>
+        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 405 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q406">
-        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 405 - 1), NA())</f>
+        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 405 - 1), NA())</f>
         <v/>
       </c>
       <c r="R406">
-        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 405 - 1), NA())</f>
+        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 405 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="407">
       <c r="P407" s="2">
-        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 406 - 1), NA())</f>
+        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 406 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q407">
-        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 406 - 1), NA())</f>
+        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 406 - 1), NA())</f>
         <v/>
       </c>
       <c r="R407">
-        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 406 - 1), NA())</f>
+        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 406 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="408">
       <c r="P408" s="2">
-        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 407 - 1), NA())</f>
+        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 407 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q408">
-        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 407 - 1), NA())</f>
+        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 407 - 1), NA())</f>
         <v/>
       </c>
       <c r="R408">
-        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 407 - 1), NA())</f>
+        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 407 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="409">
       <c r="P409" s="2">
-        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 408 - 1), NA())</f>
+        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 408 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q409">
-        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 408 - 1), NA())</f>
+        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 408 - 1), NA())</f>
         <v/>
       </c>
       <c r="R409">
-        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 408 - 1), NA())</f>
+        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 408 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="410">
       <c r="P410" s="2">
-        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 409 - 1), NA())</f>
+        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 409 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q410">
-        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 409 - 1), NA())</f>
+        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 409 - 1), NA())</f>
         <v/>
       </c>
       <c r="R410">
-        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 409 - 1), NA())</f>
+        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 409 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="411">
       <c r="P411" s="2">
-        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 410 - 1), NA())</f>
+        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 410 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q411">
-        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 410 - 1), NA())</f>
+        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 410 - 1), NA())</f>
         <v/>
       </c>
       <c r="R411">
-        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 410 - 1), NA())</f>
+        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 410 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="412">
       <c r="P412" s="2">
-        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 411 - 1), NA())</f>
+        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 411 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q412">
-        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 411 - 1), NA())</f>
+        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 411 - 1), NA())</f>
         <v/>
       </c>
       <c r="R412">
-        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 411 - 1), NA())</f>
+        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 411 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="413">
       <c r="P413" s="2">
-        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 412 - 1), NA())</f>
+        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 412 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q413">
-        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 412 - 1), NA())</f>
+        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 412 - 1), NA())</f>
         <v/>
       </c>
       <c r="R413">
-        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 412 - 1), NA())</f>
+        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 412 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="414">
       <c r="P414" s="2">
-        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 413 - 1), NA())</f>
+        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 413 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q414">
-        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 413 - 1), NA())</f>
+        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 413 - 1), NA())</f>
         <v/>
       </c>
       <c r="R414">
-        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 413 - 1), NA())</f>
+        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 413 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="415">
       <c r="P415" s="2">
-        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 414 - 1), NA())</f>
+        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 414 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q415">
-        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 414 - 1), NA())</f>
+        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 414 - 1), NA())</f>
         <v/>
       </c>
       <c r="R415">
-        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 414 - 1), NA())</f>
+        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 414 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="416">
       <c r="P416" s="2">
-        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 415 - 1), NA())</f>
+        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 415 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q416">
-        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 415 - 1), NA())</f>
+        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 415 - 1), NA())</f>
         <v/>
       </c>
       <c r="R416">
-        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 415 - 1), NA())</f>
+        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 415 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="417">
       <c r="P417" s="2">
-        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 416 - 1), NA())</f>
+        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 416 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q417">
-        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 416 - 1), NA())</f>
+        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 416 - 1), NA())</f>
         <v/>
       </c>
       <c r="R417">
-        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 416 - 1), NA())</f>
+        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 416 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="418">
       <c r="P418" s="2">
-        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 417 - 1), NA())</f>
+        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 417 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q418">
-        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 417 - 1), NA())</f>
+        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 417 - 1), NA())</f>
         <v/>
       </c>
       <c r="R418">
-        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 417 - 1), NA())</f>
+        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 417 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="419">
       <c r="P419" s="2">
-        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 418 - 1), NA())</f>
+        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 418 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q419">
-        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 418 - 1), NA())</f>
+        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 418 - 1), NA())</f>
         <v/>
       </c>
       <c r="R419">
-        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 418 - 1), NA())</f>
+        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 418 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="420">
       <c r="P420" s="2">
-        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 419 - 1), NA())</f>
+        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 419 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q420">
-        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 419 - 1), NA())</f>
+        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 419 - 1), NA())</f>
         <v/>
       </c>
       <c r="R420">
-        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 419 - 1), NA())</f>
+        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 419 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="421">
       <c r="P421" s="2">
-        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 420 - 1), NA())</f>
+        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 420 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q421">
-        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 420 - 1), NA())</f>
+        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 420 - 1), NA())</f>
         <v/>
       </c>
       <c r="R421">
-        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 420 - 1), NA())</f>
+        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 420 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="422">
       <c r="P422" s="2">
-        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 421 - 1), NA())</f>
+        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 421 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q422">
-        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 421 - 1), NA())</f>
+        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 421 - 1), NA())</f>
         <v/>
       </c>
       <c r="R422">
-        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 421 - 1), NA())</f>
+        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 421 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="423">
       <c r="P423" s="2">
-        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 422 - 1), NA())</f>
+        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 422 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q423">
-        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 422 - 1), NA())</f>
+        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 422 - 1), NA())</f>
         <v/>
       </c>
       <c r="R423">
-        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 422 - 1), NA())</f>
+        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 422 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="424">
       <c r="P424" s="2">
-        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 423 - 1), NA())</f>
+        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 423 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q424">
-        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 423 - 1), NA())</f>
+        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 423 - 1), NA())</f>
         <v/>
       </c>
       <c r="R424">
-        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 423 - 1), NA())</f>
+        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 423 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="425">
       <c r="P425" s="2">
-        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 424 - 1), NA())</f>
+        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 424 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q425">
-        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 424 - 1), NA())</f>
+        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 424 - 1), NA())</f>
         <v/>
       </c>
       <c r="R425">
-        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 424 - 1), NA())</f>
+        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 424 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="426">
       <c r="P426" s="2">
-        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 425 - 1), NA())</f>
+        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 425 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q426">
-        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 425 - 1), NA())</f>
+        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 425 - 1), NA())</f>
         <v/>
       </c>
       <c r="R426">
-        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 425 - 1), NA())</f>
+        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 425 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="427">
       <c r="P427" s="2">
-        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 426 - 1), NA())</f>
+        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 426 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q427">
-        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 426 - 1), NA())</f>
+        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 426 - 1), NA())</f>
         <v/>
       </c>
       <c r="R427">
-        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 426 - 1), NA())</f>
+        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 426 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="428">
       <c r="P428" s="2">
-        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 427 - 1), NA())</f>
+        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 427 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q428">
-        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 427 - 1), NA())</f>
+        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 427 - 1), NA())</f>
         <v/>
       </c>
       <c r="R428">
-        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 427 - 1), NA())</f>
+        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 427 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="429">
       <c r="P429" s="2">
-        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 428 - 1), NA())</f>
+        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 428 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q429">
-        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 428 - 1), NA())</f>
+        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 428 - 1), NA())</f>
         <v/>
       </c>
       <c r="R429">
-        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 428 - 1), NA())</f>
+        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 428 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="430">
       <c r="P430" s="2">
-        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 429 - 1), NA())</f>
+        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 429 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q430">
-        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 429 - 1), NA())</f>
+        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 429 - 1), NA())</f>
         <v/>
       </c>
       <c r="R430">
-        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 429 - 1), NA())</f>
+        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 429 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="431">
       <c r="P431" s="2">
-        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 430 - 1), NA())</f>
+        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 430 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q431">
-        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 430 - 1), NA())</f>
+        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 430 - 1), NA())</f>
         <v/>
       </c>
       <c r="R431">
-        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 430 - 1), NA())</f>
+        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 430 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="432">
       <c r="P432" s="2">
-        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 431 - 1), NA())</f>
+        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 431 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q432">
-        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 431 - 1), NA())</f>
+        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 431 - 1), NA())</f>
         <v/>
       </c>
       <c r="R432">
-        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 431 - 1), NA())</f>
+        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 431 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="433">
       <c r="P433" s="2">
-        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 432 - 1), NA())</f>
+        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 432 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q433">
-        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 432 - 1), NA())</f>
+        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 432 - 1), NA())</f>
         <v/>
       </c>
       <c r="R433">
-        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 432 - 1), NA())</f>
+        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 432 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="434">
       <c r="P434" s="2">
-        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 433 - 1), NA())</f>
+        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 433 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q434">
-        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 433 - 1), NA())</f>
+        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 433 - 1), NA())</f>
         <v/>
       </c>
       <c r="R434">
-        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 433 - 1), NA())</f>
+        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 433 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="435">
       <c r="P435" s="2">
-        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 434 - 1), NA())</f>
+        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 434 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q435">
-        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 434 - 1), NA())</f>
+        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 434 - 1), NA())</f>
         <v/>
       </c>
       <c r="R435">
-        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 434 - 1), NA())</f>
+        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 434 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="436">
       <c r="P436" s="2">
-        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 435 - 1), NA())</f>
+        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 435 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q436">
-        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 435 - 1), NA())</f>
+        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 435 - 1), NA())</f>
         <v/>
       </c>
       <c r="R436">
-        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 435 - 1), NA())</f>
+        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 435 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="437">
       <c r="P437" s="2">
-        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 436 - 1), NA())</f>
+        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 436 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q437">
-        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 436 - 1), NA())</f>
+        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 436 - 1), NA())</f>
         <v/>
       </c>
       <c r="R437">
-        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 436 - 1), NA())</f>
+        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 436 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="438">
       <c r="P438" s="2">
-        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 437 - 1), NA())</f>
+        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 437 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q438">
-        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 437 - 1), NA())</f>
+        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 437 - 1), NA())</f>
         <v/>
       </c>
       <c r="R438">
-        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 437 - 1), NA())</f>
+        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 437 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="439">
       <c r="P439" s="2">
-        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 438 - 1), NA())</f>
+        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 438 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q439">
-        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 438 - 1), NA())</f>
+        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 438 - 1), NA())</f>
         <v/>
       </c>
       <c r="R439">
-        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 438 - 1), NA())</f>
+        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 438 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="440">
       <c r="P440" s="2">
-        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 439 - 1), NA())</f>
+        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 439 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q440">
-        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 439 - 1), NA())</f>
+        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 439 - 1), NA())</f>
         <v/>
       </c>
       <c r="R440">
-        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 439 - 1), NA())</f>
+        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 439 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="441">
       <c r="P441" s="2">
-        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 440 - 1), NA())</f>
+        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 440 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q441">
-        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 440 - 1), NA())</f>
+        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 440 - 1), NA())</f>
         <v/>
       </c>
       <c r="R441">
-        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 440 - 1), NA())</f>
+        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 440 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="442">
       <c r="P442" s="2">
-        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 441 - 1), NA())</f>
+        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 441 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q442">
-        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 441 - 1), NA())</f>
+        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 441 - 1), NA())</f>
         <v/>
       </c>
       <c r="R442">
-        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 441 - 1), NA())</f>
+        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 441 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="443">
       <c r="P443" s="2">
-        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 442 - 1), NA())</f>
+        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 442 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q443">
-        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 442 - 1), NA())</f>
+        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 442 - 1), NA())</f>
         <v/>
       </c>
       <c r="R443">
-        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 442 - 1), NA())</f>
+        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 442 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="444">
       <c r="P444" s="2">
-        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 443 - 1), NA())</f>
+        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 443 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q444">
-        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 443 - 1), NA())</f>
+        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 443 - 1), NA())</f>
         <v/>
       </c>
       <c r="R444">
-        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 443 - 1), NA())</f>
+        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 443 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="445">
       <c r="P445" s="2">
-        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 444 - 1), NA())</f>
+        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 444 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q445">
-        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 444 - 1), NA())</f>
+        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 444 - 1), NA())</f>
         <v/>
       </c>
       <c r="R445">
-        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 444 - 1), NA())</f>
+        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 444 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="446">
       <c r="P446" s="2">
-        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 445 - 1), NA())</f>
+        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 445 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q446">
-        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 445 - 1), NA())</f>
+        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 445 - 1), NA())</f>
         <v/>
       </c>
       <c r="R446">
-        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 445 - 1), NA())</f>
+        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 445 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="447">
       <c r="P447" s="2">
-        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 446 - 1), NA())</f>
+        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 446 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q447">
-        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 446 - 1), NA())</f>
+        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 446 - 1), NA())</f>
         <v/>
       </c>
       <c r="R447">
-        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 446 - 1), NA())</f>
+        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 446 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="448">
       <c r="P448" s="2">
-        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 447 - 1), NA())</f>
+        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 447 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q448">
-        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 447 - 1), NA())</f>
+        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 447 - 1), NA())</f>
         <v/>
       </c>
       <c r="R448">
-        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 447 - 1), NA())</f>
+        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 447 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="449">
       <c r="P449" s="2">
-        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 448 - 1), NA())</f>
+        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 448 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q449">
-        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 448 - 1), NA())</f>
+        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 448 - 1), NA())</f>
         <v/>
       </c>
       <c r="R449">
-        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 448 - 1), NA())</f>
+        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 448 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="450">
       <c r="P450" s="2">
-        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 449 - 1), NA())</f>
+        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 449 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q450">
-        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 449 - 1), NA())</f>
+        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 449 - 1), NA())</f>
         <v/>
       </c>
       <c r="R450">
-        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 449 - 1), NA())</f>
+        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 449 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="451">
       <c r="P451" s="2">
-        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 450 - 1), NA())</f>
+        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 450 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q451">
-        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 450 - 1), NA())</f>
+        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 450 - 1), NA())</f>
         <v/>
       </c>
       <c r="R451">
-        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 450 - 1), NA())</f>
+        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 450 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="452">
       <c r="P452" s="2">
-        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 451 - 1), NA())</f>
+        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 451 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q452">
-        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 451 - 1), NA())</f>
+        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 451 - 1), NA())</f>
         <v/>
       </c>
       <c r="R452">
-        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 451 - 1), NA())</f>
+        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 451 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="453">
       <c r="P453" s="2">
-        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 452 - 1), NA())</f>
+        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 452 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q453">
-        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 452 - 1), NA())</f>
+        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 452 - 1), NA())</f>
         <v/>
       </c>
       <c r="R453">
-        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 452 - 1), NA())</f>
+        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 452 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="454">
       <c r="P454" s="2">
-        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 453 - 1), NA())</f>
+        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 453 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q454">
-        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 453 - 1), NA())</f>
+        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 453 - 1), NA())</f>
         <v/>
       </c>
       <c r="R454">
-        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 453 - 1), NA())</f>
+        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 453 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="455">
       <c r="P455" s="2">
-        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 454 - 1), NA())</f>
+        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 454 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q455">
-        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 454 - 1), NA())</f>
+        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 454 - 1), NA())</f>
         <v/>
       </c>
       <c r="R455">
-        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 454 - 1), NA())</f>
+        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 454 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="456">
       <c r="P456" s="2">
-        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 455 - 1), NA())</f>
+        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 455 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q456">
-        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 455 - 1), NA())</f>
+        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 455 - 1), NA())</f>
         <v/>
       </c>
       <c r="R456">
-        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 455 - 1), NA())</f>
+        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 455 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="457">
       <c r="P457" s="2">
-        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 456 - 1), NA())</f>
+        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 456 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q457">
-        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 456 - 1), NA())</f>
+        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 456 - 1), NA())</f>
         <v/>
       </c>
       <c r="R457">
-        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 456 - 1), NA())</f>
+        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 456 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="458">
       <c r="P458" s="2">
-        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 457 - 1), NA())</f>
+        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 457 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q458">
-        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 457 - 1), NA())</f>
+        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 457 - 1), NA())</f>
         <v/>
       </c>
       <c r="R458">
-        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 457 - 1), NA())</f>
+        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 457 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="459">
       <c r="P459" s="2">
-        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 458 - 1), NA())</f>
+        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 458 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q459">
-        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 458 - 1), NA())</f>
+        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 458 - 1), NA())</f>
         <v/>
       </c>
       <c r="R459">
-        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 458 - 1), NA())</f>
+        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 458 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="460">
       <c r="P460" s="2">
-        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 459 - 1), NA())</f>
+        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 459 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q460">
-        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 459 - 1), NA())</f>
+        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 459 - 1), NA())</f>
         <v/>
       </c>
       <c r="R460">
-        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 459 - 1), NA())</f>
+        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 459 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="461">
       <c r="P461" s="2">
-        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 460 - 1), NA())</f>
+        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 460 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q461">
-        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 460 - 1), NA())</f>
+        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 460 - 1), NA())</f>
         <v/>
       </c>
       <c r="R461">
-        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 460 - 1), NA())</f>
+        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 460 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="462">
       <c r="P462" s="2">
-        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 461 - 1), NA())</f>
+        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 461 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q462">
-        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 461 - 1), NA())</f>
+        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 461 - 1), NA())</f>
         <v/>
       </c>
       <c r="R462">
-        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 461 - 1), NA())</f>
+        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 461 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="463">
       <c r="P463" s="2">
-        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 462 - 1), NA())</f>
+        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 462 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q463">
-        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 462 - 1), NA())</f>
+        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 462 - 1), NA())</f>
         <v/>
       </c>
       <c r="R463">
-        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 462 - 1), NA())</f>
+        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 462 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="464">
       <c r="P464" s="2">
-        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 463 - 1), NA())</f>
+        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 463 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q464">
-        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 463 - 1), NA())</f>
+        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 463 - 1), NA())</f>
         <v/>
       </c>
       <c r="R464">
-        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 463 - 1), NA())</f>
+        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 463 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="465">
       <c r="P465" s="2">
-        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 464 - 1), NA())</f>
+        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 464 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q465">
-        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 464 - 1), NA())</f>
+        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 464 - 1), NA())</f>
         <v/>
       </c>
       <c r="R465">
-        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 464 - 1), NA())</f>
+        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 464 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="466">
       <c r="P466" s="2">
-        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 465 - 1), NA())</f>
+        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 465 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q466">
-        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 465 - 1), NA())</f>
+        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 465 - 1), NA())</f>
         <v/>
       </c>
       <c r="R466">
-        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 465 - 1), NA())</f>
+        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 465 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="467">
       <c r="P467" s="2">
-        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 466 - 1), NA())</f>
+        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 466 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q467">
-        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 466 - 1), NA())</f>
+        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 466 - 1), NA())</f>
         <v/>
       </c>
       <c r="R467">
-        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 466 - 1), NA())</f>
+        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 466 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="468">
       <c r="P468" s="2">
-        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 467 - 1), NA())</f>
+        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 467 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q468">
-        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 467 - 1), NA())</f>
+        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 467 - 1), NA())</f>
         <v/>
       </c>
       <c r="R468">
-        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 467 - 1), NA())</f>
+        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 467 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="469">
       <c r="P469" s="2">
-        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 468 - 1), NA())</f>
+        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 468 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q469">
-        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 468 - 1), NA())</f>
+        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 468 - 1), NA())</f>
         <v/>
       </c>
       <c r="R469">
-        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 468 - 1), NA())</f>
+        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 468 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="470">
       <c r="P470" s="2">
-        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 469 - 1), NA())</f>
+        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 469 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q470">
-        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 469 - 1), NA())</f>
+        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 469 - 1), NA())</f>
         <v/>
       </c>
       <c r="R470">
-        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 469 - 1), NA())</f>
+        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 469 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="471">
       <c r="P471" s="2">
-        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 470 - 1), NA())</f>
+        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 470 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q471">
-        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 470 - 1), NA())</f>
+        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 470 - 1), NA())</f>
         <v/>
       </c>
       <c r="R471">
-        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 470 - 1), NA())</f>
+        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 470 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="472">
       <c r="P472" s="2">
-        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 471 - 1), NA())</f>
+        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 471 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q472">
-        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 471 - 1), NA())</f>
+        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 471 - 1), NA())</f>
         <v/>
       </c>
       <c r="R472">
-        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 471 - 1), NA())</f>
+        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 471 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="473">
       <c r="P473" s="2">
-        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 472 - 1), NA())</f>
+        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 472 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q473">
-        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 472 - 1), NA())</f>
+        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 472 - 1), NA())</f>
         <v/>
       </c>
       <c r="R473">
-        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 472 - 1), NA())</f>
+        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 472 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="474">
       <c r="P474" s="2">
-        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 473 - 1), NA())</f>
+        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 473 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q474">
-        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 473 - 1), NA())</f>
+        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 473 - 1), NA())</f>
         <v/>
       </c>
       <c r="R474">
-        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 473 - 1), NA())</f>
+        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 473 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="475">
       <c r="P475" s="2">
-        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 474 - 1), NA())</f>
+        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 474 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q475">
-        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 474 - 1), NA())</f>
+        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 474 - 1), NA())</f>
         <v/>
       </c>
       <c r="R475">
-        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 474 - 1), NA())</f>
+        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 474 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="476">
       <c r="P476" s="2">
-        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 475 - 1), NA())</f>
+        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 475 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q476">
-        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 475 - 1), NA())</f>
+        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 475 - 1), NA())</f>
         <v/>
       </c>
       <c r="R476">
-        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 475 - 1), NA())</f>
+        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 475 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="477">
       <c r="P477" s="2">
-        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 476 - 1), NA())</f>
+        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 476 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q477">
-        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 476 - 1), NA())</f>
+        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 476 - 1), NA())</f>
         <v/>
       </c>
       <c r="R477">
-        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 476 - 1), NA())</f>
+        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 476 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="478">
       <c r="P478" s="2">
-        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 477 - 1), NA())</f>
+        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 477 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q478">
-        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 477 - 1), NA())</f>
+        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 477 - 1), NA())</f>
         <v/>
       </c>
       <c r="R478">
-        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 477 - 1), NA())</f>
+        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 477 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="479">
       <c r="P479" s="2">
-        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 478 - 1), NA())</f>
+        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 478 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q479">
-        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 478 - 1), NA())</f>
+        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 478 - 1), NA())</f>
         <v/>
       </c>
       <c r="R479">
-        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 478 - 1), NA())</f>
+        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 478 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="480">
       <c r="P480" s="2">
-        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 479 - 1), NA())</f>
+        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 479 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q480">
-        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 479 - 1), NA())</f>
+        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 479 - 1), NA())</f>
         <v/>
       </c>
       <c r="R480">
-        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 479 - 1), NA())</f>
+        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 479 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="481">
       <c r="P481" s="2">
-        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 480 - 1), NA())</f>
+        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 480 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q481">
-        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 480 - 1), NA())</f>
+        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 480 - 1), NA())</f>
         <v/>
       </c>
       <c r="R481">
-        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 480 - 1), NA())</f>
+        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 480 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="482">
       <c r="P482" s="2">
-        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 481 - 1), NA())</f>
+        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 481 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q482">
-        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 481 - 1), NA())</f>
+        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 481 - 1), NA())</f>
         <v/>
       </c>
       <c r="R482">
-        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 481 - 1), NA())</f>
+        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 481 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="483">
       <c r="P483" s="2">
-        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 482 - 1), NA())</f>
+        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 482 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q483">
-        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 482 - 1), NA())</f>
+        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 482 - 1), NA())</f>
         <v/>
       </c>
       <c r="R483">
-        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 482 - 1), NA())</f>
+        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 482 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="484">
       <c r="P484" s="2">
-        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 483 - 1), NA())</f>
+        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 483 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q484">
-        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 483 - 1), NA())</f>
+        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 483 - 1), NA())</f>
         <v/>
       </c>
       <c r="R484">
-        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 483 - 1), NA())</f>
+        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 483 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="485">
       <c r="P485" s="2">
-        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$485, $G$8 - 1 + 484 - 1), NA())</f>
+        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 484 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q485">
-        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$485, $G$8 - 1 + 484 - 1), NA())</f>
+        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 484 - 1), NA())</f>
         <v/>
       </c>
       <c r="R485">
-        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$485, $G$8 - 1 + 484 - 1), NA())</f>
+        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 484 - 1), NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="486">
+      <c r="P486" s="2">
+        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 485 - 1), NA())</f>
+        <v/>
+      </c>
+      <c r="Q486">
+        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 485 - 1), NA())</f>
+        <v/>
+      </c>
+      <c r="R486">
+        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 485 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -8036,7 +8050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H485"/>
+  <dimension ref="A1:H486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22554,10 +22568,10 @@
         <v>46269</v>
       </c>
       <c r="B484" s="15" t="n">
-        <v>4477.2001953125</v>
+        <v>4429.7998046875</v>
       </c>
       <c r="C484" s="15" t="n">
-        <v>66.81999969482422</v>
+        <v>66.0469970703125</v>
       </c>
       <c r="D484" s="15" t="n">
         <v>3152.179931640625</v>
@@ -22581,16 +22595,16 @@
     </row>
     <row r="485" ht="20" customHeight="1">
       <c r="A485" s="18" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B485" s="19" t="n">
-        <v>4477.2001953125</v>
+        <v>4429.7998046875</v>
       </c>
       <c r="C485" s="19" t="n">
-        <v>66.81999969482422</v>
+        <v>66.0469970703125</v>
       </c>
       <c r="D485" s="19" t="n">
-        <v>3124.489990234375</v>
+        <v>3128.340087890625</v>
       </c>
       <c r="E485" s="20">
         <f>ROUND((B485/31.1034768)*D485, 2)</f>
@@ -22609,8 +22623,38 @@
         <v/>
       </c>
     </row>
+    <row r="486" ht="20" customHeight="1">
+      <c r="A486" s="14" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B486" s="15" t="n">
+        <v>4468.89990234375</v>
+      </c>
+      <c r="C486" s="15" t="n">
+        <v>67.05000305175781</v>
+      </c>
+      <c r="D486" s="15" t="n">
+        <v>3121.18994140625</v>
+      </c>
+      <c r="E486" s="16">
+        <f>ROUND((B486/31.1034768)*D486, 2)</f>
+        <v/>
+      </c>
+      <c r="F486" s="16">
+        <f>ROUND((C486/31.1034768)*D486, 2)</f>
+        <v/>
+      </c>
+      <c r="G486" s="17">
+        <f>IFERROR((E486-E485)/E485, 0)</f>
+        <v/>
+      </c>
+      <c r="H486" s="17">
+        <f>IFERROR((F486-F485)/F485, 0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H485"/>
+  <autoFilter ref="A1:H486"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Precios_Metales_COP.xlsx
+++ b/Precios_Metales_COP.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Precios Diarios" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Precios Diarios'!$A$1:$H$486</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Precios Diarios'!$A$1:$H$487</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -321,12 +321,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard y Gráficos'!$P$2:$P$486</f>
+              <f>'Dashboard y Gráficos'!$P$2:$P$487</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$Q$2:$Q$486</f>
+              <f>'Dashboard y Gráficos'!$Q$2:$Q$487</f>
             </numRef>
           </val>
         </ser>
@@ -446,12 +446,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard y Gráficos'!$P$2:$P$486</f>
+              <f>'Dashboard y Gráficos'!$P$2:$P$487</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$R$2:$R$486</f>
+              <f>'Dashboard y Gráficos'!$R$2:$R$487</f>
             </numRef>
           </val>
         </ser>
@@ -570,12 +570,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard y Gráficos'!$P$2:$P$486</f>
+              <f>'Dashboard y Gráficos'!$P$2:$P$487</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$Q$2:$Q$486</f>
+              <f>'Dashboard y Gráficos'!$Q$2:$Q$487</f>
             </numRef>
           </val>
         </ser>
@@ -610,7 +610,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$R$2:$R$486</f>
+              <f>'Dashboard y Gráficos'!$R$2:$R$487</f>
             </numRef>
           </val>
         </ser>
@@ -1074,7 +1074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R486"/>
+  <dimension ref="A1:R487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1118,15 +1118,15 @@
     </row>
     <row r="2">
       <c r="P2" s="2">
-        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 1 - 1), NA())</f>
+        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 1 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q2">
-        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 1 - 1), NA())</f>
+        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 1 - 1), NA())</f>
         <v/>
       </c>
       <c r="R2">
-        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 1 - 1), NA())</f>
+        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 1 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1166,58 +1166,58 @@
       </c>
       <c r="N3" s="4" t="n"/>
       <c r="P3" s="2">
-        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 2 - 1), NA())</f>
+        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 2 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q3">
-        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 2 - 1), NA())</f>
+        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 2 - 1), NA())</f>
         <v/>
       </c>
       <c r="R3">
-        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 2 - 1), NA())</f>
+        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 2 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5">
-        <f>'Precios Diarios'!A486</f>
+        <f>'Precios Diarios'!A487</f>
         <v/>
       </c>
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="6">
-        <f>'Precios Diarios'!E486</f>
+        <f>'Precios Diarios'!E487</f>
         <v/>
       </c>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="6">
-        <f>'Precios Diarios'!F486</f>
+        <f>'Precios Diarios'!F487</f>
         <v/>
       </c>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="6">
-        <f>'Precios Diarios'!D486</f>
+        <f>'Precios Diarios'!D487</f>
         <v/>
       </c>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="7">
-        <f>'Precios Diarios'!G486</f>
+        <f>'Precios Diarios'!G487</f>
         <v/>
       </c>
       <c r="N4" s="4" t="n"/>
       <c r="P4" s="2">
-        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 3 - 1), NA())</f>
+        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 3 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q4">
-        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 3 - 1), NA())</f>
+        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 3 - 1), NA())</f>
         <v/>
       </c>
       <c r="R4">
-        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 3 - 1), NA())</f>
+        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 3 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1237,29 +1237,29 @@
       <c r="M5" s="4" t="n"/>
       <c r="N5" s="4" t="n"/>
       <c r="P5" s="2">
-        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 4 - 1), NA())</f>
+        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 4 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q5">
-        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 4 - 1), NA())</f>
+        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 4 - 1), NA())</f>
         <v/>
       </c>
       <c r="R5">
-        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 4 - 1), NA())</f>
+        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 4 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="P6" s="2">
-        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 5 - 1), NA())</f>
+        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 5 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q6">
-        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 5 - 1), NA())</f>
+        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 5 - 1), NA())</f>
         <v/>
       </c>
       <c r="R6">
-        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 5 - 1), NA())</f>
+        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 5 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1270,15 +1270,15 @@
         </is>
       </c>
       <c r="P7" s="2">
-        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 6 - 1), NA())</f>
+        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 6 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q7">
-        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 6 - 1), NA())</f>
+        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 6 - 1), NA())</f>
         <v/>
       </c>
       <c r="R7">
-        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 6 - 1), NA())</f>
+        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 6 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1297,11 +1297,11 @@
         <v/>
       </c>
       <c r="G8" s="11">
-        <f>IFERROR(MATCH(E8, 'Precios Diarios'!$A$2:$A$486, 1), 1) + 1</f>
+        <f>IFERROR(MATCH(E8, 'Precios Diarios'!$A$2:$A$487, 1), 1) + 1</f>
         <v/>
       </c>
       <c r="H8" s="11">
-        <f>IFERROR(MATCH(F8, 'Precios Diarios'!$A$2:$A$486, 1), 485) + 1</f>
+        <f>IFERROR(MATCH(F8, 'Precios Diarios'!$A$2:$A$487, 1), 486) + 1</f>
         <v/>
       </c>
       <c r="I8" s="11">
@@ -1309,15 +1309,15 @@
         <v/>
       </c>
       <c r="P8" s="2">
-        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 7 - 1), NA())</f>
+        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 7 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q8">
-        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 7 - 1), NA())</f>
+        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 7 - 1), NA())</f>
         <v/>
       </c>
       <c r="R8">
-        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 7 - 1), NA())</f>
+        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 7 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1328,6693 +1328,6707 @@
         </is>
       </c>
       <c r="P9" s="2">
-        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 8 - 1), NA())</f>
+        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 8 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q9">
-        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 8 - 1), NA())</f>
+        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 8 - 1), NA())</f>
         <v/>
       </c>
       <c r="R9">
-        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 8 - 1), NA())</f>
+        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 8 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="P10" s="2">
-        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 9 - 1), NA())</f>
+        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 9 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q10">
-        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 9 - 1), NA())</f>
+        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 9 - 1), NA())</f>
         <v/>
       </c>
       <c r="R10">
-        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 9 - 1), NA())</f>
+        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 9 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="P11" s="2">
-        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 10 - 1), NA())</f>
+        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 10 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q11">
-        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 10 - 1), NA())</f>
+        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 10 - 1), NA())</f>
         <v/>
       </c>
       <c r="R11">
-        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 10 - 1), NA())</f>
+        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 10 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="P12" s="2">
-        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 11 - 1), NA())</f>
+        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 11 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q12">
-        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 11 - 1), NA())</f>
+        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 11 - 1), NA())</f>
         <v/>
       </c>
       <c r="R12">
-        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 11 - 1), NA())</f>
+        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 11 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="P13" s="2">
-        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 12 - 1), NA())</f>
+        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 12 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q13">
-        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 12 - 1), NA())</f>
+        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 12 - 1), NA())</f>
         <v/>
       </c>
       <c r="R13">
-        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 12 - 1), NA())</f>
+        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 12 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="P14" s="2">
-        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 13 - 1), NA())</f>
+        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 13 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q14">
-        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 13 - 1), NA())</f>
+        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 13 - 1), NA())</f>
         <v/>
       </c>
       <c r="R14">
-        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 13 - 1), NA())</f>
+        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 13 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="P15" s="2">
-        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 14 - 1), NA())</f>
+        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 14 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q15">
-        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 14 - 1), NA())</f>
+        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 14 - 1), NA())</f>
         <v/>
       </c>
       <c r="R15">
-        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 14 - 1), NA())</f>
+        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 14 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="P16" s="2">
-        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 15 - 1), NA())</f>
+        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 15 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q16">
-        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 15 - 1), NA())</f>
+        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 15 - 1), NA())</f>
         <v/>
       </c>
       <c r="R16">
-        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 15 - 1), NA())</f>
+        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 15 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="P17" s="2">
-        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 16 - 1), NA())</f>
+        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 16 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q17">
-        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 16 - 1), NA())</f>
+        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 16 - 1), NA())</f>
         <v/>
       </c>
       <c r="R17">
-        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 16 - 1), NA())</f>
+        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 16 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="P18" s="2">
-        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 17 - 1), NA())</f>
+        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 17 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q18">
-        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 17 - 1), NA())</f>
+        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 17 - 1), NA())</f>
         <v/>
       </c>
       <c r="R18">
-        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 17 - 1), NA())</f>
+        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 17 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="P19" s="2">
-        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 18 - 1), NA())</f>
+        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 18 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q19">
-        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 18 - 1), NA())</f>
+        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 18 - 1), NA())</f>
         <v/>
       </c>
       <c r="R19">
-        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 18 - 1), NA())</f>
+        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 18 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="P20" s="2">
-        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 19 - 1), NA())</f>
+        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 19 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q20">
-        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 19 - 1), NA())</f>
+        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 19 - 1), NA())</f>
         <v/>
       </c>
       <c r="R20">
-        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 19 - 1), NA())</f>
+        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 19 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="P21" s="2">
-        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 20 - 1), NA())</f>
+        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 20 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q21">
-        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 20 - 1), NA())</f>
+        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 20 - 1), NA())</f>
         <v/>
       </c>
       <c r="R21">
-        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 20 - 1), NA())</f>
+        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 20 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="P22" s="2">
-        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 21 - 1), NA())</f>
+        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 21 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q22">
-        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 21 - 1), NA())</f>
+        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 21 - 1), NA())</f>
         <v/>
       </c>
       <c r="R22">
-        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 21 - 1), NA())</f>
+        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 21 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="P23" s="2">
-        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 22 - 1), NA())</f>
+        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 22 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q23">
-        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 22 - 1), NA())</f>
+        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 22 - 1), NA())</f>
         <v/>
       </c>
       <c r="R23">
-        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 22 - 1), NA())</f>
+        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 22 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="P24" s="2">
-        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 23 - 1), NA())</f>
+        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 23 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q24">
-        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 23 - 1), NA())</f>
+        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 23 - 1), NA())</f>
         <v/>
       </c>
       <c r="R24">
-        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 23 - 1), NA())</f>
+        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 23 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="P25" s="2">
-        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 24 - 1), NA())</f>
+        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 24 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q25">
-        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 24 - 1), NA())</f>
+        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 24 - 1), NA())</f>
         <v/>
       </c>
       <c r="R25">
-        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 24 - 1), NA())</f>
+        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 24 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="P26" s="2">
-        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 25 - 1), NA())</f>
+        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 25 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q26">
-        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 25 - 1), NA())</f>
+        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 25 - 1), NA())</f>
         <v/>
       </c>
       <c r="R26">
-        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 25 - 1), NA())</f>
+        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 25 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="P27" s="2">
-        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 26 - 1), NA())</f>
+        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 26 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q27">
-        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 26 - 1), NA())</f>
+        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 26 - 1), NA())</f>
         <v/>
       </c>
       <c r="R27">
-        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 26 - 1), NA())</f>
+        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 26 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="P28" s="2">
-        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 27 - 1), NA())</f>
+        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 27 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q28">
-        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 27 - 1), NA())</f>
+        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 27 - 1), NA())</f>
         <v/>
       </c>
       <c r="R28">
-        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 27 - 1), NA())</f>
+        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 27 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="P29" s="2">
-        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 28 - 1), NA())</f>
+        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 28 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q29">
-        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 28 - 1), NA())</f>
+        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 28 - 1), NA())</f>
         <v/>
       </c>
       <c r="R29">
-        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 28 - 1), NA())</f>
+        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 28 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="P30" s="2">
-        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 29 - 1), NA())</f>
+        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 29 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q30">
-        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 29 - 1), NA())</f>
+        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 29 - 1), NA())</f>
         <v/>
       </c>
       <c r="R30">
-        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 29 - 1), NA())</f>
+        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 29 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="P31" s="2">
-        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 30 - 1), NA())</f>
+        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 30 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q31">
-        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 30 - 1), NA())</f>
+        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 30 - 1), NA())</f>
         <v/>
       </c>
       <c r="R31">
-        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 30 - 1), NA())</f>
+        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 30 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="P32" s="2">
-        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 31 - 1), NA())</f>
+        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 31 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q32">
-        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 31 - 1), NA())</f>
+        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 31 - 1), NA())</f>
         <v/>
       </c>
       <c r="R32">
-        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 31 - 1), NA())</f>
+        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 31 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="P33" s="2">
-        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 32 - 1), NA())</f>
+        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 32 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q33">
-        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 32 - 1), NA())</f>
+        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 32 - 1), NA())</f>
         <v/>
       </c>
       <c r="R33">
-        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 32 - 1), NA())</f>
+        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 32 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="P34" s="2">
-        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 33 - 1), NA())</f>
+        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 33 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q34">
-        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 33 - 1), NA())</f>
+        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 33 - 1), NA())</f>
         <v/>
       </c>
       <c r="R34">
-        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 33 - 1), NA())</f>
+        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 33 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="P35" s="2">
-        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 34 - 1), NA())</f>
+        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 34 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q35">
-        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 34 - 1), NA())</f>
+        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 34 - 1), NA())</f>
         <v/>
       </c>
       <c r="R35">
-        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 34 - 1), NA())</f>
+        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 34 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="P36" s="2">
-        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 35 - 1), NA())</f>
+        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 35 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q36">
-        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 35 - 1), NA())</f>
+        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 35 - 1), NA())</f>
         <v/>
       </c>
       <c r="R36">
-        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 35 - 1), NA())</f>
+        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 35 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="P37" s="2">
-        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 36 - 1), NA())</f>
+        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 36 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q37">
-        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 36 - 1), NA())</f>
+        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 36 - 1), NA())</f>
         <v/>
       </c>
       <c r="R37">
-        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 36 - 1), NA())</f>
+        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 36 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="P38" s="2">
-        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 37 - 1), NA())</f>
+        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 37 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q38">
-        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 37 - 1), NA())</f>
+        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 37 - 1), NA())</f>
         <v/>
       </c>
       <c r="R38">
-        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 37 - 1), NA())</f>
+        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 37 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="P39" s="2">
-        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 38 - 1), NA())</f>
+        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 38 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q39">
-        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 38 - 1), NA())</f>
+        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 38 - 1), NA())</f>
         <v/>
       </c>
       <c r="R39">
-        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 38 - 1), NA())</f>
+        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 38 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="P40" s="2">
-        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 39 - 1), NA())</f>
+        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 39 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q40">
-        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 39 - 1), NA())</f>
+        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 39 - 1), NA())</f>
         <v/>
       </c>
       <c r="R40">
-        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 39 - 1), NA())</f>
+        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 39 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="P41" s="2">
-        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 40 - 1), NA())</f>
+        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 40 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q41">
-        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 40 - 1), NA())</f>
+        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 40 - 1), NA())</f>
         <v/>
       </c>
       <c r="R41">
-        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 40 - 1), NA())</f>
+        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 40 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="P42" s="2">
-        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 41 - 1), NA())</f>
+        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 41 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q42">
-        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 41 - 1), NA())</f>
+        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 41 - 1), NA())</f>
         <v/>
       </c>
       <c r="R42">
-        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 41 - 1), NA())</f>
+        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 41 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="P43" s="2">
-        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 42 - 1), NA())</f>
+        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 42 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q43">
-        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 42 - 1), NA())</f>
+        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 42 - 1), NA())</f>
         <v/>
       </c>
       <c r="R43">
-        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 42 - 1), NA())</f>
+        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 42 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="P44" s="2">
-        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 43 - 1), NA())</f>
+        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 43 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q44">
-        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 43 - 1), NA())</f>
+        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 43 - 1), NA())</f>
         <v/>
       </c>
       <c r="R44">
-        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 43 - 1), NA())</f>
+        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 43 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="P45" s="2">
-        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 44 - 1), NA())</f>
+        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 44 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q45">
-        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 44 - 1), NA())</f>
+        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 44 - 1), NA())</f>
         <v/>
       </c>
       <c r="R45">
-        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 44 - 1), NA())</f>
+        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 44 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="P46" s="2">
-        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 45 - 1), NA())</f>
+        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 45 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q46">
-        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 45 - 1), NA())</f>
+        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 45 - 1), NA())</f>
         <v/>
       </c>
       <c r="R46">
-        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 45 - 1), NA())</f>
+        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 45 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="P47" s="2">
-        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 46 - 1), NA())</f>
+        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 46 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q47">
-        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 46 - 1), NA())</f>
+        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 46 - 1), NA())</f>
         <v/>
       </c>
       <c r="R47">
-        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 46 - 1), NA())</f>
+        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 46 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="P48" s="2">
-        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 47 - 1), NA())</f>
+        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 47 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q48">
-        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 47 - 1), NA())</f>
+        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 47 - 1), NA())</f>
         <v/>
       </c>
       <c r="R48">
-        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 47 - 1), NA())</f>
+        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 47 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="P49" s="2">
-        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 48 - 1), NA())</f>
+        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 48 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q49">
-        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 48 - 1), NA())</f>
+        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 48 - 1), NA())</f>
         <v/>
       </c>
       <c r="R49">
-        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 48 - 1), NA())</f>
+        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 48 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="P50" s="2">
-        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 49 - 1), NA())</f>
+        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 49 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q50">
-        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 49 - 1), NA())</f>
+        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 49 - 1), NA())</f>
         <v/>
       </c>
       <c r="R50">
-        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 49 - 1), NA())</f>
+        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 49 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="P51" s="2">
-        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 50 - 1), NA())</f>
+        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 50 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q51">
-        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 50 - 1), NA())</f>
+        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 50 - 1), NA())</f>
         <v/>
       </c>
       <c r="R51">
-        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 50 - 1), NA())</f>
+        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 50 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="P52" s="2">
-        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 51 - 1), NA())</f>
+        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 51 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q52">
-        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 51 - 1), NA())</f>
+        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 51 - 1), NA())</f>
         <v/>
       </c>
       <c r="R52">
-        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 51 - 1), NA())</f>
+        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 51 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="P53" s="2">
-        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 52 - 1), NA())</f>
+        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 52 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q53">
-        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 52 - 1), NA())</f>
+        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 52 - 1), NA())</f>
         <v/>
       </c>
       <c r="R53">
-        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 52 - 1), NA())</f>
+        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 52 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="P54" s="2">
-        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 53 - 1), NA())</f>
+        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 53 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q54">
-        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 53 - 1), NA())</f>
+        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 53 - 1), NA())</f>
         <v/>
       </c>
       <c r="R54">
-        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 53 - 1), NA())</f>
+        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 53 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="P55" s="2">
-        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 54 - 1), NA())</f>
+        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 54 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q55">
-        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 54 - 1), NA())</f>
+        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 54 - 1), NA())</f>
         <v/>
       </c>
       <c r="R55">
-        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 54 - 1), NA())</f>
+        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 54 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="P56" s="2">
-        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 55 - 1), NA())</f>
+        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 55 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q56">
-        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 55 - 1), NA())</f>
+        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 55 - 1), NA())</f>
         <v/>
       </c>
       <c r="R56">
-        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 55 - 1), NA())</f>
+        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 55 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="P57" s="2">
-        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 56 - 1), NA())</f>
+        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 56 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q57">
-        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 56 - 1), NA())</f>
+        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 56 - 1), NA())</f>
         <v/>
       </c>
       <c r="R57">
-        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 56 - 1), NA())</f>
+        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 56 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="P58" s="2">
-        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 57 - 1), NA())</f>
+        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 57 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q58">
-        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 57 - 1), NA())</f>
+        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 57 - 1), NA())</f>
         <v/>
       </c>
       <c r="R58">
-        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 57 - 1), NA())</f>
+        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 57 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="P59" s="2">
-        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 58 - 1), NA())</f>
+        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 58 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q59">
-        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 58 - 1), NA())</f>
+        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 58 - 1), NA())</f>
         <v/>
       </c>
       <c r="R59">
-        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 58 - 1), NA())</f>
+        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 58 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="P60" s="2">
-        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 59 - 1), NA())</f>
+        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 59 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q60">
-        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 59 - 1), NA())</f>
+        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 59 - 1), NA())</f>
         <v/>
       </c>
       <c r="R60">
-        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 59 - 1), NA())</f>
+        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 59 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="P61" s="2">
-        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 60 - 1), NA())</f>
+        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 60 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q61">
-        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 60 - 1), NA())</f>
+        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 60 - 1), NA())</f>
         <v/>
       </c>
       <c r="R61">
-        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 60 - 1), NA())</f>
+        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 60 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="P62" s="2">
-        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 61 - 1), NA())</f>
+        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 61 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q62">
-        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 61 - 1), NA())</f>
+        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 61 - 1), NA())</f>
         <v/>
       </c>
       <c r="R62">
-        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 61 - 1), NA())</f>
+        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 61 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="P63" s="2">
-        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 62 - 1), NA())</f>
+        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 62 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q63">
-        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 62 - 1), NA())</f>
+        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 62 - 1), NA())</f>
         <v/>
       </c>
       <c r="R63">
-        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 62 - 1), NA())</f>
+        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 62 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="P64" s="2">
-        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 63 - 1), NA())</f>
+        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 63 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q64">
-        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 63 - 1), NA())</f>
+        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 63 - 1), NA())</f>
         <v/>
       </c>
       <c r="R64">
-        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 63 - 1), NA())</f>
+        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 63 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="P65" s="2">
-        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 64 - 1), NA())</f>
+        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 64 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q65">
-        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 64 - 1), NA())</f>
+        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 64 - 1), NA())</f>
         <v/>
       </c>
       <c r="R65">
-        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 64 - 1), NA())</f>
+        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 64 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="P66" s="2">
-        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 65 - 1), NA())</f>
+        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 65 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q66">
-        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 65 - 1), NA())</f>
+        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 65 - 1), NA())</f>
         <v/>
       </c>
       <c r="R66">
-        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 65 - 1), NA())</f>
+        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 65 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="P67" s="2">
-        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 66 - 1), NA())</f>
+        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 66 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q67">
-        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 66 - 1), NA())</f>
+        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 66 - 1), NA())</f>
         <v/>
       </c>
       <c r="R67">
-        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 66 - 1), NA())</f>
+        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 66 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="P68" s="2">
-        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 67 - 1), NA())</f>
+        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 67 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q68">
-        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 67 - 1), NA())</f>
+        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 67 - 1), NA())</f>
         <v/>
       </c>
       <c r="R68">
-        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 67 - 1), NA())</f>
+        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 67 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="P69" s="2">
-        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 68 - 1), NA())</f>
+        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 68 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q69">
-        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 68 - 1), NA())</f>
+        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 68 - 1), NA())</f>
         <v/>
       </c>
       <c r="R69">
-        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 68 - 1), NA())</f>
+        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 68 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="P70" s="2">
-        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 69 - 1), NA())</f>
+        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 69 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q70">
-        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 69 - 1), NA())</f>
+        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 69 - 1), NA())</f>
         <v/>
       </c>
       <c r="R70">
-        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 69 - 1), NA())</f>
+        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 69 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="P71" s="2">
-        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 70 - 1), NA())</f>
+        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 70 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q71">
-        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 70 - 1), NA())</f>
+        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 70 - 1), NA())</f>
         <v/>
       </c>
       <c r="R71">
-        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 70 - 1), NA())</f>
+        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 70 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="P72" s="2">
-        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 71 - 1), NA())</f>
+        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 71 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q72">
-        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 71 - 1), NA())</f>
+        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 71 - 1), NA())</f>
         <v/>
       </c>
       <c r="R72">
-        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 71 - 1), NA())</f>
+        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 71 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="P73" s="2">
-        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 72 - 1), NA())</f>
+        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 72 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q73">
-        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 72 - 1), NA())</f>
+        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 72 - 1), NA())</f>
         <v/>
       </c>
       <c r="R73">
-        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 72 - 1), NA())</f>
+        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 72 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="P74" s="2">
-        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 73 - 1), NA())</f>
+        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 73 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q74">
-        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 73 - 1), NA())</f>
+        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 73 - 1), NA())</f>
         <v/>
       </c>
       <c r="R74">
-        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 73 - 1), NA())</f>
+        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 73 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="P75" s="2">
-        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 74 - 1), NA())</f>
+        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 74 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q75">
-        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 74 - 1), NA())</f>
+        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 74 - 1), NA())</f>
         <v/>
       </c>
       <c r="R75">
-        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 74 - 1), NA())</f>
+        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 74 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="P76" s="2">
-        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 75 - 1), NA())</f>
+        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 75 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q76">
-        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 75 - 1), NA())</f>
+        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 75 - 1), NA())</f>
         <v/>
       </c>
       <c r="R76">
-        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 75 - 1), NA())</f>
+        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 75 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="P77" s="2">
-        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 76 - 1), NA())</f>
+        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 76 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q77">
-        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 76 - 1), NA())</f>
+        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 76 - 1), NA())</f>
         <v/>
       </c>
       <c r="R77">
-        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 76 - 1), NA())</f>
+        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 76 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="P78" s="2">
-        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 77 - 1), NA())</f>
+        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 77 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q78">
-        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 77 - 1), NA())</f>
+        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 77 - 1), NA())</f>
         <v/>
       </c>
       <c r="R78">
-        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 77 - 1), NA())</f>
+        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 77 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="P79" s="2">
-        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 78 - 1), NA())</f>
+        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 78 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q79">
-        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 78 - 1), NA())</f>
+        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 78 - 1), NA())</f>
         <v/>
       </c>
       <c r="R79">
-        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 78 - 1), NA())</f>
+        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 78 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="P80" s="2">
-        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 79 - 1), NA())</f>
+        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 79 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q80">
-        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 79 - 1), NA())</f>
+        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 79 - 1), NA())</f>
         <v/>
       </c>
       <c r="R80">
-        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 79 - 1), NA())</f>
+        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 79 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="P81" s="2">
-        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 80 - 1), NA())</f>
+        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 80 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q81">
-        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 80 - 1), NA())</f>
+        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 80 - 1), NA())</f>
         <v/>
       </c>
       <c r="R81">
-        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 80 - 1), NA())</f>
+        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 80 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="P82" s="2">
-        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 81 - 1), NA())</f>
+        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 81 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q82">
-        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 81 - 1), NA())</f>
+        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 81 - 1), NA())</f>
         <v/>
       </c>
       <c r="R82">
-        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 81 - 1), NA())</f>
+        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 81 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="P83" s="2">
-        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 82 - 1), NA())</f>
+        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 82 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q83">
-        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 82 - 1), NA())</f>
+        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 82 - 1), NA())</f>
         <v/>
       </c>
       <c r="R83">
-        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 82 - 1), NA())</f>
+        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 82 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="P84" s="2">
-        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 83 - 1), NA())</f>
+        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 83 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q84">
-        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 83 - 1), NA())</f>
+        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 83 - 1), NA())</f>
         <v/>
       </c>
       <c r="R84">
-        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 83 - 1), NA())</f>
+        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 83 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="P85" s="2">
-        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 84 - 1), NA())</f>
+        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 84 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q85">
-        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 84 - 1), NA())</f>
+        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 84 - 1), NA())</f>
         <v/>
       </c>
       <c r="R85">
-        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 84 - 1), NA())</f>
+        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 84 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="P86" s="2">
-        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 85 - 1), NA())</f>
+        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 85 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q86">
-        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 85 - 1), NA())</f>
+        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 85 - 1), NA())</f>
         <v/>
       </c>
       <c r="R86">
-        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 85 - 1), NA())</f>
+        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 85 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="P87" s="2">
-        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 86 - 1), NA())</f>
+        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 86 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q87">
-        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 86 - 1), NA())</f>
+        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 86 - 1), NA())</f>
         <v/>
       </c>
       <c r="R87">
-        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 86 - 1), NA())</f>
+        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 86 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="P88" s="2">
-        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 87 - 1), NA())</f>
+        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 87 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q88">
-        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 87 - 1), NA())</f>
+        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 87 - 1), NA())</f>
         <v/>
       </c>
       <c r="R88">
-        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 87 - 1), NA())</f>
+        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 87 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="P89" s="2">
-        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 88 - 1), NA())</f>
+        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 88 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q89">
-        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 88 - 1), NA())</f>
+        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 88 - 1), NA())</f>
         <v/>
       </c>
       <c r="R89">
-        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 88 - 1), NA())</f>
+        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 88 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="P90" s="2">
-        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 89 - 1), NA())</f>
+        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 89 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q90">
-        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 89 - 1), NA())</f>
+        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 89 - 1), NA())</f>
         <v/>
       </c>
       <c r="R90">
-        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 89 - 1), NA())</f>
+        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 89 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="P91" s="2">
-        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 90 - 1), NA())</f>
+        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 90 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q91">
-        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 90 - 1), NA())</f>
+        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 90 - 1), NA())</f>
         <v/>
       </c>
       <c r="R91">
-        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 90 - 1), NA())</f>
+        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 90 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="P92" s="2">
-        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 91 - 1), NA())</f>
+        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 91 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q92">
-        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 91 - 1), NA())</f>
+        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 91 - 1), NA())</f>
         <v/>
       </c>
       <c r="R92">
-        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 91 - 1), NA())</f>
+        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 91 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="P93" s="2">
-        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 92 - 1), NA())</f>
+        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 92 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q93">
-        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 92 - 1), NA())</f>
+        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 92 - 1), NA())</f>
         <v/>
       </c>
       <c r="R93">
-        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 92 - 1), NA())</f>
+        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 92 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="P94" s="2">
-        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 93 - 1), NA())</f>
+        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 93 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q94">
-        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 93 - 1), NA())</f>
+        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 93 - 1), NA())</f>
         <v/>
       </c>
       <c r="R94">
-        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 93 - 1), NA())</f>
+        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 93 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="P95" s="2">
-        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 94 - 1), NA())</f>
+        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 94 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q95">
-        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 94 - 1), NA())</f>
+        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 94 - 1), NA())</f>
         <v/>
       </c>
       <c r="R95">
-        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 94 - 1), NA())</f>
+        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 94 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="P96" s="2">
-        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 95 - 1), NA())</f>
+        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 95 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q96">
-        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 95 - 1), NA())</f>
+        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 95 - 1), NA())</f>
         <v/>
       </c>
       <c r="R96">
-        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 95 - 1), NA())</f>
+        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 95 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="P97" s="2">
-        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 96 - 1), NA())</f>
+        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 96 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q97">
-        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 96 - 1), NA())</f>
+        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 96 - 1), NA())</f>
         <v/>
       </c>
       <c r="R97">
-        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 96 - 1), NA())</f>
+        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 96 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="P98" s="2">
-        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 97 - 1), NA())</f>
+        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 97 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q98">
-        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 97 - 1), NA())</f>
+        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 97 - 1), NA())</f>
         <v/>
       </c>
       <c r="R98">
-        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 97 - 1), NA())</f>
+        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 97 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="P99" s="2">
-        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 98 - 1), NA())</f>
+        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 98 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q99">
-        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 98 - 1), NA())</f>
+        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 98 - 1), NA())</f>
         <v/>
       </c>
       <c r="R99">
-        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 98 - 1), NA())</f>
+        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 98 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="P100" s="2">
-        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 99 - 1), NA())</f>
+        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 99 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q100">
-        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 99 - 1), NA())</f>
+        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 99 - 1), NA())</f>
         <v/>
       </c>
       <c r="R100">
-        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 99 - 1), NA())</f>
+        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 99 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="P101" s="2">
-        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 100 - 1), NA())</f>
+        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 100 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q101">
-        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 100 - 1), NA())</f>
+        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 100 - 1), NA())</f>
         <v/>
       </c>
       <c r="R101">
-        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 100 - 1), NA())</f>
+        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 100 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="P102" s="2">
-        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 101 - 1), NA())</f>
+        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 101 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q102">
-        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 101 - 1), NA())</f>
+        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 101 - 1), NA())</f>
         <v/>
       </c>
       <c r="R102">
-        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 101 - 1), NA())</f>
+        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 101 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="P103" s="2">
-        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 102 - 1), NA())</f>
+        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 102 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q103">
-        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 102 - 1), NA())</f>
+        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 102 - 1), NA())</f>
         <v/>
       </c>
       <c r="R103">
-        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 102 - 1), NA())</f>
+        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 102 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="P104" s="2">
-        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 103 - 1), NA())</f>
+        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 103 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q104">
-        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 103 - 1), NA())</f>
+        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 103 - 1), NA())</f>
         <v/>
       </c>
       <c r="R104">
-        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 103 - 1), NA())</f>
+        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 103 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="P105" s="2">
-        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 104 - 1), NA())</f>
+        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 104 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q105">
-        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 104 - 1), NA())</f>
+        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 104 - 1), NA())</f>
         <v/>
       </c>
       <c r="R105">
-        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 104 - 1), NA())</f>
+        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 104 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="P106" s="2">
-        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 105 - 1), NA())</f>
+        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 105 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q106">
-        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 105 - 1), NA())</f>
+        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 105 - 1), NA())</f>
         <v/>
       </c>
       <c r="R106">
-        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 105 - 1), NA())</f>
+        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 105 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="P107" s="2">
-        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 106 - 1), NA())</f>
+        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 106 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q107">
-        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 106 - 1), NA())</f>
+        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 106 - 1), NA())</f>
         <v/>
       </c>
       <c r="R107">
-        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 106 - 1), NA())</f>
+        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 106 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="P108" s="2">
-        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 107 - 1), NA())</f>
+        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 107 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q108">
-        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 107 - 1), NA())</f>
+        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 107 - 1), NA())</f>
         <v/>
       </c>
       <c r="R108">
-        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 107 - 1), NA())</f>
+        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 107 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="P109" s="2">
-        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 108 - 1), NA())</f>
+        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 108 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q109">
-        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 108 - 1), NA())</f>
+        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 108 - 1), NA())</f>
         <v/>
       </c>
       <c r="R109">
-        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 108 - 1), NA())</f>
+        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 108 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="P110" s="2">
-        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 109 - 1), NA())</f>
+        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 109 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q110">
-        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 109 - 1), NA())</f>
+        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 109 - 1), NA())</f>
         <v/>
       </c>
       <c r="R110">
-        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 109 - 1), NA())</f>
+        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 109 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="P111" s="2">
-        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 110 - 1), NA())</f>
+        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 110 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q111">
-        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 110 - 1), NA())</f>
+        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 110 - 1), NA())</f>
         <v/>
       </c>
       <c r="R111">
-        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 110 - 1), NA())</f>
+        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 110 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="P112" s="2">
-        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 111 - 1), NA())</f>
+        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 111 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q112">
-        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 111 - 1), NA())</f>
+        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 111 - 1), NA())</f>
         <v/>
       </c>
       <c r="R112">
-        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 111 - 1), NA())</f>
+        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 111 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="P113" s="2">
-        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 112 - 1), NA())</f>
+        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 112 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q113">
-        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 112 - 1), NA())</f>
+        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 112 - 1), NA())</f>
         <v/>
       </c>
       <c r="R113">
-        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 112 - 1), NA())</f>
+        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 112 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="P114" s="2">
-        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 113 - 1), NA())</f>
+        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 113 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q114">
-        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 113 - 1), NA())</f>
+        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 113 - 1), NA())</f>
         <v/>
       </c>
       <c r="R114">
-        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 113 - 1), NA())</f>
+        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 113 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="P115" s="2">
-        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 114 - 1), NA())</f>
+        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 114 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q115">
-        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 114 - 1), NA())</f>
+        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 114 - 1), NA())</f>
         <v/>
       </c>
       <c r="R115">
-        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 114 - 1), NA())</f>
+        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 114 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="P116" s="2">
-        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 115 - 1), NA())</f>
+        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 115 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q116">
-        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 115 - 1), NA())</f>
+        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 115 - 1), NA())</f>
         <v/>
       </c>
       <c r="R116">
-        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 115 - 1), NA())</f>
+        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 115 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="P117" s="2">
-        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 116 - 1), NA())</f>
+        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 116 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q117">
-        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 116 - 1), NA())</f>
+        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 116 - 1), NA())</f>
         <v/>
       </c>
       <c r="R117">
-        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 116 - 1), NA())</f>
+        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 116 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="P118" s="2">
-        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 117 - 1), NA())</f>
+        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 117 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q118">
-        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 117 - 1), NA())</f>
+        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 117 - 1), NA())</f>
         <v/>
       </c>
       <c r="R118">
-        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 117 - 1), NA())</f>
+        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 117 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="P119" s="2">
-        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 118 - 1), NA())</f>
+        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 118 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q119">
-        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 118 - 1), NA())</f>
+        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 118 - 1), NA())</f>
         <v/>
       </c>
       <c r="R119">
-        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 118 - 1), NA())</f>
+        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 118 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="P120" s="2">
-        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 119 - 1), NA())</f>
+        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 119 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q120">
-        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 119 - 1), NA())</f>
+        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 119 - 1), NA())</f>
         <v/>
       </c>
       <c r="R120">
-        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 119 - 1), NA())</f>
+        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 119 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="P121" s="2">
-        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 120 - 1), NA())</f>
+        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 120 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q121">
-        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 120 - 1), NA())</f>
+        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 120 - 1), NA())</f>
         <v/>
       </c>
       <c r="R121">
-        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 120 - 1), NA())</f>
+        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 120 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="P122" s="2">
-        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 121 - 1), NA())</f>
+        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 121 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q122">
-        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 121 - 1), NA())</f>
+        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 121 - 1), NA())</f>
         <v/>
       </c>
       <c r="R122">
-        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 121 - 1), NA())</f>
+        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 121 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="123">
       <c r="P123" s="2">
-        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 122 - 1), NA())</f>
+        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 122 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q123">
-        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 122 - 1), NA())</f>
+        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 122 - 1), NA())</f>
         <v/>
       </c>
       <c r="R123">
-        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 122 - 1), NA())</f>
+        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 122 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="124">
       <c r="P124" s="2">
-        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 123 - 1), NA())</f>
+        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 123 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q124">
-        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 123 - 1), NA())</f>
+        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 123 - 1), NA())</f>
         <v/>
       </c>
       <c r="R124">
-        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 123 - 1), NA())</f>
+        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 123 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="125">
       <c r="P125" s="2">
-        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 124 - 1), NA())</f>
+        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 124 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q125">
-        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 124 - 1), NA())</f>
+        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 124 - 1), NA())</f>
         <v/>
       </c>
       <c r="R125">
-        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 124 - 1), NA())</f>
+        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 124 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="126">
       <c r="P126" s="2">
-        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 125 - 1), NA())</f>
+        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 125 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q126">
-        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 125 - 1), NA())</f>
+        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 125 - 1), NA())</f>
         <v/>
       </c>
       <c r="R126">
-        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 125 - 1), NA())</f>
+        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 125 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="127">
       <c r="P127" s="2">
-        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 126 - 1), NA())</f>
+        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 126 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q127">
-        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 126 - 1), NA())</f>
+        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 126 - 1), NA())</f>
         <v/>
       </c>
       <c r="R127">
-        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 126 - 1), NA())</f>
+        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 126 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="P128" s="2">
-        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 127 - 1), NA())</f>
+        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 127 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q128">
-        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 127 - 1), NA())</f>
+        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 127 - 1), NA())</f>
         <v/>
       </c>
       <c r="R128">
-        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 127 - 1), NA())</f>
+        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 127 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="129">
       <c r="P129" s="2">
-        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 128 - 1), NA())</f>
+        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 128 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q129">
-        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 128 - 1), NA())</f>
+        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 128 - 1), NA())</f>
         <v/>
       </c>
       <c r="R129">
-        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 128 - 1), NA())</f>
+        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 128 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="130">
       <c r="P130" s="2">
-        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 129 - 1), NA())</f>
+        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 129 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q130">
-        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 129 - 1), NA())</f>
+        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 129 - 1), NA())</f>
         <v/>
       </c>
       <c r="R130">
-        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 129 - 1), NA())</f>
+        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 129 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="131">
       <c r="P131" s="2">
-        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 130 - 1), NA())</f>
+        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 130 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q131">
-        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 130 - 1), NA())</f>
+        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 130 - 1), NA())</f>
         <v/>
       </c>
       <c r="R131">
-        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 130 - 1), NA())</f>
+        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 130 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="132">
       <c r="P132" s="2">
-        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 131 - 1), NA())</f>
+        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 131 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q132">
-        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 131 - 1), NA())</f>
+        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 131 - 1), NA())</f>
         <v/>
       </c>
       <c r="R132">
-        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 131 - 1), NA())</f>
+        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 131 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="133">
       <c r="P133" s="2">
-        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 132 - 1), NA())</f>
+        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 132 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q133">
-        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 132 - 1), NA())</f>
+        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 132 - 1), NA())</f>
         <v/>
       </c>
       <c r="R133">
-        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 132 - 1), NA())</f>
+        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 132 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="134">
       <c r="P134" s="2">
-        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 133 - 1), NA())</f>
+        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 133 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q134">
-        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 133 - 1), NA())</f>
+        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 133 - 1), NA())</f>
         <v/>
       </c>
       <c r="R134">
-        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 133 - 1), NA())</f>
+        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 133 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="135">
       <c r="P135" s="2">
-        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 134 - 1), NA())</f>
+        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 134 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q135">
-        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 134 - 1), NA())</f>
+        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 134 - 1), NA())</f>
         <v/>
       </c>
       <c r="R135">
-        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 134 - 1), NA())</f>
+        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 134 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="136">
       <c r="P136" s="2">
-        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 135 - 1), NA())</f>
+        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 135 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q136">
-        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 135 - 1), NA())</f>
+        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 135 - 1), NA())</f>
         <v/>
       </c>
       <c r="R136">
-        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 135 - 1), NA())</f>
+        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 135 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="137">
       <c r="P137" s="2">
-        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 136 - 1), NA())</f>
+        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 136 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q137">
-        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 136 - 1), NA())</f>
+        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 136 - 1), NA())</f>
         <v/>
       </c>
       <c r="R137">
-        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 136 - 1), NA())</f>
+        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 136 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="138">
       <c r="P138" s="2">
-        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 137 - 1), NA())</f>
+        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 137 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q138">
-        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 137 - 1), NA())</f>
+        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 137 - 1), NA())</f>
         <v/>
       </c>
       <c r="R138">
-        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 137 - 1), NA())</f>
+        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 137 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="139">
       <c r="P139" s="2">
-        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 138 - 1), NA())</f>
+        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 138 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q139">
-        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 138 - 1), NA())</f>
+        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 138 - 1), NA())</f>
         <v/>
       </c>
       <c r="R139">
-        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 138 - 1), NA())</f>
+        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 138 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="140">
       <c r="P140" s="2">
-        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 139 - 1), NA())</f>
+        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 139 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q140">
-        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 139 - 1), NA())</f>
+        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 139 - 1), NA())</f>
         <v/>
       </c>
       <c r="R140">
-        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 139 - 1), NA())</f>
+        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 139 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="141">
       <c r="P141" s="2">
-        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 140 - 1), NA())</f>
+        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 140 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q141">
-        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 140 - 1), NA())</f>
+        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 140 - 1), NA())</f>
         <v/>
       </c>
       <c r="R141">
-        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 140 - 1), NA())</f>
+        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 140 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="142">
       <c r="P142" s="2">
-        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 141 - 1), NA())</f>
+        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 141 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q142">
-        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 141 - 1), NA())</f>
+        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 141 - 1), NA())</f>
         <v/>
       </c>
       <c r="R142">
-        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 141 - 1), NA())</f>
+        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 141 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="143">
       <c r="P143" s="2">
-        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 142 - 1), NA())</f>
+        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 142 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q143">
-        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 142 - 1), NA())</f>
+        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 142 - 1), NA())</f>
         <v/>
       </c>
       <c r="R143">
-        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 142 - 1), NA())</f>
+        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 142 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="144">
       <c r="P144" s="2">
-        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 143 - 1), NA())</f>
+        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 143 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q144">
-        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 143 - 1), NA())</f>
+        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 143 - 1), NA())</f>
         <v/>
       </c>
       <c r="R144">
-        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 143 - 1), NA())</f>
+        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 143 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="145">
       <c r="P145" s="2">
-        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 144 - 1), NA())</f>
+        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 144 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q145">
-        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 144 - 1), NA())</f>
+        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 144 - 1), NA())</f>
         <v/>
       </c>
       <c r="R145">
-        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 144 - 1), NA())</f>
+        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 144 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="146">
       <c r="P146" s="2">
-        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 145 - 1), NA())</f>
+        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 145 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q146">
-        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 145 - 1), NA())</f>
+        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 145 - 1), NA())</f>
         <v/>
       </c>
       <c r="R146">
-        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 145 - 1), NA())</f>
+        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 145 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="147">
       <c r="P147" s="2">
-        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 146 - 1), NA())</f>
+        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 146 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q147">
-        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 146 - 1), NA())</f>
+        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 146 - 1), NA())</f>
         <v/>
       </c>
       <c r="R147">
-        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 146 - 1), NA())</f>
+        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 146 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="148">
       <c r="P148" s="2">
-        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 147 - 1), NA())</f>
+        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 147 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q148">
-        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 147 - 1), NA())</f>
+        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 147 - 1), NA())</f>
         <v/>
       </c>
       <c r="R148">
-        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 147 - 1), NA())</f>
+        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 147 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="149">
       <c r="P149" s="2">
-        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 148 - 1), NA())</f>
+        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 148 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q149">
-        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 148 - 1), NA())</f>
+        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 148 - 1), NA())</f>
         <v/>
       </c>
       <c r="R149">
-        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 148 - 1), NA())</f>
+        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 148 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="150">
       <c r="P150" s="2">
-        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 149 - 1), NA())</f>
+        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 149 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q150">
-        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 149 - 1), NA())</f>
+        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 149 - 1), NA())</f>
         <v/>
       </c>
       <c r="R150">
-        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 149 - 1), NA())</f>
+        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 149 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="151">
       <c r="P151" s="2">
-        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 150 - 1), NA())</f>
+        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 150 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q151">
-        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 150 - 1), NA())</f>
+        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 150 - 1), NA())</f>
         <v/>
       </c>
       <c r="R151">
-        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 150 - 1), NA())</f>
+        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 150 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="152">
       <c r="P152" s="2">
-        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 151 - 1), NA())</f>
+        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 151 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q152">
-        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 151 - 1), NA())</f>
+        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 151 - 1), NA())</f>
         <v/>
       </c>
       <c r="R152">
-        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 151 - 1), NA())</f>
+        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 151 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="153">
       <c r="P153" s="2">
-        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 152 - 1), NA())</f>
+        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 152 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q153">
-        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 152 - 1), NA())</f>
+        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 152 - 1), NA())</f>
         <v/>
       </c>
       <c r="R153">
-        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 152 - 1), NA())</f>
+        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 152 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="154">
       <c r="P154" s="2">
-        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 153 - 1), NA())</f>
+        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 153 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q154">
-        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 153 - 1), NA())</f>
+        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 153 - 1), NA())</f>
         <v/>
       </c>
       <c r="R154">
-        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 153 - 1), NA())</f>
+        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 153 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="155">
       <c r="P155" s="2">
-        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 154 - 1), NA())</f>
+        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 154 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q155">
-        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 154 - 1), NA())</f>
+        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 154 - 1), NA())</f>
         <v/>
       </c>
       <c r="R155">
-        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 154 - 1), NA())</f>
+        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 154 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="156">
       <c r="P156" s="2">
-        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 155 - 1), NA())</f>
+        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 155 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q156">
-        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 155 - 1), NA())</f>
+        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 155 - 1), NA())</f>
         <v/>
       </c>
       <c r="R156">
-        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 155 - 1), NA())</f>
+        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 155 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="157">
       <c r="P157" s="2">
-        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 156 - 1), NA())</f>
+        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 156 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q157">
-        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 156 - 1), NA())</f>
+        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 156 - 1), NA())</f>
         <v/>
       </c>
       <c r="R157">
-        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 156 - 1), NA())</f>
+        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 156 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="158">
       <c r="P158" s="2">
-        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 157 - 1), NA())</f>
+        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 157 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q158">
-        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 157 - 1), NA())</f>
+        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 157 - 1), NA())</f>
         <v/>
       </c>
       <c r="R158">
-        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 157 - 1), NA())</f>
+        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 157 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="159">
       <c r="P159" s="2">
-        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 158 - 1), NA())</f>
+        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 158 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q159">
-        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 158 - 1), NA())</f>
+        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 158 - 1), NA())</f>
         <v/>
       </c>
       <c r="R159">
-        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 158 - 1), NA())</f>
+        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 158 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="160">
       <c r="P160" s="2">
-        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 159 - 1), NA())</f>
+        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 159 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q160">
-        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 159 - 1), NA())</f>
+        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 159 - 1), NA())</f>
         <v/>
       </c>
       <c r="R160">
-        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 159 - 1), NA())</f>
+        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 159 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="161">
       <c r="P161" s="2">
-        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 160 - 1), NA())</f>
+        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 160 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q161">
-        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 160 - 1), NA())</f>
+        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 160 - 1), NA())</f>
         <v/>
       </c>
       <c r="R161">
-        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 160 - 1), NA())</f>
+        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 160 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="162">
       <c r="P162" s="2">
-        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 161 - 1), NA())</f>
+        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 161 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q162">
-        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 161 - 1), NA())</f>
+        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 161 - 1), NA())</f>
         <v/>
       </c>
       <c r="R162">
-        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 161 - 1), NA())</f>
+        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 161 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="163">
       <c r="P163" s="2">
-        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 162 - 1), NA())</f>
+        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 162 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q163">
-        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 162 - 1), NA())</f>
+        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 162 - 1), NA())</f>
         <v/>
       </c>
       <c r="R163">
-        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 162 - 1), NA())</f>
+        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 162 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="164">
       <c r="P164" s="2">
-        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 163 - 1), NA())</f>
+        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 163 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q164">
-        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 163 - 1), NA())</f>
+        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 163 - 1), NA())</f>
         <v/>
       </c>
       <c r="R164">
-        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 163 - 1), NA())</f>
+        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 163 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="165">
       <c r="P165" s="2">
-        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 164 - 1), NA())</f>
+        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 164 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q165">
-        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 164 - 1), NA())</f>
+        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 164 - 1), NA())</f>
         <v/>
       </c>
       <c r="R165">
-        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 164 - 1), NA())</f>
+        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 164 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="166">
       <c r="P166" s="2">
-        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 165 - 1), NA())</f>
+        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 165 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q166">
-        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 165 - 1), NA())</f>
+        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 165 - 1), NA())</f>
         <v/>
       </c>
       <c r="R166">
-        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 165 - 1), NA())</f>
+        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 165 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="167">
       <c r="P167" s="2">
-        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 166 - 1), NA())</f>
+        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 166 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q167">
-        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 166 - 1), NA())</f>
+        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 166 - 1), NA())</f>
         <v/>
       </c>
       <c r="R167">
-        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 166 - 1), NA())</f>
+        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 166 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="168">
       <c r="P168" s="2">
-        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 167 - 1), NA())</f>
+        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 167 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q168">
-        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 167 - 1), NA())</f>
+        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 167 - 1), NA())</f>
         <v/>
       </c>
       <c r="R168">
-        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 167 - 1), NA())</f>
+        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 167 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="169">
       <c r="P169" s="2">
-        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 168 - 1), NA())</f>
+        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 168 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q169">
-        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 168 - 1), NA())</f>
+        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 168 - 1), NA())</f>
         <v/>
       </c>
       <c r="R169">
-        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 168 - 1), NA())</f>
+        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 168 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="170">
       <c r="P170" s="2">
-        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 169 - 1), NA())</f>
+        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 169 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q170">
-        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 169 - 1), NA())</f>
+        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 169 - 1), NA())</f>
         <v/>
       </c>
       <c r="R170">
-        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 169 - 1), NA())</f>
+        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 169 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="171">
       <c r="P171" s="2">
-        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 170 - 1), NA())</f>
+        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 170 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q171">
-        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 170 - 1), NA())</f>
+        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 170 - 1), NA())</f>
         <v/>
       </c>
       <c r="R171">
-        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 170 - 1), NA())</f>
+        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 170 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="172">
       <c r="P172" s="2">
-        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 171 - 1), NA())</f>
+        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 171 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q172">
-        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 171 - 1), NA())</f>
+        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 171 - 1), NA())</f>
         <v/>
       </c>
       <c r="R172">
-        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 171 - 1), NA())</f>
+        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 171 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="173">
       <c r="P173" s="2">
-        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 172 - 1), NA())</f>
+        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 172 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q173">
-        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 172 - 1), NA())</f>
+        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 172 - 1), NA())</f>
         <v/>
       </c>
       <c r="R173">
-        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 172 - 1), NA())</f>
+        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 172 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="174">
       <c r="P174" s="2">
-        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 173 - 1), NA())</f>
+        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 173 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q174">
-        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 173 - 1), NA())</f>
+        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 173 - 1), NA())</f>
         <v/>
       </c>
       <c r="R174">
-        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 173 - 1), NA())</f>
+        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 173 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="175">
       <c r="P175" s="2">
-        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 174 - 1), NA())</f>
+        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 174 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q175">
-        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 174 - 1), NA())</f>
+        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 174 - 1), NA())</f>
         <v/>
       </c>
       <c r="R175">
-        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 174 - 1), NA())</f>
+        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 174 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="176">
       <c r="P176" s="2">
-        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 175 - 1), NA())</f>
+        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 175 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q176">
-        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 175 - 1), NA())</f>
+        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 175 - 1), NA())</f>
         <v/>
       </c>
       <c r="R176">
-        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 175 - 1), NA())</f>
+        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 175 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="177">
       <c r="P177" s="2">
-        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 176 - 1), NA())</f>
+        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 176 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q177">
-        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 176 - 1), NA())</f>
+        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 176 - 1), NA())</f>
         <v/>
       </c>
       <c r="R177">
-        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 176 - 1), NA())</f>
+        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 176 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="178">
       <c r="P178" s="2">
-        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 177 - 1), NA())</f>
+        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 177 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q178">
-        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 177 - 1), NA())</f>
+        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 177 - 1), NA())</f>
         <v/>
       </c>
       <c r="R178">
-        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 177 - 1), NA())</f>
+        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 177 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="179">
       <c r="P179" s="2">
-        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 178 - 1), NA())</f>
+        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 178 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q179">
-        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 178 - 1), NA())</f>
+        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 178 - 1), NA())</f>
         <v/>
       </c>
       <c r="R179">
-        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 178 - 1), NA())</f>
+        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 178 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="180">
       <c r="P180" s="2">
-        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 179 - 1), NA())</f>
+        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 179 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q180">
-        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 179 - 1), NA())</f>
+        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 179 - 1), NA())</f>
         <v/>
       </c>
       <c r="R180">
-        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 179 - 1), NA())</f>
+        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 179 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="181">
       <c r="P181" s="2">
-        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 180 - 1), NA())</f>
+        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 180 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q181">
-        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 180 - 1), NA())</f>
+        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 180 - 1), NA())</f>
         <v/>
       </c>
       <c r="R181">
-        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 180 - 1), NA())</f>
+        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 180 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="182">
       <c r="P182" s="2">
-        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 181 - 1), NA())</f>
+        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 181 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q182">
-        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 181 - 1), NA())</f>
+        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 181 - 1), NA())</f>
         <v/>
       </c>
       <c r="R182">
-        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 181 - 1), NA())</f>
+        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 181 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="183">
       <c r="P183" s="2">
-        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 182 - 1), NA())</f>
+        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 182 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q183">
-        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 182 - 1), NA())</f>
+        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 182 - 1), NA())</f>
         <v/>
       </c>
       <c r="R183">
-        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 182 - 1), NA())</f>
+        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 182 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="184">
       <c r="P184" s="2">
-        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 183 - 1), NA())</f>
+        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 183 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q184">
-        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 183 - 1), NA())</f>
+        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 183 - 1), NA())</f>
         <v/>
       </c>
       <c r="R184">
-        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 183 - 1), NA())</f>
+        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 183 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="185">
       <c r="P185" s="2">
-        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 184 - 1), NA())</f>
+        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 184 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q185">
-        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 184 - 1), NA())</f>
+        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 184 - 1), NA())</f>
         <v/>
       </c>
       <c r="R185">
-        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 184 - 1), NA())</f>
+        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 184 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="186">
       <c r="P186" s="2">
-        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 185 - 1), NA())</f>
+        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 185 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q186">
-        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 185 - 1), NA())</f>
+        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 185 - 1), NA())</f>
         <v/>
       </c>
       <c r="R186">
-        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 185 - 1), NA())</f>
+        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 185 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="187">
       <c r="P187" s="2">
-        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 186 - 1), NA())</f>
+        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 186 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q187">
-        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 186 - 1), NA())</f>
+        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 186 - 1), NA())</f>
         <v/>
       </c>
       <c r="R187">
-        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 186 - 1), NA())</f>
+        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 186 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="188">
       <c r="P188" s="2">
-        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 187 - 1), NA())</f>
+        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 187 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q188">
-        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 187 - 1), NA())</f>
+        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 187 - 1), NA())</f>
         <v/>
       </c>
       <c r="R188">
-        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 187 - 1), NA())</f>
+        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 187 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="189">
       <c r="P189" s="2">
-        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 188 - 1), NA())</f>
+        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 188 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q189">
-        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 188 - 1), NA())</f>
+        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 188 - 1), NA())</f>
         <v/>
       </c>
       <c r="R189">
-        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 188 - 1), NA())</f>
+        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 188 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="190">
       <c r="P190" s="2">
-        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 189 - 1), NA())</f>
+        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 189 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q190">
-        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 189 - 1), NA())</f>
+        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 189 - 1), NA())</f>
         <v/>
       </c>
       <c r="R190">
-        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 189 - 1), NA())</f>
+        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 189 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="191">
       <c r="P191" s="2">
-        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 190 - 1), NA())</f>
+        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 190 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q191">
-        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 190 - 1), NA())</f>
+        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 190 - 1), NA())</f>
         <v/>
       </c>
       <c r="R191">
-        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 190 - 1), NA())</f>
+        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 190 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="192">
       <c r="P192" s="2">
-        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 191 - 1), NA())</f>
+        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 191 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q192">
-        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 191 - 1), NA())</f>
+        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 191 - 1), NA())</f>
         <v/>
       </c>
       <c r="R192">
-        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 191 - 1), NA())</f>
+        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 191 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="193">
       <c r="P193" s="2">
-        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 192 - 1), NA())</f>
+        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 192 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q193">
-        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 192 - 1), NA())</f>
+        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 192 - 1), NA())</f>
         <v/>
       </c>
       <c r="R193">
-        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 192 - 1), NA())</f>
+        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 192 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="194">
       <c r="P194" s="2">
-        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 193 - 1), NA())</f>
+        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 193 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q194">
-        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 193 - 1), NA())</f>
+        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 193 - 1), NA())</f>
         <v/>
       </c>
       <c r="R194">
-        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 193 - 1), NA())</f>
+        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 193 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="195">
       <c r="P195" s="2">
-        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 194 - 1), NA())</f>
+        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 194 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q195">
-        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 194 - 1), NA())</f>
+        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 194 - 1), NA())</f>
         <v/>
       </c>
       <c r="R195">
-        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 194 - 1), NA())</f>
+        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 194 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="196">
       <c r="P196" s="2">
-        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 195 - 1), NA())</f>
+        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 195 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q196">
-        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 195 - 1), NA())</f>
+        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 195 - 1), NA())</f>
         <v/>
       </c>
       <c r="R196">
-        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 195 - 1), NA())</f>
+        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 195 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="197">
       <c r="P197" s="2">
-        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 196 - 1), NA())</f>
+        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 196 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q197">
-        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 196 - 1), NA())</f>
+        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 196 - 1), NA())</f>
         <v/>
       </c>
       <c r="R197">
-        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 196 - 1), NA())</f>
+        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 196 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="198">
       <c r="P198" s="2">
-        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 197 - 1), NA())</f>
+        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 197 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q198">
-        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 197 - 1), NA())</f>
+        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 197 - 1), NA())</f>
         <v/>
       </c>
       <c r="R198">
-        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 197 - 1), NA())</f>
+        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 197 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="199">
       <c r="P199" s="2">
-        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 198 - 1), NA())</f>
+        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 198 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q199">
-        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 198 - 1), NA())</f>
+        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 198 - 1), NA())</f>
         <v/>
       </c>
       <c r="R199">
-        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 198 - 1), NA())</f>
+        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 198 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="200">
       <c r="P200" s="2">
-        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 199 - 1), NA())</f>
+        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 199 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q200">
-        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 199 - 1), NA())</f>
+        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 199 - 1), NA())</f>
         <v/>
       </c>
       <c r="R200">
-        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 199 - 1), NA())</f>
+        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 199 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="201">
       <c r="P201" s="2">
-        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 200 - 1), NA())</f>
+        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 200 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q201">
-        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 200 - 1), NA())</f>
+        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 200 - 1), NA())</f>
         <v/>
       </c>
       <c r="R201">
-        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 200 - 1), NA())</f>
+        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 200 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="202">
       <c r="P202" s="2">
-        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 201 - 1), NA())</f>
+        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 201 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q202">
-        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 201 - 1), NA())</f>
+        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 201 - 1), NA())</f>
         <v/>
       </c>
       <c r="R202">
-        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 201 - 1), NA())</f>
+        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 201 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="203">
       <c r="P203" s="2">
-        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 202 - 1), NA())</f>
+        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 202 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q203">
-        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 202 - 1), NA())</f>
+        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 202 - 1), NA())</f>
         <v/>
       </c>
       <c r="R203">
-        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 202 - 1), NA())</f>
+        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 202 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="204">
       <c r="P204" s="2">
-        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 203 - 1), NA())</f>
+        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 203 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q204">
-        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 203 - 1), NA())</f>
+        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 203 - 1), NA())</f>
         <v/>
       </c>
       <c r="R204">
-        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 203 - 1), NA())</f>
+        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 203 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="205">
       <c r="P205" s="2">
-        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 204 - 1), NA())</f>
+        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 204 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q205">
-        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 204 - 1), NA())</f>
+        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 204 - 1), NA())</f>
         <v/>
       </c>
       <c r="R205">
-        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 204 - 1), NA())</f>
+        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 204 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="206">
       <c r="P206" s="2">
-        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 205 - 1), NA())</f>
+        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 205 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q206">
-        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 205 - 1), NA())</f>
+        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 205 - 1), NA())</f>
         <v/>
       </c>
       <c r="R206">
-        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 205 - 1), NA())</f>
+        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 205 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="207">
       <c r="P207" s="2">
-        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 206 - 1), NA())</f>
+        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 206 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q207">
-        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 206 - 1), NA())</f>
+        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 206 - 1), NA())</f>
         <v/>
       </c>
       <c r="R207">
-        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 206 - 1), NA())</f>
+        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 206 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="208">
       <c r="P208" s="2">
-        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 207 - 1), NA())</f>
+        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 207 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q208">
-        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 207 - 1), NA())</f>
+        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 207 - 1), NA())</f>
         <v/>
       </c>
       <c r="R208">
-        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 207 - 1), NA())</f>
+        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 207 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="209">
       <c r="P209" s="2">
-        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 208 - 1), NA())</f>
+        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 208 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q209">
-        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 208 - 1), NA())</f>
+        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 208 - 1), NA())</f>
         <v/>
       </c>
       <c r="R209">
-        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 208 - 1), NA())</f>
+        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 208 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="210">
       <c r="P210" s="2">
-        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 209 - 1), NA())</f>
+        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 209 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q210">
-        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 209 - 1), NA())</f>
+        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 209 - 1), NA())</f>
         <v/>
       </c>
       <c r="R210">
-        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 209 - 1), NA())</f>
+        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 209 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="211">
       <c r="P211" s="2">
-        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 210 - 1), NA())</f>
+        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 210 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q211">
-        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 210 - 1), NA())</f>
+        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 210 - 1), NA())</f>
         <v/>
       </c>
       <c r="R211">
-        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 210 - 1), NA())</f>
+        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 210 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="212">
       <c r="P212" s="2">
-        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 211 - 1), NA())</f>
+        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 211 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q212">
-        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 211 - 1), NA())</f>
+        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 211 - 1), NA())</f>
         <v/>
       </c>
       <c r="R212">
-        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 211 - 1), NA())</f>
+        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 211 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="213">
       <c r="P213" s="2">
-        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 212 - 1), NA())</f>
+        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 212 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q213">
-        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 212 - 1), NA())</f>
+        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 212 - 1), NA())</f>
         <v/>
       </c>
       <c r="R213">
-        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 212 - 1), NA())</f>
+        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 212 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="214">
       <c r="P214" s="2">
-        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 213 - 1), NA())</f>
+        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 213 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q214">
-        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 213 - 1), NA())</f>
+        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 213 - 1), NA())</f>
         <v/>
       </c>
       <c r="R214">
-        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 213 - 1), NA())</f>
+        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 213 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="215">
       <c r="P215" s="2">
-        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 214 - 1), NA())</f>
+        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 214 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q215">
-        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 214 - 1), NA())</f>
+        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 214 - 1), NA())</f>
         <v/>
       </c>
       <c r="R215">
-        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 214 - 1), NA())</f>
+        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 214 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="216">
       <c r="P216" s="2">
-        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 215 - 1), NA())</f>
+        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 215 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q216">
-        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 215 - 1), NA())</f>
+        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 215 - 1), NA())</f>
         <v/>
       </c>
       <c r="R216">
-        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 215 - 1), NA())</f>
+        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 215 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="217">
       <c r="P217" s="2">
-        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 216 - 1), NA())</f>
+        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 216 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q217">
-        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 216 - 1), NA())</f>
+        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 216 - 1), NA())</f>
         <v/>
       </c>
       <c r="R217">
-        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 216 - 1), NA())</f>
+        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 216 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="218">
       <c r="P218" s="2">
-        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 217 - 1), NA())</f>
+        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 217 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q218">
-        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 217 - 1), NA())</f>
+        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 217 - 1), NA())</f>
         <v/>
       </c>
       <c r="R218">
-        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 217 - 1), NA())</f>
+        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 217 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="219">
       <c r="P219" s="2">
-        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 218 - 1), NA())</f>
+        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 218 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q219">
-        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 218 - 1), NA())</f>
+        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 218 - 1), NA())</f>
         <v/>
       </c>
       <c r="R219">
-        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 218 - 1), NA())</f>
+        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 218 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="220">
       <c r="P220" s="2">
-        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 219 - 1), NA())</f>
+        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 219 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q220">
-        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 219 - 1), NA())</f>
+        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 219 - 1), NA())</f>
         <v/>
       </c>
       <c r="R220">
-        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 219 - 1), NA())</f>
+        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 219 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="221">
       <c r="P221" s="2">
-        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 220 - 1), NA())</f>
+        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 220 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q221">
-        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 220 - 1), NA())</f>
+        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 220 - 1), NA())</f>
         <v/>
       </c>
       <c r="R221">
-        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 220 - 1), NA())</f>
+        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 220 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="222">
       <c r="P222" s="2">
-        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 221 - 1), NA())</f>
+        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 221 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q222">
-        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 221 - 1), NA())</f>
+        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 221 - 1), NA())</f>
         <v/>
       </c>
       <c r="R222">
-        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 221 - 1), NA())</f>
+        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 221 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="223">
       <c r="P223" s="2">
-        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 222 - 1), NA())</f>
+        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 222 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q223">
-        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 222 - 1), NA())</f>
+        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 222 - 1), NA())</f>
         <v/>
       </c>
       <c r="R223">
-        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 222 - 1), NA())</f>
+        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 222 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="224">
       <c r="P224" s="2">
-        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 223 - 1), NA())</f>
+        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 223 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q224">
-        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 223 - 1), NA())</f>
+        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 223 - 1), NA())</f>
         <v/>
       </c>
       <c r="R224">
-        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 223 - 1), NA())</f>
+        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 223 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="225">
       <c r="P225" s="2">
-        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 224 - 1), NA())</f>
+        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 224 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q225">
-        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 224 - 1), NA())</f>
+        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 224 - 1), NA())</f>
         <v/>
       </c>
       <c r="R225">
-        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 224 - 1), NA())</f>
+        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 224 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="226">
       <c r="P226" s="2">
-        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 225 - 1), NA())</f>
+        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 225 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q226">
-        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 225 - 1), NA())</f>
+        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 225 - 1), NA())</f>
         <v/>
       </c>
       <c r="R226">
-        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 225 - 1), NA())</f>
+        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 225 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="227">
       <c r="P227" s="2">
-        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 226 - 1), NA())</f>
+        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 226 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q227">
-        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 226 - 1), NA())</f>
+        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 226 - 1), NA())</f>
         <v/>
       </c>
       <c r="R227">
-        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 226 - 1), NA())</f>
+        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 226 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="228">
       <c r="P228" s="2">
-        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 227 - 1), NA())</f>
+        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 227 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q228">
-        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 227 - 1), NA())</f>
+        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 227 - 1), NA())</f>
         <v/>
       </c>
       <c r="R228">
-        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 227 - 1), NA())</f>
+        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 227 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="229">
       <c r="P229" s="2">
-        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 228 - 1), NA())</f>
+        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 228 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q229">
-        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 228 - 1), NA())</f>
+        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 228 - 1), NA())</f>
         <v/>
       </c>
       <c r="R229">
-        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 228 - 1), NA())</f>
+        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 228 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="230">
       <c r="P230" s="2">
-        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 229 - 1), NA())</f>
+        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 229 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q230">
-        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 229 - 1), NA())</f>
+        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 229 - 1), NA())</f>
         <v/>
       </c>
       <c r="R230">
-        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 229 - 1), NA())</f>
+        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 229 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="231">
       <c r="P231" s="2">
-        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 230 - 1), NA())</f>
+        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 230 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q231">
-        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 230 - 1), NA())</f>
+        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 230 - 1), NA())</f>
         <v/>
       </c>
       <c r="R231">
-        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 230 - 1), NA())</f>
+        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 230 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="232">
       <c r="P232" s="2">
-        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 231 - 1), NA())</f>
+        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 231 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q232">
-        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 231 - 1), NA())</f>
+        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 231 - 1), NA())</f>
         <v/>
       </c>
       <c r="R232">
-        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 231 - 1), NA())</f>
+        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 231 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="233">
       <c r="P233" s="2">
-        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 232 - 1), NA())</f>
+        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 232 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q233">
-        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 232 - 1), NA())</f>
+        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 232 - 1), NA())</f>
         <v/>
       </c>
       <c r="R233">
-        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 232 - 1), NA())</f>
+        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 232 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="234">
       <c r="P234" s="2">
-        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 233 - 1), NA())</f>
+        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 233 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q234">
-        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 233 - 1), NA())</f>
+        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 233 - 1), NA())</f>
         <v/>
       </c>
       <c r="R234">
-        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 233 - 1), NA())</f>
+        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 233 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="235">
       <c r="P235" s="2">
-        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 234 - 1), NA())</f>
+        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 234 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q235">
-        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 234 - 1), NA())</f>
+        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 234 - 1), NA())</f>
         <v/>
       </c>
       <c r="R235">
-        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 234 - 1), NA())</f>
+        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 234 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="236">
       <c r="P236" s="2">
-        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 235 - 1), NA())</f>
+        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 235 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q236">
-        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 235 - 1), NA())</f>
+        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 235 - 1), NA())</f>
         <v/>
       </c>
       <c r="R236">
-        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 235 - 1), NA())</f>
+        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 235 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="237">
       <c r="P237" s="2">
-        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 236 - 1), NA())</f>
+        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 236 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q237">
-        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 236 - 1), NA())</f>
+        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 236 - 1), NA())</f>
         <v/>
       </c>
       <c r="R237">
-        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 236 - 1), NA())</f>
+        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 236 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="238">
       <c r="P238" s="2">
-        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 237 - 1), NA())</f>
+        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 237 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q238">
-        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 237 - 1), NA())</f>
+        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 237 - 1), NA())</f>
         <v/>
       </c>
       <c r="R238">
-        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 237 - 1), NA())</f>
+        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 237 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="239">
       <c r="P239" s="2">
-        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 238 - 1), NA())</f>
+        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 238 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q239">
-        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 238 - 1), NA())</f>
+        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 238 - 1), NA())</f>
         <v/>
       </c>
       <c r="R239">
-        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 238 - 1), NA())</f>
+        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 238 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="240">
       <c r="P240" s="2">
-        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 239 - 1), NA())</f>
+        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 239 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q240">
-        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 239 - 1), NA())</f>
+        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 239 - 1), NA())</f>
         <v/>
       </c>
       <c r="R240">
-        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 239 - 1), NA())</f>
+        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 239 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="241">
       <c r="P241" s="2">
-        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 240 - 1), NA())</f>
+        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 240 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q241">
-        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 240 - 1), NA())</f>
+        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 240 - 1), NA())</f>
         <v/>
       </c>
       <c r="R241">
-        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 240 - 1), NA())</f>
+        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 240 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="242">
       <c r="P242" s="2">
-        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 241 - 1), NA())</f>
+        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 241 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q242">
-        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 241 - 1), NA())</f>
+        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 241 - 1), NA())</f>
         <v/>
       </c>
       <c r="R242">
-        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 241 - 1), NA())</f>
+        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 241 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="243">
       <c r="P243" s="2">
-        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 242 - 1), NA())</f>
+        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 242 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q243">
-        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 242 - 1), NA())</f>
+        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 242 - 1), NA())</f>
         <v/>
       </c>
       <c r="R243">
-        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 242 - 1), NA())</f>
+        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 242 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="244">
       <c r="P244" s="2">
-        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 243 - 1), NA())</f>
+        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 243 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q244">
-        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 243 - 1), NA())</f>
+        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 243 - 1), NA())</f>
         <v/>
       </c>
       <c r="R244">
-        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 243 - 1), NA())</f>
+        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 243 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="245">
       <c r="P245" s="2">
-        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 244 - 1), NA())</f>
+        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 244 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q245">
-        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 244 - 1), NA())</f>
+        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 244 - 1), NA())</f>
         <v/>
       </c>
       <c r="R245">
-        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 244 - 1), NA())</f>
+        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 244 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="246">
       <c r="P246" s="2">
-        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 245 - 1), NA())</f>
+        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 245 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q246">
-        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 245 - 1), NA())</f>
+        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 245 - 1), NA())</f>
         <v/>
       </c>
       <c r="R246">
-        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 245 - 1), NA())</f>
+        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 245 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="247">
       <c r="P247" s="2">
-        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 246 - 1), NA())</f>
+        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 246 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q247">
-        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 246 - 1), NA())</f>
+        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 246 - 1), NA())</f>
         <v/>
       </c>
       <c r="R247">
-        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 246 - 1), NA())</f>
+        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 246 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="248">
       <c r="P248" s="2">
-        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 247 - 1), NA())</f>
+        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 247 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q248">
-        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 247 - 1), NA())</f>
+        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 247 - 1), NA())</f>
         <v/>
       </c>
       <c r="R248">
-        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 247 - 1), NA())</f>
+        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 247 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="249">
       <c r="P249" s="2">
-        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 248 - 1), NA())</f>
+        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 248 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q249">
-        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 248 - 1), NA())</f>
+        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 248 - 1), NA())</f>
         <v/>
       </c>
       <c r="R249">
-        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 248 - 1), NA())</f>
+        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 248 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="250">
       <c r="P250" s="2">
-        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 249 - 1), NA())</f>
+        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 249 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q250">
-        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 249 - 1), NA())</f>
+        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 249 - 1), NA())</f>
         <v/>
       </c>
       <c r="R250">
-        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 249 - 1), NA())</f>
+        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 249 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="251">
       <c r="P251" s="2">
-        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 250 - 1), NA())</f>
+        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 250 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q251">
-        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 250 - 1), NA())</f>
+        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 250 - 1), NA())</f>
         <v/>
       </c>
       <c r="R251">
-        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 250 - 1), NA())</f>
+        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 250 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="252">
       <c r="P252" s="2">
-        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 251 - 1), NA())</f>
+        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 251 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q252">
-        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 251 - 1), NA())</f>
+        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 251 - 1), NA())</f>
         <v/>
       </c>
       <c r="R252">
-        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 251 - 1), NA())</f>
+        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 251 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="253">
       <c r="P253" s="2">
-        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 252 - 1), NA())</f>
+        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 252 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q253">
-        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 252 - 1), NA())</f>
+        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 252 - 1), NA())</f>
         <v/>
       </c>
       <c r="R253">
-        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 252 - 1), NA())</f>
+        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 252 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="254">
       <c r="P254" s="2">
-        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 253 - 1), NA())</f>
+        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 253 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q254">
-        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 253 - 1), NA())</f>
+        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 253 - 1), NA())</f>
         <v/>
       </c>
       <c r="R254">
-        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 253 - 1), NA())</f>
+        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 253 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="255">
       <c r="P255" s="2">
-        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 254 - 1), NA())</f>
+        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 254 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q255">
-        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 254 - 1), NA())</f>
+        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 254 - 1), NA())</f>
         <v/>
       </c>
       <c r="R255">
-        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 254 - 1), NA())</f>
+        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 254 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="256">
       <c r="P256" s="2">
-        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 255 - 1), NA())</f>
+        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 255 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q256">
-        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 255 - 1), NA())</f>
+        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 255 - 1), NA())</f>
         <v/>
       </c>
       <c r="R256">
-        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 255 - 1), NA())</f>
+        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 255 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="257">
       <c r="P257" s="2">
-        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 256 - 1), NA())</f>
+        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 256 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q257">
-        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 256 - 1), NA())</f>
+        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 256 - 1), NA())</f>
         <v/>
       </c>
       <c r="R257">
-        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 256 - 1), NA())</f>
+        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 256 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="258">
       <c r="P258" s="2">
-        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 257 - 1), NA())</f>
+        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 257 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q258">
-        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 257 - 1), NA())</f>
+        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 257 - 1), NA())</f>
         <v/>
       </c>
       <c r="R258">
-        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 257 - 1), NA())</f>
+        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 257 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="259">
       <c r="P259" s="2">
-        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 258 - 1), NA())</f>
+        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 258 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q259">
-        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 258 - 1), NA())</f>
+        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 258 - 1), NA())</f>
         <v/>
       </c>
       <c r="R259">
-        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 258 - 1), NA())</f>
+        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 258 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="260">
       <c r="P260" s="2">
-        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 259 - 1), NA())</f>
+        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 259 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q260">
-        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 259 - 1), NA())</f>
+        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 259 - 1), NA())</f>
         <v/>
       </c>
       <c r="R260">
-        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 259 - 1), NA())</f>
+        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 259 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="261">
       <c r="P261" s="2">
-        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 260 - 1), NA())</f>
+        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 260 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q261">
-        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 260 - 1), NA())</f>
+        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 260 - 1), NA())</f>
         <v/>
       </c>
       <c r="R261">
-        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 260 - 1), NA())</f>
+        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 260 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="262">
       <c r="P262" s="2">
-        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 261 - 1), NA())</f>
+        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 261 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q262">
-        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 261 - 1), NA())</f>
+        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 261 - 1), NA())</f>
         <v/>
       </c>
       <c r="R262">
-        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 261 - 1), NA())</f>
+        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 261 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="263">
       <c r="P263" s="2">
-        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 262 - 1), NA())</f>
+        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 262 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q263">
-        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 262 - 1), NA())</f>
+        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 262 - 1), NA())</f>
         <v/>
       </c>
       <c r="R263">
-        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 262 - 1), NA())</f>
+        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 262 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="264">
       <c r="P264" s="2">
-        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 263 - 1), NA())</f>
+        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 263 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q264">
-        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 263 - 1), NA())</f>
+        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 263 - 1), NA())</f>
         <v/>
       </c>
       <c r="R264">
-        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 263 - 1), NA())</f>
+        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 263 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="265">
       <c r="P265" s="2">
-        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 264 - 1), NA())</f>
+        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 264 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q265">
-        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 264 - 1), NA())</f>
+        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 264 - 1), NA())</f>
         <v/>
       </c>
       <c r="R265">
-        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 264 - 1), NA())</f>
+        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 264 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="266">
       <c r="P266" s="2">
-        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 265 - 1), NA())</f>
+        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 265 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q266">
-        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 265 - 1), NA())</f>
+        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 265 - 1), NA())</f>
         <v/>
       </c>
       <c r="R266">
-        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 265 - 1), NA())</f>
+        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 265 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="267">
       <c r="P267" s="2">
-        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 266 - 1), NA())</f>
+        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 266 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q267">
-        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 266 - 1), NA())</f>
+        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 266 - 1), NA())</f>
         <v/>
       </c>
       <c r="R267">
-        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 266 - 1), NA())</f>
+        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 266 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="268">
       <c r="P268" s="2">
-        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 267 - 1), NA())</f>
+        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 267 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q268">
-        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 267 - 1), NA())</f>
+        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 267 - 1), NA())</f>
         <v/>
       </c>
       <c r="R268">
-        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 267 - 1), NA())</f>
+        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 267 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="269">
       <c r="P269" s="2">
-        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 268 - 1), NA())</f>
+        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 268 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q269">
-        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 268 - 1), NA())</f>
+        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 268 - 1), NA())</f>
         <v/>
       </c>
       <c r="R269">
-        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 268 - 1), NA())</f>
+        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 268 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="270">
       <c r="P270" s="2">
-        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 269 - 1), NA())</f>
+        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 269 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q270">
-        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 269 - 1), NA())</f>
+        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 269 - 1), NA())</f>
         <v/>
       </c>
       <c r="R270">
-        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 269 - 1), NA())</f>
+        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 269 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="271">
       <c r="P271" s="2">
-        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 270 - 1), NA())</f>
+        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 270 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q271">
-        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 270 - 1), NA())</f>
+        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 270 - 1), NA())</f>
         <v/>
       </c>
       <c r="R271">
-        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 270 - 1), NA())</f>
+        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 270 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="272">
       <c r="P272" s="2">
-        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 271 - 1), NA())</f>
+        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 271 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q272">
-        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 271 - 1), NA())</f>
+        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 271 - 1), NA())</f>
         <v/>
       </c>
       <c r="R272">
-        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 271 - 1), NA())</f>
+        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 271 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="273">
       <c r="P273" s="2">
-        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 272 - 1), NA())</f>
+        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 272 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q273">
-        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 272 - 1), NA())</f>
+        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 272 - 1), NA())</f>
         <v/>
       </c>
       <c r="R273">
-        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 272 - 1), NA())</f>
+        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 272 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="274">
       <c r="P274" s="2">
-        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 273 - 1), NA())</f>
+        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 273 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q274">
-        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 273 - 1), NA())</f>
+        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 273 - 1), NA())</f>
         <v/>
       </c>
       <c r="R274">
-        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 273 - 1), NA())</f>
+        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 273 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="275">
       <c r="P275" s="2">
-        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 274 - 1), NA())</f>
+        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 274 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q275">
-        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 274 - 1), NA())</f>
+        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 274 - 1), NA())</f>
         <v/>
       </c>
       <c r="R275">
-        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 274 - 1), NA())</f>
+        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 274 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="276">
       <c r="P276" s="2">
-        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 275 - 1), NA())</f>
+        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 275 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q276">
-        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 275 - 1), NA())</f>
+        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 275 - 1), NA())</f>
         <v/>
       </c>
       <c r="R276">
-        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 275 - 1), NA())</f>
+        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 275 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="277">
       <c r="P277" s="2">
-        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 276 - 1), NA())</f>
+        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 276 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q277">
-        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 276 - 1), NA())</f>
+        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 276 - 1), NA())</f>
         <v/>
       </c>
       <c r="R277">
-        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 276 - 1), NA())</f>
+        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 276 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="278">
       <c r="P278" s="2">
-        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 277 - 1), NA())</f>
+        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 277 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q278">
-        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 277 - 1), NA())</f>
+        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 277 - 1), NA())</f>
         <v/>
       </c>
       <c r="R278">
-        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 277 - 1), NA())</f>
+        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 277 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="279">
       <c r="P279" s="2">
-        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 278 - 1), NA())</f>
+        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 278 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q279">
-        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 278 - 1), NA())</f>
+        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 278 - 1), NA())</f>
         <v/>
       </c>
       <c r="R279">
-        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 278 - 1), NA())</f>
+        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 278 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="280">
       <c r="P280" s="2">
-        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 279 - 1), NA())</f>
+        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 279 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q280">
-        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 279 - 1), NA())</f>
+        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 279 - 1), NA())</f>
         <v/>
       </c>
       <c r="R280">
-        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 279 - 1), NA())</f>
+        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 279 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="281">
       <c r="P281" s="2">
-        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 280 - 1), NA())</f>
+        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 280 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q281">
-        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 280 - 1), NA())</f>
+        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 280 - 1), NA())</f>
         <v/>
       </c>
       <c r="R281">
-        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 280 - 1), NA())</f>
+        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 280 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="282">
       <c r="P282" s="2">
-        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 281 - 1), NA())</f>
+        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 281 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q282">
-        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 281 - 1), NA())</f>
+        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 281 - 1), NA())</f>
         <v/>
       </c>
       <c r="R282">
-        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 281 - 1), NA())</f>
+        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 281 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="283">
       <c r="P283" s="2">
-        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 282 - 1), NA())</f>
+        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 282 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q283">
-        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 282 - 1), NA())</f>
+        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 282 - 1), NA())</f>
         <v/>
       </c>
       <c r="R283">
-        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 282 - 1), NA())</f>
+        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 282 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="284">
       <c r="P284" s="2">
-        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 283 - 1), NA())</f>
+        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 283 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q284">
-        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 283 - 1), NA())</f>
+        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 283 - 1), NA())</f>
         <v/>
       </c>
       <c r="R284">
-        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 283 - 1), NA())</f>
+        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 283 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="285">
       <c r="P285" s="2">
-        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 284 - 1), NA())</f>
+        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 284 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q285">
-        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 284 - 1), NA())</f>
+        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 284 - 1), NA())</f>
         <v/>
       </c>
       <c r="R285">
-        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 284 - 1), NA())</f>
+        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 284 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="286">
       <c r="P286" s="2">
-        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 285 - 1), NA())</f>
+        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 285 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q286">
-        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 285 - 1), NA())</f>
+        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 285 - 1), NA())</f>
         <v/>
       </c>
       <c r="R286">
-        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 285 - 1), NA())</f>
+        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 285 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="287">
       <c r="P287" s="2">
-        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 286 - 1), NA())</f>
+        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 286 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q287">
-        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 286 - 1), NA())</f>
+        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 286 - 1), NA())</f>
         <v/>
       </c>
       <c r="R287">
-        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 286 - 1), NA())</f>
+        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 286 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="288">
       <c r="P288" s="2">
-        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 287 - 1), NA())</f>
+        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 287 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q288">
-        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 287 - 1), NA())</f>
+        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 287 - 1), NA())</f>
         <v/>
       </c>
       <c r="R288">
-        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 287 - 1), NA())</f>
+        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 287 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="289">
       <c r="P289" s="2">
-        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 288 - 1), NA())</f>
+        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 288 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q289">
-        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 288 - 1), NA())</f>
+        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 288 - 1), NA())</f>
         <v/>
       </c>
       <c r="R289">
-        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 288 - 1), NA())</f>
+        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 288 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="290">
       <c r="P290" s="2">
-        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 289 - 1), NA())</f>
+        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 289 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q290">
-        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 289 - 1), NA())</f>
+        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 289 - 1), NA())</f>
         <v/>
       </c>
       <c r="R290">
-        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 289 - 1), NA())</f>
+        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 289 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="291">
       <c r="P291" s="2">
-        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 290 - 1), NA())</f>
+        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 290 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q291">
-        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 290 - 1), NA())</f>
+        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 290 - 1), NA())</f>
         <v/>
       </c>
       <c r="R291">
-        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 290 - 1), NA())</f>
+        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 290 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="292">
       <c r="P292" s="2">
-        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 291 - 1), NA())</f>
+        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 291 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q292">
-        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 291 - 1), NA())</f>
+        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 291 - 1), NA())</f>
         <v/>
       </c>
       <c r="R292">
-        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 291 - 1), NA())</f>
+        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 291 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="293">
       <c r="P293" s="2">
-        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 292 - 1), NA())</f>
+        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 292 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q293">
-        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 292 - 1), NA())</f>
+        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 292 - 1), NA())</f>
         <v/>
       </c>
       <c r="R293">
-        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 292 - 1), NA())</f>
+        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 292 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="294">
       <c r="P294" s="2">
-        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 293 - 1), NA())</f>
+        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 293 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q294">
-        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 293 - 1), NA())</f>
+        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 293 - 1), NA())</f>
         <v/>
       </c>
       <c r="R294">
-        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 293 - 1), NA())</f>
+        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 293 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="295">
       <c r="P295" s="2">
-        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 294 - 1), NA())</f>
+        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 294 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q295">
-        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 294 - 1), NA())</f>
+        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 294 - 1), NA())</f>
         <v/>
       </c>
       <c r="R295">
-        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 294 - 1), NA())</f>
+        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 294 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="296">
       <c r="P296" s="2">
-        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 295 - 1), NA())</f>
+        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 295 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q296">
-        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 295 - 1), NA())</f>
+        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 295 - 1), NA())</f>
         <v/>
       </c>
       <c r="R296">
-        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 295 - 1), NA())</f>
+        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 295 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="297">
       <c r="P297" s="2">
-        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 296 - 1), NA())</f>
+        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 296 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q297">
-        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 296 - 1), NA())</f>
+        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 296 - 1), NA())</f>
         <v/>
       </c>
       <c r="R297">
-        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 296 - 1), NA())</f>
+        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 296 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="298">
       <c r="P298" s="2">
-        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 297 - 1), NA())</f>
+        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 297 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q298">
-        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 297 - 1), NA())</f>
+        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 297 - 1), NA())</f>
         <v/>
       </c>
       <c r="R298">
-        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 297 - 1), NA())</f>
+        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 297 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="299">
       <c r="P299" s="2">
-        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 298 - 1), NA())</f>
+        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 298 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q299">
-        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 298 - 1), NA())</f>
+        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 298 - 1), NA())</f>
         <v/>
       </c>
       <c r="R299">
-        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 298 - 1), NA())</f>
+        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 298 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="300">
       <c r="P300" s="2">
-        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 299 - 1), NA())</f>
+        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 299 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q300">
-        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 299 - 1), NA())</f>
+        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 299 - 1), NA())</f>
         <v/>
       </c>
       <c r="R300">
-        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 299 - 1), NA())</f>
+        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 299 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="301">
       <c r="P301" s="2">
-        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 300 - 1), NA())</f>
+        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 300 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q301">
-        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 300 - 1), NA())</f>
+        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 300 - 1), NA())</f>
         <v/>
       </c>
       <c r="R301">
-        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 300 - 1), NA())</f>
+        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 300 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="302">
       <c r="P302" s="2">
-        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 301 - 1), NA())</f>
+        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 301 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q302">
-        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 301 - 1), NA())</f>
+        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 301 - 1), NA())</f>
         <v/>
       </c>
       <c r="R302">
-        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 301 - 1), NA())</f>
+        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 301 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="303">
       <c r="P303" s="2">
-        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 302 - 1), NA())</f>
+        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 302 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q303">
-        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 302 - 1), NA())</f>
+        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 302 - 1), NA())</f>
         <v/>
       </c>
       <c r="R303">
-        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 302 - 1), NA())</f>
+        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 302 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="304">
       <c r="P304" s="2">
-        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 303 - 1), NA())</f>
+        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 303 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q304">
-        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 303 - 1), NA())</f>
+        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 303 - 1), NA())</f>
         <v/>
       </c>
       <c r="R304">
-        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 303 - 1), NA())</f>
+        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 303 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="305">
       <c r="P305" s="2">
-        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 304 - 1), NA())</f>
+        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 304 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q305">
-        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 304 - 1), NA())</f>
+        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 304 - 1), NA())</f>
         <v/>
       </c>
       <c r="R305">
-        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 304 - 1), NA())</f>
+        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 304 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="306">
       <c r="P306" s="2">
-        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 305 - 1), NA())</f>
+        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 305 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q306">
-        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 305 - 1), NA())</f>
+        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 305 - 1), NA())</f>
         <v/>
       </c>
       <c r="R306">
-        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 305 - 1), NA())</f>
+        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 305 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="307">
       <c r="P307" s="2">
-        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 306 - 1), NA())</f>
+        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 306 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q307">
-        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 306 - 1), NA())</f>
+        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 306 - 1), NA())</f>
         <v/>
       </c>
       <c r="R307">
-        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 306 - 1), NA())</f>
+        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 306 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="308">
       <c r="P308" s="2">
-        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 307 - 1), NA())</f>
+        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 307 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q308">
-        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 307 - 1), NA())</f>
+        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 307 - 1), NA())</f>
         <v/>
       </c>
       <c r="R308">
-        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 307 - 1), NA())</f>
+        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 307 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="309">
       <c r="P309" s="2">
-        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 308 - 1), NA())</f>
+        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 308 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q309">
-        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 308 - 1), NA())</f>
+        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 308 - 1), NA())</f>
         <v/>
       </c>
       <c r="R309">
-        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 308 - 1), NA())</f>
+        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 308 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="310">
       <c r="P310" s="2">
-        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 309 - 1), NA())</f>
+        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 309 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q310">
-        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 309 - 1), NA())</f>
+        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 309 - 1), NA())</f>
         <v/>
       </c>
       <c r="R310">
-        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 309 - 1), NA())</f>
+        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 309 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="311">
       <c r="P311" s="2">
-        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 310 - 1), NA())</f>
+        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 310 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q311">
-        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 310 - 1), NA())</f>
+        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 310 - 1), NA())</f>
         <v/>
       </c>
       <c r="R311">
-        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 310 - 1), NA())</f>
+        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 310 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="312">
       <c r="P312" s="2">
-        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 311 - 1), NA())</f>
+        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 311 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q312">
-        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 311 - 1), NA())</f>
+        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 311 - 1), NA())</f>
         <v/>
       </c>
       <c r="R312">
-        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 311 - 1), NA())</f>
+        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 311 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="313">
       <c r="P313" s="2">
-        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 312 - 1), NA())</f>
+        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 312 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q313">
-        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 312 - 1), NA())</f>
+        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 312 - 1), NA())</f>
         <v/>
       </c>
       <c r="R313">
-        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 312 - 1), NA())</f>
+        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 312 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="314">
       <c r="P314" s="2">
-        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 313 - 1), NA())</f>
+        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 313 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q314">
-        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 313 - 1), NA())</f>
+        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 313 - 1), NA())</f>
         <v/>
       </c>
       <c r="R314">
-        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 313 - 1), NA())</f>
+        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 313 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="315">
       <c r="P315" s="2">
-        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 314 - 1), NA())</f>
+        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 314 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q315">
-        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 314 - 1), NA())</f>
+        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 314 - 1), NA())</f>
         <v/>
       </c>
       <c r="R315">
-        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 314 - 1), NA())</f>
+        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 314 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="316">
       <c r="P316" s="2">
-        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 315 - 1), NA())</f>
+        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 315 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q316">
-        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 315 - 1), NA())</f>
+        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 315 - 1), NA())</f>
         <v/>
       </c>
       <c r="R316">
-        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 315 - 1), NA())</f>
+        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 315 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="317">
       <c r="P317" s="2">
-        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 316 - 1), NA())</f>
+        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 316 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q317">
-        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 316 - 1), NA())</f>
+        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 316 - 1), NA())</f>
         <v/>
       </c>
       <c r="R317">
-        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 316 - 1), NA())</f>
+        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 316 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="318">
       <c r="P318" s="2">
-        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 317 - 1), NA())</f>
+        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 317 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q318">
-        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 317 - 1), NA())</f>
+        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 317 - 1), NA())</f>
         <v/>
       </c>
       <c r="R318">
-        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 317 - 1), NA())</f>
+        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 317 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="319">
       <c r="P319" s="2">
-        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 318 - 1), NA())</f>
+        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 318 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q319">
-        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 318 - 1), NA())</f>
+        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 318 - 1), NA())</f>
         <v/>
       </c>
       <c r="R319">
-        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 318 - 1), NA())</f>
+        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 318 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="320">
       <c r="P320" s="2">
-        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 319 - 1), NA())</f>
+        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 319 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q320">
-        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 319 - 1), NA())</f>
+        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 319 - 1), NA())</f>
         <v/>
       </c>
       <c r="R320">
-        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 319 - 1), NA())</f>
+        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 319 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="321">
       <c r="P321" s="2">
-        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 320 - 1), NA())</f>
+        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 320 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q321">
-        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 320 - 1), NA())</f>
+        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 320 - 1), NA())</f>
         <v/>
       </c>
       <c r="R321">
-        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 320 - 1), NA())</f>
+        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 320 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="322">
       <c r="P322" s="2">
-        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 321 - 1), NA())</f>
+        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 321 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q322">
-        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 321 - 1), NA())</f>
+        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 321 - 1), NA())</f>
         <v/>
       </c>
       <c r="R322">
-        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 321 - 1), NA())</f>
+        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 321 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="323">
       <c r="P323" s="2">
-        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 322 - 1), NA())</f>
+        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 322 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q323">
-        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 322 - 1), NA())</f>
+        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 322 - 1), NA())</f>
         <v/>
       </c>
       <c r="R323">
-        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 322 - 1), NA())</f>
+        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 322 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="324">
       <c r="P324" s="2">
-        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 323 - 1), NA())</f>
+        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 323 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q324">
-        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 323 - 1), NA())</f>
+        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 323 - 1), NA())</f>
         <v/>
       </c>
       <c r="R324">
-        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 323 - 1), NA())</f>
+        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 323 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="325">
       <c r="P325" s="2">
-        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 324 - 1), NA())</f>
+        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 324 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q325">
-        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 324 - 1), NA())</f>
+        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 324 - 1), NA())</f>
         <v/>
       </c>
       <c r="R325">
-        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 324 - 1), NA())</f>
+        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 324 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="326">
       <c r="P326" s="2">
-        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 325 - 1), NA())</f>
+        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 325 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q326">
-        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 325 - 1), NA())</f>
+        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 325 - 1), NA())</f>
         <v/>
       </c>
       <c r="R326">
-        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 325 - 1), NA())</f>
+        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 325 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="327">
       <c r="P327" s="2">
-        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 326 - 1), NA())</f>
+        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 326 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q327">
-        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 326 - 1), NA())</f>
+        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 326 - 1), NA())</f>
         <v/>
       </c>
       <c r="R327">
-        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 326 - 1), NA())</f>
+        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 326 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="328">
       <c r="P328" s="2">
-        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 327 - 1), NA())</f>
+        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 327 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q328">
-        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 327 - 1), NA())</f>
+        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 327 - 1), NA())</f>
         <v/>
       </c>
       <c r="R328">
-        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 327 - 1), NA())</f>
+        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 327 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="329">
       <c r="P329" s="2">
-        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 328 - 1), NA())</f>
+        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 328 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q329">
-        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 328 - 1), NA())</f>
+        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 328 - 1), NA())</f>
         <v/>
       </c>
       <c r="R329">
-        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 328 - 1), NA())</f>
+        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 328 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="330">
       <c r="P330" s="2">
-        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 329 - 1), NA())</f>
+        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 329 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q330">
-        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 329 - 1), NA())</f>
+        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 329 - 1), NA())</f>
         <v/>
       </c>
       <c r="R330">
-        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 329 - 1), NA())</f>
+        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 329 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="331">
       <c r="P331" s="2">
-        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 330 - 1), NA())</f>
+        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 330 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q331">
-        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 330 - 1), NA())</f>
+        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 330 - 1), NA())</f>
         <v/>
       </c>
       <c r="R331">
-        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 330 - 1), NA())</f>
+        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 330 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="332">
       <c r="P332" s="2">
-        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 331 - 1), NA())</f>
+        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 331 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q332">
-        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 331 - 1), NA())</f>
+        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 331 - 1), NA())</f>
         <v/>
       </c>
       <c r="R332">
-        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 331 - 1), NA())</f>
+        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 331 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="333">
       <c r="P333" s="2">
-        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 332 - 1), NA())</f>
+        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 332 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q333">
-        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 332 - 1), NA())</f>
+        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 332 - 1), NA())</f>
         <v/>
       </c>
       <c r="R333">
-        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 332 - 1), NA())</f>
+        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 332 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="334">
       <c r="P334" s="2">
-        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 333 - 1), NA())</f>
+        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 333 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q334">
-        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 333 - 1), NA())</f>
+        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 333 - 1), NA())</f>
         <v/>
       </c>
       <c r="R334">
-        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 333 - 1), NA())</f>
+        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 333 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="335">
       <c r="P335" s="2">
-        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 334 - 1), NA())</f>
+        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 334 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q335">
-        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 334 - 1), NA())</f>
+        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 334 - 1), NA())</f>
         <v/>
       </c>
       <c r="R335">
-        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 334 - 1), NA())</f>
+        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 334 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="336">
       <c r="P336" s="2">
-        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 335 - 1), NA())</f>
+        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 335 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q336">
-        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 335 - 1), NA())</f>
+        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 335 - 1), NA())</f>
         <v/>
       </c>
       <c r="R336">
-        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 335 - 1), NA())</f>
+        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 335 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="337">
       <c r="P337" s="2">
-        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 336 - 1), NA())</f>
+        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 336 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q337">
-        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 336 - 1), NA())</f>
+        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 336 - 1), NA())</f>
         <v/>
       </c>
       <c r="R337">
-        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 336 - 1), NA())</f>
+        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 336 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="338">
       <c r="P338" s="2">
-        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 337 - 1), NA())</f>
+        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 337 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q338">
-        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 337 - 1), NA())</f>
+        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 337 - 1), NA())</f>
         <v/>
       </c>
       <c r="R338">
-        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 337 - 1), NA())</f>
+        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 337 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="339">
       <c r="P339" s="2">
-        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 338 - 1), NA())</f>
+        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 338 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q339">
-        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 338 - 1), NA())</f>
+        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 338 - 1), NA())</f>
         <v/>
       </c>
       <c r="R339">
-        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 338 - 1), NA())</f>
+        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 338 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="340">
       <c r="P340" s="2">
-        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 339 - 1), NA())</f>
+        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 339 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q340">
-        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 339 - 1), NA())</f>
+        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 339 - 1), NA())</f>
         <v/>
       </c>
       <c r="R340">
-        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 339 - 1), NA())</f>
+        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 339 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="341">
       <c r="P341" s="2">
-        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 340 - 1), NA())</f>
+        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 340 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q341">
-        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 340 - 1), NA())</f>
+        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 340 - 1), NA())</f>
         <v/>
       </c>
       <c r="R341">
-        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 340 - 1), NA())</f>
+        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 340 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="342">
       <c r="P342" s="2">
-        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 341 - 1), NA())</f>
+        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 341 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q342">
-        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 341 - 1), NA())</f>
+        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 341 - 1), NA())</f>
         <v/>
       </c>
       <c r="R342">
-        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 341 - 1), NA())</f>
+        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 341 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="343">
       <c r="P343" s="2">
-        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 342 - 1), NA())</f>
+        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 342 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q343">
-        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 342 - 1), NA())</f>
+        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 342 - 1), NA())</f>
         <v/>
       </c>
       <c r="R343">
-        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 342 - 1), NA())</f>
+        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 342 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="344">
       <c r="P344" s="2">
-        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 343 - 1), NA())</f>
+        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 343 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q344">
-        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 343 - 1), NA())</f>
+        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 343 - 1), NA())</f>
         <v/>
       </c>
       <c r="R344">
-        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 343 - 1), NA())</f>
+        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 343 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="345">
       <c r="P345" s="2">
-        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 344 - 1), NA())</f>
+        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 344 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q345">
-        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 344 - 1), NA())</f>
+        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 344 - 1), NA())</f>
         <v/>
       </c>
       <c r="R345">
-        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 344 - 1), NA())</f>
+        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 344 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="346">
       <c r="P346" s="2">
-        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 345 - 1), NA())</f>
+        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 345 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q346">
-        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 345 - 1), NA())</f>
+        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 345 - 1), NA())</f>
         <v/>
       </c>
       <c r="R346">
-        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 345 - 1), NA())</f>
+        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 345 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="347">
       <c r="P347" s="2">
-        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 346 - 1), NA())</f>
+        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 346 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q347">
-        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 346 - 1), NA())</f>
+        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 346 - 1), NA())</f>
         <v/>
       </c>
       <c r="R347">
-        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 346 - 1), NA())</f>
+        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 346 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="348">
       <c r="P348" s="2">
-        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 347 - 1), NA())</f>
+        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 347 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q348">
-        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 347 - 1), NA())</f>
+        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 347 - 1), NA())</f>
         <v/>
       </c>
       <c r="R348">
-        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 347 - 1), NA())</f>
+        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 347 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="349">
       <c r="P349" s="2">
-        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 348 - 1), NA())</f>
+        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 348 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q349">
-        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 348 - 1), NA())</f>
+        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 348 - 1), NA())</f>
         <v/>
       </c>
       <c r="R349">
-        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 348 - 1), NA())</f>
+        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 348 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="350">
       <c r="P350" s="2">
-        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 349 - 1), NA())</f>
+        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 349 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q350">
-        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 349 - 1), NA())</f>
+        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 349 - 1), NA())</f>
         <v/>
       </c>
       <c r="R350">
-        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 349 - 1), NA())</f>
+        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 349 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="351">
       <c r="P351" s="2">
-        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 350 - 1), NA())</f>
+        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 350 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q351">
-        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 350 - 1), NA())</f>
+        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 350 - 1), NA())</f>
         <v/>
       </c>
       <c r="R351">
-        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 350 - 1), NA())</f>
+        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 350 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="352">
       <c r="P352" s="2">
-        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 351 - 1), NA())</f>
+        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 351 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q352">
-        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 351 - 1), NA())</f>
+        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 351 - 1), NA())</f>
         <v/>
       </c>
       <c r="R352">
-        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 351 - 1), NA())</f>
+        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 351 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="353">
       <c r="P353" s="2">
-        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 352 - 1), NA())</f>
+        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 352 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q353">
-        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 352 - 1), NA())</f>
+        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 352 - 1), NA())</f>
         <v/>
       </c>
       <c r="R353">
-        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 352 - 1), NA())</f>
+        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 352 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="354">
       <c r="P354" s="2">
-        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 353 - 1), NA())</f>
+        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 353 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q354">
-        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 353 - 1), NA())</f>
+        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 353 - 1), NA())</f>
         <v/>
       </c>
       <c r="R354">
-        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 353 - 1), NA())</f>
+        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 353 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="355">
       <c r="P355" s="2">
-        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 354 - 1), NA())</f>
+        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 354 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q355">
-        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 354 - 1), NA())</f>
+        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 354 - 1), NA())</f>
         <v/>
       </c>
       <c r="R355">
-        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 354 - 1), NA())</f>
+        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 354 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="356">
       <c r="P356" s="2">
-        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 355 - 1), NA())</f>
+        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 355 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q356">
-        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 355 - 1), NA())</f>
+        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 355 - 1), NA())</f>
         <v/>
       </c>
       <c r="R356">
-        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 355 - 1), NA())</f>
+        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 355 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="357">
       <c r="P357" s="2">
-        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 356 - 1), NA())</f>
+        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 356 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q357">
-        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 356 - 1), NA())</f>
+        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 356 - 1), NA())</f>
         <v/>
       </c>
       <c r="R357">
-        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 356 - 1), NA())</f>
+        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 356 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="358">
       <c r="P358" s="2">
-        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 357 - 1), NA())</f>
+        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 357 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q358">
-        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 357 - 1), NA())</f>
+        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 357 - 1), NA())</f>
         <v/>
       </c>
       <c r="R358">
-        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 357 - 1), NA())</f>
+        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 357 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="359">
       <c r="P359" s="2">
-        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 358 - 1), NA())</f>
+        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 358 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q359">
-        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 358 - 1), NA())</f>
+        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 358 - 1), NA())</f>
         <v/>
       </c>
       <c r="R359">
-        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 358 - 1), NA())</f>
+        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 358 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="360">
       <c r="P360" s="2">
-        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 359 - 1), NA())</f>
+        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 359 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q360">
-        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 359 - 1), NA())</f>
+        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 359 - 1), NA())</f>
         <v/>
       </c>
       <c r="R360">
-        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 359 - 1), NA())</f>
+        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 359 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="361">
       <c r="P361" s="2">
-        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 360 - 1), NA())</f>
+        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 360 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q361">
-        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 360 - 1), NA())</f>
+        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 360 - 1), NA())</f>
         <v/>
       </c>
       <c r="R361">
-        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 360 - 1), NA())</f>
+        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 360 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="362">
       <c r="P362" s="2">
-        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 361 - 1), NA())</f>
+        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 361 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q362">
-        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 361 - 1), NA())</f>
+        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 361 - 1), NA())</f>
         <v/>
       </c>
       <c r="R362">
-        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 361 - 1), NA())</f>
+        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 361 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="363">
       <c r="P363" s="2">
-        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 362 - 1), NA())</f>
+        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 362 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q363">
-        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 362 - 1), NA())</f>
+        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 362 - 1), NA())</f>
         <v/>
       </c>
       <c r="R363">
-        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 362 - 1), NA())</f>
+        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 362 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="364">
       <c r="P364" s="2">
-        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 363 - 1), NA())</f>
+        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 363 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q364">
-        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 363 - 1), NA())</f>
+        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 363 - 1), NA())</f>
         <v/>
       </c>
       <c r="R364">
-        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 363 - 1), NA())</f>
+        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 363 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="365">
       <c r="P365" s="2">
-        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 364 - 1), NA())</f>
+        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 364 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q365">
-        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 364 - 1), NA())</f>
+        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 364 - 1), NA())</f>
         <v/>
       </c>
       <c r="R365">
-        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 364 - 1), NA())</f>
+        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 364 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="366">
       <c r="P366" s="2">
-        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 365 - 1), NA())</f>
+        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 365 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q366">
-        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 365 - 1), NA())</f>
+        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 365 - 1), NA())</f>
         <v/>
       </c>
       <c r="R366">
-        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 365 - 1), NA())</f>
+        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 365 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="367">
       <c r="P367" s="2">
-        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 366 - 1), NA())</f>
+        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 366 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q367">
-        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 366 - 1), NA())</f>
+        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 366 - 1), NA())</f>
         <v/>
       </c>
       <c r="R367">
-        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 366 - 1), NA())</f>
+        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 366 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="368">
       <c r="P368" s="2">
-        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 367 - 1), NA())</f>
+        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 367 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q368">
-        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 367 - 1), NA())</f>
+        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 367 - 1), NA())</f>
         <v/>
       </c>
       <c r="R368">
-        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 367 - 1), NA())</f>
+        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 367 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="369">
       <c r="P369" s="2">
-        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 368 - 1), NA())</f>
+        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 368 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q369">
-        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 368 - 1), NA())</f>
+        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 368 - 1), NA())</f>
         <v/>
       </c>
       <c r="R369">
-        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 368 - 1), NA())</f>
+        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 368 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="370">
       <c r="P370" s="2">
-        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 369 - 1), NA())</f>
+        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 369 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q370">
-        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 369 - 1), NA())</f>
+        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 369 - 1), NA())</f>
         <v/>
       </c>
       <c r="R370">
-        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 369 - 1), NA())</f>
+        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 369 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="371">
       <c r="P371" s="2">
-        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 370 - 1), NA())</f>
+        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 370 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q371">
-        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 370 - 1), NA())</f>
+        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 370 - 1), NA())</f>
         <v/>
       </c>
       <c r="R371">
-        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 370 - 1), NA())</f>
+        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 370 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="372">
       <c r="P372" s="2">
-        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 371 - 1), NA())</f>
+        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 371 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q372">
-        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 371 - 1), NA())</f>
+        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 371 - 1), NA())</f>
         <v/>
       </c>
       <c r="R372">
-        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 371 - 1), NA())</f>
+        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 371 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="373">
       <c r="P373" s="2">
-        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 372 - 1), NA())</f>
+        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 372 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q373">
-        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 372 - 1), NA())</f>
+        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 372 - 1), NA())</f>
         <v/>
       </c>
       <c r="R373">
-        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 372 - 1), NA())</f>
+        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 372 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="374">
       <c r="P374" s="2">
-        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 373 - 1), NA())</f>
+        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 373 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q374">
-        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 373 - 1), NA())</f>
+        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 373 - 1), NA())</f>
         <v/>
       </c>
       <c r="R374">
-        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 373 - 1), NA())</f>
+        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 373 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="375">
       <c r="P375" s="2">
-        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 374 - 1), NA())</f>
+        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 374 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q375">
-        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 374 - 1), NA())</f>
+        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 374 - 1), NA())</f>
         <v/>
       </c>
       <c r="R375">
-        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 374 - 1), NA())</f>
+        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 374 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="376">
       <c r="P376" s="2">
-        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 375 - 1), NA())</f>
+        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 375 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q376">
-        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 375 - 1), NA())</f>
+        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 375 - 1), NA())</f>
         <v/>
       </c>
       <c r="R376">
-        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 375 - 1), NA())</f>
+        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 375 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="377">
       <c r="P377" s="2">
-        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 376 - 1), NA())</f>
+        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 376 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q377">
-        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 376 - 1), NA())</f>
+        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 376 - 1), NA())</f>
         <v/>
       </c>
       <c r="R377">
-        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 376 - 1), NA())</f>
+        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 376 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="378">
       <c r="P378" s="2">
-        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 377 - 1), NA())</f>
+        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 377 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q378">
-        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 377 - 1), NA())</f>
+        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 377 - 1), NA())</f>
         <v/>
       </c>
       <c r="R378">
-        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 377 - 1), NA())</f>
+        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 377 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="379">
       <c r="P379" s="2">
-        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 378 - 1), NA())</f>
+        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 378 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q379">
-        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 378 - 1), NA())</f>
+        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 378 - 1), NA())</f>
         <v/>
       </c>
       <c r="R379">
-        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 378 - 1), NA())</f>
+        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 378 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="380">
       <c r="P380" s="2">
-        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 379 - 1), NA())</f>
+        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 379 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q380">
-        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 379 - 1), NA())</f>
+        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 379 - 1), NA())</f>
         <v/>
       </c>
       <c r="R380">
-        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 379 - 1), NA())</f>
+        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 379 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="381">
       <c r="P381" s="2">
-        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 380 - 1), NA())</f>
+        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 380 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q381">
-        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 380 - 1), NA())</f>
+        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 380 - 1), NA())</f>
         <v/>
       </c>
       <c r="R381">
-        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 380 - 1), NA())</f>
+        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 380 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="382">
       <c r="P382" s="2">
-        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 381 - 1), NA())</f>
+        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 381 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q382">
-        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 381 - 1), NA())</f>
+        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 381 - 1), NA())</f>
         <v/>
       </c>
       <c r="R382">
-        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 381 - 1), NA())</f>
+        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 381 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="383">
       <c r="P383" s="2">
-        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 382 - 1), NA())</f>
+        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 382 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q383">
-        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 382 - 1), NA())</f>
+        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 382 - 1), NA())</f>
         <v/>
       </c>
       <c r="R383">
-        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 382 - 1), NA())</f>
+        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 382 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="384">
       <c r="P384" s="2">
-        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 383 - 1), NA())</f>
+        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 383 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q384">
-        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 383 - 1), NA())</f>
+        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 383 - 1), NA())</f>
         <v/>
       </c>
       <c r="R384">
-        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 383 - 1), NA())</f>
+        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 383 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="385">
       <c r="P385" s="2">
-        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 384 - 1), NA())</f>
+        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 384 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q385">
-        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 384 - 1), NA())</f>
+        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 384 - 1), NA())</f>
         <v/>
       </c>
       <c r="R385">
-        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 384 - 1), NA())</f>
+        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 384 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="386">
       <c r="P386" s="2">
-        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 385 - 1), NA())</f>
+        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 385 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q386">
-        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 385 - 1), NA())</f>
+        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 385 - 1), NA())</f>
         <v/>
       </c>
       <c r="R386">
-        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 385 - 1), NA())</f>
+        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 385 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="387">
       <c r="P387" s="2">
-        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 386 - 1), NA())</f>
+        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 386 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q387">
-        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 386 - 1), NA())</f>
+        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 386 - 1), NA())</f>
         <v/>
       </c>
       <c r="R387">
-        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 386 - 1), NA())</f>
+        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 386 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="388">
       <c r="P388" s="2">
-        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 387 - 1), NA())</f>
+        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 387 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q388">
-        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 387 - 1), NA())</f>
+        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 387 - 1), NA())</f>
         <v/>
       </c>
       <c r="R388">
-        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 387 - 1), NA())</f>
+        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 387 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="389">
       <c r="P389" s="2">
-        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 388 - 1), NA())</f>
+        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 388 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q389">
-        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 388 - 1), NA())</f>
+        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 388 - 1), NA())</f>
         <v/>
       </c>
       <c r="R389">
-        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 388 - 1), NA())</f>
+        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 388 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="390">
       <c r="P390" s="2">
-        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 389 - 1), NA())</f>
+        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 389 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q390">
-        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 389 - 1), NA())</f>
+        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 389 - 1), NA())</f>
         <v/>
       </c>
       <c r="R390">
-        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 389 - 1), NA())</f>
+        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 389 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="391">
       <c r="P391" s="2">
-        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 390 - 1), NA())</f>
+        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 390 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q391">
-        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 390 - 1), NA())</f>
+        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 390 - 1), NA())</f>
         <v/>
       </c>
       <c r="R391">
-        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 390 - 1), NA())</f>
+        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 390 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="392">
       <c r="P392" s="2">
-        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 391 - 1), NA())</f>
+        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 391 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q392">
-        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 391 - 1), NA())</f>
+        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 391 - 1), NA())</f>
         <v/>
       </c>
       <c r="R392">
-        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 391 - 1), NA())</f>
+        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 391 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="393">
       <c r="P393" s="2">
-        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 392 - 1), NA())</f>
+        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 392 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q393">
-        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 392 - 1), NA())</f>
+        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 392 - 1), NA())</f>
         <v/>
       </c>
       <c r="R393">
-        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 392 - 1), NA())</f>
+        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 392 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="394">
       <c r="P394" s="2">
-        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 393 - 1), NA())</f>
+        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 393 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q394">
-        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 393 - 1), NA())</f>
+        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 393 - 1), NA())</f>
         <v/>
       </c>
       <c r="R394">
-        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 393 - 1), NA())</f>
+        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 393 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="395">
       <c r="P395" s="2">
-        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 394 - 1), NA())</f>
+        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 394 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q395">
-        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 394 - 1), NA())</f>
+        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 394 - 1), NA())</f>
         <v/>
       </c>
       <c r="R395">
-        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 394 - 1), NA())</f>
+        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 394 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="396">
       <c r="P396" s="2">
-        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 395 - 1), NA())</f>
+        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 395 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q396">
-        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 395 - 1), NA())</f>
+        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 395 - 1), NA())</f>
         <v/>
       </c>
       <c r="R396">
-        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 395 - 1), NA())</f>
+        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 395 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="397">
       <c r="P397" s="2">
-        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 396 - 1), NA())</f>
+        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 396 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q397">
-        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 396 - 1), NA())</f>
+        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 396 - 1), NA())</f>
         <v/>
       </c>
       <c r="R397">
-        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 396 - 1), NA())</f>
+        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 396 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="398">
       <c r="P398" s="2">
-        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 397 - 1), NA())</f>
+        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 397 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q398">
-        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 397 - 1), NA())</f>
+        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 397 - 1), NA())</f>
         <v/>
       </c>
       <c r="R398">
-        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 397 - 1), NA())</f>
+        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 397 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="399">
       <c r="P399" s="2">
-        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 398 - 1), NA())</f>
+        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 398 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q399">
-        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 398 - 1), NA())</f>
+        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 398 - 1), NA())</f>
         <v/>
       </c>
       <c r="R399">
-        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 398 - 1), NA())</f>
+        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 398 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="400">
       <c r="P400" s="2">
-        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 399 - 1), NA())</f>
+        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 399 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q400">
-        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 399 - 1), NA())</f>
+        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 399 - 1), NA())</f>
         <v/>
       </c>
       <c r="R400">
-        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 399 - 1), NA())</f>
+        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 399 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="401">
       <c r="P401" s="2">
-        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 400 - 1), NA())</f>
+        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 400 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q401">
-        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 400 - 1), NA())</f>
+        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 400 - 1), NA())</f>
         <v/>
       </c>
       <c r="R401">
-        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 400 - 1), NA())</f>
+        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 400 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="402">
       <c r="P402" s="2">
-        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 401 - 1), NA())</f>
+        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 401 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q402">
-        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 401 - 1), NA())</f>
+        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 401 - 1), NA())</f>
         <v/>
       </c>
       <c r="R402">
-        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 401 - 1), NA())</f>
+        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 401 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="403">
       <c r="P403" s="2">
-        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 402 - 1), NA())</f>
+        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 402 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q403">
-        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 402 - 1), NA())</f>
+        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 402 - 1), NA())</f>
         <v/>
       </c>
       <c r="R403">
-        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 402 - 1), NA())</f>
+        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 402 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="404">
       <c r="P404" s="2">
-        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 403 - 1), NA())</f>
+        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 403 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q404">
-        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 403 - 1), NA())</f>
+        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 403 - 1), NA())</f>
         <v/>
       </c>
       <c r="R404">
-        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 403 - 1), NA())</f>
+        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 403 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="405">
       <c r="P405" s="2">
-        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 404 - 1), NA())</f>
+        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 404 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q405">
-        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 404 - 1), NA())</f>
+        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 404 - 1), NA())</f>
         <v/>
       </c>
       <c r="R405">
-        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 404 - 1), NA())</f>
+        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 404 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="406">
       <c r="P406" s="2">
-        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 405 - 1), NA())</f>
+        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 405 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q406">
-        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 405 - 1), NA())</f>
+        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 405 - 1), NA())</f>
         <v/>
       </c>
       <c r="R406">
-        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 405 - 1), NA())</f>
+        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 405 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="407">
       <c r="P407" s="2">
-        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 406 - 1), NA())</f>
+        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 406 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q407">
-        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 406 - 1), NA())</f>
+        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 406 - 1), NA())</f>
         <v/>
       </c>
       <c r="R407">
-        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 406 - 1), NA())</f>
+        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 406 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="408">
       <c r="P408" s="2">
-        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 407 - 1), NA())</f>
+        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 407 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q408">
-        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 407 - 1), NA())</f>
+        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 407 - 1), NA())</f>
         <v/>
       </c>
       <c r="R408">
-        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 407 - 1), NA())</f>
+        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 407 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="409">
       <c r="P409" s="2">
-        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 408 - 1), NA())</f>
+        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 408 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q409">
-        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 408 - 1), NA())</f>
+        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 408 - 1), NA())</f>
         <v/>
       </c>
       <c r="R409">
-        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 408 - 1), NA())</f>
+        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 408 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="410">
       <c r="P410" s="2">
-        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 409 - 1), NA())</f>
+        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 409 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q410">
-        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 409 - 1), NA())</f>
+        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 409 - 1), NA())</f>
         <v/>
       </c>
       <c r="R410">
-        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 409 - 1), NA())</f>
+        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 409 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="411">
       <c r="P411" s="2">
-        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 410 - 1), NA())</f>
+        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 410 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q411">
-        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 410 - 1), NA())</f>
+        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 410 - 1), NA())</f>
         <v/>
       </c>
       <c r="R411">
-        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 410 - 1), NA())</f>
+        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 410 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="412">
       <c r="P412" s="2">
-        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 411 - 1), NA())</f>
+        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 411 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q412">
-        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 411 - 1), NA())</f>
+        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 411 - 1), NA())</f>
         <v/>
       </c>
       <c r="R412">
-        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 411 - 1), NA())</f>
+        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 411 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="413">
       <c r="P413" s="2">
-        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 412 - 1), NA())</f>
+        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 412 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q413">
-        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 412 - 1), NA())</f>
+        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 412 - 1), NA())</f>
         <v/>
       </c>
       <c r="R413">
-        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 412 - 1), NA())</f>
+        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 412 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="414">
       <c r="P414" s="2">
-        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 413 - 1), NA())</f>
+        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 413 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q414">
-        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 413 - 1), NA())</f>
+        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 413 - 1), NA())</f>
         <v/>
       </c>
       <c r="R414">
-        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 413 - 1), NA())</f>
+        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 413 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="415">
       <c r="P415" s="2">
-        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 414 - 1), NA())</f>
+        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 414 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q415">
-        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 414 - 1), NA())</f>
+        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 414 - 1), NA())</f>
         <v/>
       </c>
       <c r="R415">
-        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 414 - 1), NA())</f>
+        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 414 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="416">
       <c r="P416" s="2">
-        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 415 - 1), NA())</f>
+        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 415 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q416">
-        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 415 - 1), NA())</f>
+        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 415 - 1), NA())</f>
         <v/>
       </c>
       <c r="R416">
-        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 415 - 1), NA())</f>
+        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 415 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="417">
       <c r="P417" s="2">
-        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 416 - 1), NA())</f>
+        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 416 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q417">
-        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 416 - 1), NA())</f>
+        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 416 - 1), NA())</f>
         <v/>
       </c>
       <c r="R417">
-        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 416 - 1), NA())</f>
+        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 416 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="418">
       <c r="P418" s="2">
-        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 417 - 1), NA())</f>
+        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 417 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q418">
-        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 417 - 1), NA())</f>
+        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 417 - 1), NA())</f>
         <v/>
       </c>
       <c r="R418">
-        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 417 - 1), NA())</f>
+        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 417 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="419">
       <c r="P419" s="2">
-        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 418 - 1), NA())</f>
+        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 418 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q419">
-        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 418 - 1), NA())</f>
+        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 418 - 1), NA())</f>
         <v/>
       </c>
       <c r="R419">
-        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 418 - 1), NA())</f>
+        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 418 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="420">
       <c r="P420" s="2">
-        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 419 - 1), NA())</f>
+        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 419 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q420">
-        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 419 - 1), NA())</f>
+        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 419 - 1), NA())</f>
         <v/>
       </c>
       <c r="R420">
-        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 419 - 1), NA())</f>
+        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 419 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="421">
       <c r="P421" s="2">
-        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 420 - 1), NA())</f>
+        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 420 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q421">
-        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 420 - 1), NA())</f>
+        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 420 - 1), NA())</f>
         <v/>
       </c>
       <c r="R421">
-        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 420 - 1), NA())</f>
+        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 420 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="422">
       <c r="P422" s="2">
-        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 421 - 1), NA())</f>
+        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 421 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q422">
-        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 421 - 1), NA())</f>
+        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 421 - 1), NA())</f>
         <v/>
       </c>
       <c r="R422">
-        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 421 - 1), NA())</f>
+        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 421 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="423">
       <c r="P423" s="2">
-        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 422 - 1), NA())</f>
+        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 422 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q423">
-        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 422 - 1), NA())</f>
+        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 422 - 1), NA())</f>
         <v/>
       </c>
       <c r="R423">
-        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 422 - 1), NA())</f>
+        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 422 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="424">
       <c r="P424" s="2">
-        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 423 - 1), NA())</f>
+        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 423 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q424">
-        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 423 - 1), NA())</f>
+        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 423 - 1), NA())</f>
         <v/>
       </c>
       <c r="R424">
-        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 423 - 1), NA())</f>
+        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 423 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="425">
       <c r="P425" s="2">
-        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 424 - 1), NA())</f>
+        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 424 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q425">
-        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 424 - 1), NA())</f>
+        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 424 - 1), NA())</f>
         <v/>
       </c>
       <c r="R425">
-        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 424 - 1), NA())</f>
+        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 424 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="426">
       <c r="P426" s="2">
-        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 425 - 1), NA())</f>
+        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 425 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q426">
-        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 425 - 1), NA())</f>
+        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 425 - 1), NA())</f>
         <v/>
       </c>
       <c r="R426">
-        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 425 - 1), NA())</f>
+        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 425 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="427">
       <c r="P427" s="2">
-        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 426 - 1), NA())</f>
+        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 426 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q427">
-        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 426 - 1), NA())</f>
+        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 426 - 1), NA())</f>
         <v/>
       </c>
       <c r="R427">
-        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 426 - 1), NA())</f>
+        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 426 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="428">
       <c r="P428" s="2">
-        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 427 - 1), NA())</f>
+        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 427 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q428">
-        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 427 - 1), NA())</f>
+        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 427 - 1), NA())</f>
         <v/>
       </c>
       <c r="R428">
-        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 427 - 1), NA())</f>
+        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 427 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="429">
       <c r="P429" s="2">
-        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 428 - 1), NA())</f>
+        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 428 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q429">
-        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 428 - 1), NA())</f>
+        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 428 - 1), NA())</f>
         <v/>
       </c>
       <c r="R429">
-        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 428 - 1), NA())</f>
+        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 428 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="430">
       <c r="P430" s="2">
-        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 429 - 1), NA())</f>
+        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 429 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q430">
-        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 429 - 1), NA())</f>
+        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 429 - 1), NA())</f>
         <v/>
       </c>
       <c r="R430">
-        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 429 - 1), NA())</f>
+        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 429 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="431">
       <c r="P431" s="2">
-        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 430 - 1), NA())</f>
+        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 430 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q431">
-        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 430 - 1), NA())</f>
+        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 430 - 1), NA())</f>
         <v/>
       </c>
       <c r="R431">
-        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 430 - 1), NA())</f>
+        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 430 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="432">
       <c r="P432" s="2">
-        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 431 - 1), NA())</f>
+        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 431 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q432">
-        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 431 - 1), NA())</f>
+        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 431 - 1), NA())</f>
         <v/>
       </c>
       <c r="R432">
-        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 431 - 1), NA())</f>
+        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 431 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="433">
       <c r="P433" s="2">
-        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 432 - 1), NA())</f>
+        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 432 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q433">
-        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 432 - 1), NA())</f>
+        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 432 - 1), NA())</f>
         <v/>
       </c>
       <c r="R433">
-        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 432 - 1), NA())</f>
+        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 432 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="434">
       <c r="P434" s="2">
-        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 433 - 1), NA())</f>
+        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 433 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q434">
-        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 433 - 1), NA())</f>
+        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 433 - 1), NA())</f>
         <v/>
       </c>
       <c r="R434">
-        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 433 - 1), NA())</f>
+        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 433 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="435">
       <c r="P435" s="2">
-        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 434 - 1), NA())</f>
+        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 434 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q435">
-        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 434 - 1), NA())</f>
+        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 434 - 1), NA())</f>
         <v/>
       </c>
       <c r="R435">
-        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 434 - 1), NA())</f>
+        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 434 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="436">
       <c r="P436" s="2">
-        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 435 - 1), NA())</f>
+        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 435 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q436">
-        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 435 - 1), NA())</f>
+        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 435 - 1), NA())</f>
         <v/>
       </c>
       <c r="R436">
-        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 435 - 1), NA())</f>
+        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 435 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="437">
       <c r="P437" s="2">
-        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 436 - 1), NA())</f>
+        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 436 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q437">
-        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 436 - 1), NA())</f>
+        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 436 - 1), NA())</f>
         <v/>
       </c>
       <c r="R437">
-        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 436 - 1), NA())</f>
+        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 436 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="438">
       <c r="P438" s="2">
-        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 437 - 1), NA())</f>
+        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 437 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q438">
-        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 437 - 1), NA())</f>
+        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 437 - 1), NA())</f>
         <v/>
       </c>
       <c r="R438">
-        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 437 - 1), NA())</f>
+        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 437 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="439">
       <c r="P439" s="2">
-        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 438 - 1), NA())</f>
+        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 438 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q439">
-        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 438 - 1), NA())</f>
+        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 438 - 1), NA())</f>
         <v/>
       </c>
       <c r="R439">
-        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 438 - 1), NA())</f>
+        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 438 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="440">
       <c r="P440" s="2">
-        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 439 - 1), NA())</f>
+        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 439 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q440">
-        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 439 - 1), NA())</f>
+        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 439 - 1), NA())</f>
         <v/>
       </c>
       <c r="R440">
-        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 439 - 1), NA())</f>
+        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 439 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="441">
       <c r="P441" s="2">
-        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 440 - 1), NA())</f>
+        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 440 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q441">
-        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 440 - 1), NA())</f>
+        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 440 - 1), NA())</f>
         <v/>
       </c>
       <c r="R441">
-        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 440 - 1), NA())</f>
+        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 440 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="442">
       <c r="P442" s="2">
-        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 441 - 1), NA())</f>
+        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 441 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q442">
-        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 441 - 1), NA())</f>
+        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 441 - 1), NA())</f>
         <v/>
       </c>
       <c r="R442">
-        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 441 - 1), NA())</f>
+        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 441 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="443">
       <c r="P443" s="2">
-        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 442 - 1), NA())</f>
+        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 442 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q443">
-        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 442 - 1), NA())</f>
+        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 442 - 1), NA())</f>
         <v/>
       </c>
       <c r="R443">
-        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 442 - 1), NA())</f>
+        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 442 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="444">
       <c r="P444" s="2">
-        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 443 - 1), NA())</f>
+        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 443 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q444">
-        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 443 - 1), NA())</f>
+        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 443 - 1), NA())</f>
         <v/>
       </c>
       <c r="R444">
-        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 443 - 1), NA())</f>
+        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 443 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="445">
       <c r="P445" s="2">
-        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 444 - 1), NA())</f>
+        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 444 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q445">
-        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 444 - 1), NA())</f>
+        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 444 - 1), NA())</f>
         <v/>
       </c>
       <c r="R445">
-        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 444 - 1), NA())</f>
+        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 444 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="446">
       <c r="P446" s="2">
-        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 445 - 1), NA())</f>
+        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 445 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q446">
-        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 445 - 1), NA())</f>
+        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 445 - 1), NA())</f>
         <v/>
       </c>
       <c r="R446">
-        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 445 - 1), NA())</f>
+        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 445 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="447">
       <c r="P447" s="2">
-        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 446 - 1), NA())</f>
+        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 446 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q447">
-        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 446 - 1), NA())</f>
+        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 446 - 1), NA())</f>
         <v/>
       </c>
       <c r="R447">
-        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 446 - 1), NA())</f>
+        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 446 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="448">
       <c r="P448" s="2">
-        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 447 - 1), NA())</f>
+        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 447 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q448">
-        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 447 - 1), NA())</f>
+        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 447 - 1), NA())</f>
         <v/>
       </c>
       <c r="R448">
-        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 447 - 1), NA())</f>
+        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 447 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="449">
       <c r="P449" s="2">
-        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 448 - 1), NA())</f>
+        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 448 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q449">
-        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 448 - 1), NA())</f>
+        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 448 - 1), NA())</f>
         <v/>
       </c>
       <c r="R449">
-        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 448 - 1), NA())</f>
+        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 448 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="450">
       <c r="P450" s="2">
-        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 449 - 1), NA())</f>
+        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 449 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q450">
-        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 449 - 1), NA())</f>
+        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 449 - 1), NA())</f>
         <v/>
       </c>
       <c r="R450">
-        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 449 - 1), NA())</f>
+        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 449 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="451">
       <c r="P451" s="2">
-        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 450 - 1), NA())</f>
+        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 450 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q451">
-        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 450 - 1), NA())</f>
+        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 450 - 1), NA())</f>
         <v/>
       </c>
       <c r="R451">
-        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 450 - 1), NA())</f>
+        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 450 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="452">
       <c r="P452" s="2">
-        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 451 - 1), NA())</f>
+        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 451 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q452">
-        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 451 - 1), NA())</f>
+        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 451 - 1), NA())</f>
         <v/>
       </c>
       <c r="R452">
-        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 451 - 1), NA())</f>
+        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 451 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="453">
       <c r="P453" s="2">
-        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 452 - 1), NA())</f>
+        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 452 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q453">
-        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 452 - 1), NA())</f>
+        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 452 - 1), NA())</f>
         <v/>
       </c>
       <c r="R453">
-        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 452 - 1), NA())</f>
+        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 452 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="454">
       <c r="P454" s="2">
-        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 453 - 1), NA())</f>
+        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 453 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q454">
-        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 453 - 1), NA())</f>
+        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 453 - 1), NA())</f>
         <v/>
       </c>
       <c r="R454">
-        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 453 - 1), NA())</f>
+        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 453 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="455">
       <c r="P455" s="2">
-        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 454 - 1), NA())</f>
+        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 454 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q455">
-        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 454 - 1), NA())</f>
+        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 454 - 1), NA())</f>
         <v/>
       </c>
       <c r="R455">
-        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 454 - 1), NA())</f>
+        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 454 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="456">
       <c r="P456" s="2">
-        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 455 - 1), NA())</f>
+        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 455 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q456">
-        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 455 - 1), NA())</f>
+        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 455 - 1), NA())</f>
         <v/>
       </c>
       <c r="R456">
-        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 455 - 1), NA())</f>
+        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 455 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="457">
       <c r="P457" s="2">
-        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 456 - 1), NA())</f>
+        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 456 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q457">
-        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 456 - 1), NA())</f>
+        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 456 - 1), NA())</f>
         <v/>
       </c>
       <c r="R457">
-        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 456 - 1), NA())</f>
+        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 456 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="458">
       <c r="P458" s="2">
-        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 457 - 1), NA())</f>
+        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 457 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q458">
-        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 457 - 1), NA())</f>
+        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 457 - 1), NA())</f>
         <v/>
       </c>
       <c r="R458">
-        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 457 - 1), NA())</f>
+        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 457 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="459">
       <c r="P459" s="2">
-        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 458 - 1), NA())</f>
+        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 458 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q459">
-        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 458 - 1), NA())</f>
+        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 458 - 1), NA())</f>
         <v/>
       </c>
       <c r="R459">
-        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 458 - 1), NA())</f>
+        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 458 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="460">
       <c r="P460" s="2">
-        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 459 - 1), NA())</f>
+        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 459 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q460">
-        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 459 - 1), NA())</f>
+        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 459 - 1), NA())</f>
         <v/>
       </c>
       <c r="R460">
-        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 459 - 1), NA())</f>
+        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 459 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="461">
       <c r="P461" s="2">
-        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 460 - 1), NA())</f>
+        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 460 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q461">
-        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 460 - 1), NA())</f>
+        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 460 - 1), NA())</f>
         <v/>
       </c>
       <c r="R461">
-        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 460 - 1), NA())</f>
+        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 460 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="462">
       <c r="P462" s="2">
-        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 461 - 1), NA())</f>
+        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 461 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q462">
-        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 461 - 1), NA())</f>
+        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 461 - 1), NA())</f>
         <v/>
       </c>
       <c r="R462">
-        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 461 - 1), NA())</f>
+        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 461 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="463">
       <c r="P463" s="2">
-        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 462 - 1), NA())</f>
+        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 462 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q463">
-        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 462 - 1), NA())</f>
+        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 462 - 1), NA())</f>
         <v/>
       </c>
       <c r="R463">
-        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 462 - 1), NA())</f>
+        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 462 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="464">
       <c r="P464" s="2">
-        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 463 - 1), NA())</f>
+        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 463 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q464">
-        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 463 - 1), NA())</f>
+        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 463 - 1), NA())</f>
         <v/>
       </c>
       <c r="R464">
-        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 463 - 1), NA())</f>
+        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 463 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="465">
       <c r="P465" s="2">
-        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 464 - 1), NA())</f>
+        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 464 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q465">
-        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 464 - 1), NA())</f>
+        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 464 - 1), NA())</f>
         <v/>
       </c>
       <c r="R465">
-        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 464 - 1), NA())</f>
+        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 464 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="466">
       <c r="P466" s="2">
-        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 465 - 1), NA())</f>
+        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 465 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q466">
-        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 465 - 1), NA())</f>
+        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 465 - 1), NA())</f>
         <v/>
       </c>
       <c r="R466">
-        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 465 - 1), NA())</f>
+        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 465 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="467">
       <c r="P467" s="2">
-        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 466 - 1), NA())</f>
+        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 466 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q467">
-        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 466 - 1), NA())</f>
+        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 466 - 1), NA())</f>
         <v/>
       </c>
       <c r="R467">
-        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 466 - 1), NA())</f>
+        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 466 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="468">
       <c r="P468" s="2">
-        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 467 - 1), NA())</f>
+        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 467 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q468">
-        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 467 - 1), NA())</f>
+        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 467 - 1), NA())</f>
         <v/>
       </c>
       <c r="R468">
-        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 467 - 1), NA())</f>
+        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 467 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="469">
       <c r="P469" s="2">
-        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 468 - 1), NA())</f>
+        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 468 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q469">
-        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 468 - 1), NA())</f>
+        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 468 - 1), NA())</f>
         <v/>
       </c>
       <c r="R469">
-        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 468 - 1), NA())</f>
+        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 468 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="470">
       <c r="P470" s="2">
-        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 469 - 1), NA())</f>
+        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 469 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q470">
-        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 469 - 1), NA())</f>
+        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 469 - 1), NA())</f>
         <v/>
       </c>
       <c r="R470">
-        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 469 - 1), NA())</f>
+        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 469 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="471">
       <c r="P471" s="2">
-        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 470 - 1), NA())</f>
+        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 470 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q471">
-        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 470 - 1), NA())</f>
+        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 470 - 1), NA())</f>
         <v/>
       </c>
       <c r="R471">
-        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 470 - 1), NA())</f>
+        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 470 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="472">
       <c r="P472" s="2">
-        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 471 - 1), NA())</f>
+        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 471 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q472">
-        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 471 - 1), NA())</f>
+        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 471 - 1), NA())</f>
         <v/>
       </c>
       <c r="R472">
-        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 471 - 1), NA())</f>
+        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 471 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="473">
       <c r="P473" s="2">
-        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 472 - 1), NA())</f>
+        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 472 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q473">
-        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 472 - 1), NA())</f>
+        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 472 - 1), NA())</f>
         <v/>
       </c>
       <c r="R473">
-        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 472 - 1), NA())</f>
+        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 472 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="474">
       <c r="P474" s="2">
-        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 473 - 1), NA())</f>
+        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 473 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q474">
-        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 473 - 1), NA())</f>
+        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 473 - 1), NA())</f>
         <v/>
       </c>
       <c r="R474">
-        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 473 - 1), NA())</f>
+        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 473 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="475">
       <c r="P475" s="2">
-        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 474 - 1), NA())</f>
+        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 474 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q475">
-        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 474 - 1), NA())</f>
+        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 474 - 1), NA())</f>
         <v/>
       </c>
       <c r="R475">
-        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 474 - 1), NA())</f>
+        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 474 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="476">
       <c r="P476" s="2">
-        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 475 - 1), NA())</f>
+        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 475 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q476">
-        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 475 - 1), NA())</f>
+        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 475 - 1), NA())</f>
         <v/>
       </c>
       <c r="R476">
-        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 475 - 1), NA())</f>
+        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 475 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="477">
       <c r="P477" s="2">
-        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 476 - 1), NA())</f>
+        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 476 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q477">
-        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 476 - 1), NA())</f>
+        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 476 - 1), NA())</f>
         <v/>
       </c>
       <c r="R477">
-        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 476 - 1), NA())</f>
+        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 476 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="478">
       <c r="P478" s="2">
-        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 477 - 1), NA())</f>
+        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 477 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q478">
-        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 477 - 1), NA())</f>
+        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 477 - 1), NA())</f>
         <v/>
       </c>
       <c r="R478">
-        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 477 - 1), NA())</f>
+        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 477 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="479">
       <c r="P479" s="2">
-        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 478 - 1), NA())</f>
+        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 478 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q479">
-        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 478 - 1), NA())</f>
+        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 478 - 1), NA())</f>
         <v/>
       </c>
       <c r="R479">
-        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 478 - 1), NA())</f>
+        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 478 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="480">
       <c r="P480" s="2">
-        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 479 - 1), NA())</f>
+        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 479 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q480">
-        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 479 - 1), NA())</f>
+        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 479 - 1), NA())</f>
         <v/>
       </c>
       <c r="R480">
-        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 479 - 1), NA())</f>
+        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 479 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="481">
       <c r="P481" s="2">
-        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 480 - 1), NA())</f>
+        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 480 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q481">
-        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 480 - 1), NA())</f>
+        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 480 - 1), NA())</f>
         <v/>
       </c>
       <c r="R481">
-        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 480 - 1), NA())</f>
+        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 480 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="482">
       <c r="P482" s="2">
-        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 481 - 1), NA())</f>
+        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 481 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q482">
-        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 481 - 1), NA())</f>
+        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 481 - 1), NA())</f>
         <v/>
       </c>
       <c r="R482">
-        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 481 - 1), NA())</f>
+        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 481 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="483">
       <c r="P483" s="2">
-        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 482 - 1), NA())</f>
+        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 482 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q483">
-        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 482 - 1), NA())</f>
+        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 482 - 1), NA())</f>
         <v/>
       </c>
       <c r="R483">
-        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 482 - 1), NA())</f>
+        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 482 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="484">
       <c r="P484" s="2">
-        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 483 - 1), NA())</f>
+        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 483 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q484">
-        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 483 - 1), NA())</f>
+        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 483 - 1), NA())</f>
         <v/>
       </c>
       <c r="R484">
-        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 483 - 1), NA())</f>
+        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 483 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="485">
       <c r="P485" s="2">
-        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 484 - 1), NA())</f>
+        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 484 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q485">
-        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 484 - 1), NA())</f>
+        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 484 - 1), NA())</f>
         <v/>
       </c>
       <c r="R485">
-        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 484 - 1), NA())</f>
+        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 484 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="486">
       <c r="P486" s="2">
-        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$486, $G$8 - 1 + 485 - 1), NA())</f>
+        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 485 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q486">
-        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$486, $G$8 - 1 + 485 - 1), NA())</f>
+        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 485 - 1), NA())</f>
         <v/>
       </c>
       <c r="R486">
-        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$486, $G$8 - 1 + 485 - 1), NA())</f>
+        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 485 - 1), NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="487">
+      <c r="P487" s="2">
+        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 486 - 1), NA())</f>
+        <v/>
+      </c>
+      <c r="Q487">
+        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 486 - 1), NA())</f>
+        <v/>
+      </c>
+      <c r="R487">
+        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 486 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -8050,7 +8064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H486"/>
+  <dimension ref="A1:H487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22625,16 +22639,16 @@
     </row>
     <row r="486" ht="20" customHeight="1">
       <c r="A486" s="14" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B486" s="15" t="n">
-        <v>4468.89990234375</v>
+        <v>4429.7998046875</v>
       </c>
       <c r="C486" s="15" t="n">
-        <v>67.05000305175781</v>
+        <v>66.0469970703125</v>
       </c>
       <c r="D486" s="15" t="n">
-        <v>3121.18994140625</v>
+        <v>3126.2900390625</v>
       </c>
       <c r="E486" s="16">
         <f>ROUND((B486/31.1034768)*D486, 2)</f>
@@ -22653,8 +22667,38 @@
         <v/>
       </c>
     </row>
+    <row r="487" ht="20" customHeight="1">
+      <c r="A487" s="18" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B487" s="19" t="n">
+        <v>4392.2998046875</v>
+      </c>
+      <c r="C487" s="19" t="n">
+        <v>66.47000122070312</v>
+      </c>
+      <c r="D487" s="19" t="n">
+        <v>3112.889892578125</v>
+      </c>
+      <c r="E487" s="20">
+        <f>ROUND((B487/31.1034768)*D487, 2)</f>
+        <v/>
+      </c>
+      <c r="F487" s="20">
+        <f>ROUND((C487/31.1034768)*D487, 2)</f>
+        <v/>
+      </c>
+      <c r="G487" s="21">
+        <f>IFERROR((E487-E486)/E486, 0)</f>
+        <v/>
+      </c>
+      <c r="H487" s="21">
+        <f>IFERROR((F487-F486)/F486, 0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H486"/>
+  <autoFilter ref="A1:H487"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Precios_Metales_COP.xlsx
+++ b/Precios_Metales_COP.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Precios Diarios" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Precios Diarios'!$A$1:$H$487</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Precios Diarios'!$A$1:$H$489</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -321,12 +321,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard y Gráficos'!$P$2:$P$487</f>
+              <f>'Dashboard y Gráficos'!$P$2:$P$489</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$Q$2:$Q$487</f>
+              <f>'Dashboard y Gráficos'!$Q$2:$Q$489</f>
             </numRef>
           </val>
         </ser>
@@ -446,12 +446,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard y Gráficos'!$P$2:$P$487</f>
+              <f>'Dashboard y Gráficos'!$P$2:$P$489</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$R$2:$R$487</f>
+              <f>'Dashboard y Gráficos'!$R$2:$R$489</f>
             </numRef>
           </val>
         </ser>
@@ -570,12 +570,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard y Gráficos'!$P$2:$P$487</f>
+              <f>'Dashboard y Gráficos'!$P$2:$P$489</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$Q$2:$Q$487</f>
+              <f>'Dashboard y Gráficos'!$Q$2:$Q$489</f>
             </numRef>
           </val>
         </ser>
@@ -610,7 +610,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$R$2:$R$487</f>
+              <f>'Dashboard y Gráficos'!$R$2:$R$489</f>
             </numRef>
           </val>
         </ser>
@@ -1074,7 +1074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R487"/>
+  <dimension ref="A1:R489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1118,15 +1118,15 @@
     </row>
     <row r="2">
       <c r="P2" s="2">
-        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 1 - 1), NA())</f>
+        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 1 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q2">
-        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 1 - 1), NA())</f>
+        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 1 - 1), NA())</f>
         <v/>
       </c>
       <c r="R2">
-        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 1 - 1), NA())</f>
+        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 1 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1166,58 +1166,58 @@
       </c>
       <c r="N3" s="4" t="n"/>
       <c r="P3" s="2">
-        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 2 - 1), NA())</f>
+        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 2 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q3">
-        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 2 - 1), NA())</f>
+        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 2 - 1), NA())</f>
         <v/>
       </c>
       <c r="R3">
-        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 2 - 1), NA())</f>
+        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 2 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5">
-        <f>'Precios Diarios'!A487</f>
+        <f>'Precios Diarios'!A489</f>
         <v/>
       </c>
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="6">
-        <f>'Precios Diarios'!E487</f>
+        <f>'Precios Diarios'!E489</f>
         <v/>
       </c>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="6">
-        <f>'Precios Diarios'!F487</f>
+        <f>'Precios Diarios'!F489</f>
         <v/>
       </c>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="6">
-        <f>'Precios Diarios'!D487</f>
+        <f>'Precios Diarios'!D489</f>
         <v/>
       </c>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="7">
-        <f>'Precios Diarios'!G487</f>
+        <f>'Precios Diarios'!G489</f>
         <v/>
       </c>
       <c r="N4" s="4" t="n"/>
       <c r="P4" s="2">
-        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 3 - 1), NA())</f>
+        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 3 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q4">
-        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 3 - 1), NA())</f>
+        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 3 - 1), NA())</f>
         <v/>
       </c>
       <c r="R4">
-        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 3 - 1), NA())</f>
+        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 3 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1237,29 +1237,29 @@
       <c r="M5" s="4" t="n"/>
       <c r="N5" s="4" t="n"/>
       <c r="P5" s="2">
-        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 4 - 1), NA())</f>
+        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 4 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q5">
-        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 4 - 1), NA())</f>
+        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 4 - 1), NA())</f>
         <v/>
       </c>
       <c r="R5">
-        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 4 - 1), NA())</f>
+        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 4 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="P6" s="2">
-        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 5 - 1), NA())</f>
+        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 5 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q6">
-        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 5 - 1), NA())</f>
+        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 5 - 1), NA())</f>
         <v/>
       </c>
       <c r="R6">
-        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 5 - 1), NA())</f>
+        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 5 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1270,15 +1270,15 @@
         </is>
       </c>
       <c r="P7" s="2">
-        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 6 - 1), NA())</f>
+        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 6 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q7">
-        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 6 - 1), NA())</f>
+        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 6 - 1), NA())</f>
         <v/>
       </c>
       <c r="R7">
-        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 6 - 1), NA())</f>
+        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 6 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1297,11 +1297,11 @@
         <v/>
       </c>
       <c r="G8" s="11">
-        <f>IFERROR(MATCH(E8, 'Precios Diarios'!$A$2:$A$487, 1), 1) + 1</f>
+        <f>IFERROR(MATCH(E8, 'Precios Diarios'!$A$2:$A$489, 1), 1) + 1</f>
         <v/>
       </c>
       <c r="H8" s="11">
-        <f>IFERROR(MATCH(F8, 'Precios Diarios'!$A$2:$A$487, 1), 486) + 1</f>
+        <f>IFERROR(MATCH(F8, 'Precios Diarios'!$A$2:$A$489, 1), 488) + 1</f>
         <v/>
       </c>
       <c r="I8" s="11">
@@ -1309,15 +1309,15 @@
         <v/>
       </c>
       <c r="P8" s="2">
-        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 7 - 1), NA())</f>
+        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 7 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q8">
-        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 7 - 1), NA())</f>
+        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 7 - 1), NA())</f>
         <v/>
       </c>
       <c r="R8">
-        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 7 - 1), NA())</f>
+        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 7 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1328,6707 +1328,6735 @@
         </is>
       </c>
       <c r="P9" s="2">
-        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 8 - 1), NA())</f>
+        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 8 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q9">
-        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 8 - 1), NA())</f>
+        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 8 - 1), NA())</f>
         <v/>
       </c>
       <c r="R9">
-        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 8 - 1), NA())</f>
+        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 8 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="P10" s="2">
-        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 9 - 1), NA())</f>
+        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 9 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q10">
-        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 9 - 1), NA())</f>
+        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 9 - 1), NA())</f>
         <v/>
       </c>
       <c r="R10">
-        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 9 - 1), NA())</f>
+        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 9 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="P11" s="2">
-        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 10 - 1), NA())</f>
+        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 10 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q11">
-        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 10 - 1), NA())</f>
+        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 10 - 1), NA())</f>
         <v/>
       </c>
       <c r="R11">
-        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 10 - 1), NA())</f>
+        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 10 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="P12" s="2">
-        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 11 - 1), NA())</f>
+        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 11 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q12">
-        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 11 - 1), NA())</f>
+        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 11 - 1), NA())</f>
         <v/>
       </c>
       <c r="R12">
-        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 11 - 1), NA())</f>
+        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 11 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="P13" s="2">
-        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 12 - 1), NA())</f>
+        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 12 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q13">
-        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 12 - 1), NA())</f>
+        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 12 - 1), NA())</f>
         <v/>
       </c>
       <c r="R13">
-        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 12 - 1), NA())</f>
+        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 12 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="P14" s="2">
-        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 13 - 1), NA())</f>
+        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 13 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q14">
-        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 13 - 1), NA())</f>
+        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 13 - 1), NA())</f>
         <v/>
       </c>
       <c r="R14">
-        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 13 - 1), NA())</f>
+        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 13 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="P15" s="2">
-        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 14 - 1), NA())</f>
+        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 14 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q15">
-        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 14 - 1), NA())</f>
+        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 14 - 1), NA())</f>
         <v/>
       </c>
       <c r="R15">
-        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 14 - 1), NA())</f>
+        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 14 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="P16" s="2">
-        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 15 - 1), NA())</f>
+        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 15 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q16">
-        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 15 - 1), NA())</f>
+        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 15 - 1), NA())</f>
         <v/>
       </c>
       <c r="R16">
-        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 15 - 1), NA())</f>
+        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 15 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="P17" s="2">
-        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 16 - 1), NA())</f>
+        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 16 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q17">
-        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 16 - 1), NA())</f>
+        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 16 - 1), NA())</f>
         <v/>
       </c>
       <c r="R17">
-        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 16 - 1), NA())</f>
+        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 16 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="P18" s="2">
-        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 17 - 1), NA())</f>
+        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 17 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q18">
-        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 17 - 1), NA())</f>
+        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 17 - 1), NA())</f>
         <v/>
       </c>
       <c r="R18">
-        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 17 - 1), NA())</f>
+        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 17 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="P19" s="2">
-        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 18 - 1), NA())</f>
+        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 18 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q19">
-        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 18 - 1), NA())</f>
+        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 18 - 1), NA())</f>
         <v/>
       </c>
       <c r="R19">
-        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 18 - 1), NA())</f>
+        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 18 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="P20" s="2">
-        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 19 - 1), NA())</f>
+        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 19 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q20">
-        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 19 - 1), NA())</f>
+        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 19 - 1), NA())</f>
         <v/>
       </c>
       <c r="R20">
-        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 19 - 1), NA())</f>
+        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 19 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="P21" s="2">
-        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 20 - 1), NA())</f>
+        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 20 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q21">
-        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 20 - 1), NA())</f>
+        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 20 - 1), NA())</f>
         <v/>
       </c>
       <c r="R21">
-        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 20 - 1), NA())</f>
+        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 20 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="P22" s="2">
-        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 21 - 1), NA())</f>
+        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 21 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q22">
-        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 21 - 1), NA())</f>
+        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 21 - 1), NA())</f>
         <v/>
       </c>
       <c r="R22">
-        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 21 - 1), NA())</f>
+        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 21 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="P23" s="2">
-        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 22 - 1), NA())</f>
+        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 22 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q23">
-        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 22 - 1), NA())</f>
+        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 22 - 1), NA())</f>
         <v/>
       </c>
       <c r="R23">
-        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 22 - 1), NA())</f>
+        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 22 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="P24" s="2">
-        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 23 - 1), NA())</f>
+        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 23 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q24">
-        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 23 - 1), NA())</f>
+        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 23 - 1), NA())</f>
         <v/>
       </c>
       <c r="R24">
-        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 23 - 1), NA())</f>
+        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 23 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="P25" s="2">
-        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 24 - 1), NA())</f>
+        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 24 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q25">
-        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 24 - 1), NA())</f>
+        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 24 - 1), NA())</f>
         <v/>
       </c>
       <c r="R25">
-        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 24 - 1), NA())</f>
+        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 24 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="P26" s="2">
-        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 25 - 1), NA())</f>
+        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 25 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q26">
-        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 25 - 1), NA())</f>
+        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 25 - 1), NA())</f>
         <v/>
       </c>
       <c r="R26">
-        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 25 - 1), NA())</f>
+        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 25 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="P27" s="2">
-        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 26 - 1), NA())</f>
+        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 26 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q27">
-        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 26 - 1), NA())</f>
+        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 26 - 1), NA())</f>
         <v/>
       </c>
       <c r="R27">
-        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 26 - 1), NA())</f>
+        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 26 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="P28" s="2">
-        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 27 - 1), NA())</f>
+        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 27 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q28">
-        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 27 - 1), NA())</f>
+        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 27 - 1), NA())</f>
         <v/>
       </c>
       <c r="R28">
-        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 27 - 1), NA())</f>
+        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 27 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="P29" s="2">
-        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 28 - 1), NA())</f>
+        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 28 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q29">
-        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 28 - 1), NA())</f>
+        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 28 - 1), NA())</f>
         <v/>
       </c>
       <c r="R29">
-        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 28 - 1), NA())</f>
+        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 28 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="P30" s="2">
-        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 29 - 1), NA())</f>
+        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 29 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q30">
-        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 29 - 1), NA())</f>
+        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 29 - 1), NA())</f>
         <v/>
       </c>
       <c r="R30">
-        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 29 - 1), NA())</f>
+        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 29 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="P31" s="2">
-        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 30 - 1), NA())</f>
+        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 30 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q31">
-        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 30 - 1), NA())</f>
+        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 30 - 1), NA())</f>
         <v/>
       </c>
       <c r="R31">
-        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 30 - 1), NA())</f>
+        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 30 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="P32" s="2">
-        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 31 - 1), NA())</f>
+        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 31 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q32">
-        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 31 - 1), NA())</f>
+        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 31 - 1), NA())</f>
         <v/>
       </c>
       <c r="R32">
-        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 31 - 1), NA())</f>
+        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 31 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="P33" s="2">
-        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 32 - 1), NA())</f>
+        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 32 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q33">
-        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 32 - 1), NA())</f>
+        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 32 - 1), NA())</f>
         <v/>
       </c>
       <c r="R33">
-        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 32 - 1), NA())</f>
+        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 32 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="P34" s="2">
-        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 33 - 1), NA())</f>
+        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 33 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q34">
-        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 33 - 1), NA())</f>
+        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 33 - 1), NA())</f>
         <v/>
       </c>
       <c r="R34">
-        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 33 - 1), NA())</f>
+        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 33 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="P35" s="2">
-        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 34 - 1), NA())</f>
+        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 34 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q35">
-        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 34 - 1), NA())</f>
+        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 34 - 1), NA())</f>
         <v/>
       </c>
       <c r="R35">
-        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 34 - 1), NA())</f>
+        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 34 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="P36" s="2">
-        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 35 - 1), NA())</f>
+        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 35 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q36">
-        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 35 - 1), NA())</f>
+        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 35 - 1), NA())</f>
         <v/>
       </c>
       <c r="R36">
-        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 35 - 1), NA())</f>
+        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 35 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="P37" s="2">
-        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 36 - 1), NA())</f>
+        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 36 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q37">
-        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 36 - 1), NA())</f>
+        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 36 - 1), NA())</f>
         <v/>
       </c>
       <c r="R37">
-        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 36 - 1), NA())</f>
+        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 36 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="P38" s="2">
-        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 37 - 1), NA())</f>
+        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 37 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q38">
-        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 37 - 1), NA())</f>
+        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 37 - 1), NA())</f>
         <v/>
       </c>
       <c r="R38">
-        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 37 - 1), NA())</f>
+        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 37 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="P39" s="2">
-        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 38 - 1), NA())</f>
+        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 38 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q39">
-        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 38 - 1), NA())</f>
+        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 38 - 1), NA())</f>
         <v/>
       </c>
       <c r="R39">
-        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 38 - 1), NA())</f>
+        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 38 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="P40" s="2">
-        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 39 - 1), NA())</f>
+        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 39 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q40">
-        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 39 - 1), NA())</f>
+        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 39 - 1), NA())</f>
         <v/>
       </c>
       <c r="R40">
-        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 39 - 1), NA())</f>
+        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 39 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="P41" s="2">
-        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 40 - 1), NA())</f>
+        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 40 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q41">
-        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 40 - 1), NA())</f>
+        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 40 - 1), NA())</f>
         <v/>
       </c>
       <c r="R41">
-        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 40 - 1), NA())</f>
+        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 40 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="P42" s="2">
-        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 41 - 1), NA())</f>
+        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 41 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q42">
-        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 41 - 1), NA())</f>
+        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 41 - 1), NA())</f>
         <v/>
       </c>
       <c r="R42">
-        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 41 - 1), NA())</f>
+        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 41 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="P43" s="2">
-        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 42 - 1), NA())</f>
+        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 42 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q43">
-        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 42 - 1), NA())</f>
+        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 42 - 1), NA())</f>
         <v/>
       </c>
       <c r="R43">
-        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 42 - 1), NA())</f>
+        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 42 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="P44" s="2">
-        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 43 - 1), NA())</f>
+        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 43 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q44">
-        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 43 - 1), NA())</f>
+        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 43 - 1), NA())</f>
         <v/>
       </c>
       <c r="R44">
-        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 43 - 1), NA())</f>
+        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 43 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="P45" s="2">
-        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 44 - 1), NA())</f>
+        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 44 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q45">
-        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 44 - 1), NA())</f>
+        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 44 - 1), NA())</f>
         <v/>
       </c>
       <c r="R45">
-        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 44 - 1), NA())</f>
+        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 44 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="P46" s="2">
-        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 45 - 1), NA())</f>
+        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 45 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q46">
-        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 45 - 1), NA())</f>
+        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 45 - 1), NA())</f>
         <v/>
       </c>
       <c r="R46">
-        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 45 - 1), NA())</f>
+        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 45 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="P47" s="2">
-        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 46 - 1), NA())</f>
+        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 46 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q47">
-        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 46 - 1), NA())</f>
+        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 46 - 1), NA())</f>
         <v/>
       </c>
       <c r="R47">
-        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 46 - 1), NA())</f>
+        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 46 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="P48" s="2">
-        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 47 - 1), NA())</f>
+        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 47 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q48">
-        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 47 - 1), NA())</f>
+        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 47 - 1), NA())</f>
         <v/>
       </c>
       <c r="R48">
-        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 47 - 1), NA())</f>
+        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 47 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="P49" s="2">
-        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 48 - 1), NA())</f>
+        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 48 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q49">
-        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 48 - 1), NA())</f>
+        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 48 - 1), NA())</f>
         <v/>
       </c>
       <c r="R49">
-        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 48 - 1), NA())</f>
+        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 48 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="P50" s="2">
-        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 49 - 1), NA())</f>
+        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 49 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q50">
-        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 49 - 1), NA())</f>
+        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 49 - 1), NA())</f>
         <v/>
       </c>
       <c r="R50">
-        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 49 - 1), NA())</f>
+        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 49 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="P51" s="2">
-        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 50 - 1), NA())</f>
+        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 50 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q51">
-        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 50 - 1), NA())</f>
+        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 50 - 1), NA())</f>
         <v/>
       </c>
       <c r="R51">
-        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 50 - 1), NA())</f>
+        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 50 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="P52" s="2">
-        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 51 - 1), NA())</f>
+        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 51 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q52">
-        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 51 - 1), NA())</f>
+        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 51 - 1), NA())</f>
         <v/>
       </c>
       <c r="R52">
-        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 51 - 1), NA())</f>
+        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 51 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="P53" s="2">
-        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 52 - 1), NA())</f>
+        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 52 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q53">
-        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 52 - 1), NA())</f>
+        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 52 - 1), NA())</f>
         <v/>
       </c>
       <c r="R53">
-        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 52 - 1), NA())</f>
+        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 52 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="P54" s="2">
-        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 53 - 1), NA())</f>
+        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 53 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q54">
-        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 53 - 1), NA())</f>
+        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 53 - 1), NA())</f>
         <v/>
       </c>
       <c r="R54">
-        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 53 - 1), NA())</f>
+        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 53 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="P55" s="2">
-        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 54 - 1), NA())</f>
+        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 54 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q55">
-        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 54 - 1), NA())</f>
+        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 54 - 1), NA())</f>
         <v/>
       </c>
       <c r="R55">
-        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 54 - 1), NA())</f>
+        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 54 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="P56" s="2">
-        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 55 - 1), NA())</f>
+        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 55 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q56">
-        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 55 - 1), NA())</f>
+        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 55 - 1), NA())</f>
         <v/>
       </c>
       <c r="R56">
-        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 55 - 1), NA())</f>
+        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 55 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="P57" s="2">
-        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 56 - 1), NA())</f>
+        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 56 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q57">
-        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 56 - 1), NA())</f>
+        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 56 - 1), NA())</f>
         <v/>
       </c>
       <c r="R57">
-        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 56 - 1), NA())</f>
+        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 56 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="P58" s="2">
-        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 57 - 1), NA())</f>
+        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 57 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q58">
-        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 57 - 1), NA())</f>
+        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 57 - 1), NA())</f>
         <v/>
       </c>
       <c r="R58">
-        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 57 - 1), NA())</f>
+        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 57 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="P59" s="2">
-        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 58 - 1), NA())</f>
+        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 58 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q59">
-        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 58 - 1), NA())</f>
+        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 58 - 1), NA())</f>
         <v/>
       </c>
       <c r="R59">
-        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 58 - 1), NA())</f>
+        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 58 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="P60" s="2">
-        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 59 - 1), NA())</f>
+        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 59 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q60">
-        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 59 - 1), NA())</f>
+        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 59 - 1), NA())</f>
         <v/>
       </c>
       <c r="R60">
-        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 59 - 1), NA())</f>
+        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 59 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="P61" s="2">
-        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 60 - 1), NA())</f>
+        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 60 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q61">
-        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 60 - 1), NA())</f>
+        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 60 - 1), NA())</f>
         <v/>
       </c>
       <c r="R61">
-        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 60 - 1), NA())</f>
+        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 60 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="P62" s="2">
-        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 61 - 1), NA())</f>
+        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 61 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q62">
-        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 61 - 1), NA())</f>
+        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 61 - 1), NA())</f>
         <v/>
       </c>
       <c r="R62">
-        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 61 - 1), NA())</f>
+        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 61 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="P63" s="2">
-        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 62 - 1), NA())</f>
+        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 62 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q63">
-        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 62 - 1), NA())</f>
+        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 62 - 1), NA())</f>
         <v/>
       </c>
       <c r="R63">
-        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 62 - 1), NA())</f>
+        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 62 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="P64" s="2">
-        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 63 - 1), NA())</f>
+        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 63 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q64">
-        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 63 - 1), NA())</f>
+        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 63 - 1), NA())</f>
         <v/>
       </c>
       <c r="R64">
-        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 63 - 1), NA())</f>
+        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 63 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="P65" s="2">
-        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 64 - 1), NA())</f>
+        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 64 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q65">
-        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 64 - 1), NA())</f>
+        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 64 - 1), NA())</f>
         <v/>
       </c>
       <c r="R65">
-        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 64 - 1), NA())</f>
+        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 64 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="P66" s="2">
-        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 65 - 1), NA())</f>
+        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 65 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q66">
-        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 65 - 1), NA())</f>
+        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 65 - 1), NA())</f>
         <v/>
       </c>
       <c r="R66">
-        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 65 - 1), NA())</f>
+        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 65 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="P67" s="2">
-        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 66 - 1), NA())</f>
+        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 66 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q67">
-        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 66 - 1), NA())</f>
+        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 66 - 1), NA())</f>
         <v/>
       </c>
       <c r="R67">
-        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 66 - 1), NA())</f>
+        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 66 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="P68" s="2">
-        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 67 - 1), NA())</f>
+        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 67 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q68">
-        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 67 - 1), NA())</f>
+        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 67 - 1), NA())</f>
         <v/>
       </c>
       <c r="R68">
-        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 67 - 1), NA())</f>
+        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 67 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="P69" s="2">
-        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 68 - 1), NA())</f>
+        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 68 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q69">
-        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 68 - 1), NA())</f>
+        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 68 - 1), NA())</f>
         <v/>
       </c>
       <c r="R69">
-        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 68 - 1), NA())</f>
+        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 68 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="P70" s="2">
-        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 69 - 1), NA())</f>
+        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 69 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q70">
-        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 69 - 1), NA())</f>
+        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 69 - 1), NA())</f>
         <v/>
       </c>
       <c r="R70">
-        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 69 - 1), NA())</f>
+        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 69 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="P71" s="2">
-        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 70 - 1), NA())</f>
+        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 70 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q71">
-        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 70 - 1), NA())</f>
+        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 70 - 1), NA())</f>
         <v/>
       </c>
       <c r="R71">
-        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 70 - 1), NA())</f>
+        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 70 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="P72" s="2">
-        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 71 - 1), NA())</f>
+        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 71 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q72">
-        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 71 - 1), NA())</f>
+        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 71 - 1), NA())</f>
         <v/>
       </c>
       <c r="R72">
-        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 71 - 1), NA())</f>
+        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 71 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="P73" s="2">
-        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 72 - 1), NA())</f>
+        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 72 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q73">
-        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 72 - 1), NA())</f>
+        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 72 - 1), NA())</f>
         <v/>
       </c>
       <c r="R73">
-        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 72 - 1), NA())</f>
+        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 72 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="P74" s="2">
-        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 73 - 1), NA())</f>
+        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 73 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q74">
-        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 73 - 1), NA())</f>
+        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 73 - 1), NA())</f>
         <v/>
       </c>
       <c r="R74">
-        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 73 - 1), NA())</f>
+        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 73 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="P75" s="2">
-        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 74 - 1), NA())</f>
+        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 74 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q75">
-        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 74 - 1), NA())</f>
+        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 74 - 1), NA())</f>
         <v/>
       </c>
       <c r="R75">
-        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 74 - 1), NA())</f>
+        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 74 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="P76" s="2">
-        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 75 - 1), NA())</f>
+        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 75 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q76">
-        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 75 - 1), NA())</f>
+        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 75 - 1), NA())</f>
         <v/>
       </c>
       <c r="R76">
-        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 75 - 1), NA())</f>
+        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 75 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="P77" s="2">
-        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 76 - 1), NA())</f>
+        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 76 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q77">
-        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 76 - 1), NA())</f>
+        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 76 - 1), NA())</f>
         <v/>
       </c>
       <c r="R77">
-        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 76 - 1), NA())</f>
+        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 76 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="P78" s="2">
-        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 77 - 1), NA())</f>
+        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 77 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q78">
-        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 77 - 1), NA())</f>
+        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 77 - 1), NA())</f>
         <v/>
       </c>
       <c r="R78">
-        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 77 - 1), NA())</f>
+        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 77 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="P79" s="2">
-        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 78 - 1), NA())</f>
+        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 78 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q79">
-        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 78 - 1), NA())</f>
+        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 78 - 1), NA())</f>
         <v/>
       </c>
       <c r="R79">
-        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 78 - 1), NA())</f>
+        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 78 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="P80" s="2">
-        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 79 - 1), NA())</f>
+        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 79 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q80">
-        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 79 - 1), NA())</f>
+        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 79 - 1), NA())</f>
         <v/>
       </c>
       <c r="R80">
-        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 79 - 1), NA())</f>
+        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 79 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="P81" s="2">
-        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 80 - 1), NA())</f>
+        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 80 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q81">
-        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 80 - 1), NA())</f>
+        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 80 - 1), NA())</f>
         <v/>
       </c>
       <c r="R81">
-        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 80 - 1), NA())</f>
+        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 80 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="P82" s="2">
-        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 81 - 1), NA())</f>
+        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 81 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q82">
-        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 81 - 1), NA())</f>
+        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 81 - 1), NA())</f>
         <v/>
       </c>
       <c r="R82">
-        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 81 - 1), NA())</f>
+        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 81 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="P83" s="2">
-        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 82 - 1), NA())</f>
+        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 82 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q83">
-        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 82 - 1), NA())</f>
+        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 82 - 1), NA())</f>
         <v/>
       </c>
       <c r="R83">
-        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 82 - 1), NA())</f>
+        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 82 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="P84" s="2">
-        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 83 - 1), NA())</f>
+        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 83 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q84">
-        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 83 - 1), NA())</f>
+        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 83 - 1), NA())</f>
         <v/>
       </c>
       <c r="R84">
-        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 83 - 1), NA())</f>
+        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 83 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="P85" s="2">
-        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 84 - 1), NA())</f>
+        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 84 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q85">
-        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 84 - 1), NA())</f>
+        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 84 - 1), NA())</f>
         <v/>
       </c>
       <c r="R85">
-        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 84 - 1), NA())</f>
+        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 84 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="P86" s="2">
-        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 85 - 1), NA())</f>
+        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 85 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q86">
-        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 85 - 1), NA())</f>
+        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 85 - 1), NA())</f>
         <v/>
       </c>
       <c r="R86">
-        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 85 - 1), NA())</f>
+        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 85 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="P87" s="2">
-        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 86 - 1), NA())</f>
+        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 86 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q87">
-        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 86 - 1), NA())</f>
+        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 86 - 1), NA())</f>
         <v/>
       </c>
       <c r="R87">
-        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 86 - 1), NA())</f>
+        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 86 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="P88" s="2">
-        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 87 - 1), NA())</f>
+        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 87 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q88">
-        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 87 - 1), NA())</f>
+        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 87 - 1), NA())</f>
         <v/>
       </c>
       <c r="R88">
-        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 87 - 1), NA())</f>
+        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 87 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="P89" s="2">
-        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 88 - 1), NA())</f>
+        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 88 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q89">
-        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 88 - 1), NA())</f>
+        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 88 - 1), NA())</f>
         <v/>
       </c>
       <c r="R89">
-        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 88 - 1), NA())</f>
+        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 88 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="P90" s="2">
-        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 89 - 1), NA())</f>
+        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 89 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q90">
-        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 89 - 1), NA())</f>
+        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 89 - 1), NA())</f>
         <v/>
       </c>
       <c r="R90">
-        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 89 - 1), NA())</f>
+        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 89 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="P91" s="2">
-        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 90 - 1), NA())</f>
+        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 90 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q91">
-        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 90 - 1), NA())</f>
+        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 90 - 1), NA())</f>
         <v/>
       </c>
       <c r="R91">
-        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 90 - 1), NA())</f>
+        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 90 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="P92" s="2">
-        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 91 - 1), NA())</f>
+        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 91 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q92">
-        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 91 - 1), NA())</f>
+        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 91 - 1), NA())</f>
         <v/>
       </c>
       <c r="R92">
-        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 91 - 1), NA())</f>
+        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 91 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="P93" s="2">
-        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 92 - 1), NA())</f>
+        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 92 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q93">
-        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 92 - 1), NA())</f>
+        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 92 - 1), NA())</f>
         <v/>
       </c>
       <c r="R93">
-        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 92 - 1), NA())</f>
+        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 92 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="P94" s="2">
-        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 93 - 1), NA())</f>
+        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 93 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q94">
-        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 93 - 1), NA())</f>
+        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 93 - 1), NA())</f>
         <v/>
       </c>
       <c r="R94">
-        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 93 - 1), NA())</f>
+        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 93 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="P95" s="2">
-        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 94 - 1), NA())</f>
+        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 94 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q95">
-        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 94 - 1), NA())</f>
+        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 94 - 1), NA())</f>
         <v/>
       </c>
       <c r="R95">
-        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 94 - 1), NA())</f>
+        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 94 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="P96" s="2">
-        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 95 - 1), NA())</f>
+        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 95 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q96">
-        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 95 - 1), NA())</f>
+        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 95 - 1), NA())</f>
         <v/>
       </c>
       <c r="R96">
-        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 95 - 1), NA())</f>
+        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 95 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="P97" s="2">
-        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 96 - 1), NA())</f>
+        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 96 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q97">
-        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 96 - 1), NA())</f>
+        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 96 - 1), NA())</f>
         <v/>
       </c>
       <c r="R97">
-        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 96 - 1), NA())</f>
+        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 96 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="P98" s="2">
-        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 97 - 1), NA())</f>
+        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 97 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q98">
-        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 97 - 1), NA())</f>
+        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 97 - 1), NA())</f>
         <v/>
       </c>
       <c r="R98">
-        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 97 - 1), NA())</f>
+        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 97 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="P99" s="2">
-        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 98 - 1), NA())</f>
+        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 98 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q99">
-        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 98 - 1), NA())</f>
+        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 98 - 1), NA())</f>
         <v/>
       </c>
       <c r="R99">
-        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 98 - 1), NA())</f>
+        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 98 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="P100" s="2">
-        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 99 - 1), NA())</f>
+        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 99 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q100">
-        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 99 - 1), NA())</f>
+        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 99 - 1), NA())</f>
         <v/>
       </c>
       <c r="R100">
-        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 99 - 1), NA())</f>
+        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 99 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="P101" s="2">
-        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 100 - 1), NA())</f>
+        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 100 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q101">
-        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 100 - 1), NA())</f>
+        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 100 - 1), NA())</f>
         <v/>
       </c>
       <c r="R101">
-        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 100 - 1), NA())</f>
+        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 100 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="P102" s="2">
-        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 101 - 1), NA())</f>
+        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 101 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q102">
-        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 101 - 1), NA())</f>
+        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 101 - 1), NA())</f>
         <v/>
       </c>
       <c r="R102">
-        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 101 - 1), NA())</f>
+        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 101 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="P103" s="2">
-        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 102 - 1), NA())</f>
+        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 102 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q103">
-        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 102 - 1), NA())</f>
+        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 102 - 1), NA())</f>
         <v/>
       </c>
       <c r="R103">
-        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 102 - 1), NA())</f>
+        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 102 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="P104" s="2">
-        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 103 - 1), NA())</f>
+        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 103 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q104">
-        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 103 - 1), NA())</f>
+        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 103 - 1), NA())</f>
         <v/>
       </c>
       <c r="R104">
-        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 103 - 1), NA())</f>
+        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 103 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="P105" s="2">
-        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 104 - 1), NA())</f>
+        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 104 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q105">
-        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 104 - 1), NA())</f>
+        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 104 - 1), NA())</f>
         <v/>
       </c>
       <c r="R105">
-        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 104 - 1), NA())</f>
+        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 104 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="P106" s="2">
-        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 105 - 1), NA())</f>
+        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 105 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q106">
-        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 105 - 1), NA())</f>
+        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 105 - 1), NA())</f>
         <v/>
       </c>
       <c r="R106">
-        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 105 - 1), NA())</f>
+        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 105 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="P107" s="2">
-        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 106 - 1), NA())</f>
+        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 106 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q107">
-        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 106 - 1), NA())</f>
+        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 106 - 1), NA())</f>
         <v/>
       </c>
       <c r="R107">
-        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 106 - 1), NA())</f>
+        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 106 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="P108" s="2">
-        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 107 - 1), NA())</f>
+        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 107 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q108">
-        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 107 - 1), NA())</f>
+        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 107 - 1), NA())</f>
         <v/>
       </c>
       <c r="R108">
-        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 107 - 1), NA())</f>
+        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 107 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="P109" s="2">
-        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 108 - 1), NA())</f>
+        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 108 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q109">
-        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 108 - 1), NA())</f>
+        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 108 - 1), NA())</f>
         <v/>
       </c>
       <c r="R109">
-        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 108 - 1), NA())</f>
+        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 108 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="P110" s="2">
-        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 109 - 1), NA())</f>
+        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 109 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q110">
-        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 109 - 1), NA())</f>
+        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 109 - 1), NA())</f>
         <v/>
       </c>
       <c r="R110">
-        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 109 - 1), NA())</f>
+        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 109 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="P111" s="2">
-        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 110 - 1), NA())</f>
+        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 110 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q111">
-        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 110 - 1), NA())</f>
+        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 110 - 1), NA())</f>
         <v/>
       </c>
       <c r="R111">
-        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 110 - 1), NA())</f>
+        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 110 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="P112" s="2">
-        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 111 - 1), NA())</f>
+        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 111 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q112">
-        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 111 - 1), NA())</f>
+        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 111 - 1), NA())</f>
         <v/>
       </c>
       <c r="R112">
-        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 111 - 1), NA())</f>
+        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 111 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="P113" s="2">
-        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 112 - 1), NA())</f>
+        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 112 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q113">
-        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 112 - 1), NA())</f>
+        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 112 - 1), NA())</f>
         <v/>
       </c>
       <c r="R113">
-        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 112 - 1), NA())</f>
+        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 112 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="P114" s="2">
-        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 113 - 1), NA())</f>
+        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 113 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q114">
-        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 113 - 1), NA())</f>
+        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 113 - 1), NA())</f>
         <v/>
       </c>
       <c r="R114">
-        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 113 - 1), NA())</f>
+        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 113 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="P115" s="2">
-        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 114 - 1), NA())</f>
+        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 114 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q115">
-        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 114 - 1), NA())</f>
+        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 114 - 1), NA())</f>
         <v/>
       </c>
       <c r="R115">
-        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 114 - 1), NA())</f>
+        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 114 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="P116" s="2">
-        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 115 - 1), NA())</f>
+        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 115 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q116">
-        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 115 - 1), NA())</f>
+        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 115 - 1), NA())</f>
         <v/>
       </c>
       <c r="R116">
-        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 115 - 1), NA())</f>
+        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 115 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="P117" s="2">
-        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 116 - 1), NA())</f>
+        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 116 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q117">
-        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 116 - 1), NA())</f>
+        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 116 - 1), NA())</f>
         <v/>
       </c>
       <c r="R117">
-        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 116 - 1), NA())</f>
+        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 116 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="P118" s="2">
-        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 117 - 1), NA())</f>
+        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 117 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q118">
-        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 117 - 1), NA())</f>
+        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 117 - 1), NA())</f>
         <v/>
       </c>
       <c r="R118">
-        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 117 - 1), NA())</f>
+        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 117 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="P119" s="2">
-        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 118 - 1), NA())</f>
+        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 118 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q119">
-        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 118 - 1), NA())</f>
+        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 118 - 1), NA())</f>
         <v/>
       </c>
       <c r="R119">
-        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 118 - 1), NA())</f>
+        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 118 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="P120" s="2">
-        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 119 - 1), NA())</f>
+        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 119 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q120">
-        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 119 - 1), NA())</f>
+        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 119 - 1), NA())</f>
         <v/>
       </c>
       <c r="R120">
-        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 119 - 1), NA())</f>
+        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 119 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="P121" s="2">
-        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 120 - 1), NA())</f>
+        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 120 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q121">
-        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 120 - 1), NA())</f>
+        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 120 - 1), NA())</f>
         <v/>
       </c>
       <c r="R121">
-        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 120 - 1), NA())</f>
+        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 120 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="P122" s="2">
-        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 121 - 1), NA())</f>
+        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 121 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q122">
-        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 121 - 1), NA())</f>
+        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 121 - 1), NA())</f>
         <v/>
       </c>
       <c r="R122">
-        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 121 - 1), NA())</f>
+        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 121 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="123">
       <c r="P123" s="2">
-        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 122 - 1), NA())</f>
+        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 122 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q123">
-        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 122 - 1), NA())</f>
+        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 122 - 1), NA())</f>
         <v/>
       </c>
       <c r="R123">
-        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 122 - 1), NA())</f>
+        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 122 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="124">
       <c r="P124" s="2">
-        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 123 - 1), NA())</f>
+        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 123 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q124">
-        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 123 - 1), NA())</f>
+        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 123 - 1), NA())</f>
         <v/>
       </c>
       <c r="R124">
-        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 123 - 1), NA())</f>
+        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 123 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="125">
       <c r="P125" s="2">
-        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 124 - 1), NA())</f>
+        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 124 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q125">
-        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 124 - 1), NA())</f>
+        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 124 - 1), NA())</f>
         <v/>
       </c>
       <c r="R125">
-        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 124 - 1), NA())</f>
+        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 124 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="126">
       <c r="P126" s="2">
-        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 125 - 1), NA())</f>
+        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 125 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q126">
-        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 125 - 1), NA())</f>
+        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 125 - 1), NA())</f>
         <v/>
       </c>
       <c r="R126">
-        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 125 - 1), NA())</f>
+        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 125 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="127">
       <c r="P127" s="2">
-        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 126 - 1), NA())</f>
+        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 126 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q127">
-        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 126 - 1), NA())</f>
+        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 126 - 1), NA())</f>
         <v/>
       </c>
       <c r="R127">
-        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 126 - 1), NA())</f>
+        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 126 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="P128" s="2">
-        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 127 - 1), NA())</f>
+        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 127 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q128">
-        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 127 - 1), NA())</f>
+        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 127 - 1), NA())</f>
         <v/>
       </c>
       <c r="R128">
-        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 127 - 1), NA())</f>
+        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 127 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="129">
       <c r="P129" s="2">
-        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 128 - 1), NA())</f>
+        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 128 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q129">
-        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 128 - 1), NA())</f>
+        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 128 - 1), NA())</f>
         <v/>
       </c>
       <c r="R129">
-        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 128 - 1), NA())</f>
+        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 128 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="130">
       <c r="P130" s="2">
-        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 129 - 1), NA())</f>
+        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 129 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q130">
-        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 129 - 1), NA())</f>
+        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 129 - 1), NA())</f>
         <v/>
       </c>
       <c r="R130">
-        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 129 - 1), NA())</f>
+        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 129 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="131">
       <c r="P131" s="2">
-        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 130 - 1), NA())</f>
+        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 130 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q131">
-        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 130 - 1), NA())</f>
+        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 130 - 1), NA())</f>
         <v/>
       </c>
       <c r="R131">
-        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 130 - 1), NA())</f>
+        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 130 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="132">
       <c r="P132" s="2">
-        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 131 - 1), NA())</f>
+        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 131 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q132">
-        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 131 - 1), NA())</f>
+        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 131 - 1), NA())</f>
         <v/>
       </c>
       <c r="R132">
-        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 131 - 1), NA())</f>
+        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 131 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="133">
       <c r="P133" s="2">
-        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 132 - 1), NA())</f>
+        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 132 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q133">
-        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 132 - 1), NA())</f>
+        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 132 - 1), NA())</f>
         <v/>
       </c>
       <c r="R133">
-        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 132 - 1), NA())</f>
+        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 132 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="134">
       <c r="P134" s="2">
-        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 133 - 1), NA())</f>
+        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 133 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q134">
-        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 133 - 1), NA())</f>
+        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 133 - 1), NA())</f>
         <v/>
       </c>
       <c r="R134">
-        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 133 - 1), NA())</f>
+        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 133 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="135">
       <c r="P135" s="2">
-        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 134 - 1), NA())</f>
+        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 134 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q135">
-        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 134 - 1), NA())</f>
+        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 134 - 1), NA())</f>
         <v/>
       </c>
       <c r="R135">
-        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 134 - 1), NA())</f>
+        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 134 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="136">
       <c r="P136" s="2">
-        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 135 - 1), NA())</f>
+        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 135 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q136">
-        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 135 - 1), NA())</f>
+        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 135 - 1), NA())</f>
         <v/>
       </c>
       <c r="R136">
-        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 135 - 1), NA())</f>
+        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 135 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="137">
       <c r="P137" s="2">
-        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 136 - 1), NA())</f>
+        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 136 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q137">
-        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 136 - 1), NA())</f>
+        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 136 - 1), NA())</f>
         <v/>
       </c>
       <c r="R137">
-        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 136 - 1), NA())</f>
+        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 136 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="138">
       <c r="P138" s="2">
-        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 137 - 1), NA())</f>
+        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 137 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q138">
-        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 137 - 1), NA())</f>
+        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 137 - 1), NA())</f>
         <v/>
       </c>
       <c r="R138">
-        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 137 - 1), NA())</f>
+        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 137 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="139">
       <c r="P139" s="2">
-        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 138 - 1), NA())</f>
+        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 138 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q139">
-        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 138 - 1), NA())</f>
+        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 138 - 1), NA())</f>
         <v/>
       </c>
       <c r="R139">
-        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 138 - 1), NA())</f>
+        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 138 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="140">
       <c r="P140" s="2">
-        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 139 - 1), NA())</f>
+        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 139 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q140">
-        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 139 - 1), NA())</f>
+        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 139 - 1), NA())</f>
         <v/>
       </c>
       <c r="R140">
-        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 139 - 1), NA())</f>
+        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 139 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="141">
       <c r="P141" s="2">
-        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 140 - 1), NA())</f>
+        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 140 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q141">
-        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 140 - 1), NA())</f>
+        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 140 - 1), NA())</f>
         <v/>
       </c>
       <c r="R141">
-        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 140 - 1), NA())</f>
+        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 140 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="142">
       <c r="P142" s="2">
-        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 141 - 1), NA())</f>
+        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 141 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q142">
-        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 141 - 1), NA())</f>
+        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 141 - 1), NA())</f>
         <v/>
       </c>
       <c r="R142">
-        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 141 - 1), NA())</f>
+        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 141 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="143">
       <c r="P143" s="2">
-        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 142 - 1), NA())</f>
+        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 142 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q143">
-        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 142 - 1), NA())</f>
+        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 142 - 1), NA())</f>
         <v/>
       </c>
       <c r="R143">
-        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 142 - 1), NA())</f>
+        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 142 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="144">
       <c r="P144" s="2">
-        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 143 - 1), NA())</f>
+        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 143 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q144">
-        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 143 - 1), NA())</f>
+        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 143 - 1), NA())</f>
         <v/>
       </c>
       <c r="R144">
-        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 143 - 1), NA())</f>
+        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 143 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="145">
       <c r="P145" s="2">
-        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 144 - 1), NA())</f>
+        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 144 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q145">
-        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 144 - 1), NA())</f>
+        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 144 - 1), NA())</f>
         <v/>
       </c>
       <c r="R145">
-        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 144 - 1), NA())</f>
+        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 144 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="146">
       <c r="P146" s="2">
-        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 145 - 1), NA())</f>
+        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 145 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q146">
-        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 145 - 1), NA())</f>
+        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 145 - 1), NA())</f>
         <v/>
       </c>
       <c r="R146">
-        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 145 - 1), NA())</f>
+        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 145 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="147">
       <c r="P147" s="2">
-        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 146 - 1), NA())</f>
+        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 146 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q147">
-        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 146 - 1), NA())</f>
+        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 146 - 1), NA())</f>
         <v/>
       </c>
       <c r="R147">
-        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 146 - 1), NA())</f>
+        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 146 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="148">
       <c r="P148" s="2">
-        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 147 - 1), NA())</f>
+        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 147 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q148">
-        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 147 - 1), NA())</f>
+        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 147 - 1), NA())</f>
         <v/>
       </c>
       <c r="R148">
-        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 147 - 1), NA())</f>
+        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 147 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="149">
       <c r="P149" s="2">
-        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 148 - 1), NA())</f>
+        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 148 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q149">
-        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 148 - 1), NA())</f>
+        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 148 - 1), NA())</f>
         <v/>
       </c>
       <c r="R149">
-        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 148 - 1), NA())</f>
+        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 148 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="150">
       <c r="P150" s="2">
-        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 149 - 1), NA())</f>
+        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 149 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q150">
-        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 149 - 1), NA())</f>
+        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 149 - 1), NA())</f>
         <v/>
       </c>
       <c r="R150">
-        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 149 - 1), NA())</f>
+        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 149 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="151">
       <c r="P151" s="2">
-        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 150 - 1), NA())</f>
+        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 150 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q151">
-        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 150 - 1), NA())</f>
+        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 150 - 1), NA())</f>
         <v/>
       </c>
       <c r="R151">
-        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 150 - 1), NA())</f>
+        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 150 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="152">
       <c r="P152" s="2">
-        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 151 - 1), NA())</f>
+        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 151 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q152">
-        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 151 - 1), NA())</f>
+        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 151 - 1), NA())</f>
         <v/>
       </c>
       <c r="R152">
-        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 151 - 1), NA())</f>
+        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 151 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="153">
       <c r="P153" s="2">
-        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 152 - 1), NA())</f>
+        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 152 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q153">
-        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 152 - 1), NA())</f>
+        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 152 - 1), NA())</f>
         <v/>
       </c>
       <c r="R153">
-        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 152 - 1), NA())</f>
+        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 152 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="154">
       <c r="P154" s="2">
-        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 153 - 1), NA())</f>
+        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 153 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q154">
-        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 153 - 1), NA())</f>
+        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 153 - 1), NA())</f>
         <v/>
       </c>
       <c r="R154">
-        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 153 - 1), NA())</f>
+        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 153 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="155">
       <c r="P155" s="2">
-        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 154 - 1), NA())</f>
+        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 154 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q155">
-        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 154 - 1), NA())</f>
+        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 154 - 1), NA())</f>
         <v/>
       </c>
       <c r="R155">
-        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 154 - 1), NA())</f>
+        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 154 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="156">
       <c r="P156" s="2">
-        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 155 - 1), NA())</f>
+        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 155 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q156">
-        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 155 - 1), NA())</f>
+        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 155 - 1), NA())</f>
         <v/>
       </c>
       <c r="R156">
-        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 155 - 1), NA())</f>
+        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 155 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="157">
       <c r="P157" s="2">
-        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 156 - 1), NA())</f>
+        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 156 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q157">
-        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 156 - 1), NA())</f>
+        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 156 - 1), NA())</f>
         <v/>
       </c>
       <c r="R157">
-        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 156 - 1), NA())</f>
+        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 156 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="158">
       <c r="P158" s="2">
-        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 157 - 1), NA())</f>
+        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 157 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q158">
-        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 157 - 1), NA())</f>
+        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 157 - 1), NA())</f>
         <v/>
       </c>
       <c r="R158">
-        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 157 - 1), NA())</f>
+        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 157 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="159">
       <c r="P159" s="2">
-        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 158 - 1), NA())</f>
+        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 158 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q159">
-        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 158 - 1), NA())</f>
+        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 158 - 1), NA())</f>
         <v/>
       </c>
       <c r="R159">
-        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 158 - 1), NA())</f>
+        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 158 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="160">
       <c r="P160" s="2">
-        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 159 - 1), NA())</f>
+        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 159 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q160">
-        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 159 - 1), NA())</f>
+        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 159 - 1), NA())</f>
         <v/>
       </c>
       <c r="R160">
-        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 159 - 1), NA())</f>
+        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 159 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="161">
       <c r="P161" s="2">
-        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 160 - 1), NA())</f>
+        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 160 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q161">
-        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 160 - 1), NA())</f>
+        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 160 - 1), NA())</f>
         <v/>
       </c>
       <c r="R161">
-        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 160 - 1), NA())</f>
+        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 160 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="162">
       <c r="P162" s="2">
-        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 161 - 1), NA())</f>
+        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 161 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q162">
-        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 161 - 1), NA())</f>
+        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 161 - 1), NA())</f>
         <v/>
       </c>
       <c r="R162">
-        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 161 - 1), NA())</f>
+        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 161 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="163">
       <c r="P163" s="2">
-        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 162 - 1), NA())</f>
+        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 162 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q163">
-        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 162 - 1), NA())</f>
+        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 162 - 1), NA())</f>
         <v/>
       </c>
       <c r="R163">
-        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 162 - 1), NA())</f>
+        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 162 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="164">
       <c r="P164" s="2">
-        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 163 - 1), NA())</f>
+        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 163 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q164">
-        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 163 - 1), NA())</f>
+        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 163 - 1), NA())</f>
         <v/>
       </c>
       <c r="R164">
-        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 163 - 1), NA())</f>
+        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 163 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="165">
       <c r="P165" s="2">
-        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 164 - 1), NA())</f>
+        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 164 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q165">
-        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 164 - 1), NA())</f>
+        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 164 - 1), NA())</f>
         <v/>
       </c>
       <c r="R165">
-        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 164 - 1), NA())</f>
+        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 164 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="166">
       <c r="P166" s="2">
-        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 165 - 1), NA())</f>
+        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 165 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q166">
-        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 165 - 1), NA())</f>
+        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 165 - 1), NA())</f>
         <v/>
       </c>
       <c r="R166">
-        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 165 - 1), NA())</f>
+        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 165 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="167">
       <c r="P167" s="2">
-        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 166 - 1), NA())</f>
+        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 166 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q167">
-        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 166 - 1), NA())</f>
+        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 166 - 1), NA())</f>
         <v/>
       </c>
       <c r="R167">
-        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 166 - 1), NA())</f>
+        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 166 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="168">
       <c r="P168" s="2">
-        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 167 - 1), NA())</f>
+        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 167 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q168">
-        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 167 - 1), NA())</f>
+        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 167 - 1), NA())</f>
         <v/>
       </c>
       <c r="R168">
-        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 167 - 1), NA())</f>
+        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 167 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="169">
       <c r="P169" s="2">
-        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 168 - 1), NA())</f>
+        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 168 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q169">
-        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 168 - 1), NA())</f>
+        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 168 - 1), NA())</f>
         <v/>
       </c>
       <c r="R169">
-        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 168 - 1), NA())</f>
+        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 168 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="170">
       <c r="P170" s="2">
-        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 169 - 1), NA())</f>
+        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 169 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q170">
-        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 169 - 1), NA())</f>
+        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 169 - 1), NA())</f>
         <v/>
       </c>
       <c r="R170">
-        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 169 - 1), NA())</f>
+        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 169 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="171">
       <c r="P171" s="2">
-        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 170 - 1), NA())</f>
+        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 170 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q171">
-        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 170 - 1), NA())</f>
+        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 170 - 1), NA())</f>
         <v/>
       </c>
       <c r="R171">
-        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 170 - 1), NA())</f>
+        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 170 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="172">
       <c r="P172" s="2">
-        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 171 - 1), NA())</f>
+        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 171 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q172">
-        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 171 - 1), NA())</f>
+        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 171 - 1), NA())</f>
         <v/>
       </c>
       <c r="R172">
-        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 171 - 1), NA())</f>
+        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 171 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="173">
       <c r="P173" s="2">
-        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 172 - 1), NA())</f>
+        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 172 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q173">
-        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 172 - 1), NA())</f>
+        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 172 - 1), NA())</f>
         <v/>
       </c>
       <c r="R173">
-        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 172 - 1), NA())</f>
+        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 172 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="174">
       <c r="P174" s="2">
-        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 173 - 1), NA())</f>
+        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 173 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q174">
-        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 173 - 1), NA())</f>
+        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 173 - 1), NA())</f>
         <v/>
       </c>
       <c r="R174">
-        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 173 - 1), NA())</f>
+        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 173 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="175">
       <c r="P175" s="2">
-        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 174 - 1), NA())</f>
+        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 174 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q175">
-        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 174 - 1), NA())</f>
+        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 174 - 1), NA())</f>
         <v/>
       </c>
       <c r="R175">
-        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 174 - 1), NA())</f>
+        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 174 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="176">
       <c r="P176" s="2">
-        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 175 - 1), NA())</f>
+        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 175 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q176">
-        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 175 - 1), NA())</f>
+        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 175 - 1), NA())</f>
         <v/>
       </c>
       <c r="R176">
-        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 175 - 1), NA())</f>
+        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 175 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="177">
       <c r="P177" s="2">
-        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 176 - 1), NA())</f>
+        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 176 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q177">
-        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 176 - 1), NA())</f>
+        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 176 - 1), NA())</f>
         <v/>
       </c>
       <c r="R177">
-        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 176 - 1), NA())</f>
+        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 176 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="178">
       <c r="P178" s="2">
-        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 177 - 1), NA())</f>
+        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 177 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q178">
-        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 177 - 1), NA())</f>
+        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 177 - 1), NA())</f>
         <v/>
       </c>
       <c r="R178">
-        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 177 - 1), NA())</f>
+        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 177 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="179">
       <c r="P179" s="2">
-        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 178 - 1), NA())</f>
+        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 178 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q179">
-        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 178 - 1), NA())</f>
+        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 178 - 1), NA())</f>
         <v/>
       </c>
       <c r="R179">
-        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 178 - 1), NA())</f>
+        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 178 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="180">
       <c r="P180" s="2">
-        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 179 - 1), NA())</f>
+        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 179 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q180">
-        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 179 - 1), NA())</f>
+        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 179 - 1), NA())</f>
         <v/>
       </c>
       <c r="R180">
-        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 179 - 1), NA())</f>
+        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 179 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="181">
       <c r="P181" s="2">
-        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 180 - 1), NA())</f>
+        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 180 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q181">
-        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 180 - 1), NA())</f>
+        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 180 - 1), NA())</f>
         <v/>
       </c>
       <c r="R181">
-        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 180 - 1), NA())</f>
+        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 180 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="182">
       <c r="P182" s="2">
-        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 181 - 1), NA())</f>
+        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 181 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q182">
-        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 181 - 1), NA())</f>
+        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 181 - 1), NA())</f>
         <v/>
       </c>
       <c r="R182">
-        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 181 - 1), NA())</f>
+        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 181 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="183">
       <c r="P183" s="2">
-        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 182 - 1), NA())</f>
+        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 182 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q183">
-        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 182 - 1), NA())</f>
+        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 182 - 1), NA())</f>
         <v/>
       </c>
       <c r="R183">
-        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 182 - 1), NA())</f>
+        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 182 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="184">
       <c r="P184" s="2">
-        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 183 - 1), NA())</f>
+        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 183 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q184">
-        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 183 - 1), NA())</f>
+        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 183 - 1), NA())</f>
         <v/>
       </c>
       <c r="R184">
-        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 183 - 1), NA())</f>
+        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 183 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="185">
       <c r="P185" s="2">
-        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 184 - 1), NA())</f>
+        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 184 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q185">
-        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 184 - 1), NA())</f>
+        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 184 - 1), NA())</f>
         <v/>
       </c>
       <c r="R185">
-        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 184 - 1), NA())</f>
+        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 184 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="186">
       <c r="P186" s="2">
-        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 185 - 1), NA())</f>
+        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 185 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q186">
-        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 185 - 1), NA())</f>
+        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 185 - 1), NA())</f>
         <v/>
       </c>
       <c r="R186">
-        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 185 - 1), NA())</f>
+        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 185 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="187">
       <c r="P187" s="2">
-        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 186 - 1), NA())</f>
+        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 186 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q187">
-        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 186 - 1), NA())</f>
+        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 186 - 1), NA())</f>
         <v/>
       </c>
       <c r="R187">
-        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 186 - 1), NA())</f>
+        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 186 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="188">
       <c r="P188" s="2">
-        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 187 - 1), NA())</f>
+        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 187 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q188">
-        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 187 - 1), NA())</f>
+        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 187 - 1), NA())</f>
         <v/>
       </c>
       <c r="R188">
-        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 187 - 1), NA())</f>
+        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 187 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="189">
       <c r="P189" s="2">
-        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 188 - 1), NA())</f>
+        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 188 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q189">
-        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 188 - 1), NA())</f>
+        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 188 - 1), NA())</f>
         <v/>
       </c>
       <c r="R189">
-        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 188 - 1), NA())</f>
+        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 188 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="190">
       <c r="P190" s="2">
-        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 189 - 1), NA())</f>
+        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 189 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q190">
-        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 189 - 1), NA())</f>
+        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 189 - 1), NA())</f>
         <v/>
       </c>
       <c r="R190">
-        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 189 - 1), NA())</f>
+        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 189 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="191">
       <c r="P191" s="2">
-        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 190 - 1), NA())</f>
+        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 190 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q191">
-        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 190 - 1), NA())</f>
+        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 190 - 1), NA())</f>
         <v/>
       </c>
       <c r="R191">
-        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 190 - 1), NA())</f>
+        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 190 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="192">
       <c r="P192" s="2">
-        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 191 - 1), NA())</f>
+        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 191 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q192">
-        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 191 - 1), NA())</f>
+        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 191 - 1), NA())</f>
         <v/>
       </c>
       <c r="R192">
-        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 191 - 1), NA())</f>
+        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 191 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="193">
       <c r="P193" s="2">
-        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 192 - 1), NA())</f>
+        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 192 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q193">
-        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 192 - 1), NA())</f>
+        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 192 - 1), NA())</f>
         <v/>
       </c>
       <c r="R193">
-        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 192 - 1), NA())</f>
+        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 192 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="194">
       <c r="P194" s="2">
-        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 193 - 1), NA())</f>
+        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 193 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q194">
-        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 193 - 1), NA())</f>
+        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 193 - 1), NA())</f>
         <v/>
       </c>
       <c r="R194">
-        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 193 - 1), NA())</f>
+        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 193 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="195">
       <c r="P195" s="2">
-        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 194 - 1), NA())</f>
+        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 194 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q195">
-        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 194 - 1), NA())</f>
+        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 194 - 1), NA())</f>
         <v/>
       </c>
       <c r="R195">
-        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 194 - 1), NA())</f>
+        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 194 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="196">
       <c r="P196" s="2">
-        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 195 - 1), NA())</f>
+        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 195 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q196">
-        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 195 - 1), NA())</f>
+        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 195 - 1), NA())</f>
         <v/>
       </c>
       <c r="R196">
-        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 195 - 1), NA())</f>
+        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 195 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="197">
       <c r="P197" s="2">
-        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 196 - 1), NA())</f>
+        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 196 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q197">
-        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 196 - 1), NA())</f>
+        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 196 - 1), NA())</f>
         <v/>
       </c>
       <c r="R197">
-        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 196 - 1), NA())</f>
+        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 196 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="198">
       <c r="P198" s="2">
-        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 197 - 1), NA())</f>
+        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 197 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q198">
-        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 197 - 1), NA())</f>
+        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 197 - 1), NA())</f>
         <v/>
       </c>
       <c r="R198">
-        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 197 - 1), NA())</f>
+        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 197 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="199">
       <c r="P199" s="2">
-        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 198 - 1), NA())</f>
+        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 198 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q199">
-        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 198 - 1), NA())</f>
+        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 198 - 1), NA())</f>
         <v/>
       </c>
       <c r="R199">
-        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 198 - 1), NA())</f>
+        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 198 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="200">
       <c r="P200" s="2">
-        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 199 - 1), NA())</f>
+        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 199 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q200">
-        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 199 - 1), NA())</f>
+        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 199 - 1), NA())</f>
         <v/>
       </c>
       <c r="R200">
-        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 199 - 1), NA())</f>
+        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 199 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="201">
       <c r="P201" s="2">
-        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 200 - 1), NA())</f>
+        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 200 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q201">
-        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 200 - 1), NA())</f>
+        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 200 - 1), NA())</f>
         <v/>
       </c>
       <c r="R201">
-        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 200 - 1), NA())</f>
+        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 200 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="202">
       <c r="P202" s="2">
-        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 201 - 1), NA())</f>
+        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 201 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q202">
-        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 201 - 1), NA())</f>
+        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 201 - 1), NA())</f>
         <v/>
       </c>
       <c r="R202">
-        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 201 - 1), NA())</f>
+        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 201 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="203">
       <c r="P203" s="2">
-        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 202 - 1), NA())</f>
+        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 202 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q203">
-        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 202 - 1), NA())</f>
+        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 202 - 1), NA())</f>
         <v/>
       </c>
       <c r="R203">
-        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 202 - 1), NA())</f>
+        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 202 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="204">
       <c r="P204" s="2">
-        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 203 - 1), NA())</f>
+        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 203 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q204">
-        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 203 - 1), NA())</f>
+        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 203 - 1), NA())</f>
         <v/>
       </c>
       <c r="R204">
-        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 203 - 1), NA())</f>
+        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 203 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="205">
       <c r="P205" s="2">
-        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 204 - 1), NA())</f>
+        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 204 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q205">
-        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 204 - 1), NA())</f>
+        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 204 - 1), NA())</f>
         <v/>
       </c>
       <c r="R205">
-        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 204 - 1), NA())</f>
+        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 204 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="206">
       <c r="P206" s="2">
-        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 205 - 1), NA())</f>
+        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 205 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q206">
-        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 205 - 1), NA())</f>
+        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 205 - 1), NA())</f>
         <v/>
       </c>
       <c r="R206">
-        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 205 - 1), NA())</f>
+        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 205 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="207">
       <c r="P207" s="2">
-        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 206 - 1), NA())</f>
+        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 206 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q207">
-        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 206 - 1), NA())</f>
+        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 206 - 1), NA())</f>
         <v/>
       </c>
       <c r="R207">
-        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 206 - 1), NA())</f>
+        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 206 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="208">
       <c r="P208" s="2">
-        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 207 - 1), NA())</f>
+        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 207 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q208">
-        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 207 - 1), NA())</f>
+        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 207 - 1), NA())</f>
         <v/>
       </c>
       <c r="R208">
-        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 207 - 1), NA())</f>
+        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 207 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="209">
       <c r="P209" s="2">
-        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 208 - 1), NA())</f>
+        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 208 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q209">
-        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 208 - 1), NA())</f>
+        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 208 - 1), NA())</f>
         <v/>
       </c>
       <c r="R209">
-        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 208 - 1), NA())</f>
+        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 208 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="210">
       <c r="P210" s="2">
-        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 209 - 1), NA())</f>
+        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 209 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q210">
-        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 209 - 1), NA())</f>
+        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 209 - 1), NA())</f>
         <v/>
       </c>
       <c r="R210">
-        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 209 - 1), NA())</f>
+        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 209 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="211">
       <c r="P211" s="2">
-        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 210 - 1), NA())</f>
+        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 210 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q211">
-        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 210 - 1), NA())</f>
+        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 210 - 1), NA())</f>
         <v/>
       </c>
       <c r="R211">
-        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 210 - 1), NA())</f>
+        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 210 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="212">
       <c r="P212" s="2">
-        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 211 - 1), NA())</f>
+        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 211 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q212">
-        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 211 - 1), NA())</f>
+        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 211 - 1), NA())</f>
         <v/>
       </c>
       <c r="R212">
-        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 211 - 1), NA())</f>
+        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 211 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="213">
       <c r="P213" s="2">
-        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 212 - 1), NA())</f>
+        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 212 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q213">
-        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 212 - 1), NA())</f>
+        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 212 - 1), NA())</f>
         <v/>
       </c>
       <c r="R213">
-        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 212 - 1), NA())</f>
+        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 212 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="214">
       <c r="P214" s="2">
-        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 213 - 1), NA())</f>
+        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 213 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q214">
-        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 213 - 1), NA())</f>
+        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 213 - 1), NA())</f>
         <v/>
       </c>
       <c r="R214">
-        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 213 - 1), NA())</f>
+        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 213 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="215">
       <c r="P215" s="2">
-        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 214 - 1), NA())</f>
+        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 214 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q215">
-        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 214 - 1), NA())</f>
+        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 214 - 1), NA())</f>
         <v/>
       </c>
       <c r="R215">
-        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 214 - 1), NA())</f>
+        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 214 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="216">
       <c r="P216" s="2">
-        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 215 - 1), NA())</f>
+        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 215 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q216">
-        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 215 - 1), NA())</f>
+        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 215 - 1), NA())</f>
         <v/>
       </c>
       <c r="R216">
-        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 215 - 1), NA())</f>
+        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 215 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="217">
       <c r="P217" s="2">
-        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 216 - 1), NA())</f>
+        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 216 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q217">
-        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 216 - 1), NA())</f>
+        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 216 - 1), NA())</f>
         <v/>
       </c>
       <c r="R217">
-        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 216 - 1), NA())</f>
+        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 216 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="218">
       <c r="P218" s="2">
-        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 217 - 1), NA())</f>
+        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 217 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q218">
-        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 217 - 1), NA())</f>
+        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 217 - 1), NA())</f>
         <v/>
       </c>
       <c r="R218">
-        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 217 - 1), NA())</f>
+        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 217 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="219">
       <c r="P219" s="2">
-        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 218 - 1), NA())</f>
+        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 218 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q219">
-        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 218 - 1), NA())</f>
+        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 218 - 1), NA())</f>
         <v/>
       </c>
       <c r="R219">
-        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 218 - 1), NA())</f>
+        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 218 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="220">
       <c r="P220" s="2">
-        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 219 - 1), NA())</f>
+        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 219 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q220">
-        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 219 - 1), NA())</f>
+        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 219 - 1), NA())</f>
         <v/>
       </c>
       <c r="R220">
-        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 219 - 1), NA())</f>
+        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 219 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="221">
       <c r="P221" s="2">
-        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 220 - 1), NA())</f>
+        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 220 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q221">
-        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 220 - 1), NA())</f>
+        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 220 - 1), NA())</f>
         <v/>
       </c>
       <c r="R221">
-        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 220 - 1), NA())</f>
+        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 220 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="222">
       <c r="P222" s="2">
-        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 221 - 1), NA())</f>
+        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 221 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q222">
-        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 221 - 1), NA())</f>
+        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 221 - 1), NA())</f>
         <v/>
       </c>
       <c r="R222">
-        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 221 - 1), NA())</f>
+        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 221 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="223">
       <c r="P223" s="2">
-        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 222 - 1), NA())</f>
+        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 222 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q223">
-        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 222 - 1), NA())</f>
+        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 222 - 1), NA())</f>
         <v/>
       </c>
       <c r="R223">
-        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 222 - 1), NA())</f>
+        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 222 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="224">
       <c r="P224" s="2">
-        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 223 - 1), NA())</f>
+        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 223 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q224">
-        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 223 - 1), NA())</f>
+        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 223 - 1), NA())</f>
         <v/>
       </c>
       <c r="R224">
-        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 223 - 1), NA())</f>
+        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 223 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="225">
       <c r="P225" s="2">
-        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 224 - 1), NA())</f>
+        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 224 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q225">
-        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 224 - 1), NA())</f>
+        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 224 - 1), NA())</f>
         <v/>
       </c>
       <c r="R225">
-        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 224 - 1), NA())</f>
+        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 224 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="226">
       <c r="P226" s="2">
-        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 225 - 1), NA())</f>
+        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 225 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q226">
-        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 225 - 1), NA())</f>
+        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 225 - 1), NA())</f>
         <v/>
       </c>
       <c r="R226">
-        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 225 - 1), NA())</f>
+        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 225 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="227">
       <c r="P227" s="2">
-        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 226 - 1), NA())</f>
+        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 226 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q227">
-        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 226 - 1), NA())</f>
+        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 226 - 1), NA())</f>
         <v/>
       </c>
       <c r="R227">
-        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 226 - 1), NA())</f>
+        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 226 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="228">
       <c r="P228" s="2">
-        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 227 - 1), NA())</f>
+        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 227 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q228">
-        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 227 - 1), NA())</f>
+        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 227 - 1), NA())</f>
         <v/>
       </c>
       <c r="R228">
-        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 227 - 1), NA())</f>
+        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 227 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="229">
       <c r="P229" s="2">
-        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 228 - 1), NA())</f>
+        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 228 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q229">
-        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 228 - 1), NA())</f>
+        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 228 - 1), NA())</f>
         <v/>
       </c>
       <c r="R229">
-        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 228 - 1), NA())</f>
+        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 228 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="230">
       <c r="P230" s="2">
-        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 229 - 1), NA())</f>
+        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 229 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q230">
-        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 229 - 1), NA())</f>
+        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 229 - 1), NA())</f>
         <v/>
       </c>
       <c r="R230">
-        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 229 - 1), NA())</f>
+        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 229 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="231">
       <c r="P231" s="2">
-        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 230 - 1), NA())</f>
+        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 230 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q231">
-        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 230 - 1), NA())</f>
+        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 230 - 1), NA())</f>
         <v/>
       </c>
       <c r="R231">
-        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 230 - 1), NA())</f>
+        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 230 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="232">
       <c r="P232" s="2">
-        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 231 - 1), NA())</f>
+        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 231 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q232">
-        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 231 - 1), NA())</f>
+        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 231 - 1), NA())</f>
         <v/>
       </c>
       <c r="R232">
-        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 231 - 1), NA())</f>
+        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 231 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="233">
       <c r="P233" s="2">
-        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 232 - 1), NA())</f>
+        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 232 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q233">
-        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 232 - 1), NA())</f>
+        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 232 - 1), NA())</f>
         <v/>
       </c>
       <c r="R233">
-        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 232 - 1), NA())</f>
+        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 232 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="234">
       <c r="P234" s="2">
-        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 233 - 1), NA())</f>
+        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 233 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q234">
-        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 233 - 1), NA())</f>
+        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 233 - 1), NA())</f>
         <v/>
       </c>
       <c r="R234">
-        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 233 - 1), NA())</f>
+        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 233 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="235">
       <c r="P235" s="2">
-        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 234 - 1), NA())</f>
+        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 234 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q235">
-        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 234 - 1), NA())</f>
+        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 234 - 1), NA())</f>
         <v/>
       </c>
       <c r="R235">
-        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 234 - 1), NA())</f>
+        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 234 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="236">
       <c r="P236" s="2">
-        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 235 - 1), NA())</f>
+        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 235 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q236">
-        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 235 - 1), NA())</f>
+        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 235 - 1), NA())</f>
         <v/>
       </c>
       <c r="R236">
-        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 235 - 1), NA())</f>
+        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 235 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="237">
       <c r="P237" s="2">
-        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 236 - 1), NA())</f>
+        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 236 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q237">
-        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 236 - 1), NA())</f>
+        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 236 - 1), NA())</f>
         <v/>
       </c>
       <c r="R237">
-        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 236 - 1), NA())</f>
+        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 236 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="238">
       <c r="P238" s="2">
-        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 237 - 1), NA())</f>
+        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 237 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q238">
-        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 237 - 1), NA())</f>
+        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 237 - 1), NA())</f>
         <v/>
       </c>
       <c r="R238">
-        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 237 - 1), NA())</f>
+        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 237 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="239">
       <c r="P239" s="2">
-        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 238 - 1), NA())</f>
+        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 238 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q239">
-        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 238 - 1), NA())</f>
+        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 238 - 1), NA())</f>
         <v/>
       </c>
       <c r="R239">
-        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 238 - 1), NA())</f>
+        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 238 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="240">
       <c r="P240" s="2">
-        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 239 - 1), NA())</f>
+        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 239 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q240">
-        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 239 - 1), NA())</f>
+        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 239 - 1), NA())</f>
         <v/>
       </c>
       <c r="R240">
-        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 239 - 1), NA())</f>
+        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 239 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="241">
       <c r="P241" s="2">
-        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 240 - 1), NA())</f>
+        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 240 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q241">
-        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 240 - 1), NA())</f>
+        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 240 - 1), NA())</f>
         <v/>
       </c>
       <c r="R241">
-        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 240 - 1), NA())</f>
+        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 240 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="242">
       <c r="P242" s="2">
-        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 241 - 1), NA())</f>
+        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 241 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q242">
-        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 241 - 1), NA())</f>
+        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 241 - 1), NA())</f>
         <v/>
       </c>
       <c r="R242">
-        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 241 - 1), NA())</f>
+        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 241 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="243">
       <c r="P243" s="2">
-        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 242 - 1), NA())</f>
+        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 242 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q243">
-        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 242 - 1), NA())</f>
+        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 242 - 1), NA())</f>
         <v/>
       </c>
       <c r="R243">
-        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 242 - 1), NA())</f>
+        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 242 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="244">
       <c r="P244" s="2">
-        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 243 - 1), NA())</f>
+        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 243 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q244">
-        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 243 - 1), NA())</f>
+        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 243 - 1), NA())</f>
         <v/>
       </c>
       <c r="R244">
-        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 243 - 1), NA())</f>
+        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 243 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="245">
       <c r="P245" s="2">
-        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 244 - 1), NA())</f>
+        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 244 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q245">
-        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 244 - 1), NA())</f>
+        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 244 - 1), NA())</f>
         <v/>
       </c>
       <c r="R245">
-        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 244 - 1), NA())</f>
+        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 244 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="246">
       <c r="P246" s="2">
-        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 245 - 1), NA())</f>
+        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 245 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q246">
-        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 245 - 1), NA())</f>
+        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 245 - 1), NA())</f>
         <v/>
       </c>
       <c r="R246">
-        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 245 - 1), NA())</f>
+        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 245 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="247">
       <c r="P247" s="2">
-        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 246 - 1), NA())</f>
+        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 246 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q247">
-        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 246 - 1), NA())</f>
+        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 246 - 1), NA())</f>
         <v/>
       </c>
       <c r="R247">
-        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 246 - 1), NA())</f>
+        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 246 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="248">
       <c r="P248" s="2">
-        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 247 - 1), NA())</f>
+        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 247 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q248">
-        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 247 - 1), NA())</f>
+        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 247 - 1), NA())</f>
         <v/>
       </c>
       <c r="R248">
-        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 247 - 1), NA())</f>
+        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 247 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="249">
       <c r="P249" s="2">
-        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 248 - 1), NA())</f>
+        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 248 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q249">
-        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 248 - 1), NA())</f>
+        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 248 - 1), NA())</f>
         <v/>
       </c>
       <c r="R249">
-        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 248 - 1), NA())</f>
+        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 248 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="250">
       <c r="P250" s="2">
-        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 249 - 1), NA())</f>
+        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 249 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q250">
-        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 249 - 1), NA())</f>
+        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 249 - 1), NA())</f>
         <v/>
       </c>
       <c r="R250">
-        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 249 - 1), NA())</f>
+        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 249 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="251">
       <c r="P251" s="2">
-        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 250 - 1), NA())</f>
+        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 250 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q251">
-        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 250 - 1), NA())</f>
+        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 250 - 1), NA())</f>
         <v/>
       </c>
       <c r="R251">
-        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 250 - 1), NA())</f>
+        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 250 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="252">
       <c r="P252" s="2">
-        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 251 - 1), NA())</f>
+        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 251 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q252">
-        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 251 - 1), NA())</f>
+        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 251 - 1), NA())</f>
         <v/>
       </c>
       <c r="R252">
-        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 251 - 1), NA())</f>
+        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 251 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="253">
       <c r="P253" s="2">
-        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 252 - 1), NA())</f>
+        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 252 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q253">
-        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 252 - 1), NA())</f>
+        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 252 - 1), NA())</f>
         <v/>
       </c>
       <c r="R253">
-        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 252 - 1), NA())</f>
+        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 252 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="254">
       <c r="P254" s="2">
-        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 253 - 1), NA())</f>
+        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 253 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q254">
-        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 253 - 1), NA())</f>
+        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 253 - 1), NA())</f>
         <v/>
       </c>
       <c r="R254">
-        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 253 - 1), NA())</f>
+        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 253 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="255">
       <c r="P255" s="2">
-        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 254 - 1), NA())</f>
+        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 254 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q255">
-        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 254 - 1), NA())</f>
+        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 254 - 1), NA())</f>
         <v/>
       </c>
       <c r="R255">
-        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 254 - 1), NA())</f>
+        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 254 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="256">
       <c r="P256" s="2">
-        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 255 - 1), NA())</f>
+        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 255 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q256">
-        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 255 - 1), NA())</f>
+        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 255 - 1), NA())</f>
         <v/>
       </c>
       <c r="R256">
-        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 255 - 1), NA())</f>
+        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 255 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="257">
       <c r="P257" s="2">
-        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 256 - 1), NA())</f>
+        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 256 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q257">
-        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 256 - 1), NA())</f>
+        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 256 - 1), NA())</f>
         <v/>
       </c>
       <c r="R257">
-        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 256 - 1), NA())</f>
+        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 256 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="258">
       <c r="P258" s="2">
-        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 257 - 1), NA())</f>
+        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 257 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q258">
-        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 257 - 1), NA())</f>
+        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 257 - 1), NA())</f>
         <v/>
       </c>
       <c r="R258">
-        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 257 - 1), NA())</f>
+        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 257 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="259">
       <c r="P259" s="2">
-        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 258 - 1), NA())</f>
+        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 258 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q259">
-        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 258 - 1), NA())</f>
+        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 258 - 1), NA())</f>
         <v/>
       </c>
       <c r="R259">
-        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 258 - 1), NA())</f>
+        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 258 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="260">
       <c r="P260" s="2">
-        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 259 - 1), NA())</f>
+        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 259 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q260">
-        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 259 - 1), NA())</f>
+        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 259 - 1), NA())</f>
         <v/>
       </c>
       <c r="R260">
-        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 259 - 1), NA())</f>
+        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 259 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="261">
       <c r="P261" s="2">
-        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 260 - 1), NA())</f>
+        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 260 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q261">
-        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 260 - 1), NA())</f>
+        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 260 - 1), NA())</f>
         <v/>
       </c>
       <c r="R261">
-        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 260 - 1), NA())</f>
+        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 260 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="262">
       <c r="P262" s="2">
-        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 261 - 1), NA())</f>
+        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 261 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q262">
-        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 261 - 1), NA())</f>
+        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 261 - 1), NA())</f>
         <v/>
       </c>
       <c r="R262">
-        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 261 - 1), NA())</f>
+        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 261 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="263">
       <c r="P263" s="2">
-        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 262 - 1), NA())</f>
+        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 262 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q263">
-        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 262 - 1), NA())</f>
+        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 262 - 1), NA())</f>
         <v/>
       </c>
       <c r="R263">
-        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 262 - 1), NA())</f>
+        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 262 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="264">
       <c r="P264" s="2">
-        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 263 - 1), NA())</f>
+        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 263 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q264">
-        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 263 - 1), NA())</f>
+        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 263 - 1), NA())</f>
         <v/>
       </c>
       <c r="R264">
-        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 263 - 1), NA())</f>
+        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 263 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="265">
       <c r="P265" s="2">
-        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 264 - 1), NA())</f>
+        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 264 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q265">
-        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 264 - 1), NA())</f>
+        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 264 - 1), NA())</f>
         <v/>
       </c>
       <c r="R265">
-        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 264 - 1), NA())</f>
+        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 264 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="266">
       <c r="P266" s="2">
-        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 265 - 1), NA())</f>
+        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 265 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q266">
-        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 265 - 1), NA())</f>
+        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 265 - 1), NA())</f>
         <v/>
       </c>
       <c r="R266">
-        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 265 - 1), NA())</f>
+        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 265 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="267">
       <c r="P267" s="2">
-        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 266 - 1), NA())</f>
+        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 266 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q267">
-        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 266 - 1), NA())</f>
+        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 266 - 1), NA())</f>
         <v/>
       </c>
       <c r="R267">
-        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 266 - 1), NA())</f>
+        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 266 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="268">
       <c r="P268" s="2">
-        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 267 - 1), NA())</f>
+        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 267 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q268">
-        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 267 - 1), NA())</f>
+        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 267 - 1), NA())</f>
         <v/>
       </c>
       <c r="R268">
-        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 267 - 1), NA())</f>
+        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 267 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="269">
       <c r="P269" s="2">
-        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 268 - 1), NA())</f>
+        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 268 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q269">
-        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 268 - 1), NA())</f>
+        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 268 - 1), NA())</f>
         <v/>
       </c>
       <c r="R269">
-        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 268 - 1), NA())</f>
+        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 268 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="270">
       <c r="P270" s="2">
-        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 269 - 1), NA())</f>
+        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 269 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q270">
-        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 269 - 1), NA())</f>
+        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 269 - 1), NA())</f>
         <v/>
       </c>
       <c r="R270">
-        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 269 - 1), NA())</f>
+        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 269 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="271">
       <c r="P271" s="2">
-        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 270 - 1), NA())</f>
+        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 270 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q271">
-        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 270 - 1), NA())</f>
+        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 270 - 1), NA())</f>
         <v/>
       </c>
       <c r="R271">
-        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 270 - 1), NA())</f>
+        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 270 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="272">
       <c r="P272" s="2">
-        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 271 - 1), NA())</f>
+        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 271 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q272">
-        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 271 - 1), NA())</f>
+        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 271 - 1), NA())</f>
         <v/>
       </c>
       <c r="R272">
-        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 271 - 1), NA())</f>
+        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 271 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="273">
       <c r="P273" s="2">
-        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 272 - 1), NA())</f>
+        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 272 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q273">
-        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 272 - 1), NA())</f>
+        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 272 - 1), NA())</f>
         <v/>
       </c>
       <c r="R273">
-        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 272 - 1), NA())</f>
+        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 272 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="274">
       <c r="P274" s="2">
-        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 273 - 1), NA())</f>
+        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 273 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q274">
-        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 273 - 1), NA())</f>
+        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 273 - 1), NA())</f>
         <v/>
       </c>
       <c r="R274">
-        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 273 - 1), NA())</f>
+        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 273 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="275">
       <c r="P275" s="2">
-        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 274 - 1), NA())</f>
+        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 274 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q275">
-        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 274 - 1), NA())</f>
+        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 274 - 1), NA())</f>
         <v/>
       </c>
       <c r="R275">
-        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 274 - 1), NA())</f>
+        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 274 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="276">
       <c r="P276" s="2">
-        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 275 - 1), NA())</f>
+        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 275 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q276">
-        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 275 - 1), NA())</f>
+        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 275 - 1), NA())</f>
         <v/>
       </c>
       <c r="R276">
-        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 275 - 1), NA())</f>
+        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 275 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="277">
       <c r="P277" s="2">
-        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 276 - 1), NA())</f>
+        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 276 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q277">
-        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 276 - 1), NA())</f>
+        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 276 - 1), NA())</f>
         <v/>
       </c>
       <c r="R277">
-        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 276 - 1), NA())</f>
+        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 276 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="278">
       <c r="P278" s="2">
-        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 277 - 1), NA())</f>
+        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 277 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q278">
-        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 277 - 1), NA())</f>
+        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 277 - 1), NA())</f>
         <v/>
       </c>
       <c r="R278">
-        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 277 - 1), NA())</f>
+        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 277 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="279">
       <c r="P279" s="2">
-        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 278 - 1), NA())</f>
+        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 278 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q279">
-        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 278 - 1), NA())</f>
+        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 278 - 1), NA())</f>
         <v/>
       </c>
       <c r="R279">
-        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 278 - 1), NA())</f>
+        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 278 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="280">
       <c r="P280" s="2">
-        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 279 - 1), NA())</f>
+        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 279 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q280">
-        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 279 - 1), NA())</f>
+        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 279 - 1), NA())</f>
         <v/>
       </c>
       <c r="R280">
-        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 279 - 1), NA())</f>
+        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 279 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="281">
       <c r="P281" s="2">
-        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 280 - 1), NA())</f>
+        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 280 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q281">
-        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 280 - 1), NA())</f>
+        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 280 - 1), NA())</f>
         <v/>
       </c>
       <c r="R281">
-        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 280 - 1), NA())</f>
+        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 280 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="282">
       <c r="P282" s="2">
-        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 281 - 1), NA())</f>
+        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 281 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q282">
-        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 281 - 1), NA())</f>
+        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 281 - 1), NA())</f>
         <v/>
       </c>
       <c r="R282">
-        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 281 - 1), NA())</f>
+        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 281 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="283">
       <c r="P283" s="2">
-        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 282 - 1), NA())</f>
+        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 282 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q283">
-        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 282 - 1), NA())</f>
+        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 282 - 1), NA())</f>
         <v/>
       </c>
       <c r="R283">
-        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 282 - 1), NA())</f>
+        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 282 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="284">
       <c r="P284" s="2">
-        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 283 - 1), NA())</f>
+        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 283 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q284">
-        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 283 - 1), NA())</f>
+        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 283 - 1), NA())</f>
         <v/>
       </c>
       <c r="R284">
-        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 283 - 1), NA())</f>
+        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 283 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="285">
       <c r="P285" s="2">
-        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 284 - 1), NA())</f>
+        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 284 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q285">
-        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 284 - 1), NA())</f>
+        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 284 - 1), NA())</f>
         <v/>
       </c>
       <c r="R285">
-        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 284 - 1), NA())</f>
+        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 284 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="286">
       <c r="P286" s="2">
-        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 285 - 1), NA())</f>
+        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 285 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q286">
-        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 285 - 1), NA())</f>
+        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 285 - 1), NA())</f>
         <v/>
       </c>
       <c r="R286">
-        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 285 - 1), NA())</f>
+        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 285 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="287">
       <c r="P287" s="2">
-        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 286 - 1), NA())</f>
+        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 286 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q287">
-        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 286 - 1), NA())</f>
+        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 286 - 1), NA())</f>
         <v/>
       </c>
       <c r="R287">
-        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 286 - 1), NA())</f>
+        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 286 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="288">
       <c r="P288" s="2">
-        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 287 - 1), NA())</f>
+        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 287 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q288">
-        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 287 - 1), NA())</f>
+        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 287 - 1), NA())</f>
         <v/>
       </c>
       <c r="R288">
-        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 287 - 1), NA())</f>
+        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 287 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="289">
       <c r="P289" s="2">
-        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 288 - 1), NA())</f>
+        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 288 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q289">
-        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 288 - 1), NA())</f>
+        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 288 - 1), NA())</f>
         <v/>
       </c>
       <c r="R289">
-        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 288 - 1), NA())</f>
+        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 288 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="290">
       <c r="P290" s="2">
-        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 289 - 1), NA())</f>
+        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 289 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q290">
-        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 289 - 1), NA())</f>
+        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 289 - 1), NA())</f>
         <v/>
       </c>
       <c r="R290">
-        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 289 - 1), NA())</f>
+        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 289 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="291">
       <c r="P291" s="2">
-        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 290 - 1), NA())</f>
+        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 290 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q291">
-        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 290 - 1), NA())</f>
+        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 290 - 1), NA())</f>
         <v/>
       </c>
       <c r="R291">
-        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 290 - 1), NA())</f>
+        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 290 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="292">
       <c r="P292" s="2">
-        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 291 - 1), NA())</f>
+        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 291 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q292">
-        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 291 - 1), NA())</f>
+        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 291 - 1), NA())</f>
         <v/>
       </c>
       <c r="R292">
-        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 291 - 1), NA())</f>
+        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 291 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="293">
       <c r="P293" s="2">
-        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 292 - 1), NA())</f>
+        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 292 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q293">
-        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 292 - 1), NA())</f>
+        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 292 - 1), NA())</f>
         <v/>
       </c>
       <c r="R293">
-        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 292 - 1), NA())</f>
+        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 292 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="294">
       <c r="P294" s="2">
-        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 293 - 1), NA())</f>
+        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 293 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q294">
-        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 293 - 1), NA())</f>
+        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 293 - 1), NA())</f>
         <v/>
       </c>
       <c r="R294">
-        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 293 - 1), NA())</f>
+        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 293 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="295">
       <c r="P295" s="2">
-        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 294 - 1), NA())</f>
+        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 294 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q295">
-        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 294 - 1), NA())</f>
+        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 294 - 1), NA())</f>
         <v/>
       </c>
       <c r="R295">
-        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 294 - 1), NA())</f>
+        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 294 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="296">
       <c r="P296" s="2">
-        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 295 - 1), NA())</f>
+        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 295 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q296">
-        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 295 - 1), NA())</f>
+        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 295 - 1), NA())</f>
         <v/>
       </c>
       <c r="R296">
-        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 295 - 1), NA())</f>
+        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 295 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="297">
       <c r="P297" s="2">
-        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 296 - 1), NA())</f>
+        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 296 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q297">
-        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 296 - 1), NA())</f>
+        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 296 - 1), NA())</f>
         <v/>
       </c>
       <c r="R297">
-        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 296 - 1), NA())</f>
+        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 296 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="298">
       <c r="P298" s="2">
-        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 297 - 1), NA())</f>
+        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 297 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q298">
-        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 297 - 1), NA())</f>
+        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 297 - 1), NA())</f>
         <v/>
       </c>
       <c r="R298">
-        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 297 - 1), NA())</f>
+        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 297 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="299">
       <c r="P299" s="2">
-        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 298 - 1), NA())</f>
+        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 298 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q299">
-        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 298 - 1), NA())</f>
+        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 298 - 1), NA())</f>
         <v/>
       </c>
       <c r="R299">
-        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 298 - 1), NA())</f>
+        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 298 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="300">
       <c r="P300" s="2">
-        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 299 - 1), NA())</f>
+        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 299 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q300">
-        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 299 - 1), NA())</f>
+        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 299 - 1), NA())</f>
         <v/>
       </c>
       <c r="R300">
-        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 299 - 1), NA())</f>
+        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 299 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="301">
       <c r="P301" s="2">
-        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 300 - 1), NA())</f>
+        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 300 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q301">
-        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 300 - 1), NA())</f>
+        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 300 - 1), NA())</f>
         <v/>
       </c>
       <c r="R301">
-        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 300 - 1), NA())</f>
+        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 300 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="302">
       <c r="P302" s="2">
-        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 301 - 1), NA())</f>
+        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 301 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q302">
-        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 301 - 1), NA())</f>
+        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 301 - 1), NA())</f>
         <v/>
       </c>
       <c r="R302">
-        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 301 - 1), NA())</f>
+        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 301 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="303">
       <c r="P303" s="2">
-        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 302 - 1), NA())</f>
+        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 302 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q303">
-        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 302 - 1), NA())</f>
+        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 302 - 1), NA())</f>
         <v/>
       </c>
       <c r="R303">
-        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 302 - 1), NA())</f>
+        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 302 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="304">
       <c r="P304" s="2">
-        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 303 - 1), NA())</f>
+        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 303 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q304">
-        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 303 - 1), NA())</f>
+        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 303 - 1), NA())</f>
         <v/>
       </c>
       <c r="R304">
-        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 303 - 1), NA())</f>
+        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 303 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="305">
       <c r="P305" s="2">
-        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 304 - 1), NA())</f>
+        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 304 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q305">
-        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 304 - 1), NA())</f>
+        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 304 - 1), NA())</f>
         <v/>
       </c>
       <c r="R305">
-        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 304 - 1), NA())</f>
+        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 304 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="306">
       <c r="P306" s="2">
-        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 305 - 1), NA())</f>
+        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 305 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q306">
-        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 305 - 1), NA())</f>
+        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 305 - 1), NA())</f>
         <v/>
       </c>
       <c r="R306">
-        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 305 - 1), NA())</f>
+        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 305 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="307">
       <c r="P307" s="2">
-        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 306 - 1), NA())</f>
+        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 306 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q307">
-        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 306 - 1), NA())</f>
+        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 306 - 1), NA())</f>
         <v/>
       </c>
       <c r="R307">
-        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 306 - 1), NA())</f>
+        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 306 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="308">
       <c r="P308" s="2">
-        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 307 - 1), NA())</f>
+        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 307 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q308">
-        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 307 - 1), NA())</f>
+        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 307 - 1), NA())</f>
         <v/>
       </c>
       <c r="R308">
-        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 307 - 1), NA())</f>
+        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 307 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="309">
       <c r="P309" s="2">
-        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 308 - 1), NA())</f>
+        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 308 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q309">
-        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 308 - 1), NA())</f>
+        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 308 - 1), NA())</f>
         <v/>
       </c>
       <c r="R309">
-        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 308 - 1), NA())</f>
+        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 308 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="310">
       <c r="P310" s="2">
-        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 309 - 1), NA())</f>
+        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 309 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q310">
-        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 309 - 1), NA())</f>
+        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 309 - 1), NA())</f>
         <v/>
       </c>
       <c r="R310">
-        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 309 - 1), NA())</f>
+        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 309 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="311">
       <c r="P311" s="2">
-        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 310 - 1), NA())</f>
+        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 310 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q311">
-        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 310 - 1), NA())</f>
+        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 310 - 1), NA())</f>
         <v/>
       </c>
       <c r="R311">
-        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 310 - 1), NA())</f>
+        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 310 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="312">
       <c r="P312" s="2">
-        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 311 - 1), NA())</f>
+        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 311 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q312">
-        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 311 - 1), NA())</f>
+        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 311 - 1), NA())</f>
         <v/>
       </c>
       <c r="R312">
-        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 311 - 1), NA())</f>
+        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 311 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="313">
       <c r="P313" s="2">
-        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 312 - 1), NA())</f>
+        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 312 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q313">
-        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 312 - 1), NA())</f>
+        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 312 - 1), NA())</f>
         <v/>
       </c>
       <c r="R313">
-        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 312 - 1), NA())</f>
+        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 312 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="314">
       <c r="P314" s="2">
-        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 313 - 1), NA())</f>
+        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 313 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q314">
-        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 313 - 1), NA())</f>
+        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 313 - 1), NA())</f>
         <v/>
       </c>
       <c r="R314">
-        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 313 - 1), NA())</f>
+        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 313 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="315">
       <c r="P315" s="2">
-        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 314 - 1), NA())</f>
+        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 314 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q315">
-        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 314 - 1), NA())</f>
+        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 314 - 1), NA())</f>
         <v/>
       </c>
       <c r="R315">
-        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 314 - 1), NA())</f>
+        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 314 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="316">
       <c r="P316" s="2">
-        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 315 - 1), NA())</f>
+        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 315 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q316">
-        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 315 - 1), NA())</f>
+        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 315 - 1), NA())</f>
         <v/>
       </c>
       <c r="R316">
-        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 315 - 1), NA())</f>
+        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 315 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="317">
       <c r="P317" s="2">
-        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 316 - 1), NA())</f>
+        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 316 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q317">
-        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 316 - 1), NA())</f>
+        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 316 - 1), NA())</f>
         <v/>
       </c>
       <c r="R317">
-        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 316 - 1), NA())</f>
+        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 316 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="318">
       <c r="P318" s="2">
-        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 317 - 1), NA())</f>
+        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 317 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q318">
-        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 317 - 1), NA())</f>
+        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 317 - 1), NA())</f>
         <v/>
       </c>
       <c r="R318">
-        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 317 - 1), NA())</f>
+        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 317 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="319">
       <c r="P319" s="2">
-        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 318 - 1), NA())</f>
+        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 318 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q319">
-        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 318 - 1), NA())</f>
+        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 318 - 1), NA())</f>
         <v/>
       </c>
       <c r="R319">
-        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 318 - 1), NA())</f>
+        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 318 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="320">
       <c r="P320" s="2">
-        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 319 - 1), NA())</f>
+        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 319 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q320">
-        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 319 - 1), NA())</f>
+        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 319 - 1), NA())</f>
         <v/>
       </c>
       <c r="R320">
-        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 319 - 1), NA())</f>
+        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 319 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="321">
       <c r="P321" s="2">
-        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 320 - 1), NA())</f>
+        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 320 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q321">
-        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 320 - 1), NA())</f>
+        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 320 - 1), NA())</f>
         <v/>
       </c>
       <c r="R321">
-        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 320 - 1), NA())</f>
+        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 320 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="322">
       <c r="P322" s="2">
-        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 321 - 1), NA())</f>
+        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 321 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q322">
-        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 321 - 1), NA())</f>
+        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 321 - 1), NA())</f>
         <v/>
       </c>
       <c r="R322">
-        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 321 - 1), NA())</f>
+        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 321 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="323">
       <c r="P323" s="2">
-        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 322 - 1), NA())</f>
+        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 322 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q323">
-        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 322 - 1), NA())</f>
+        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 322 - 1), NA())</f>
         <v/>
       </c>
       <c r="R323">
-        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 322 - 1), NA())</f>
+        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 322 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="324">
       <c r="P324" s="2">
-        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 323 - 1), NA())</f>
+        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 323 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q324">
-        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 323 - 1), NA())</f>
+        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 323 - 1), NA())</f>
         <v/>
       </c>
       <c r="R324">
-        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 323 - 1), NA())</f>
+        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 323 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="325">
       <c r="P325" s="2">
-        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 324 - 1), NA())</f>
+        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 324 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q325">
-        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 324 - 1), NA())</f>
+        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 324 - 1), NA())</f>
         <v/>
       </c>
       <c r="R325">
-        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 324 - 1), NA())</f>
+        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 324 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="326">
       <c r="P326" s="2">
-        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 325 - 1), NA())</f>
+        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 325 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q326">
-        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 325 - 1), NA())</f>
+        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 325 - 1), NA())</f>
         <v/>
       </c>
       <c r="R326">
-        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 325 - 1), NA())</f>
+        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 325 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="327">
       <c r="P327" s="2">
-        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 326 - 1), NA())</f>
+        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 326 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q327">
-        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 326 - 1), NA())</f>
+        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 326 - 1), NA())</f>
         <v/>
       </c>
       <c r="R327">
-        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 326 - 1), NA())</f>
+        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 326 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="328">
       <c r="P328" s="2">
-        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 327 - 1), NA())</f>
+        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 327 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q328">
-        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 327 - 1), NA())</f>
+        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 327 - 1), NA())</f>
         <v/>
       </c>
       <c r="R328">
-        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 327 - 1), NA())</f>
+        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 327 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="329">
       <c r="P329" s="2">
-        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 328 - 1), NA())</f>
+        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 328 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q329">
-        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 328 - 1), NA())</f>
+        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 328 - 1), NA())</f>
         <v/>
       </c>
       <c r="R329">
-        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 328 - 1), NA())</f>
+        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 328 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="330">
       <c r="P330" s="2">
-        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 329 - 1), NA())</f>
+        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 329 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q330">
-        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 329 - 1), NA())</f>
+        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 329 - 1), NA())</f>
         <v/>
       </c>
       <c r="R330">
-        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 329 - 1), NA())</f>
+        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 329 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="331">
       <c r="P331" s="2">
-        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 330 - 1), NA())</f>
+        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 330 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q331">
-        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 330 - 1), NA())</f>
+        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 330 - 1), NA())</f>
         <v/>
       </c>
       <c r="R331">
-        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 330 - 1), NA())</f>
+        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 330 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="332">
       <c r="P332" s="2">
-        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 331 - 1), NA())</f>
+        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 331 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q332">
-        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 331 - 1), NA())</f>
+        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 331 - 1), NA())</f>
         <v/>
       </c>
       <c r="R332">
-        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 331 - 1), NA())</f>
+        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 331 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="333">
       <c r="P333" s="2">
-        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 332 - 1), NA())</f>
+        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 332 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q333">
-        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 332 - 1), NA())</f>
+        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 332 - 1), NA())</f>
         <v/>
       </c>
       <c r="R333">
-        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 332 - 1), NA())</f>
+        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 332 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="334">
       <c r="P334" s="2">
-        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 333 - 1), NA())</f>
+        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 333 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q334">
-        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 333 - 1), NA())</f>
+        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 333 - 1), NA())</f>
         <v/>
       </c>
       <c r="R334">
-        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 333 - 1), NA())</f>
+        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 333 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="335">
       <c r="P335" s="2">
-        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 334 - 1), NA())</f>
+        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 334 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q335">
-        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 334 - 1), NA())</f>
+        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 334 - 1), NA())</f>
         <v/>
       </c>
       <c r="R335">
-        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 334 - 1), NA())</f>
+        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 334 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="336">
       <c r="P336" s="2">
-        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 335 - 1), NA())</f>
+        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 335 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q336">
-        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 335 - 1), NA())</f>
+        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 335 - 1), NA())</f>
         <v/>
       </c>
       <c r="R336">
-        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 335 - 1), NA())</f>
+        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 335 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="337">
       <c r="P337" s="2">
-        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 336 - 1), NA())</f>
+        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 336 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q337">
-        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 336 - 1), NA())</f>
+        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 336 - 1), NA())</f>
         <v/>
       </c>
       <c r="R337">
-        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 336 - 1), NA())</f>
+        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 336 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="338">
       <c r="P338" s="2">
-        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 337 - 1), NA())</f>
+        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 337 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q338">
-        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 337 - 1), NA())</f>
+        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 337 - 1), NA())</f>
         <v/>
       </c>
       <c r="R338">
-        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 337 - 1), NA())</f>
+        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 337 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="339">
       <c r="P339" s="2">
-        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 338 - 1), NA())</f>
+        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 338 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q339">
-        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 338 - 1), NA())</f>
+        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 338 - 1), NA())</f>
         <v/>
       </c>
       <c r="R339">
-        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 338 - 1), NA())</f>
+        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 338 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="340">
       <c r="P340" s="2">
-        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 339 - 1), NA())</f>
+        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 339 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q340">
-        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 339 - 1), NA())</f>
+        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 339 - 1), NA())</f>
         <v/>
       </c>
       <c r="R340">
-        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 339 - 1), NA())</f>
+        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 339 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="341">
       <c r="P341" s="2">
-        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 340 - 1), NA())</f>
+        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 340 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q341">
-        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 340 - 1), NA())</f>
+        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 340 - 1), NA())</f>
         <v/>
       </c>
       <c r="R341">
-        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 340 - 1), NA())</f>
+        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 340 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="342">
       <c r="P342" s="2">
-        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 341 - 1), NA())</f>
+        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 341 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q342">
-        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 341 - 1), NA())</f>
+        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 341 - 1), NA())</f>
         <v/>
       </c>
       <c r="R342">
-        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 341 - 1), NA())</f>
+        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 341 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="343">
       <c r="P343" s="2">
-        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 342 - 1), NA())</f>
+        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 342 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q343">
-        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 342 - 1), NA())</f>
+        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 342 - 1), NA())</f>
         <v/>
       </c>
       <c r="R343">
-        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 342 - 1), NA())</f>
+        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 342 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="344">
       <c r="P344" s="2">
-        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 343 - 1), NA())</f>
+        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 343 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q344">
-        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 343 - 1), NA())</f>
+        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 343 - 1), NA())</f>
         <v/>
       </c>
       <c r="R344">
-        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 343 - 1), NA())</f>
+        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 343 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="345">
       <c r="P345" s="2">
-        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 344 - 1), NA())</f>
+        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 344 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q345">
-        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 344 - 1), NA())</f>
+        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 344 - 1), NA())</f>
         <v/>
       </c>
       <c r="R345">
-        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 344 - 1), NA())</f>
+        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 344 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="346">
       <c r="P346" s="2">
-        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 345 - 1), NA())</f>
+        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 345 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q346">
-        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 345 - 1), NA())</f>
+        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 345 - 1), NA())</f>
         <v/>
       </c>
       <c r="R346">
-        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 345 - 1), NA())</f>
+        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 345 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="347">
       <c r="P347" s="2">
-        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 346 - 1), NA())</f>
+        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 346 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q347">
-        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 346 - 1), NA())</f>
+        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 346 - 1), NA())</f>
         <v/>
       </c>
       <c r="R347">
-        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 346 - 1), NA())</f>
+        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 346 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="348">
       <c r="P348" s="2">
-        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 347 - 1), NA())</f>
+        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 347 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q348">
-        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 347 - 1), NA())</f>
+        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 347 - 1), NA())</f>
         <v/>
       </c>
       <c r="R348">
-        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 347 - 1), NA())</f>
+        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 347 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="349">
       <c r="P349" s="2">
-        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 348 - 1), NA())</f>
+        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 348 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q349">
-        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 348 - 1), NA())</f>
+        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 348 - 1), NA())</f>
         <v/>
       </c>
       <c r="R349">
-        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 348 - 1), NA())</f>
+        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 348 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="350">
       <c r="P350" s="2">
-        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 349 - 1), NA())</f>
+        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 349 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q350">
-        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 349 - 1), NA())</f>
+        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 349 - 1), NA())</f>
         <v/>
       </c>
       <c r="R350">
-        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 349 - 1), NA())</f>
+        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 349 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="351">
       <c r="P351" s="2">
-        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 350 - 1), NA())</f>
+        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 350 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q351">
-        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 350 - 1), NA())</f>
+        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 350 - 1), NA())</f>
         <v/>
       </c>
       <c r="R351">
-        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 350 - 1), NA())</f>
+        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 350 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="352">
       <c r="P352" s="2">
-        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 351 - 1), NA())</f>
+        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 351 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q352">
-        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 351 - 1), NA())</f>
+        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 351 - 1), NA())</f>
         <v/>
       </c>
       <c r="R352">
-        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 351 - 1), NA())</f>
+        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 351 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="353">
       <c r="P353" s="2">
-        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 352 - 1), NA())</f>
+        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 352 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q353">
-        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 352 - 1), NA())</f>
+        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 352 - 1), NA())</f>
         <v/>
       </c>
       <c r="R353">
-        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 352 - 1), NA())</f>
+        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 352 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="354">
       <c r="P354" s="2">
-        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 353 - 1), NA())</f>
+        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 353 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q354">
-        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 353 - 1), NA())</f>
+        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 353 - 1), NA())</f>
         <v/>
       </c>
       <c r="R354">
-        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 353 - 1), NA())</f>
+        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 353 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="355">
       <c r="P355" s="2">
-        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 354 - 1), NA())</f>
+        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 354 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q355">
-        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 354 - 1), NA())</f>
+        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 354 - 1), NA())</f>
         <v/>
       </c>
       <c r="R355">
-        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 354 - 1), NA())</f>
+        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 354 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="356">
       <c r="P356" s="2">
-        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 355 - 1), NA())</f>
+        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 355 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q356">
-        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 355 - 1), NA())</f>
+        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 355 - 1), NA())</f>
         <v/>
       </c>
       <c r="R356">
-        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 355 - 1), NA())</f>
+        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 355 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="357">
       <c r="P357" s="2">
-        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 356 - 1), NA())</f>
+        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 356 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q357">
-        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 356 - 1), NA())</f>
+        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 356 - 1), NA())</f>
         <v/>
       </c>
       <c r="R357">
-        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 356 - 1), NA())</f>
+        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 356 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="358">
       <c r="P358" s="2">
-        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 357 - 1), NA())</f>
+        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 357 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q358">
-        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 357 - 1), NA())</f>
+        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 357 - 1), NA())</f>
         <v/>
       </c>
       <c r="R358">
-        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 357 - 1), NA())</f>
+        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 357 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="359">
       <c r="P359" s="2">
-        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 358 - 1), NA())</f>
+        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 358 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q359">
-        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 358 - 1), NA())</f>
+        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 358 - 1), NA())</f>
         <v/>
       </c>
       <c r="R359">
-        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 358 - 1), NA())</f>
+        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 358 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="360">
       <c r="P360" s="2">
-        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 359 - 1), NA())</f>
+        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 359 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q360">
-        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 359 - 1), NA())</f>
+        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 359 - 1), NA())</f>
         <v/>
       </c>
       <c r="R360">
-        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 359 - 1), NA())</f>
+        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 359 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="361">
       <c r="P361" s="2">
-        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 360 - 1), NA())</f>
+        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 360 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q361">
-        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 360 - 1), NA())</f>
+        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 360 - 1), NA())</f>
         <v/>
       </c>
       <c r="R361">
-        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 360 - 1), NA())</f>
+        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 360 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="362">
       <c r="P362" s="2">
-        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 361 - 1), NA())</f>
+        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 361 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q362">
-        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 361 - 1), NA())</f>
+        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 361 - 1), NA())</f>
         <v/>
       </c>
       <c r="R362">
-        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 361 - 1), NA())</f>
+        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 361 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="363">
       <c r="P363" s="2">
-        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 362 - 1), NA())</f>
+        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 362 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q363">
-        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 362 - 1), NA())</f>
+        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 362 - 1), NA())</f>
         <v/>
       </c>
       <c r="R363">
-        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 362 - 1), NA())</f>
+        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 362 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="364">
       <c r="P364" s="2">
-        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 363 - 1), NA())</f>
+        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 363 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q364">
-        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 363 - 1), NA())</f>
+        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 363 - 1), NA())</f>
         <v/>
       </c>
       <c r="R364">
-        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 363 - 1), NA())</f>
+        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 363 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="365">
       <c r="P365" s="2">
-        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 364 - 1), NA())</f>
+        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 364 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q365">
-        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 364 - 1), NA())</f>
+        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 364 - 1), NA())</f>
         <v/>
       </c>
       <c r="R365">
-        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 364 - 1), NA())</f>
+        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 364 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="366">
       <c r="P366" s="2">
-        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 365 - 1), NA())</f>
+        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 365 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q366">
-        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 365 - 1), NA())</f>
+        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 365 - 1), NA())</f>
         <v/>
       </c>
       <c r="R366">
-        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 365 - 1), NA())</f>
+        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 365 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="367">
       <c r="P367" s="2">
-        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 366 - 1), NA())</f>
+        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 366 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q367">
-        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 366 - 1), NA())</f>
+        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 366 - 1), NA())</f>
         <v/>
       </c>
       <c r="R367">
-        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 366 - 1), NA())</f>
+        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 366 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="368">
       <c r="P368" s="2">
-        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 367 - 1), NA())</f>
+        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 367 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q368">
-        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 367 - 1), NA())</f>
+        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 367 - 1), NA())</f>
         <v/>
       </c>
       <c r="R368">
-        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 367 - 1), NA())</f>
+        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 367 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="369">
       <c r="P369" s="2">
-        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 368 - 1), NA())</f>
+        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 368 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q369">
-        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 368 - 1), NA())</f>
+        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 368 - 1), NA())</f>
         <v/>
       </c>
       <c r="R369">
-        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 368 - 1), NA())</f>
+        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 368 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="370">
       <c r="P370" s="2">
-        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 369 - 1), NA())</f>
+        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 369 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q370">
-        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 369 - 1), NA())</f>
+        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 369 - 1), NA())</f>
         <v/>
       </c>
       <c r="R370">
-        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 369 - 1), NA())</f>
+        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 369 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="371">
       <c r="P371" s="2">
-        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 370 - 1), NA())</f>
+        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 370 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q371">
-        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 370 - 1), NA())</f>
+        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 370 - 1), NA())</f>
         <v/>
       </c>
       <c r="R371">
-        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 370 - 1), NA())</f>
+        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 370 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="372">
       <c r="P372" s="2">
-        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 371 - 1), NA())</f>
+        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 371 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q372">
-        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 371 - 1), NA())</f>
+        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 371 - 1), NA())</f>
         <v/>
       </c>
       <c r="R372">
-        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 371 - 1), NA())</f>
+        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 371 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="373">
       <c r="P373" s="2">
-        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 372 - 1), NA())</f>
+        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 372 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q373">
-        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 372 - 1), NA())</f>
+        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 372 - 1), NA())</f>
         <v/>
       </c>
       <c r="R373">
-        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 372 - 1), NA())</f>
+        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 372 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="374">
       <c r="P374" s="2">
-        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 373 - 1), NA())</f>
+        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 373 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q374">
-        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 373 - 1), NA())</f>
+        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 373 - 1), NA())</f>
         <v/>
       </c>
       <c r="R374">
-        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 373 - 1), NA())</f>
+        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 373 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="375">
       <c r="P375" s="2">
-        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 374 - 1), NA())</f>
+        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 374 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q375">
-        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 374 - 1), NA())</f>
+        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 374 - 1), NA())</f>
         <v/>
       </c>
       <c r="R375">
-        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 374 - 1), NA())</f>
+        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 374 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="376">
       <c r="P376" s="2">
-        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 375 - 1), NA())</f>
+        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 375 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q376">
-        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 375 - 1), NA())</f>
+        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 375 - 1), NA())</f>
         <v/>
       </c>
       <c r="R376">
-        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 375 - 1), NA())</f>
+        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 375 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="377">
       <c r="P377" s="2">
-        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 376 - 1), NA())</f>
+        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 376 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q377">
-        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 376 - 1), NA())</f>
+        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 376 - 1), NA())</f>
         <v/>
       </c>
       <c r="R377">
-        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 376 - 1), NA())</f>
+        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 376 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="378">
       <c r="P378" s="2">
-        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 377 - 1), NA())</f>
+        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 377 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q378">
-        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 377 - 1), NA())</f>
+        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 377 - 1), NA())</f>
         <v/>
       </c>
       <c r="R378">
-        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 377 - 1), NA())</f>
+        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 377 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="379">
       <c r="P379" s="2">
-        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 378 - 1), NA())</f>
+        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 378 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q379">
-        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 378 - 1), NA())</f>
+        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 378 - 1), NA())</f>
         <v/>
       </c>
       <c r="R379">
-        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 378 - 1), NA())</f>
+        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 378 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="380">
       <c r="P380" s="2">
-        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 379 - 1), NA())</f>
+        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 379 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q380">
-        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 379 - 1), NA())</f>
+        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 379 - 1), NA())</f>
         <v/>
       </c>
       <c r="R380">
-        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 379 - 1), NA())</f>
+        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 379 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="381">
       <c r="P381" s="2">
-        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 380 - 1), NA())</f>
+        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 380 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q381">
-        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 380 - 1), NA())</f>
+        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 380 - 1), NA())</f>
         <v/>
       </c>
       <c r="R381">
-        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 380 - 1), NA())</f>
+        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 380 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="382">
       <c r="P382" s="2">
-        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 381 - 1), NA())</f>
+        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 381 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q382">
-        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 381 - 1), NA())</f>
+        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 381 - 1), NA())</f>
         <v/>
       </c>
       <c r="R382">
-        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 381 - 1), NA())</f>
+        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 381 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="383">
       <c r="P383" s="2">
-        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 382 - 1), NA())</f>
+        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 382 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q383">
-        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 382 - 1), NA())</f>
+        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 382 - 1), NA())</f>
         <v/>
       </c>
       <c r="R383">
-        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 382 - 1), NA())</f>
+        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 382 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="384">
       <c r="P384" s="2">
-        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 383 - 1), NA())</f>
+        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 383 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q384">
-        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 383 - 1), NA())</f>
+        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 383 - 1), NA())</f>
         <v/>
       </c>
       <c r="R384">
-        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 383 - 1), NA())</f>
+        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 383 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="385">
       <c r="P385" s="2">
-        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 384 - 1), NA())</f>
+        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 384 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q385">
-        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 384 - 1), NA())</f>
+        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 384 - 1), NA())</f>
         <v/>
       </c>
       <c r="R385">
-        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 384 - 1), NA())</f>
+        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 384 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="386">
       <c r="P386" s="2">
-        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 385 - 1), NA())</f>
+        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 385 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q386">
-        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 385 - 1), NA())</f>
+        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 385 - 1), NA())</f>
         <v/>
       </c>
       <c r="R386">
-        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 385 - 1), NA())</f>
+        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 385 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="387">
       <c r="P387" s="2">
-        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 386 - 1), NA())</f>
+        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 386 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q387">
-        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 386 - 1), NA())</f>
+        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 386 - 1), NA())</f>
         <v/>
       </c>
       <c r="R387">
-        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 386 - 1), NA())</f>
+        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 386 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="388">
       <c r="P388" s="2">
-        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 387 - 1), NA())</f>
+        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 387 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q388">
-        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 387 - 1), NA())</f>
+        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 387 - 1), NA())</f>
         <v/>
       </c>
       <c r="R388">
-        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 387 - 1), NA())</f>
+        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 387 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="389">
       <c r="P389" s="2">
-        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 388 - 1), NA())</f>
+        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 388 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q389">
-        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 388 - 1), NA())</f>
+        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 388 - 1), NA())</f>
         <v/>
       </c>
       <c r="R389">
-        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 388 - 1), NA())</f>
+        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 388 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="390">
       <c r="P390" s="2">
-        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 389 - 1), NA())</f>
+        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 389 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q390">
-        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 389 - 1), NA())</f>
+        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 389 - 1), NA())</f>
         <v/>
       </c>
       <c r="R390">
-        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 389 - 1), NA())</f>
+        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 389 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="391">
       <c r="P391" s="2">
-        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 390 - 1), NA())</f>
+        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 390 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q391">
-        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 390 - 1), NA())</f>
+        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 390 - 1), NA())</f>
         <v/>
       </c>
       <c r="R391">
-        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 390 - 1), NA())</f>
+        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 390 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="392">
       <c r="P392" s="2">
-        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 391 - 1), NA())</f>
+        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 391 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q392">
-        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 391 - 1), NA())</f>
+        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 391 - 1), NA())</f>
         <v/>
       </c>
       <c r="R392">
-        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 391 - 1), NA())</f>
+        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 391 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="393">
       <c r="P393" s="2">
-        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 392 - 1), NA())</f>
+        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 392 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q393">
-        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 392 - 1), NA())</f>
+        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 392 - 1), NA())</f>
         <v/>
       </c>
       <c r="R393">
-        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 392 - 1), NA())</f>
+        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 392 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="394">
       <c r="P394" s="2">
-        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 393 - 1), NA())</f>
+        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 393 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q394">
-        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 393 - 1), NA())</f>
+        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 393 - 1), NA())</f>
         <v/>
       </c>
       <c r="R394">
-        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 393 - 1), NA())</f>
+        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 393 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="395">
       <c r="P395" s="2">
-        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 394 - 1), NA())</f>
+        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 394 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q395">
-        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 394 - 1), NA())</f>
+        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 394 - 1), NA())</f>
         <v/>
       </c>
       <c r="R395">
-        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 394 - 1), NA())</f>
+        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 394 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="396">
       <c r="P396" s="2">
-        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 395 - 1), NA())</f>
+        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 395 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q396">
-        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 395 - 1), NA())</f>
+        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 395 - 1), NA())</f>
         <v/>
       </c>
       <c r="R396">
-        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 395 - 1), NA())</f>
+        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 395 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="397">
       <c r="P397" s="2">
-        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 396 - 1), NA())</f>
+        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 396 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q397">
-        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 396 - 1), NA())</f>
+        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 396 - 1), NA())</f>
         <v/>
       </c>
       <c r="R397">
-        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 396 - 1), NA())</f>
+        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 396 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="398">
       <c r="P398" s="2">
-        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 397 - 1), NA())</f>
+        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 397 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q398">
-        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 397 - 1), NA())</f>
+        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 397 - 1), NA())</f>
         <v/>
       </c>
       <c r="R398">
-        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 397 - 1), NA())</f>
+        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 397 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="399">
       <c r="P399" s="2">
-        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 398 - 1), NA())</f>
+        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 398 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q399">
-        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 398 - 1), NA())</f>
+        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 398 - 1), NA())</f>
         <v/>
       </c>
       <c r="R399">
-        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 398 - 1), NA())</f>
+        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 398 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="400">
       <c r="P400" s="2">
-        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 399 - 1), NA())</f>
+        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 399 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q400">
-        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 399 - 1), NA())</f>
+        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 399 - 1), NA())</f>
         <v/>
       </c>
       <c r="R400">
-        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 399 - 1), NA())</f>
+        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 399 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="401">
       <c r="P401" s="2">
-        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 400 - 1), NA())</f>
+        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 400 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q401">
-        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 400 - 1), NA())</f>
+        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 400 - 1), NA())</f>
         <v/>
       </c>
       <c r="R401">
-        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 400 - 1), NA())</f>
+        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 400 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="402">
       <c r="P402" s="2">
-        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 401 - 1), NA())</f>
+        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 401 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q402">
-        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 401 - 1), NA())</f>
+        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 401 - 1), NA())</f>
         <v/>
       </c>
       <c r="R402">
-        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 401 - 1), NA())</f>
+        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 401 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="403">
       <c r="P403" s="2">
-        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 402 - 1), NA())</f>
+        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 402 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q403">
-        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 402 - 1), NA())</f>
+        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 402 - 1), NA())</f>
         <v/>
       </c>
       <c r="R403">
-        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 402 - 1), NA())</f>
+        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 402 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="404">
       <c r="P404" s="2">
-        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 403 - 1), NA())</f>
+        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 403 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q404">
-        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 403 - 1), NA())</f>
+        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 403 - 1), NA())</f>
         <v/>
       </c>
       <c r="R404">
-        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 403 - 1), NA())</f>
+        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 403 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="405">
       <c r="P405" s="2">
-        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 404 - 1), NA())</f>
+        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 404 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q405">
-        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 404 - 1), NA())</f>
+        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 404 - 1), NA())</f>
         <v/>
       </c>
       <c r="R405">
-        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 404 - 1), NA())</f>
+        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 404 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="406">
       <c r="P406" s="2">
-        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 405 - 1), NA())</f>
+        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 405 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q406">
-        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 405 - 1), NA())</f>
+        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 405 - 1), NA())</f>
         <v/>
       </c>
       <c r="R406">
-        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 405 - 1), NA())</f>
+        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 405 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="407">
       <c r="P407" s="2">
-        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 406 - 1), NA())</f>
+        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 406 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q407">
-        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 406 - 1), NA())</f>
+        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 406 - 1), NA())</f>
         <v/>
       </c>
       <c r="R407">
-        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 406 - 1), NA())</f>
+        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 406 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="408">
       <c r="P408" s="2">
-        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 407 - 1), NA())</f>
+        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 407 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q408">
-        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 407 - 1), NA())</f>
+        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 407 - 1), NA())</f>
         <v/>
       </c>
       <c r="R408">
-        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 407 - 1), NA())</f>
+        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 407 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="409">
       <c r="P409" s="2">
-        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 408 - 1), NA())</f>
+        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 408 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q409">
-        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 408 - 1), NA())</f>
+        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 408 - 1), NA())</f>
         <v/>
       </c>
       <c r="R409">
-        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 408 - 1), NA())</f>
+        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 408 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="410">
       <c r="P410" s="2">
-        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 409 - 1), NA())</f>
+        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 409 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q410">
-        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 409 - 1), NA())</f>
+        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 409 - 1), NA())</f>
         <v/>
       </c>
       <c r="R410">
-        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 409 - 1), NA())</f>
+        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 409 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="411">
       <c r="P411" s="2">
-        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 410 - 1), NA())</f>
+        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 410 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q411">
-        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 410 - 1), NA())</f>
+        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 410 - 1), NA())</f>
         <v/>
       </c>
       <c r="R411">
-        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 410 - 1), NA())</f>
+        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 410 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="412">
       <c r="P412" s="2">
-        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 411 - 1), NA())</f>
+        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 411 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q412">
-        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 411 - 1), NA())</f>
+        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 411 - 1), NA())</f>
         <v/>
       </c>
       <c r="R412">
-        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 411 - 1), NA())</f>
+        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 411 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="413">
       <c r="P413" s="2">
-        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 412 - 1), NA())</f>
+        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 412 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q413">
-        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 412 - 1), NA())</f>
+        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 412 - 1), NA())</f>
         <v/>
       </c>
       <c r="R413">
-        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 412 - 1), NA())</f>
+        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 412 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="414">
       <c r="P414" s="2">
-        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 413 - 1), NA())</f>
+        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 413 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q414">
-        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 413 - 1), NA())</f>
+        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 413 - 1), NA())</f>
         <v/>
       </c>
       <c r="R414">
-        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 413 - 1), NA())</f>
+        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 413 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="415">
       <c r="P415" s="2">
-        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 414 - 1), NA())</f>
+        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 414 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q415">
-        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 414 - 1), NA())</f>
+        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 414 - 1), NA())</f>
         <v/>
       </c>
       <c r="R415">
-        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 414 - 1), NA())</f>
+        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 414 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="416">
       <c r="P416" s="2">
-        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 415 - 1), NA())</f>
+        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 415 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q416">
-        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 415 - 1), NA())</f>
+        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 415 - 1), NA())</f>
         <v/>
       </c>
       <c r="R416">
-        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 415 - 1), NA())</f>
+        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 415 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="417">
       <c r="P417" s="2">
-        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 416 - 1), NA())</f>
+        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 416 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q417">
-        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 416 - 1), NA())</f>
+        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 416 - 1), NA())</f>
         <v/>
       </c>
       <c r="R417">
-        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 416 - 1), NA())</f>
+        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 416 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="418">
       <c r="P418" s="2">
-        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 417 - 1), NA())</f>
+        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 417 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q418">
-        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 417 - 1), NA())</f>
+        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 417 - 1), NA())</f>
         <v/>
       </c>
       <c r="R418">
-        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 417 - 1), NA())</f>
+        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 417 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="419">
       <c r="P419" s="2">
-        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 418 - 1), NA())</f>
+        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 418 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q419">
-        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 418 - 1), NA())</f>
+        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 418 - 1), NA())</f>
         <v/>
       </c>
       <c r="R419">
-        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 418 - 1), NA())</f>
+        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 418 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="420">
       <c r="P420" s="2">
-        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 419 - 1), NA())</f>
+        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 419 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q420">
-        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 419 - 1), NA())</f>
+        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 419 - 1), NA())</f>
         <v/>
       </c>
       <c r="R420">
-        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 419 - 1), NA())</f>
+        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 419 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="421">
       <c r="P421" s="2">
-        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 420 - 1), NA())</f>
+        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 420 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q421">
-        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 420 - 1), NA())</f>
+        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 420 - 1), NA())</f>
         <v/>
       </c>
       <c r="R421">
-        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 420 - 1), NA())</f>
+        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 420 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="422">
       <c r="P422" s="2">
-        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 421 - 1), NA())</f>
+        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 421 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q422">
-        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 421 - 1), NA())</f>
+        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 421 - 1), NA())</f>
         <v/>
       </c>
       <c r="R422">
-        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 421 - 1), NA())</f>
+        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 421 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="423">
       <c r="P423" s="2">
-        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 422 - 1), NA())</f>
+        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 422 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q423">
-        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 422 - 1), NA())</f>
+        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 422 - 1), NA())</f>
         <v/>
       </c>
       <c r="R423">
-        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 422 - 1), NA())</f>
+        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 422 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="424">
       <c r="P424" s="2">
-        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 423 - 1), NA())</f>
+        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 423 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q424">
-        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 423 - 1), NA())</f>
+        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 423 - 1), NA())</f>
         <v/>
       </c>
       <c r="R424">
-        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 423 - 1), NA())</f>
+        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 423 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="425">
       <c r="P425" s="2">
-        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 424 - 1), NA())</f>
+        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 424 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q425">
-        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 424 - 1), NA())</f>
+        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 424 - 1), NA())</f>
         <v/>
       </c>
       <c r="R425">
-        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 424 - 1), NA())</f>
+        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 424 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="426">
       <c r="P426" s="2">
-        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 425 - 1), NA())</f>
+        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 425 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q426">
-        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 425 - 1), NA())</f>
+        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 425 - 1), NA())</f>
         <v/>
       </c>
       <c r="R426">
-        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 425 - 1), NA())</f>
+        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 425 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="427">
       <c r="P427" s="2">
-        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 426 - 1), NA())</f>
+        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 426 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q427">
-        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 426 - 1), NA())</f>
+        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 426 - 1), NA())</f>
         <v/>
       </c>
       <c r="R427">
-        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 426 - 1), NA())</f>
+        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 426 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="428">
       <c r="P428" s="2">
-        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 427 - 1), NA())</f>
+        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 427 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q428">
-        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 427 - 1), NA())</f>
+        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 427 - 1), NA())</f>
         <v/>
       </c>
       <c r="R428">
-        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 427 - 1), NA())</f>
+        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 427 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="429">
       <c r="P429" s="2">
-        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 428 - 1), NA())</f>
+        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 428 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q429">
-        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 428 - 1), NA())</f>
+        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 428 - 1), NA())</f>
         <v/>
       </c>
       <c r="R429">
-        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 428 - 1), NA())</f>
+        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 428 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="430">
       <c r="P430" s="2">
-        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 429 - 1), NA())</f>
+        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 429 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q430">
-        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 429 - 1), NA())</f>
+        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 429 - 1), NA())</f>
         <v/>
       </c>
       <c r="R430">
-        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 429 - 1), NA())</f>
+        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 429 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="431">
       <c r="P431" s="2">
-        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 430 - 1), NA())</f>
+        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 430 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q431">
-        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 430 - 1), NA())</f>
+        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 430 - 1), NA())</f>
         <v/>
       </c>
       <c r="R431">
-        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 430 - 1), NA())</f>
+        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 430 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="432">
       <c r="P432" s="2">
-        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 431 - 1), NA())</f>
+        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 431 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q432">
-        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 431 - 1), NA())</f>
+        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 431 - 1), NA())</f>
         <v/>
       </c>
       <c r="R432">
-        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 431 - 1), NA())</f>
+        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 431 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="433">
       <c r="P433" s="2">
-        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 432 - 1), NA())</f>
+        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 432 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q433">
-        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 432 - 1), NA())</f>
+        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 432 - 1), NA())</f>
         <v/>
       </c>
       <c r="R433">
-        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 432 - 1), NA())</f>
+        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 432 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="434">
       <c r="P434" s="2">
-        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 433 - 1), NA())</f>
+        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 433 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q434">
-        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 433 - 1), NA())</f>
+        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 433 - 1), NA())</f>
         <v/>
       </c>
       <c r="R434">
-        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 433 - 1), NA())</f>
+        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 433 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="435">
       <c r="P435" s="2">
-        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 434 - 1), NA())</f>
+        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 434 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q435">
-        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 434 - 1), NA())</f>
+        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 434 - 1), NA())</f>
         <v/>
       </c>
       <c r="R435">
-        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 434 - 1), NA())</f>
+        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 434 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="436">
       <c r="P436" s="2">
-        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 435 - 1), NA())</f>
+        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 435 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q436">
-        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 435 - 1), NA())</f>
+        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 435 - 1), NA())</f>
         <v/>
       </c>
       <c r="R436">
-        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 435 - 1), NA())</f>
+        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 435 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="437">
       <c r="P437" s="2">
-        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 436 - 1), NA())</f>
+        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 436 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q437">
-        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 436 - 1), NA())</f>
+        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 436 - 1), NA())</f>
         <v/>
       </c>
       <c r="R437">
-        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 436 - 1), NA())</f>
+        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 436 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="438">
       <c r="P438" s="2">
-        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 437 - 1), NA())</f>
+        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 437 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q438">
-        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 437 - 1), NA())</f>
+        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 437 - 1), NA())</f>
         <v/>
       </c>
       <c r="R438">
-        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 437 - 1), NA())</f>
+        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 437 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="439">
       <c r="P439" s="2">
-        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 438 - 1), NA())</f>
+        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 438 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q439">
-        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 438 - 1), NA())</f>
+        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 438 - 1), NA())</f>
         <v/>
       </c>
       <c r="R439">
-        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 438 - 1), NA())</f>
+        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 438 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="440">
       <c r="P440" s="2">
-        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 439 - 1), NA())</f>
+        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 439 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q440">
-        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 439 - 1), NA())</f>
+        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 439 - 1), NA())</f>
         <v/>
       </c>
       <c r="R440">
-        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 439 - 1), NA())</f>
+        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 439 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="441">
       <c r="P441" s="2">
-        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 440 - 1), NA())</f>
+        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 440 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q441">
-        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 440 - 1), NA())</f>
+        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 440 - 1), NA())</f>
         <v/>
       </c>
       <c r="R441">
-        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 440 - 1), NA())</f>
+        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 440 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="442">
       <c r="P442" s="2">
-        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 441 - 1), NA())</f>
+        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 441 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q442">
-        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 441 - 1), NA())</f>
+        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 441 - 1), NA())</f>
         <v/>
       </c>
       <c r="R442">
-        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 441 - 1), NA())</f>
+        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 441 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="443">
       <c r="P443" s="2">
-        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 442 - 1), NA())</f>
+        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 442 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q443">
-        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 442 - 1), NA())</f>
+        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 442 - 1), NA())</f>
         <v/>
       </c>
       <c r="R443">
-        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 442 - 1), NA())</f>
+        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 442 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="444">
       <c r="P444" s="2">
-        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 443 - 1), NA())</f>
+        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 443 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q444">
-        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 443 - 1), NA())</f>
+        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 443 - 1), NA())</f>
         <v/>
       </c>
       <c r="R444">
-        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 443 - 1), NA())</f>
+        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 443 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="445">
       <c r="P445" s="2">
-        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 444 - 1), NA())</f>
+        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 444 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q445">
-        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 444 - 1), NA())</f>
+        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 444 - 1), NA())</f>
         <v/>
       </c>
       <c r="R445">
-        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 444 - 1), NA())</f>
+        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 444 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="446">
       <c r="P446" s="2">
-        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 445 - 1), NA())</f>
+        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 445 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q446">
-        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 445 - 1), NA())</f>
+        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 445 - 1), NA())</f>
         <v/>
       </c>
       <c r="R446">
-        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 445 - 1), NA())</f>
+        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 445 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="447">
       <c r="P447" s="2">
-        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 446 - 1), NA())</f>
+        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 446 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q447">
-        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 446 - 1), NA())</f>
+        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 446 - 1), NA())</f>
         <v/>
       </c>
       <c r="R447">
-        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 446 - 1), NA())</f>
+        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 446 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="448">
       <c r="P448" s="2">
-        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 447 - 1), NA())</f>
+        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 447 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q448">
-        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 447 - 1), NA())</f>
+        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 447 - 1), NA())</f>
         <v/>
       </c>
       <c r="R448">
-        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 447 - 1), NA())</f>
+        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 447 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="449">
       <c r="P449" s="2">
-        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 448 - 1), NA())</f>
+        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 448 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q449">
-        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 448 - 1), NA())</f>
+        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 448 - 1), NA())</f>
         <v/>
       </c>
       <c r="R449">
-        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 448 - 1), NA())</f>
+        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 448 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="450">
       <c r="P450" s="2">
-        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 449 - 1), NA())</f>
+        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 449 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q450">
-        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 449 - 1), NA())</f>
+        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 449 - 1), NA())</f>
         <v/>
       </c>
       <c r="R450">
-        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 449 - 1), NA())</f>
+        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 449 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="451">
       <c r="P451" s="2">
-        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 450 - 1), NA())</f>
+        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 450 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q451">
-        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 450 - 1), NA())</f>
+        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 450 - 1), NA())</f>
         <v/>
       </c>
       <c r="R451">
-        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 450 - 1), NA())</f>
+        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 450 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="452">
       <c r="P452" s="2">
-        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 451 - 1), NA())</f>
+        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 451 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q452">
-        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 451 - 1), NA())</f>
+        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 451 - 1), NA())</f>
         <v/>
       </c>
       <c r="R452">
-        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 451 - 1), NA())</f>
+        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 451 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="453">
       <c r="P453" s="2">
-        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 452 - 1), NA())</f>
+        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 452 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q453">
-        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 452 - 1), NA())</f>
+        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 452 - 1), NA())</f>
         <v/>
       </c>
       <c r="R453">
-        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 452 - 1), NA())</f>
+        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 452 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="454">
       <c r="P454" s="2">
-        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 453 - 1), NA())</f>
+        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 453 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q454">
-        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 453 - 1), NA())</f>
+        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 453 - 1), NA())</f>
         <v/>
       </c>
       <c r="R454">
-        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 453 - 1), NA())</f>
+        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 453 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="455">
       <c r="P455" s="2">
-        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 454 - 1), NA())</f>
+        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 454 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q455">
-        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 454 - 1), NA())</f>
+        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 454 - 1), NA())</f>
         <v/>
       </c>
       <c r="R455">
-        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 454 - 1), NA())</f>
+        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 454 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="456">
       <c r="P456" s="2">
-        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 455 - 1), NA())</f>
+        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 455 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q456">
-        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 455 - 1), NA())</f>
+        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 455 - 1), NA())</f>
         <v/>
       </c>
       <c r="R456">
-        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 455 - 1), NA())</f>
+        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 455 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="457">
       <c r="P457" s="2">
-        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 456 - 1), NA())</f>
+        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 456 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q457">
-        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 456 - 1), NA())</f>
+        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 456 - 1), NA())</f>
         <v/>
       </c>
       <c r="R457">
-        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 456 - 1), NA())</f>
+        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 456 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="458">
       <c r="P458" s="2">
-        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 457 - 1), NA())</f>
+        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 457 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q458">
-        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 457 - 1), NA())</f>
+        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 457 - 1), NA())</f>
         <v/>
       </c>
       <c r="R458">
-        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 457 - 1), NA())</f>
+        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 457 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="459">
       <c r="P459" s="2">
-        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 458 - 1), NA())</f>
+        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 458 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q459">
-        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 458 - 1), NA())</f>
+        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 458 - 1), NA())</f>
         <v/>
       </c>
       <c r="R459">
-        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 458 - 1), NA())</f>
+        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 458 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="460">
       <c r="P460" s="2">
-        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 459 - 1), NA())</f>
+        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 459 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q460">
-        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 459 - 1), NA())</f>
+        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 459 - 1), NA())</f>
         <v/>
       </c>
       <c r="R460">
-        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 459 - 1), NA())</f>
+        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 459 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="461">
       <c r="P461" s="2">
-        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 460 - 1), NA())</f>
+        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 460 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q461">
-        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 460 - 1), NA())</f>
+        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 460 - 1), NA())</f>
         <v/>
       </c>
       <c r="R461">
-        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 460 - 1), NA())</f>
+        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 460 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="462">
       <c r="P462" s="2">
-        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 461 - 1), NA())</f>
+        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 461 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q462">
-        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 461 - 1), NA())</f>
+        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 461 - 1), NA())</f>
         <v/>
       </c>
       <c r="R462">
-        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 461 - 1), NA())</f>
+        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 461 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="463">
       <c r="P463" s="2">
-        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 462 - 1), NA())</f>
+        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 462 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q463">
-        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 462 - 1), NA())</f>
+        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 462 - 1), NA())</f>
         <v/>
       </c>
       <c r="R463">
-        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 462 - 1), NA())</f>
+        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 462 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="464">
       <c r="P464" s="2">
-        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 463 - 1), NA())</f>
+        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 463 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q464">
-        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 463 - 1), NA())</f>
+        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 463 - 1), NA())</f>
         <v/>
       </c>
       <c r="R464">
-        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 463 - 1), NA())</f>
+        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 463 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="465">
       <c r="P465" s="2">
-        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 464 - 1), NA())</f>
+        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 464 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q465">
-        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 464 - 1), NA())</f>
+        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 464 - 1), NA())</f>
         <v/>
       </c>
       <c r="R465">
-        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 464 - 1), NA())</f>
+        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 464 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="466">
       <c r="P466" s="2">
-        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 465 - 1), NA())</f>
+        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 465 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q466">
-        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 465 - 1), NA())</f>
+        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 465 - 1), NA())</f>
         <v/>
       </c>
       <c r="R466">
-        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 465 - 1), NA())</f>
+        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 465 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="467">
       <c r="P467" s="2">
-        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 466 - 1), NA())</f>
+        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 466 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q467">
-        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 466 - 1), NA())</f>
+        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 466 - 1), NA())</f>
         <v/>
       </c>
       <c r="R467">
-        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 466 - 1), NA())</f>
+        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 466 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="468">
       <c r="P468" s="2">
-        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 467 - 1), NA())</f>
+        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 467 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q468">
-        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 467 - 1), NA())</f>
+        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 467 - 1), NA())</f>
         <v/>
       </c>
       <c r="R468">
-        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 467 - 1), NA())</f>
+        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 467 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="469">
       <c r="P469" s="2">
-        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 468 - 1), NA())</f>
+        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 468 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q469">
-        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 468 - 1), NA())</f>
+        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 468 - 1), NA())</f>
         <v/>
       </c>
       <c r="R469">
-        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 468 - 1), NA())</f>
+        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 468 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="470">
       <c r="P470" s="2">
-        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 469 - 1), NA())</f>
+        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 469 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q470">
-        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 469 - 1), NA())</f>
+        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 469 - 1), NA())</f>
         <v/>
       </c>
       <c r="R470">
-        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 469 - 1), NA())</f>
+        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 469 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="471">
       <c r="P471" s="2">
-        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 470 - 1), NA())</f>
+        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 470 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q471">
-        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 470 - 1), NA())</f>
+        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 470 - 1), NA())</f>
         <v/>
       </c>
       <c r="R471">
-        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 470 - 1), NA())</f>
+        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 470 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="472">
       <c r="P472" s="2">
-        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 471 - 1), NA())</f>
+        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 471 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q472">
-        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 471 - 1), NA())</f>
+        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 471 - 1), NA())</f>
         <v/>
       </c>
       <c r="R472">
-        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 471 - 1), NA())</f>
+        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 471 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="473">
       <c r="P473" s="2">
-        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 472 - 1), NA())</f>
+        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 472 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q473">
-        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 472 - 1), NA())</f>
+        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 472 - 1), NA())</f>
         <v/>
       </c>
       <c r="R473">
-        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 472 - 1), NA())</f>
+        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 472 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="474">
       <c r="P474" s="2">
-        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 473 - 1), NA())</f>
+        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 473 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q474">
-        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 473 - 1), NA())</f>
+        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 473 - 1), NA())</f>
         <v/>
       </c>
       <c r="R474">
-        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 473 - 1), NA())</f>
+        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 473 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="475">
       <c r="P475" s="2">
-        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 474 - 1), NA())</f>
+        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 474 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q475">
-        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 474 - 1), NA())</f>
+        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 474 - 1), NA())</f>
         <v/>
       </c>
       <c r="R475">
-        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 474 - 1), NA())</f>
+        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 474 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="476">
       <c r="P476" s="2">
-        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 475 - 1), NA())</f>
+        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 475 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q476">
-        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 475 - 1), NA())</f>
+        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 475 - 1), NA())</f>
         <v/>
       </c>
       <c r="R476">
-        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 475 - 1), NA())</f>
+        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 475 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="477">
       <c r="P477" s="2">
-        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 476 - 1), NA())</f>
+        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 476 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q477">
-        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 476 - 1), NA())</f>
+        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 476 - 1), NA())</f>
         <v/>
       </c>
       <c r="R477">
-        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 476 - 1), NA())</f>
+        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 476 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="478">
       <c r="P478" s="2">
-        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 477 - 1), NA())</f>
+        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 477 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q478">
-        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 477 - 1), NA())</f>
+        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 477 - 1), NA())</f>
         <v/>
       </c>
       <c r="R478">
-        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 477 - 1), NA())</f>
+        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 477 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="479">
       <c r="P479" s="2">
-        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 478 - 1), NA())</f>
+        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 478 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q479">
-        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 478 - 1), NA())</f>
+        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 478 - 1), NA())</f>
         <v/>
       </c>
       <c r="R479">
-        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 478 - 1), NA())</f>
+        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 478 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="480">
       <c r="P480" s="2">
-        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 479 - 1), NA())</f>
+        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 479 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q480">
-        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 479 - 1), NA())</f>
+        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 479 - 1), NA())</f>
         <v/>
       </c>
       <c r="R480">
-        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 479 - 1), NA())</f>
+        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 479 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="481">
       <c r="P481" s="2">
-        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 480 - 1), NA())</f>
+        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 480 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q481">
-        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 480 - 1), NA())</f>
+        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 480 - 1), NA())</f>
         <v/>
       </c>
       <c r="R481">
-        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 480 - 1), NA())</f>
+        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 480 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="482">
       <c r="P482" s="2">
-        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 481 - 1), NA())</f>
+        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 481 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q482">
-        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 481 - 1), NA())</f>
+        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 481 - 1), NA())</f>
         <v/>
       </c>
       <c r="R482">
-        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 481 - 1), NA())</f>
+        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 481 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="483">
       <c r="P483" s="2">
-        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 482 - 1), NA())</f>
+        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 482 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q483">
-        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 482 - 1), NA())</f>
+        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 482 - 1), NA())</f>
         <v/>
       </c>
       <c r="R483">
-        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 482 - 1), NA())</f>
+        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 482 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="484">
       <c r="P484" s="2">
-        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 483 - 1), NA())</f>
+        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 483 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q484">
-        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 483 - 1), NA())</f>
+        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 483 - 1), NA())</f>
         <v/>
       </c>
       <c r="R484">
-        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 483 - 1), NA())</f>
+        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 483 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="485">
       <c r="P485" s="2">
-        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 484 - 1), NA())</f>
+        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 484 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q485">
-        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 484 - 1), NA())</f>
+        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 484 - 1), NA())</f>
         <v/>
       </c>
       <c r="R485">
-        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 484 - 1), NA())</f>
+        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 484 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="486">
       <c r="P486" s="2">
-        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 485 - 1), NA())</f>
+        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 485 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q486">
-        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 485 - 1), NA())</f>
+        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 485 - 1), NA())</f>
         <v/>
       </c>
       <c r="R486">
-        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 485 - 1), NA())</f>
+        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 485 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="487">
       <c r="P487" s="2">
-        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$487, $G$8 - 1 + 486 - 1), NA())</f>
+        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 486 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q487">
-        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$487, $G$8 - 1 + 486 - 1), NA())</f>
+        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 486 - 1), NA())</f>
         <v/>
       </c>
       <c r="R487">
-        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$487, $G$8 - 1 + 486 - 1), NA())</f>
+        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 486 - 1), NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="488">
+      <c r="P488" s="2">
+        <f>IF(487&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 487 - 1), NA())</f>
+        <v/>
+      </c>
+      <c r="Q488">
+        <f>IF(487&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 487 - 1), NA())</f>
+        <v/>
+      </c>
+      <c r="R488">
+        <f>IF(487&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 487 - 1), NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="489">
+      <c r="P489" s="2">
+        <f>IF(488&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 488 - 1), NA())</f>
+        <v/>
+      </c>
+      <c r="Q489">
+        <f>IF(488&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 488 - 1), NA())</f>
+        <v/>
+      </c>
+      <c r="R489">
+        <f>IF(488&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 488 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -8064,7 +8092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H487"/>
+  <dimension ref="A1:H489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22669,16 +22697,16 @@
     </row>
     <row r="487" ht="20" customHeight="1">
       <c r="A487" s="18" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B487" s="19" t="n">
-        <v>4392.2998046875</v>
+        <v>4393.89990234375</v>
       </c>
       <c r="C487" s="19" t="n">
-        <v>66.47000122070312</v>
+        <v>66.2969970703125</v>
       </c>
       <c r="D487" s="19" t="n">
-        <v>3112.889892578125</v>
+        <v>3116.929931640625</v>
       </c>
       <c r="E487" s="20">
         <f>ROUND((B487/31.1034768)*D487, 2)</f>
@@ -22697,8 +22725,68 @@
         <v/>
       </c>
     </row>
+    <row r="488" ht="20" customHeight="1">
+      <c r="A488" s="14" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B488" s="15" t="n">
+        <v>4393.89990234375</v>
+      </c>
+      <c r="C488" s="15" t="n">
+        <v>66.2969970703125</v>
+      </c>
+      <c r="D488" s="15" t="n">
+        <v>3099.47998046875</v>
+      </c>
+      <c r="E488" s="16">
+        <f>ROUND((B488/31.1034768)*D488, 2)</f>
+        <v/>
+      </c>
+      <c r="F488" s="16">
+        <f>ROUND((C488/31.1034768)*D488, 2)</f>
+        <v/>
+      </c>
+      <c r="G488" s="17">
+        <f>IFERROR((E488-E487)/E487, 0)</f>
+        <v/>
+      </c>
+      <c r="H488" s="17">
+        <f>IFERROR((F488-F487)/F487, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="489" ht="20" customHeight="1">
+      <c r="A489" s="18" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B489" s="19" t="n">
+        <v>4436.39990234375</v>
+      </c>
+      <c r="C489" s="19" t="n">
+        <v>67.91999816894531</v>
+      </c>
+      <c r="D489" s="19" t="n">
+        <v>3099.47998046875</v>
+      </c>
+      <c r="E489" s="20">
+        <f>ROUND((B489/31.1034768)*D489, 2)</f>
+        <v/>
+      </c>
+      <c r="F489" s="20">
+        <f>ROUND((C489/31.1034768)*D489, 2)</f>
+        <v/>
+      </c>
+      <c r="G489" s="21">
+        <f>IFERROR((E489-E488)/E488, 0)</f>
+        <v/>
+      </c>
+      <c r="H489" s="21">
+        <f>IFERROR((F489-F488)/F488, 0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H487"/>
+  <autoFilter ref="A1:H489"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Precios_Metales_COP.xlsx
+++ b/Precios_Metales_COP.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Precios Diarios" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Precios Diarios'!$A$1:$H$489</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Precios Diarios'!$A$1:$H$490</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -321,12 +321,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard y Gráficos'!$P$2:$P$489</f>
+              <f>'Dashboard y Gráficos'!$P$2:$P$490</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$Q$2:$Q$489</f>
+              <f>'Dashboard y Gráficos'!$Q$2:$Q$490</f>
             </numRef>
           </val>
         </ser>
@@ -446,12 +446,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard y Gráficos'!$P$2:$P$489</f>
+              <f>'Dashboard y Gráficos'!$P$2:$P$490</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$R$2:$R$489</f>
+              <f>'Dashboard y Gráficos'!$R$2:$R$490</f>
             </numRef>
           </val>
         </ser>
@@ -570,12 +570,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard y Gráficos'!$P$2:$P$489</f>
+              <f>'Dashboard y Gráficos'!$P$2:$P$490</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$Q$2:$Q$489</f>
+              <f>'Dashboard y Gráficos'!$Q$2:$Q$490</f>
             </numRef>
           </val>
         </ser>
@@ -610,7 +610,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$R$2:$R$489</f>
+              <f>'Dashboard y Gráficos'!$R$2:$R$490</f>
             </numRef>
           </val>
         </ser>
@@ -1074,7 +1074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R489"/>
+  <dimension ref="A1:R490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1118,15 +1118,15 @@
     </row>
     <row r="2">
       <c r="P2" s="2">
-        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 1 - 1), NA())</f>
+        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 1 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q2">
-        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 1 - 1), NA())</f>
+        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 1 - 1), NA())</f>
         <v/>
       </c>
       <c r="R2">
-        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 1 - 1), NA())</f>
+        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 1 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1166,58 +1166,58 @@
       </c>
       <c r="N3" s="4" t="n"/>
       <c r="P3" s="2">
-        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 2 - 1), NA())</f>
+        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 2 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q3">
-        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 2 - 1), NA())</f>
+        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 2 - 1), NA())</f>
         <v/>
       </c>
       <c r="R3">
-        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 2 - 1), NA())</f>
+        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 2 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5">
-        <f>'Precios Diarios'!A489</f>
+        <f>'Precios Diarios'!A490</f>
         <v/>
       </c>
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="6">
-        <f>'Precios Diarios'!E489</f>
+        <f>'Precios Diarios'!E490</f>
         <v/>
       </c>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="6">
-        <f>'Precios Diarios'!F489</f>
+        <f>'Precios Diarios'!F490</f>
         <v/>
       </c>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="6">
-        <f>'Precios Diarios'!D489</f>
+        <f>'Precios Diarios'!D490</f>
         <v/>
       </c>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="7">
-        <f>'Precios Diarios'!G489</f>
+        <f>'Precios Diarios'!G490</f>
         <v/>
       </c>
       <c r="N4" s="4" t="n"/>
       <c r="P4" s="2">
-        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 3 - 1), NA())</f>
+        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 3 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q4">
-        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 3 - 1), NA())</f>
+        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 3 - 1), NA())</f>
         <v/>
       </c>
       <c r="R4">
-        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 3 - 1), NA())</f>
+        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 3 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1237,29 +1237,29 @@
       <c r="M5" s="4" t="n"/>
       <c r="N5" s="4" t="n"/>
       <c r="P5" s="2">
-        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 4 - 1), NA())</f>
+        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 4 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q5">
-        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 4 - 1), NA())</f>
+        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 4 - 1), NA())</f>
         <v/>
       </c>
       <c r="R5">
-        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 4 - 1), NA())</f>
+        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 4 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="P6" s="2">
-        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 5 - 1), NA())</f>
+        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 5 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q6">
-        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 5 - 1), NA())</f>
+        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 5 - 1), NA())</f>
         <v/>
       </c>
       <c r="R6">
-        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 5 - 1), NA())</f>
+        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 5 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1270,15 +1270,15 @@
         </is>
       </c>
       <c r="P7" s="2">
-        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 6 - 1), NA())</f>
+        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 6 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q7">
-        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 6 - 1), NA())</f>
+        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 6 - 1), NA())</f>
         <v/>
       </c>
       <c r="R7">
-        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 6 - 1), NA())</f>
+        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 6 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1297,11 +1297,11 @@
         <v/>
       </c>
       <c r="G8" s="11">
-        <f>IFERROR(MATCH(E8, 'Precios Diarios'!$A$2:$A$489, 1), 1) + 1</f>
+        <f>IFERROR(MATCH(E8, 'Precios Diarios'!$A$2:$A$490, 1), 1) + 1</f>
         <v/>
       </c>
       <c r="H8" s="11">
-        <f>IFERROR(MATCH(F8, 'Precios Diarios'!$A$2:$A$489, 1), 488) + 1</f>
+        <f>IFERROR(MATCH(F8, 'Precios Diarios'!$A$2:$A$490, 1), 489) + 1</f>
         <v/>
       </c>
       <c r="I8" s="11">
@@ -1309,15 +1309,15 @@
         <v/>
       </c>
       <c r="P8" s="2">
-        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 7 - 1), NA())</f>
+        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 7 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q8">
-        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 7 - 1), NA())</f>
+        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 7 - 1), NA())</f>
         <v/>
       </c>
       <c r="R8">
-        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 7 - 1), NA())</f>
+        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 7 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1328,6735 +1328,6749 @@
         </is>
       </c>
       <c r="P9" s="2">
-        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 8 - 1), NA())</f>
+        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 8 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q9">
-        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 8 - 1), NA())</f>
+        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 8 - 1), NA())</f>
         <v/>
       </c>
       <c r="R9">
-        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 8 - 1), NA())</f>
+        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 8 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="P10" s="2">
-        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 9 - 1), NA())</f>
+        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 9 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q10">
-        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 9 - 1), NA())</f>
+        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 9 - 1), NA())</f>
         <v/>
       </c>
       <c r="R10">
-        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 9 - 1), NA())</f>
+        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 9 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="P11" s="2">
-        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 10 - 1), NA())</f>
+        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 10 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q11">
-        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 10 - 1), NA())</f>
+        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 10 - 1), NA())</f>
         <v/>
       </c>
       <c r="R11">
-        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 10 - 1), NA())</f>
+        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 10 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="P12" s="2">
-        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 11 - 1), NA())</f>
+        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 11 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q12">
-        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 11 - 1), NA())</f>
+        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 11 - 1), NA())</f>
         <v/>
       </c>
       <c r="R12">
-        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 11 - 1), NA())</f>
+        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 11 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="P13" s="2">
-        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 12 - 1), NA())</f>
+        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 12 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q13">
-        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 12 - 1), NA())</f>
+        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 12 - 1), NA())</f>
         <v/>
       </c>
       <c r="R13">
-        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 12 - 1), NA())</f>
+        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 12 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="P14" s="2">
-        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 13 - 1), NA())</f>
+        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 13 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q14">
-        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 13 - 1), NA())</f>
+        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 13 - 1), NA())</f>
         <v/>
       </c>
       <c r="R14">
-        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 13 - 1), NA())</f>
+        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 13 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="P15" s="2">
-        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 14 - 1), NA())</f>
+        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 14 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q15">
-        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 14 - 1), NA())</f>
+        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 14 - 1), NA())</f>
         <v/>
       </c>
       <c r="R15">
-        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 14 - 1), NA())</f>
+        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 14 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="P16" s="2">
-        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 15 - 1), NA())</f>
+        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 15 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q16">
-        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 15 - 1), NA())</f>
+        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 15 - 1), NA())</f>
         <v/>
       </c>
       <c r="R16">
-        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 15 - 1), NA())</f>
+        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 15 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="P17" s="2">
-        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 16 - 1), NA())</f>
+        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 16 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q17">
-        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 16 - 1), NA())</f>
+        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 16 - 1), NA())</f>
         <v/>
       </c>
       <c r="R17">
-        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 16 - 1), NA())</f>
+        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 16 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="P18" s="2">
-        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 17 - 1), NA())</f>
+        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 17 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q18">
-        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 17 - 1), NA())</f>
+        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 17 - 1), NA())</f>
         <v/>
       </c>
       <c r="R18">
-        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 17 - 1), NA())</f>
+        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 17 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="P19" s="2">
-        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 18 - 1), NA())</f>
+        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 18 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q19">
-        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 18 - 1), NA())</f>
+        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 18 - 1), NA())</f>
         <v/>
       </c>
       <c r="R19">
-        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 18 - 1), NA())</f>
+        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 18 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="P20" s="2">
-        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 19 - 1), NA())</f>
+        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 19 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q20">
-        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 19 - 1), NA())</f>
+        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 19 - 1), NA())</f>
         <v/>
       </c>
       <c r="R20">
-        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 19 - 1), NA())</f>
+        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 19 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="P21" s="2">
-        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 20 - 1), NA())</f>
+        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 20 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q21">
-        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 20 - 1), NA())</f>
+        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 20 - 1), NA())</f>
         <v/>
       </c>
       <c r="R21">
-        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 20 - 1), NA())</f>
+        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 20 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="P22" s="2">
-        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 21 - 1), NA())</f>
+        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 21 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q22">
-        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 21 - 1), NA())</f>
+        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 21 - 1), NA())</f>
         <v/>
       </c>
       <c r="R22">
-        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 21 - 1), NA())</f>
+        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 21 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="P23" s="2">
-        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 22 - 1), NA())</f>
+        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 22 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q23">
-        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 22 - 1), NA())</f>
+        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 22 - 1), NA())</f>
         <v/>
       </c>
       <c r="R23">
-        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 22 - 1), NA())</f>
+        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 22 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="P24" s="2">
-        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 23 - 1), NA())</f>
+        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 23 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q24">
-        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 23 - 1), NA())</f>
+        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 23 - 1), NA())</f>
         <v/>
       </c>
       <c r="R24">
-        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 23 - 1), NA())</f>
+        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 23 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="P25" s="2">
-        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 24 - 1), NA())</f>
+        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 24 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q25">
-        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 24 - 1), NA())</f>
+        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 24 - 1), NA())</f>
         <v/>
       </c>
       <c r="R25">
-        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 24 - 1), NA())</f>
+        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 24 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="P26" s="2">
-        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 25 - 1), NA())</f>
+        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 25 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q26">
-        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 25 - 1), NA())</f>
+        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 25 - 1), NA())</f>
         <v/>
       </c>
       <c r="R26">
-        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 25 - 1), NA())</f>
+        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 25 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="P27" s="2">
-        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 26 - 1), NA())</f>
+        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 26 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q27">
-        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 26 - 1), NA())</f>
+        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 26 - 1), NA())</f>
         <v/>
       </c>
       <c r="R27">
-        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 26 - 1), NA())</f>
+        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 26 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="P28" s="2">
-        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 27 - 1), NA())</f>
+        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 27 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q28">
-        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 27 - 1), NA())</f>
+        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 27 - 1), NA())</f>
         <v/>
       </c>
       <c r="R28">
-        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 27 - 1), NA())</f>
+        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 27 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="P29" s="2">
-        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 28 - 1), NA())</f>
+        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 28 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q29">
-        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 28 - 1), NA())</f>
+        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 28 - 1), NA())</f>
         <v/>
       </c>
       <c r="R29">
-        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 28 - 1), NA())</f>
+        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 28 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="P30" s="2">
-        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 29 - 1), NA())</f>
+        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 29 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q30">
-        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 29 - 1), NA())</f>
+        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 29 - 1), NA())</f>
         <v/>
       </c>
       <c r="R30">
-        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 29 - 1), NA())</f>
+        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 29 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="P31" s="2">
-        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 30 - 1), NA())</f>
+        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 30 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q31">
-        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 30 - 1), NA())</f>
+        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 30 - 1), NA())</f>
         <v/>
       </c>
       <c r="R31">
-        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 30 - 1), NA())</f>
+        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 30 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="P32" s="2">
-        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 31 - 1), NA())</f>
+        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 31 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q32">
-        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 31 - 1), NA())</f>
+        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 31 - 1), NA())</f>
         <v/>
       </c>
       <c r="R32">
-        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 31 - 1), NA())</f>
+        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 31 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="P33" s="2">
-        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 32 - 1), NA())</f>
+        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 32 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q33">
-        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 32 - 1), NA())</f>
+        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 32 - 1), NA())</f>
         <v/>
       </c>
       <c r="R33">
-        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 32 - 1), NA())</f>
+        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 32 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="P34" s="2">
-        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 33 - 1), NA())</f>
+        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 33 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q34">
-        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 33 - 1), NA())</f>
+        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 33 - 1), NA())</f>
         <v/>
       </c>
       <c r="R34">
-        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 33 - 1), NA())</f>
+        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 33 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="P35" s="2">
-        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 34 - 1), NA())</f>
+        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 34 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q35">
-        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 34 - 1), NA())</f>
+        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 34 - 1), NA())</f>
         <v/>
       </c>
       <c r="R35">
-        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 34 - 1), NA())</f>
+        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 34 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="P36" s="2">
-        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 35 - 1), NA())</f>
+        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 35 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q36">
-        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 35 - 1), NA())</f>
+        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 35 - 1), NA())</f>
         <v/>
       </c>
       <c r="R36">
-        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 35 - 1), NA())</f>
+        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 35 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="P37" s="2">
-        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 36 - 1), NA())</f>
+        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 36 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q37">
-        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 36 - 1), NA())</f>
+        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 36 - 1), NA())</f>
         <v/>
       </c>
       <c r="R37">
-        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 36 - 1), NA())</f>
+        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 36 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="P38" s="2">
-        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 37 - 1), NA())</f>
+        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 37 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q38">
-        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 37 - 1), NA())</f>
+        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 37 - 1), NA())</f>
         <v/>
       </c>
       <c r="R38">
-        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 37 - 1), NA())</f>
+        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 37 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="P39" s="2">
-        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 38 - 1), NA())</f>
+        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 38 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q39">
-        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 38 - 1), NA())</f>
+        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 38 - 1), NA())</f>
         <v/>
       </c>
       <c r="R39">
-        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 38 - 1), NA())</f>
+        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 38 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="P40" s="2">
-        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 39 - 1), NA())</f>
+        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 39 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q40">
-        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 39 - 1), NA())</f>
+        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 39 - 1), NA())</f>
         <v/>
       </c>
       <c r="R40">
-        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 39 - 1), NA())</f>
+        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 39 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="P41" s="2">
-        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 40 - 1), NA())</f>
+        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 40 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q41">
-        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 40 - 1), NA())</f>
+        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 40 - 1), NA())</f>
         <v/>
       </c>
       <c r="R41">
-        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 40 - 1), NA())</f>
+        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 40 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="P42" s="2">
-        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 41 - 1), NA())</f>
+        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 41 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q42">
-        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 41 - 1), NA())</f>
+        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 41 - 1), NA())</f>
         <v/>
       </c>
       <c r="R42">
-        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 41 - 1), NA())</f>
+        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 41 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="P43" s="2">
-        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 42 - 1), NA())</f>
+        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 42 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q43">
-        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 42 - 1), NA())</f>
+        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 42 - 1), NA())</f>
         <v/>
       </c>
       <c r="R43">
-        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 42 - 1), NA())</f>
+        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 42 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="P44" s="2">
-        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 43 - 1), NA())</f>
+        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 43 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q44">
-        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 43 - 1), NA())</f>
+        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 43 - 1), NA())</f>
         <v/>
       </c>
       <c r="R44">
-        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 43 - 1), NA())</f>
+        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 43 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="P45" s="2">
-        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 44 - 1), NA())</f>
+        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 44 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q45">
-        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 44 - 1), NA())</f>
+        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 44 - 1), NA())</f>
         <v/>
       </c>
       <c r="R45">
-        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 44 - 1), NA())</f>
+        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 44 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="P46" s="2">
-        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 45 - 1), NA())</f>
+        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 45 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q46">
-        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 45 - 1), NA())</f>
+        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 45 - 1), NA())</f>
         <v/>
       </c>
       <c r="R46">
-        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 45 - 1), NA())</f>
+        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 45 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="P47" s="2">
-        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 46 - 1), NA())</f>
+        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 46 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q47">
-        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 46 - 1), NA())</f>
+        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 46 - 1), NA())</f>
         <v/>
       </c>
       <c r="R47">
-        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 46 - 1), NA())</f>
+        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 46 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="P48" s="2">
-        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 47 - 1), NA())</f>
+        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 47 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q48">
-        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 47 - 1), NA())</f>
+        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 47 - 1), NA())</f>
         <v/>
       </c>
       <c r="R48">
-        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 47 - 1), NA())</f>
+        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 47 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="P49" s="2">
-        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 48 - 1), NA())</f>
+        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 48 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q49">
-        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 48 - 1), NA())</f>
+        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 48 - 1), NA())</f>
         <v/>
       </c>
       <c r="R49">
-        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 48 - 1), NA())</f>
+        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 48 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="P50" s="2">
-        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 49 - 1), NA())</f>
+        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 49 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q50">
-        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 49 - 1), NA())</f>
+        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 49 - 1), NA())</f>
         <v/>
       </c>
       <c r="R50">
-        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 49 - 1), NA())</f>
+        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 49 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="P51" s="2">
-        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 50 - 1), NA())</f>
+        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 50 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q51">
-        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 50 - 1), NA())</f>
+        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 50 - 1), NA())</f>
         <v/>
       </c>
       <c r="R51">
-        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 50 - 1), NA())</f>
+        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 50 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="P52" s="2">
-        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 51 - 1), NA())</f>
+        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 51 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q52">
-        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 51 - 1), NA())</f>
+        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 51 - 1), NA())</f>
         <v/>
       </c>
       <c r="R52">
-        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 51 - 1), NA())</f>
+        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 51 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="P53" s="2">
-        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 52 - 1), NA())</f>
+        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 52 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q53">
-        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 52 - 1), NA())</f>
+        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 52 - 1), NA())</f>
         <v/>
       </c>
       <c r="R53">
-        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 52 - 1), NA())</f>
+        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 52 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="P54" s="2">
-        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 53 - 1), NA())</f>
+        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 53 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q54">
-        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 53 - 1), NA())</f>
+        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 53 - 1), NA())</f>
         <v/>
       </c>
       <c r="R54">
-        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 53 - 1), NA())</f>
+        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 53 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="P55" s="2">
-        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 54 - 1), NA())</f>
+        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 54 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q55">
-        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 54 - 1), NA())</f>
+        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 54 - 1), NA())</f>
         <v/>
       </c>
       <c r="R55">
-        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 54 - 1), NA())</f>
+        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 54 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="P56" s="2">
-        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 55 - 1), NA())</f>
+        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 55 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q56">
-        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 55 - 1), NA())</f>
+        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 55 - 1), NA())</f>
         <v/>
       </c>
       <c r="R56">
-        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 55 - 1), NA())</f>
+        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 55 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="P57" s="2">
-        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 56 - 1), NA())</f>
+        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 56 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q57">
-        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 56 - 1), NA())</f>
+        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 56 - 1), NA())</f>
         <v/>
       </c>
       <c r="R57">
-        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 56 - 1), NA())</f>
+        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 56 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="P58" s="2">
-        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 57 - 1), NA())</f>
+        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 57 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q58">
-        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 57 - 1), NA())</f>
+        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 57 - 1), NA())</f>
         <v/>
       </c>
       <c r="R58">
-        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 57 - 1), NA())</f>
+        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 57 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="P59" s="2">
-        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 58 - 1), NA())</f>
+        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 58 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q59">
-        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 58 - 1), NA())</f>
+        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 58 - 1), NA())</f>
         <v/>
       </c>
       <c r="R59">
-        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 58 - 1), NA())</f>
+        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 58 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="P60" s="2">
-        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 59 - 1), NA())</f>
+        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 59 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q60">
-        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 59 - 1), NA())</f>
+        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 59 - 1), NA())</f>
         <v/>
       </c>
       <c r="R60">
-        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 59 - 1), NA())</f>
+        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 59 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="P61" s="2">
-        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 60 - 1), NA())</f>
+        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 60 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q61">
-        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 60 - 1), NA())</f>
+        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 60 - 1), NA())</f>
         <v/>
       </c>
       <c r="R61">
-        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 60 - 1), NA())</f>
+        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 60 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="P62" s="2">
-        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 61 - 1), NA())</f>
+        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 61 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q62">
-        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 61 - 1), NA())</f>
+        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 61 - 1), NA())</f>
         <v/>
       </c>
       <c r="R62">
-        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 61 - 1), NA())</f>
+        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 61 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="P63" s="2">
-        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 62 - 1), NA())</f>
+        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 62 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q63">
-        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 62 - 1), NA())</f>
+        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 62 - 1), NA())</f>
         <v/>
       </c>
       <c r="R63">
-        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 62 - 1), NA())</f>
+        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 62 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="P64" s="2">
-        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 63 - 1), NA())</f>
+        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 63 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q64">
-        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 63 - 1), NA())</f>
+        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 63 - 1), NA())</f>
         <v/>
       </c>
       <c r="R64">
-        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 63 - 1), NA())</f>
+        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 63 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="P65" s="2">
-        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 64 - 1), NA())</f>
+        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 64 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q65">
-        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 64 - 1), NA())</f>
+        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 64 - 1), NA())</f>
         <v/>
       </c>
       <c r="R65">
-        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 64 - 1), NA())</f>
+        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 64 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="P66" s="2">
-        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 65 - 1), NA())</f>
+        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 65 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q66">
-        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 65 - 1), NA())</f>
+        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 65 - 1), NA())</f>
         <v/>
       </c>
       <c r="R66">
-        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 65 - 1), NA())</f>
+        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 65 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="P67" s="2">
-        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 66 - 1), NA())</f>
+        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 66 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q67">
-        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 66 - 1), NA())</f>
+        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 66 - 1), NA())</f>
         <v/>
       </c>
       <c r="R67">
-        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 66 - 1), NA())</f>
+        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 66 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="P68" s="2">
-        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 67 - 1), NA())</f>
+        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 67 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q68">
-        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 67 - 1), NA())</f>
+        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 67 - 1), NA())</f>
         <v/>
       </c>
       <c r="R68">
-        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 67 - 1), NA())</f>
+        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 67 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="P69" s="2">
-        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 68 - 1), NA())</f>
+        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 68 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q69">
-        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 68 - 1), NA())</f>
+        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 68 - 1), NA())</f>
         <v/>
       </c>
       <c r="R69">
-        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 68 - 1), NA())</f>
+        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 68 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="P70" s="2">
-        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 69 - 1), NA())</f>
+        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 69 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q70">
-        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 69 - 1), NA())</f>
+        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 69 - 1), NA())</f>
         <v/>
       </c>
       <c r="R70">
-        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 69 - 1), NA())</f>
+        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 69 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="P71" s="2">
-        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 70 - 1), NA())</f>
+        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 70 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q71">
-        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 70 - 1), NA())</f>
+        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 70 - 1), NA())</f>
         <v/>
       </c>
       <c r="R71">
-        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 70 - 1), NA())</f>
+        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 70 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="P72" s="2">
-        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 71 - 1), NA())</f>
+        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 71 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q72">
-        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 71 - 1), NA())</f>
+        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 71 - 1), NA())</f>
         <v/>
       </c>
       <c r="R72">
-        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 71 - 1), NA())</f>
+        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 71 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="P73" s="2">
-        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 72 - 1), NA())</f>
+        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 72 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q73">
-        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 72 - 1), NA())</f>
+        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 72 - 1), NA())</f>
         <v/>
       </c>
       <c r="R73">
-        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 72 - 1), NA())</f>
+        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 72 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="P74" s="2">
-        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 73 - 1), NA())</f>
+        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 73 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q74">
-        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 73 - 1), NA())</f>
+        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 73 - 1), NA())</f>
         <v/>
       </c>
       <c r="R74">
-        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 73 - 1), NA())</f>
+        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 73 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="P75" s="2">
-        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 74 - 1), NA())</f>
+        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 74 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q75">
-        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 74 - 1), NA())</f>
+        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 74 - 1), NA())</f>
         <v/>
       </c>
       <c r="R75">
-        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 74 - 1), NA())</f>
+        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 74 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="P76" s="2">
-        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 75 - 1), NA())</f>
+        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 75 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q76">
-        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 75 - 1), NA())</f>
+        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 75 - 1), NA())</f>
         <v/>
       </c>
       <c r="R76">
-        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 75 - 1), NA())</f>
+        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 75 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="P77" s="2">
-        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 76 - 1), NA())</f>
+        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 76 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q77">
-        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 76 - 1), NA())</f>
+        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 76 - 1), NA())</f>
         <v/>
       </c>
       <c r="R77">
-        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 76 - 1), NA())</f>
+        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 76 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="P78" s="2">
-        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 77 - 1), NA())</f>
+        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 77 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q78">
-        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 77 - 1), NA())</f>
+        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 77 - 1), NA())</f>
         <v/>
       </c>
       <c r="R78">
-        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 77 - 1), NA())</f>
+        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 77 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="P79" s="2">
-        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 78 - 1), NA())</f>
+        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 78 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q79">
-        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 78 - 1), NA())</f>
+        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 78 - 1), NA())</f>
         <v/>
       </c>
       <c r="R79">
-        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 78 - 1), NA())</f>
+        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 78 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="P80" s="2">
-        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 79 - 1), NA())</f>
+        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 79 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q80">
-        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 79 - 1), NA())</f>
+        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 79 - 1), NA())</f>
         <v/>
       </c>
       <c r="R80">
-        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 79 - 1), NA())</f>
+        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 79 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="P81" s="2">
-        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 80 - 1), NA())</f>
+        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 80 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q81">
-        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 80 - 1), NA())</f>
+        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 80 - 1), NA())</f>
         <v/>
       </c>
       <c r="R81">
-        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 80 - 1), NA())</f>
+        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 80 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="P82" s="2">
-        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 81 - 1), NA())</f>
+        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 81 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q82">
-        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 81 - 1), NA())</f>
+        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 81 - 1), NA())</f>
         <v/>
       </c>
       <c r="R82">
-        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 81 - 1), NA())</f>
+        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 81 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="P83" s="2">
-        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 82 - 1), NA())</f>
+        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 82 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q83">
-        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 82 - 1), NA())</f>
+        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 82 - 1), NA())</f>
         <v/>
       </c>
       <c r="R83">
-        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 82 - 1), NA())</f>
+        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 82 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="P84" s="2">
-        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 83 - 1), NA())</f>
+        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 83 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q84">
-        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 83 - 1), NA())</f>
+        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 83 - 1), NA())</f>
         <v/>
       </c>
       <c r="R84">
-        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 83 - 1), NA())</f>
+        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 83 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="P85" s="2">
-        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 84 - 1), NA())</f>
+        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 84 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q85">
-        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 84 - 1), NA())</f>
+        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 84 - 1), NA())</f>
         <v/>
       </c>
       <c r="R85">
-        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 84 - 1), NA())</f>
+        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 84 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="P86" s="2">
-        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 85 - 1), NA())</f>
+        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 85 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q86">
-        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 85 - 1), NA())</f>
+        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 85 - 1), NA())</f>
         <v/>
       </c>
       <c r="R86">
-        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 85 - 1), NA())</f>
+        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 85 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="P87" s="2">
-        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 86 - 1), NA())</f>
+        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 86 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q87">
-        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 86 - 1), NA())</f>
+        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 86 - 1), NA())</f>
         <v/>
       </c>
       <c r="R87">
-        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 86 - 1), NA())</f>
+        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 86 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="P88" s="2">
-        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 87 - 1), NA())</f>
+        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 87 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q88">
-        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 87 - 1), NA())</f>
+        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 87 - 1), NA())</f>
         <v/>
       </c>
       <c r="R88">
-        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 87 - 1), NA())</f>
+        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 87 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="P89" s="2">
-        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 88 - 1), NA())</f>
+        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 88 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q89">
-        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 88 - 1), NA())</f>
+        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 88 - 1), NA())</f>
         <v/>
       </c>
       <c r="R89">
-        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 88 - 1), NA())</f>
+        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 88 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="P90" s="2">
-        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 89 - 1), NA())</f>
+        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 89 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q90">
-        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 89 - 1), NA())</f>
+        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 89 - 1), NA())</f>
         <v/>
       </c>
       <c r="R90">
-        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 89 - 1), NA())</f>
+        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 89 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="P91" s="2">
-        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 90 - 1), NA())</f>
+        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 90 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q91">
-        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 90 - 1), NA())</f>
+        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 90 - 1), NA())</f>
         <v/>
       </c>
       <c r="R91">
-        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 90 - 1), NA())</f>
+        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 90 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="P92" s="2">
-        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 91 - 1), NA())</f>
+        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 91 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q92">
-        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 91 - 1), NA())</f>
+        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 91 - 1), NA())</f>
         <v/>
       </c>
       <c r="R92">
-        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 91 - 1), NA())</f>
+        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 91 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="P93" s="2">
-        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 92 - 1), NA())</f>
+        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 92 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q93">
-        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 92 - 1), NA())</f>
+        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 92 - 1), NA())</f>
         <v/>
       </c>
       <c r="R93">
-        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 92 - 1), NA())</f>
+        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 92 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="P94" s="2">
-        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 93 - 1), NA())</f>
+        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 93 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q94">
-        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 93 - 1), NA())</f>
+        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 93 - 1), NA())</f>
         <v/>
       </c>
       <c r="R94">
-        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 93 - 1), NA())</f>
+        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 93 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="P95" s="2">
-        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 94 - 1), NA())</f>
+        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 94 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q95">
-        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 94 - 1), NA())</f>
+        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 94 - 1), NA())</f>
         <v/>
       </c>
       <c r="R95">
-        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 94 - 1), NA())</f>
+        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 94 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="P96" s="2">
-        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 95 - 1), NA())</f>
+        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 95 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q96">
-        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 95 - 1), NA())</f>
+        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 95 - 1), NA())</f>
         <v/>
       </c>
       <c r="R96">
-        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 95 - 1), NA())</f>
+        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 95 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="P97" s="2">
-        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 96 - 1), NA())</f>
+        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 96 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q97">
-        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 96 - 1), NA())</f>
+        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 96 - 1), NA())</f>
         <v/>
       </c>
       <c r="R97">
-        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 96 - 1), NA())</f>
+        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 96 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="P98" s="2">
-        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 97 - 1), NA())</f>
+        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 97 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q98">
-        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 97 - 1), NA())</f>
+        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 97 - 1), NA())</f>
         <v/>
       </c>
       <c r="R98">
-        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 97 - 1), NA())</f>
+        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 97 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="P99" s="2">
-        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 98 - 1), NA())</f>
+        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 98 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q99">
-        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 98 - 1), NA())</f>
+        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 98 - 1), NA())</f>
         <v/>
       </c>
       <c r="R99">
-        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 98 - 1), NA())</f>
+        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 98 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="P100" s="2">
-        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 99 - 1), NA())</f>
+        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 99 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q100">
-        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 99 - 1), NA())</f>
+        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 99 - 1), NA())</f>
         <v/>
       </c>
       <c r="R100">
-        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 99 - 1), NA())</f>
+        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 99 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="P101" s="2">
-        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 100 - 1), NA())</f>
+        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 100 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q101">
-        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 100 - 1), NA())</f>
+        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 100 - 1), NA())</f>
         <v/>
       </c>
       <c r="R101">
-        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 100 - 1), NA())</f>
+        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 100 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="P102" s="2">
-        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 101 - 1), NA())</f>
+        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 101 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q102">
-        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 101 - 1), NA())</f>
+        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 101 - 1), NA())</f>
         <v/>
       </c>
       <c r="R102">
-        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 101 - 1), NA())</f>
+        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 101 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="P103" s="2">
-        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 102 - 1), NA())</f>
+        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 102 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q103">
-        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 102 - 1), NA())</f>
+        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 102 - 1), NA())</f>
         <v/>
       </c>
       <c r="R103">
-        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 102 - 1), NA())</f>
+        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 102 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="P104" s="2">
-        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 103 - 1), NA())</f>
+        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 103 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q104">
-        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 103 - 1), NA())</f>
+        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 103 - 1), NA())</f>
         <v/>
       </c>
       <c r="R104">
-        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 103 - 1), NA())</f>
+        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 103 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="P105" s="2">
-        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 104 - 1), NA())</f>
+        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 104 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q105">
-        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 104 - 1), NA())</f>
+        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 104 - 1), NA())</f>
         <v/>
       </c>
       <c r="R105">
-        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 104 - 1), NA())</f>
+        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 104 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="P106" s="2">
-        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 105 - 1), NA())</f>
+        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 105 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q106">
-        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 105 - 1), NA())</f>
+        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 105 - 1), NA())</f>
         <v/>
       </c>
       <c r="R106">
-        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 105 - 1), NA())</f>
+        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 105 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="P107" s="2">
-        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 106 - 1), NA())</f>
+        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 106 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q107">
-        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 106 - 1), NA())</f>
+        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 106 - 1), NA())</f>
         <v/>
       </c>
       <c r="R107">
-        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 106 - 1), NA())</f>
+        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 106 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="P108" s="2">
-        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 107 - 1), NA())</f>
+        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 107 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q108">
-        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 107 - 1), NA())</f>
+        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 107 - 1), NA())</f>
         <v/>
       </c>
       <c r="R108">
-        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 107 - 1), NA())</f>
+        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 107 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="P109" s="2">
-        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 108 - 1), NA())</f>
+        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 108 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q109">
-        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 108 - 1), NA())</f>
+        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 108 - 1), NA())</f>
         <v/>
       </c>
       <c r="R109">
-        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 108 - 1), NA())</f>
+        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 108 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="P110" s="2">
-        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 109 - 1), NA())</f>
+        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 109 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q110">
-        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 109 - 1), NA())</f>
+        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 109 - 1), NA())</f>
         <v/>
       </c>
       <c r="R110">
-        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 109 - 1), NA())</f>
+        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 109 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="P111" s="2">
-        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 110 - 1), NA())</f>
+        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 110 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q111">
-        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 110 - 1), NA())</f>
+        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 110 - 1), NA())</f>
         <v/>
       </c>
       <c r="R111">
-        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 110 - 1), NA())</f>
+        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 110 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="P112" s="2">
-        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 111 - 1), NA())</f>
+        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 111 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q112">
-        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 111 - 1), NA())</f>
+        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 111 - 1), NA())</f>
         <v/>
       </c>
       <c r="R112">
-        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 111 - 1), NA())</f>
+        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 111 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="P113" s="2">
-        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 112 - 1), NA())</f>
+        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 112 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q113">
-        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 112 - 1), NA())</f>
+        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 112 - 1), NA())</f>
         <v/>
       </c>
       <c r="R113">
-        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 112 - 1), NA())</f>
+        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 112 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="P114" s="2">
-        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 113 - 1), NA())</f>
+        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 113 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q114">
-        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 113 - 1), NA())</f>
+        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 113 - 1), NA())</f>
         <v/>
       </c>
       <c r="R114">
-        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 113 - 1), NA())</f>
+        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 113 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="P115" s="2">
-        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 114 - 1), NA())</f>
+        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 114 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q115">
-        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 114 - 1), NA())</f>
+        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 114 - 1), NA())</f>
         <v/>
       </c>
       <c r="R115">
-        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 114 - 1), NA())</f>
+        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 114 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="P116" s="2">
-        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 115 - 1), NA())</f>
+        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 115 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q116">
-        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 115 - 1), NA())</f>
+        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 115 - 1), NA())</f>
         <v/>
       </c>
       <c r="R116">
-        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 115 - 1), NA())</f>
+        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 115 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="P117" s="2">
-        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 116 - 1), NA())</f>
+        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 116 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q117">
-        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 116 - 1), NA())</f>
+        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 116 - 1), NA())</f>
         <v/>
       </c>
       <c r="R117">
-        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 116 - 1), NA())</f>
+        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 116 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="P118" s="2">
-        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 117 - 1), NA())</f>
+        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 117 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q118">
-        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 117 - 1), NA())</f>
+        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 117 - 1), NA())</f>
         <v/>
       </c>
       <c r="R118">
-        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 117 - 1), NA())</f>
+        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 117 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="P119" s="2">
-        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 118 - 1), NA())</f>
+        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 118 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q119">
-        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 118 - 1), NA())</f>
+        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 118 - 1), NA())</f>
         <v/>
       </c>
       <c r="R119">
-        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 118 - 1), NA())</f>
+        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 118 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="P120" s="2">
-        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 119 - 1), NA())</f>
+        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 119 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q120">
-        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 119 - 1), NA())</f>
+        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 119 - 1), NA())</f>
         <v/>
       </c>
       <c r="R120">
-        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 119 - 1), NA())</f>
+        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 119 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="P121" s="2">
-        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 120 - 1), NA())</f>
+        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 120 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q121">
-        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 120 - 1), NA())</f>
+        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 120 - 1), NA())</f>
         <v/>
       </c>
       <c r="R121">
-        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 120 - 1), NA())</f>
+        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 120 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="P122" s="2">
-        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 121 - 1), NA())</f>
+        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 121 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q122">
-        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 121 - 1), NA())</f>
+        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 121 - 1), NA())</f>
         <v/>
       </c>
       <c r="R122">
-        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 121 - 1), NA())</f>
+        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 121 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="123">
       <c r="P123" s="2">
-        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 122 - 1), NA())</f>
+        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 122 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q123">
-        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 122 - 1), NA())</f>
+        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 122 - 1), NA())</f>
         <v/>
       </c>
       <c r="R123">
-        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 122 - 1), NA())</f>
+        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 122 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="124">
       <c r="P124" s="2">
-        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 123 - 1), NA())</f>
+        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 123 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q124">
-        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 123 - 1), NA())</f>
+        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 123 - 1), NA())</f>
         <v/>
       </c>
       <c r="R124">
-        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 123 - 1), NA())</f>
+        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 123 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="125">
       <c r="P125" s="2">
-        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 124 - 1), NA())</f>
+        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 124 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q125">
-        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 124 - 1), NA())</f>
+        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 124 - 1), NA())</f>
         <v/>
       </c>
       <c r="R125">
-        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 124 - 1), NA())</f>
+        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 124 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="126">
       <c r="P126" s="2">
-        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 125 - 1), NA())</f>
+        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 125 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q126">
-        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 125 - 1), NA())</f>
+        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 125 - 1), NA())</f>
         <v/>
       </c>
       <c r="R126">
-        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 125 - 1), NA())</f>
+        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 125 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="127">
       <c r="P127" s="2">
-        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 126 - 1), NA())</f>
+        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 126 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q127">
-        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 126 - 1), NA())</f>
+        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 126 - 1), NA())</f>
         <v/>
       </c>
       <c r="R127">
-        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 126 - 1), NA())</f>
+        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 126 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="P128" s="2">
-        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 127 - 1), NA())</f>
+        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 127 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q128">
-        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 127 - 1), NA())</f>
+        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 127 - 1), NA())</f>
         <v/>
       </c>
       <c r="R128">
-        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 127 - 1), NA())</f>
+        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 127 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="129">
       <c r="P129" s="2">
-        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 128 - 1), NA())</f>
+        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 128 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q129">
-        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 128 - 1), NA())</f>
+        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 128 - 1), NA())</f>
         <v/>
       </c>
       <c r="R129">
-        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 128 - 1), NA())</f>
+        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 128 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="130">
       <c r="P130" s="2">
-        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 129 - 1), NA())</f>
+        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 129 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q130">
-        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 129 - 1), NA())</f>
+        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 129 - 1), NA())</f>
         <v/>
       </c>
       <c r="R130">
-        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 129 - 1), NA())</f>
+        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 129 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="131">
       <c r="P131" s="2">
-        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 130 - 1), NA())</f>
+        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 130 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q131">
-        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 130 - 1), NA())</f>
+        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 130 - 1), NA())</f>
         <v/>
       </c>
       <c r="R131">
-        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 130 - 1), NA())</f>
+        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 130 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="132">
       <c r="P132" s="2">
-        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 131 - 1), NA())</f>
+        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 131 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q132">
-        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 131 - 1), NA())</f>
+        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 131 - 1), NA())</f>
         <v/>
       </c>
       <c r="R132">
-        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 131 - 1), NA())</f>
+        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 131 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="133">
       <c r="P133" s="2">
-        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 132 - 1), NA())</f>
+        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 132 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q133">
-        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 132 - 1), NA())</f>
+        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 132 - 1), NA())</f>
         <v/>
       </c>
       <c r="R133">
-        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 132 - 1), NA())</f>
+        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 132 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="134">
       <c r="P134" s="2">
-        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 133 - 1), NA())</f>
+        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 133 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q134">
-        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 133 - 1), NA())</f>
+        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 133 - 1), NA())</f>
         <v/>
       </c>
       <c r="R134">
-        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 133 - 1), NA())</f>
+        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 133 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="135">
       <c r="P135" s="2">
-        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 134 - 1), NA())</f>
+        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 134 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q135">
-        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 134 - 1), NA())</f>
+        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 134 - 1), NA())</f>
         <v/>
       </c>
       <c r="R135">
-        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 134 - 1), NA())</f>
+        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 134 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="136">
       <c r="P136" s="2">
-        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 135 - 1), NA())</f>
+        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 135 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q136">
-        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 135 - 1), NA())</f>
+        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 135 - 1), NA())</f>
         <v/>
       </c>
       <c r="R136">
-        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 135 - 1), NA())</f>
+        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 135 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="137">
       <c r="P137" s="2">
-        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 136 - 1), NA())</f>
+        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 136 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q137">
-        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 136 - 1), NA())</f>
+        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 136 - 1), NA())</f>
         <v/>
       </c>
       <c r="R137">
-        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 136 - 1), NA())</f>
+        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 136 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="138">
       <c r="P138" s="2">
-        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 137 - 1), NA())</f>
+        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 137 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q138">
-        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 137 - 1), NA())</f>
+        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 137 - 1), NA())</f>
         <v/>
       </c>
       <c r="R138">
-        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 137 - 1), NA())</f>
+        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 137 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="139">
       <c r="P139" s="2">
-        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 138 - 1), NA())</f>
+        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 138 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q139">
-        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 138 - 1), NA())</f>
+        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 138 - 1), NA())</f>
         <v/>
       </c>
       <c r="R139">
-        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 138 - 1), NA())</f>
+        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 138 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="140">
       <c r="P140" s="2">
-        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 139 - 1), NA())</f>
+        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 139 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q140">
-        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 139 - 1), NA())</f>
+        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 139 - 1), NA())</f>
         <v/>
       </c>
       <c r="R140">
-        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 139 - 1), NA())</f>
+        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 139 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="141">
       <c r="P141" s="2">
-        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 140 - 1), NA())</f>
+        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 140 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q141">
-        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 140 - 1), NA())</f>
+        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 140 - 1), NA())</f>
         <v/>
       </c>
       <c r="R141">
-        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 140 - 1), NA())</f>
+        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 140 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="142">
       <c r="P142" s="2">
-        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 141 - 1), NA())</f>
+        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 141 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q142">
-        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 141 - 1), NA())</f>
+        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 141 - 1), NA())</f>
         <v/>
       </c>
       <c r="R142">
-        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 141 - 1), NA())</f>
+        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 141 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="143">
       <c r="P143" s="2">
-        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 142 - 1), NA())</f>
+        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 142 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q143">
-        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 142 - 1), NA())</f>
+        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 142 - 1), NA())</f>
         <v/>
       </c>
       <c r="R143">
-        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 142 - 1), NA())</f>
+        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 142 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="144">
       <c r="P144" s="2">
-        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 143 - 1), NA())</f>
+        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 143 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q144">
-        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 143 - 1), NA())</f>
+        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 143 - 1), NA())</f>
         <v/>
       </c>
       <c r="R144">
-        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 143 - 1), NA())</f>
+        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 143 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="145">
       <c r="P145" s="2">
-        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 144 - 1), NA())</f>
+        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 144 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q145">
-        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 144 - 1), NA())</f>
+        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 144 - 1), NA())</f>
         <v/>
       </c>
       <c r="R145">
-        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 144 - 1), NA())</f>
+        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 144 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="146">
       <c r="P146" s="2">
-        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 145 - 1), NA())</f>
+        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 145 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q146">
-        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 145 - 1), NA())</f>
+        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 145 - 1), NA())</f>
         <v/>
       </c>
       <c r="R146">
-        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 145 - 1), NA())</f>
+        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 145 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="147">
       <c r="P147" s="2">
-        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 146 - 1), NA())</f>
+        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 146 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q147">
-        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 146 - 1), NA())</f>
+        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 146 - 1), NA())</f>
         <v/>
       </c>
       <c r="R147">
-        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 146 - 1), NA())</f>
+        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 146 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="148">
       <c r="P148" s="2">
-        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 147 - 1), NA())</f>
+        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 147 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q148">
-        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 147 - 1), NA())</f>
+        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 147 - 1), NA())</f>
         <v/>
       </c>
       <c r="R148">
-        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 147 - 1), NA())</f>
+        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 147 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="149">
       <c r="P149" s="2">
-        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 148 - 1), NA())</f>
+        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 148 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q149">
-        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 148 - 1), NA())</f>
+        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 148 - 1), NA())</f>
         <v/>
       </c>
       <c r="R149">
-        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 148 - 1), NA())</f>
+        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 148 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="150">
       <c r="P150" s="2">
-        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 149 - 1), NA())</f>
+        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 149 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q150">
-        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 149 - 1), NA())</f>
+        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 149 - 1), NA())</f>
         <v/>
       </c>
       <c r="R150">
-        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 149 - 1), NA())</f>
+        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 149 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="151">
       <c r="P151" s="2">
-        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 150 - 1), NA())</f>
+        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 150 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q151">
-        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 150 - 1), NA())</f>
+        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 150 - 1), NA())</f>
         <v/>
       </c>
       <c r="R151">
-        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 150 - 1), NA())</f>
+        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 150 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="152">
       <c r="P152" s="2">
-        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 151 - 1), NA())</f>
+        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 151 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q152">
-        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 151 - 1), NA())</f>
+        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 151 - 1), NA())</f>
         <v/>
       </c>
       <c r="R152">
-        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 151 - 1), NA())</f>
+        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 151 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="153">
       <c r="P153" s="2">
-        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 152 - 1), NA())</f>
+        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 152 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q153">
-        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 152 - 1), NA())</f>
+        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 152 - 1), NA())</f>
         <v/>
       </c>
       <c r="R153">
-        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 152 - 1), NA())</f>
+        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 152 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="154">
       <c r="P154" s="2">
-        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 153 - 1), NA())</f>
+        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 153 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q154">
-        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 153 - 1), NA())</f>
+        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 153 - 1), NA())</f>
         <v/>
       </c>
       <c r="R154">
-        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 153 - 1), NA())</f>
+        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 153 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="155">
       <c r="P155" s="2">
-        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 154 - 1), NA())</f>
+        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 154 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q155">
-        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 154 - 1), NA())</f>
+        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 154 - 1), NA())</f>
         <v/>
       </c>
       <c r="R155">
-        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 154 - 1), NA())</f>
+        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 154 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="156">
       <c r="P156" s="2">
-        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 155 - 1), NA())</f>
+        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 155 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q156">
-        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 155 - 1), NA())</f>
+        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 155 - 1), NA())</f>
         <v/>
       </c>
       <c r="R156">
-        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 155 - 1), NA())</f>
+        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 155 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="157">
       <c r="P157" s="2">
-        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 156 - 1), NA())</f>
+        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 156 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q157">
-        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 156 - 1), NA())</f>
+        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 156 - 1), NA())</f>
         <v/>
       </c>
       <c r="R157">
-        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 156 - 1), NA())</f>
+        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 156 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="158">
       <c r="P158" s="2">
-        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 157 - 1), NA())</f>
+        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 157 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q158">
-        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 157 - 1), NA())</f>
+        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 157 - 1), NA())</f>
         <v/>
       </c>
       <c r="R158">
-        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 157 - 1), NA())</f>
+        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 157 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="159">
       <c r="P159" s="2">
-        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 158 - 1), NA())</f>
+        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 158 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q159">
-        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 158 - 1), NA())</f>
+        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 158 - 1), NA())</f>
         <v/>
       </c>
       <c r="R159">
-        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 158 - 1), NA())</f>
+        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 158 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="160">
       <c r="P160" s="2">
-        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 159 - 1), NA())</f>
+        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 159 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q160">
-        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 159 - 1), NA())</f>
+        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 159 - 1), NA())</f>
         <v/>
       </c>
       <c r="R160">
-        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 159 - 1), NA())</f>
+        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 159 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="161">
       <c r="P161" s="2">
-        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 160 - 1), NA())</f>
+        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 160 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q161">
-        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 160 - 1), NA())</f>
+        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 160 - 1), NA())</f>
         <v/>
       </c>
       <c r="R161">
-        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 160 - 1), NA())</f>
+        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 160 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="162">
       <c r="P162" s="2">
-        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 161 - 1), NA())</f>
+        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 161 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q162">
-        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 161 - 1), NA())</f>
+        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 161 - 1), NA())</f>
         <v/>
       </c>
       <c r="R162">
-        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 161 - 1), NA())</f>
+        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 161 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="163">
       <c r="P163" s="2">
-        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 162 - 1), NA())</f>
+        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 162 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q163">
-        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 162 - 1), NA())</f>
+        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 162 - 1), NA())</f>
         <v/>
       </c>
       <c r="R163">
-        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 162 - 1), NA())</f>
+        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 162 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="164">
       <c r="P164" s="2">
-        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 163 - 1), NA())</f>
+        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 163 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q164">
-        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 163 - 1), NA())</f>
+        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 163 - 1), NA())</f>
         <v/>
       </c>
       <c r="R164">
-        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 163 - 1), NA())</f>
+        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 163 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="165">
       <c r="P165" s="2">
-        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 164 - 1), NA())</f>
+        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 164 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q165">
-        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 164 - 1), NA())</f>
+        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 164 - 1), NA())</f>
         <v/>
       </c>
       <c r="R165">
-        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 164 - 1), NA())</f>
+        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 164 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="166">
       <c r="P166" s="2">
-        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 165 - 1), NA())</f>
+        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 165 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q166">
-        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 165 - 1), NA())</f>
+        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 165 - 1), NA())</f>
         <v/>
       </c>
       <c r="R166">
-        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 165 - 1), NA())</f>
+        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 165 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="167">
       <c r="P167" s="2">
-        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 166 - 1), NA())</f>
+        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 166 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q167">
-        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 166 - 1), NA())</f>
+        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 166 - 1), NA())</f>
         <v/>
       </c>
       <c r="R167">
-        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 166 - 1), NA())</f>
+        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 166 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="168">
       <c r="P168" s="2">
-        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 167 - 1), NA())</f>
+        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 167 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q168">
-        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 167 - 1), NA())</f>
+        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 167 - 1), NA())</f>
         <v/>
       </c>
       <c r="R168">
-        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 167 - 1), NA())</f>
+        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 167 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="169">
       <c r="P169" s="2">
-        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 168 - 1), NA())</f>
+        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 168 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q169">
-        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 168 - 1), NA())</f>
+        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 168 - 1), NA())</f>
         <v/>
       </c>
       <c r="R169">
-        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 168 - 1), NA())</f>
+        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 168 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="170">
       <c r="P170" s="2">
-        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 169 - 1), NA())</f>
+        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 169 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q170">
-        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 169 - 1), NA())</f>
+        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 169 - 1), NA())</f>
         <v/>
       </c>
       <c r="R170">
-        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 169 - 1), NA())</f>
+        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 169 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="171">
       <c r="P171" s="2">
-        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 170 - 1), NA())</f>
+        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 170 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q171">
-        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 170 - 1), NA())</f>
+        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 170 - 1), NA())</f>
         <v/>
       </c>
       <c r="R171">
-        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 170 - 1), NA())</f>
+        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 170 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="172">
       <c r="P172" s="2">
-        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 171 - 1), NA())</f>
+        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 171 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q172">
-        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 171 - 1), NA())</f>
+        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 171 - 1), NA())</f>
         <v/>
       </c>
       <c r="R172">
-        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 171 - 1), NA())</f>
+        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 171 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="173">
       <c r="P173" s="2">
-        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 172 - 1), NA())</f>
+        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 172 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q173">
-        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 172 - 1), NA())</f>
+        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 172 - 1), NA())</f>
         <v/>
       </c>
       <c r="R173">
-        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 172 - 1), NA())</f>
+        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 172 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="174">
       <c r="P174" s="2">
-        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 173 - 1), NA())</f>
+        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 173 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q174">
-        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 173 - 1), NA())</f>
+        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 173 - 1), NA())</f>
         <v/>
       </c>
       <c r="R174">
-        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 173 - 1), NA())</f>
+        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 173 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="175">
       <c r="P175" s="2">
-        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 174 - 1), NA())</f>
+        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 174 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q175">
-        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 174 - 1), NA())</f>
+        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 174 - 1), NA())</f>
         <v/>
       </c>
       <c r="R175">
-        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 174 - 1), NA())</f>
+        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 174 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="176">
       <c r="P176" s="2">
-        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 175 - 1), NA())</f>
+        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 175 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q176">
-        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 175 - 1), NA())</f>
+        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 175 - 1), NA())</f>
         <v/>
       </c>
       <c r="R176">
-        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 175 - 1), NA())</f>
+        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 175 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="177">
       <c r="P177" s="2">
-        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 176 - 1), NA())</f>
+        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 176 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q177">
-        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 176 - 1), NA())</f>
+        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 176 - 1), NA())</f>
         <v/>
       </c>
       <c r="R177">
-        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 176 - 1), NA())</f>
+        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 176 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="178">
       <c r="P178" s="2">
-        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 177 - 1), NA())</f>
+        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 177 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q178">
-        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 177 - 1), NA())</f>
+        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 177 - 1), NA())</f>
         <v/>
       </c>
       <c r="R178">
-        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 177 - 1), NA())</f>
+        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 177 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="179">
       <c r="P179" s="2">
-        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 178 - 1), NA())</f>
+        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 178 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q179">
-        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 178 - 1), NA())</f>
+        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 178 - 1), NA())</f>
         <v/>
       </c>
       <c r="R179">
-        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 178 - 1), NA())</f>
+        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 178 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="180">
       <c r="P180" s="2">
-        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 179 - 1), NA())</f>
+        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 179 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q180">
-        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 179 - 1), NA())</f>
+        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 179 - 1), NA())</f>
         <v/>
       </c>
       <c r="R180">
-        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 179 - 1), NA())</f>
+        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 179 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="181">
       <c r="P181" s="2">
-        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 180 - 1), NA())</f>
+        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 180 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q181">
-        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 180 - 1), NA())</f>
+        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 180 - 1), NA())</f>
         <v/>
       </c>
       <c r="R181">
-        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 180 - 1), NA())</f>
+        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 180 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="182">
       <c r="P182" s="2">
-        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 181 - 1), NA())</f>
+        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 181 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q182">
-        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 181 - 1), NA())</f>
+        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 181 - 1), NA())</f>
         <v/>
       </c>
       <c r="R182">
-        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 181 - 1), NA())</f>
+        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 181 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="183">
       <c r="P183" s="2">
-        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 182 - 1), NA())</f>
+        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 182 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q183">
-        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 182 - 1), NA())</f>
+        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 182 - 1), NA())</f>
         <v/>
       </c>
       <c r="R183">
-        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 182 - 1), NA())</f>
+        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 182 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="184">
       <c r="P184" s="2">
-        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 183 - 1), NA())</f>
+        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 183 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q184">
-        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 183 - 1), NA())</f>
+        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 183 - 1), NA())</f>
         <v/>
       </c>
       <c r="R184">
-        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 183 - 1), NA())</f>
+        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 183 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="185">
       <c r="P185" s="2">
-        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 184 - 1), NA())</f>
+        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 184 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q185">
-        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 184 - 1), NA())</f>
+        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 184 - 1), NA())</f>
         <v/>
       </c>
       <c r="R185">
-        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 184 - 1), NA())</f>
+        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 184 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="186">
       <c r="P186" s="2">
-        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 185 - 1), NA())</f>
+        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 185 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q186">
-        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 185 - 1), NA())</f>
+        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 185 - 1), NA())</f>
         <v/>
       </c>
       <c r="R186">
-        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 185 - 1), NA())</f>
+        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 185 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="187">
       <c r="P187" s="2">
-        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 186 - 1), NA())</f>
+        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 186 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q187">
-        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 186 - 1), NA())</f>
+        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 186 - 1), NA())</f>
         <v/>
       </c>
       <c r="R187">
-        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 186 - 1), NA())</f>
+        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 186 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="188">
       <c r="P188" s="2">
-        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 187 - 1), NA())</f>
+        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 187 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q188">
-        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 187 - 1), NA())</f>
+        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 187 - 1), NA())</f>
         <v/>
       </c>
       <c r="R188">
-        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 187 - 1), NA())</f>
+        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 187 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="189">
       <c r="P189" s="2">
-        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 188 - 1), NA())</f>
+        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 188 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q189">
-        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 188 - 1), NA())</f>
+        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 188 - 1), NA())</f>
         <v/>
       </c>
       <c r="R189">
-        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 188 - 1), NA())</f>
+        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 188 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="190">
       <c r="P190" s="2">
-        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 189 - 1), NA())</f>
+        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 189 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q190">
-        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 189 - 1), NA())</f>
+        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 189 - 1), NA())</f>
         <v/>
       </c>
       <c r="R190">
-        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 189 - 1), NA())</f>
+        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 189 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="191">
       <c r="P191" s="2">
-        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 190 - 1), NA())</f>
+        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 190 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q191">
-        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 190 - 1), NA())</f>
+        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 190 - 1), NA())</f>
         <v/>
       </c>
       <c r="R191">
-        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 190 - 1), NA())</f>
+        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 190 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="192">
       <c r="P192" s="2">
-        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 191 - 1), NA())</f>
+        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 191 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q192">
-        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 191 - 1), NA())</f>
+        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 191 - 1), NA())</f>
         <v/>
       </c>
       <c r="R192">
-        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 191 - 1), NA())</f>
+        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 191 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="193">
       <c r="P193" s="2">
-        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 192 - 1), NA())</f>
+        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 192 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q193">
-        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 192 - 1), NA())</f>
+        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 192 - 1), NA())</f>
         <v/>
       </c>
       <c r="R193">
-        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 192 - 1), NA())</f>
+        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 192 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="194">
       <c r="P194" s="2">
-        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 193 - 1), NA())</f>
+        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 193 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q194">
-        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 193 - 1), NA())</f>
+        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 193 - 1), NA())</f>
         <v/>
       </c>
       <c r="R194">
-        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 193 - 1), NA())</f>
+        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 193 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="195">
       <c r="P195" s="2">
-        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 194 - 1), NA())</f>
+        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 194 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q195">
-        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 194 - 1), NA())</f>
+        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 194 - 1), NA())</f>
         <v/>
       </c>
       <c r="R195">
-        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 194 - 1), NA())</f>
+        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 194 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="196">
       <c r="P196" s="2">
-        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 195 - 1), NA())</f>
+        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 195 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q196">
-        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 195 - 1), NA())</f>
+        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 195 - 1), NA())</f>
         <v/>
       </c>
       <c r="R196">
-        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 195 - 1), NA())</f>
+        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 195 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="197">
       <c r="P197" s="2">
-        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 196 - 1), NA())</f>
+        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 196 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q197">
-        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 196 - 1), NA())</f>
+        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 196 - 1), NA())</f>
         <v/>
       </c>
       <c r="R197">
-        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 196 - 1), NA())</f>
+        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 196 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="198">
       <c r="P198" s="2">
-        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 197 - 1), NA())</f>
+        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 197 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q198">
-        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 197 - 1), NA())</f>
+        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 197 - 1), NA())</f>
         <v/>
       </c>
       <c r="R198">
-        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 197 - 1), NA())</f>
+        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 197 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="199">
       <c r="P199" s="2">
-        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 198 - 1), NA())</f>
+        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 198 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q199">
-        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 198 - 1), NA())</f>
+        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 198 - 1), NA())</f>
         <v/>
       </c>
       <c r="R199">
-        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 198 - 1), NA())</f>
+        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 198 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="200">
       <c r="P200" s="2">
-        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 199 - 1), NA())</f>
+        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 199 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q200">
-        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 199 - 1), NA())</f>
+        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 199 - 1), NA())</f>
         <v/>
       </c>
       <c r="R200">
-        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 199 - 1), NA())</f>
+        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 199 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="201">
       <c r="P201" s="2">
-        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 200 - 1), NA())</f>
+        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 200 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q201">
-        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 200 - 1), NA())</f>
+        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 200 - 1), NA())</f>
         <v/>
       </c>
       <c r="R201">
-        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 200 - 1), NA())</f>
+        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 200 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="202">
       <c r="P202" s="2">
-        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 201 - 1), NA())</f>
+        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 201 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q202">
-        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 201 - 1), NA())</f>
+        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 201 - 1), NA())</f>
         <v/>
       </c>
       <c r="R202">
-        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 201 - 1), NA())</f>
+        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 201 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="203">
       <c r="P203" s="2">
-        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 202 - 1), NA())</f>
+        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 202 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q203">
-        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 202 - 1), NA())</f>
+        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 202 - 1), NA())</f>
         <v/>
       </c>
       <c r="R203">
-        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 202 - 1), NA())</f>
+        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 202 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="204">
       <c r="P204" s="2">
-        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 203 - 1), NA())</f>
+        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 203 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q204">
-        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 203 - 1), NA())</f>
+        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 203 - 1), NA())</f>
         <v/>
       </c>
       <c r="R204">
-        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 203 - 1), NA())</f>
+        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 203 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="205">
       <c r="P205" s="2">
-        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 204 - 1), NA())</f>
+        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 204 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q205">
-        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 204 - 1), NA())</f>
+        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 204 - 1), NA())</f>
         <v/>
       </c>
       <c r="R205">
-        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 204 - 1), NA())</f>
+        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 204 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="206">
       <c r="P206" s="2">
-        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 205 - 1), NA())</f>
+        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 205 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q206">
-        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 205 - 1), NA())</f>
+        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 205 - 1), NA())</f>
         <v/>
       </c>
       <c r="R206">
-        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 205 - 1), NA())</f>
+        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 205 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="207">
       <c r="P207" s="2">
-        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 206 - 1), NA())</f>
+        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 206 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q207">
-        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 206 - 1), NA())</f>
+        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 206 - 1), NA())</f>
         <v/>
       </c>
       <c r="R207">
-        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 206 - 1), NA())</f>
+        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 206 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="208">
       <c r="P208" s="2">
-        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 207 - 1), NA())</f>
+        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 207 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q208">
-        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 207 - 1), NA())</f>
+        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 207 - 1), NA())</f>
         <v/>
       </c>
       <c r="R208">
-        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 207 - 1), NA())</f>
+        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 207 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="209">
       <c r="P209" s="2">
-        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 208 - 1), NA())</f>
+        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 208 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q209">
-        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 208 - 1), NA())</f>
+        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 208 - 1), NA())</f>
         <v/>
       </c>
       <c r="R209">
-        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 208 - 1), NA())</f>
+        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 208 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="210">
       <c r="P210" s="2">
-        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 209 - 1), NA())</f>
+        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 209 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q210">
-        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 209 - 1), NA())</f>
+        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 209 - 1), NA())</f>
         <v/>
       </c>
       <c r="R210">
-        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 209 - 1), NA())</f>
+        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 209 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="211">
       <c r="P211" s="2">
-        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 210 - 1), NA())</f>
+        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 210 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q211">
-        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 210 - 1), NA())</f>
+        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 210 - 1), NA())</f>
         <v/>
       </c>
       <c r="R211">
-        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 210 - 1), NA())</f>
+        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 210 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="212">
       <c r="P212" s="2">
-        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 211 - 1), NA())</f>
+        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 211 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q212">
-        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 211 - 1), NA())</f>
+        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 211 - 1), NA())</f>
         <v/>
       </c>
       <c r="R212">
-        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 211 - 1), NA())</f>
+        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 211 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="213">
       <c r="P213" s="2">
-        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 212 - 1), NA())</f>
+        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 212 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q213">
-        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 212 - 1), NA())</f>
+        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 212 - 1), NA())</f>
         <v/>
       </c>
       <c r="R213">
-        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 212 - 1), NA())</f>
+        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 212 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="214">
       <c r="P214" s="2">
-        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 213 - 1), NA())</f>
+        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 213 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q214">
-        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 213 - 1), NA())</f>
+        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 213 - 1), NA())</f>
         <v/>
       </c>
       <c r="R214">
-        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 213 - 1), NA())</f>
+        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 213 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="215">
       <c r="P215" s="2">
-        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 214 - 1), NA())</f>
+        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 214 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q215">
-        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 214 - 1), NA())</f>
+        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 214 - 1), NA())</f>
         <v/>
       </c>
       <c r="R215">
-        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 214 - 1), NA())</f>
+        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 214 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="216">
       <c r="P216" s="2">
-        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 215 - 1), NA())</f>
+        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 215 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q216">
-        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 215 - 1), NA())</f>
+        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 215 - 1), NA())</f>
         <v/>
       </c>
       <c r="R216">
-        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 215 - 1), NA())</f>
+        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 215 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="217">
       <c r="P217" s="2">
-        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 216 - 1), NA())</f>
+        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 216 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q217">
-        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 216 - 1), NA())</f>
+        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 216 - 1), NA())</f>
         <v/>
       </c>
       <c r="R217">
-        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 216 - 1), NA())</f>
+        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 216 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="218">
       <c r="P218" s="2">
-        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 217 - 1), NA())</f>
+        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 217 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q218">
-        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 217 - 1), NA())</f>
+        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 217 - 1), NA())</f>
         <v/>
       </c>
       <c r="R218">
-        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 217 - 1), NA())</f>
+        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 217 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="219">
       <c r="P219" s="2">
-        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 218 - 1), NA())</f>
+        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 218 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q219">
-        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 218 - 1), NA())</f>
+        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 218 - 1), NA())</f>
         <v/>
       </c>
       <c r="R219">
-        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 218 - 1), NA())</f>
+        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 218 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="220">
       <c r="P220" s="2">
-        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 219 - 1), NA())</f>
+        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 219 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q220">
-        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 219 - 1), NA())</f>
+        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 219 - 1), NA())</f>
         <v/>
       </c>
       <c r="R220">
-        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 219 - 1), NA())</f>
+        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 219 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="221">
       <c r="P221" s="2">
-        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 220 - 1), NA())</f>
+        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 220 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q221">
-        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 220 - 1), NA())</f>
+        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 220 - 1), NA())</f>
         <v/>
       </c>
       <c r="R221">
-        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 220 - 1), NA())</f>
+        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 220 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="222">
       <c r="P222" s="2">
-        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 221 - 1), NA())</f>
+        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 221 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q222">
-        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 221 - 1), NA())</f>
+        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 221 - 1), NA())</f>
         <v/>
       </c>
       <c r="R222">
-        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 221 - 1), NA())</f>
+        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 221 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="223">
       <c r="P223" s="2">
-        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 222 - 1), NA())</f>
+        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 222 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q223">
-        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 222 - 1), NA())</f>
+        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 222 - 1), NA())</f>
         <v/>
       </c>
       <c r="R223">
-        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 222 - 1), NA())</f>
+        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 222 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="224">
       <c r="P224" s="2">
-        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 223 - 1), NA())</f>
+        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 223 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q224">
-        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 223 - 1), NA())</f>
+        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 223 - 1), NA())</f>
         <v/>
       </c>
       <c r="R224">
-        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 223 - 1), NA())</f>
+        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 223 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="225">
       <c r="P225" s="2">
-        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 224 - 1), NA())</f>
+        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 224 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q225">
-        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 224 - 1), NA())</f>
+        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 224 - 1), NA())</f>
         <v/>
       </c>
       <c r="R225">
-        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 224 - 1), NA())</f>
+        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 224 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="226">
       <c r="P226" s="2">
-        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 225 - 1), NA())</f>
+        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 225 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q226">
-        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 225 - 1), NA())</f>
+        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 225 - 1), NA())</f>
         <v/>
       </c>
       <c r="R226">
-        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 225 - 1), NA())</f>
+        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 225 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="227">
       <c r="P227" s="2">
-        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 226 - 1), NA())</f>
+        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 226 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q227">
-        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 226 - 1), NA())</f>
+        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 226 - 1), NA())</f>
         <v/>
       </c>
       <c r="R227">
-        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 226 - 1), NA())</f>
+        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 226 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="228">
       <c r="P228" s="2">
-        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 227 - 1), NA())</f>
+        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 227 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q228">
-        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 227 - 1), NA())</f>
+        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 227 - 1), NA())</f>
         <v/>
       </c>
       <c r="R228">
-        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 227 - 1), NA())</f>
+        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 227 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="229">
       <c r="P229" s="2">
-        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 228 - 1), NA())</f>
+        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 228 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q229">
-        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 228 - 1), NA())</f>
+        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 228 - 1), NA())</f>
         <v/>
       </c>
       <c r="R229">
-        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 228 - 1), NA())</f>
+        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 228 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="230">
       <c r="P230" s="2">
-        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 229 - 1), NA())</f>
+        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 229 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q230">
-        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 229 - 1), NA())</f>
+        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 229 - 1), NA())</f>
         <v/>
       </c>
       <c r="R230">
-        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 229 - 1), NA())</f>
+        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 229 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="231">
       <c r="P231" s="2">
-        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 230 - 1), NA())</f>
+        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 230 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q231">
-        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 230 - 1), NA())</f>
+        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 230 - 1), NA())</f>
         <v/>
       </c>
       <c r="R231">
-        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 230 - 1), NA())</f>
+        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 230 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="232">
       <c r="P232" s="2">
-        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 231 - 1), NA())</f>
+        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 231 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q232">
-        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 231 - 1), NA())</f>
+        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 231 - 1), NA())</f>
         <v/>
       </c>
       <c r="R232">
-        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 231 - 1), NA())</f>
+        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 231 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="233">
       <c r="P233" s="2">
-        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 232 - 1), NA())</f>
+        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 232 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q233">
-        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 232 - 1), NA())</f>
+        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 232 - 1), NA())</f>
         <v/>
       </c>
       <c r="R233">
-        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 232 - 1), NA())</f>
+        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 232 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="234">
       <c r="P234" s="2">
-        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 233 - 1), NA())</f>
+        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 233 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q234">
-        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 233 - 1), NA())</f>
+        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 233 - 1), NA())</f>
         <v/>
       </c>
       <c r="R234">
-        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 233 - 1), NA())</f>
+        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 233 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="235">
       <c r="P235" s="2">
-        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 234 - 1), NA())</f>
+        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 234 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q235">
-        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 234 - 1), NA())</f>
+        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 234 - 1), NA())</f>
         <v/>
       </c>
       <c r="R235">
-        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 234 - 1), NA())</f>
+        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 234 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="236">
       <c r="P236" s="2">
-        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 235 - 1), NA())</f>
+        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 235 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q236">
-        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 235 - 1), NA())</f>
+        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 235 - 1), NA())</f>
         <v/>
       </c>
       <c r="R236">
-        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 235 - 1), NA())</f>
+        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 235 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="237">
       <c r="P237" s="2">
-        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 236 - 1), NA())</f>
+        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 236 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q237">
-        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 236 - 1), NA())</f>
+        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 236 - 1), NA())</f>
         <v/>
       </c>
       <c r="R237">
-        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 236 - 1), NA())</f>
+        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 236 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="238">
       <c r="P238" s="2">
-        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 237 - 1), NA())</f>
+        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 237 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q238">
-        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 237 - 1), NA())</f>
+        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 237 - 1), NA())</f>
         <v/>
       </c>
       <c r="R238">
-        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 237 - 1), NA())</f>
+        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 237 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="239">
       <c r="P239" s="2">
-        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 238 - 1), NA())</f>
+        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 238 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q239">
-        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 238 - 1), NA())</f>
+        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 238 - 1), NA())</f>
         <v/>
       </c>
       <c r="R239">
-        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 238 - 1), NA())</f>
+        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 238 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="240">
       <c r="P240" s="2">
-        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 239 - 1), NA())</f>
+        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 239 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q240">
-        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 239 - 1), NA())</f>
+        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 239 - 1), NA())</f>
         <v/>
       </c>
       <c r="R240">
-        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 239 - 1), NA())</f>
+        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 239 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="241">
       <c r="P241" s="2">
-        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 240 - 1), NA())</f>
+        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 240 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q241">
-        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 240 - 1), NA())</f>
+        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 240 - 1), NA())</f>
         <v/>
       </c>
       <c r="R241">
-        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 240 - 1), NA())</f>
+        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 240 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="242">
       <c r="P242" s="2">
-        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 241 - 1), NA())</f>
+        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 241 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q242">
-        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 241 - 1), NA())</f>
+        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 241 - 1), NA())</f>
         <v/>
       </c>
       <c r="R242">
-        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 241 - 1), NA())</f>
+        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 241 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="243">
       <c r="P243" s="2">
-        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 242 - 1), NA())</f>
+        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 242 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q243">
-        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 242 - 1), NA())</f>
+        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 242 - 1), NA())</f>
         <v/>
       </c>
       <c r="R243">
-        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 242 - 1), NA())</f>
+        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 242 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="244">
       <c r="P244" s="2">
-        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 243 - 1), NA())</f>
+        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 243 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q244">
-        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 243 - 1), NA())</f>
+        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 243 - 1), NA())</f>
         <v/>
       </c>
       <c r="R244">
-        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 243 - 1), NA())</f>
+        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 243 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="245">
       <c r="P245" s="2">
-        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 244 - 1), NA())</f>
+        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 244 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q245">
-        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 244 - 1), NA())</f>
+        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 244 - 1), NA())</f>
         <v/>
       </c>
       <c r="R245">
-        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 244 - 1), NA())</f>
+        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 244 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="246">
       <c r="P246" s="2">
-        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 245 - 1), NA())</f>
+        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 245 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q246">
-        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 245 - 1), NA())</f>
+        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 245 - 1), NA())</f>
         <v/>
       </c>
       <c r="R246">
-        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 245 - 1), NA())</f>
+        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 245 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="247">
       <c r="P247" s="2">
-        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 246 - 1), NA())</f>
+        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 246 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q247">
-        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 246 - 1), NA())</f>
+        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 246 - 1), NA())</f>
         <v/>
       </c>
       <c r="R247">
-        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 246 - 1), NA())</f>
+        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 246 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="248">
       <c r="P248" s="2">
-        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 247 - 1), NA())</f>
+        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 247 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q248">
-        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 247 - 1), NA())</f>
+        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 247 - 1), NA())</f>
         <v/>
       </c>
       <c r="R248">
-        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 247 - 1), NA())</f>
+        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 247 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="249">
       <c r="P249" s="2">
-        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 248 - 1), NA())</f>
+        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 248 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q249">
-        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 248 - 1), NA())</f>
+        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 248 - 1), NA())</f>
         <v/>
       </c>
       <c r="R249">
-        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 248 - 1), NA())</f>
+        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 248 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="250">
       <c r="P250" s="2">
-        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 249 - 1), NA())</f>
+        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 249 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q250">
-        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 249 - 1), NA())</f>
+        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 249 - 1), NA())</f>
         <v/>
       </c>
       <c r="R250">
-        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 249 - 1), NA())</f>
+        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 249 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="251">
       <c r="P251" s="2">
-        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 250 - 1), NA())</f>
+        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 250 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q251">
-        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 250 - 1), NA())</f>
+        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 250 - 1), NA())</f>
         <v/>
       </c>
       <c r="R251">
-        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 250 - 1), NA())</f>
+        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 250 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="252">
       <c r="P252" s="2">
-        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 251 - 1), NA())</f>
+        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 251 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q252">
-        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 251 - 1), NA())</f>
+        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 251 - 1), NA())</f>
         <v/>
       </c>
       <c r="R252">
-        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 251 - 1), NA())</f>
+        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 251 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="253">
       <c r="P253" s="2">
-        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 252 - 1), NA())</f>
+        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 252 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q253">
-        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 252 - 1), NA())</f>
+        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 252 - 1), NA())</f>
         <v/>
       </c>
       <c r="R253">
-        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 252 - 1), NA())</f>
+        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 252 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="254">
       <c r="P254" s="2">
-        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 253 - 1), NA())</f>
+        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 253 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q254">
-        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 253 - 1), NA())</f>
+        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 253 - 1), NA())</f>
         <v/>
       </c>
       <c r="R254">
-        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 253 - 1), NA())</f>
+        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 253 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="255">
       <c r="P255" s="2">
-        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 254 - 1), NA())</f>
+        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 254 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q255">
-        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 254 - 1), NA())</f>
+        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 254 - 1), NA())</f>
         <v/>
       </c>
       <c r="R255">
-        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 254 - 1), NA())</f>
+        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 254 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="256">
       <c r="P256" s="2">
-        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 255 - 1), NA())</f>
+        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 255 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q256">
-        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 255 - 1), NA())</f>
+        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 255 - 1), NA())</f>
         <v/>
       </c>
       <c r="R256">
-        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 255 - 1), NA())</f>
+        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 255 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="257">
       <c r="P257" s="2">
-        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 256 - 1), NA())</f>
+        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 256 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q257">
-        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 256 - 1), NA())</f>
+        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 256 - 1), NA())</f>
         <v/>
       </c>
       <c r="R257">
-        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 256 - 1), NA())</f>
+        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 256 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="258">
       <c r="P258" s="2">
-        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 257 - 1), NA())</f>
+        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 257 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q258">
-        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 257 - 1), NA())</f>
+        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 257 - 1), NA())</f>
         <v/>
       </c>
       <c r="R258">
-        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 257 - 1), NA())</f>
+        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 257 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="259">
       <c r="P259" s="2">
-        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 258 - 1), NA())</f>
+        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 258 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q259">
-        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 258 - 1), NA())</f>
+        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 258 - 1), NA())</f>
         <v/>
       </c>
       <c r="R259">
-        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 258 - 1), NA())</f>
+        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 258 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="260">
       <c r="P260" s="2">
-        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 259 - 1), NA())</f>
+        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 259 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q260">
-        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 259 - 1), NA())</f>
+        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 259 - 1), NA())</f>
         <v/>
       </c>
       <c r="R260">
-        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 259 - 1), NA())</f>
+        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 259 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="261">
       <c r="P261" s="2">
-        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 260 - 1), NA())</f>
+        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 260 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q261">
-        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 260 - 1), NA())</f>
+        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 260 - 1), NA())</f>
         <v/>
       </c>
       <c r="R261">
-        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 260 - 1), NA())</f>
+        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 260 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="262">
       <c r="P262" s="2">
-        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 261 - 1), NA())</f>
+        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 261 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q262">
-        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 261 - 1), NA())</f>
+        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 261 - 1), NA())</f>
         <v/>
       </c>
       <c r="R262">
-        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 261 - 1), NA())</f>
+        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 261 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="263">
       <c r="P263" s="2">
-        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 262 - 1), NA())</f>
+        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 262 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q263">
-        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 262 - 1), NA())</f>
+        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 262 - 1), NA())</f>
         <v/>
       </c>
       <c r="R263">
-        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 262 - 1), NA())</f>
+        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 262 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="264">
       <c r="P264" s="2">
-        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 263 - 1), NA())</f>
+        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 263 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q264">
-        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 263 - 1), NA())</f>
+        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 263 - 1), NA())</f>
         <v/>
       </c>
       <c r="R264">
-        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 263 - 1), NA())</f>
+        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 263 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="265">
       <c r="P265" s="2">
-        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 264 - 1), NA())</f>
+        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 264 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q265">
-        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 264 - 1), NA())</f>
+        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 264 - 1), NA())</f>
         <v/>
       </c>
       <c r="R265">
-        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 264 - 1), NA())</f>
+        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 264 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="266">
       <c r="P266" s="2">
-        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 265 - 1), NA())</f>
+        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 265 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q266">
-        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 265 - 1), NA())</f>
+        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 265 - 1), NA())</f>
         <v/>
       </c>
       <c r="R266">
-        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 265 - 1), NA())</f>
+        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 265 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="267">
       <c r="P267" s="2">
-        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 266 - 1), NA())</f>
+        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 266 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q267">
-        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 266 - 1), NA())</f>
+        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 266 - 1), NA())</f>
         <v/>
       </c>
       <c r="R267">
-        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 266 - 1), NA())</f>
+        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 266 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="268">
       <c r="P268" s="2">
-        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 267 - 1), NA())</f>
+        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 267 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q268">
-        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 267 - 1), NA())</f>
+        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 267 - 1), NA())</f>
         <v/>
       </c>
       <c r="R268">
-        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 267 - 1), NA())</f>
+        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 267 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="269">
       <c r="P269" s="2">
-        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 268 - 1), NA())</f>
+        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 268 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q269">
-        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 268 - 1), NA())</f>
+        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 268 - 1), NA())</f>
         <v/>
       </c>
       <c r="R269">
-        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 268 - 1), NA())</f>
+        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 268 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="270">
       <c r="P270" s="2">
-        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 269 - 1), NA())</f>
+        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 269 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q270">
-        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 269 - 1), NA())</f>
+        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 269 - 1), NA())</f>
         <v/>
       </c>
       <c r="R270">
-        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 269 - 1), NA())</f>
+        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 269 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="271">
       <c r="P271" s="2">
-        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 270 - 1), NA())</f>
+        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 270 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q271">
-        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 270 - 1), NA())</f>
+        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 270 - 1), NA())</f>
         <v/>
       </c>
       <c r="R271">
-        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 270 - 1), NA())</f>
+        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 270 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="272">
       <c r="P272" s="2">
-        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 271 - 1), NA())</f>
+        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 271 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q272">
-        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 271 - 1), NA())</f>
+        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 271 - 1), NA())</f>
         <v/>
       </c>
       <c r="R272">
-        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 271 - 1), NA())</f>
+        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 271 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="273">
       <c r="P273" s="2">
-        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 272 - 1), NA())</f>
+        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 272 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q273">
-        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 272 - 1), NA())</f>
+        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 272 - 1), NA())</f>
         <v/>
       </c>
       <c r="R273">
-        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 272 - 1), NA())</f>
+        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 272 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="274">
       <c r="P274" s="2">
-        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 273 - 1), NA())</f>
+        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 273 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q274">
-        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 273 - 1), NA())</f>
+        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 273 - 1), NA())</f>
         <v/>
       </c>
       <c r="R274">
-        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 273 - 1), NA())</f>
+        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 273 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="275">
       <c r="P275" s="2">
-        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 274 - 1), NA())</f>
+        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 274 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q275">
-        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 274 - 1), NA())</f>
+        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 274 - 1), NA())</f>
         <v/>
       </c>
       <c r="R275">
-        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 274 - 1), NA())</f>
+        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 274 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="276">
       <c r="P276" s="2">
-        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 275 - 1), NA())</f>
+        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 275 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q276">
-        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 275 - 1), NA())</f>
+        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 275 - 1), NA())</f>
         <v/>
       </c>
       <c r="R276">
-        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 275 - 1), NA())</f>
+        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 275 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="277">
       <c r="P277" s="2">
-        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 276 - 1), NA())</f>
+        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 276 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q277">
-        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 276 - 1), NA())</f>
+        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 276 - 1), NA())</f>
         <v/>
       </c>
       <c r="R277">
-        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 276 - 1), NA())</f>
+        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 276 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="278">
       <c r="P278" s="2">
-        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 277 - 1), NA())</f>
+        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 277 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q278">
-        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 277 - 1), NA())</f>
+        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 277 - 1), NA())</f>
         <v/>
       </c>
       <c r="R278">
-        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 277 - 1), NA())</f>
+        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 277 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="279">
       <c r="P279" s="2">
-        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 278 - 1), NA())</f>
+        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 278 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q279">
-        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 278 - 1), NA())</f>
+        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 278 - 1), NA())</f>
         <v/>
       </c>
       <c r="R279">
-        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 278 - 1), NA())</f>
+        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 278 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="280">
       <c r="P280" s="2">
-        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 279 - 1), NA())</f>
+        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 279 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q280">
-        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 279 - 1), NA())</f>
+        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 279 - 1), NA())</f>
         <v/>
       </c>
       <c r="R280">
-        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 279 - 1), NA())</f>
+        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 279 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="281">
       <c r="P281" s="2">
-        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 280 - 1), NA())</f>
+        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 280 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q281">
-        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 280 - 1), NA())</f>
+        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 280 - 1), NA())</f>
         <v/>
       </c>
       <c r="R281">
-        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 280 - 1), NA())</f>
+        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 280 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="282">
       <c r="P282" s="2">
-        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 281 - 1), NA())</f>
+        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 281 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q282">
-        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 281 - 1), NA())</f>
+        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 281 - 1), NA())</f>
         <v/>
       </c>
       <c r="R282">
-        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 281 - 1), NA())</f>
+        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 281 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="283">
       <c r="P283" s="2">
-        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 282 - 1), NA())</f>
+        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 282 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q283">
-        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 282 - 1), NA())</f>
+        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 282 - 1), NA())</f>
         <v/>
       </c>
       <c r="R283">
-        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 282 - 1), NA())</f>
+        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 282 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="284">
       <c r="P284" s="2">
-        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 283 - 1), NA())</f>
+        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 283 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q284">
-        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 283 - 1), NA())</f>
+        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 283 - 1), NA())</f>
         <v/>
       </c>
       <c r="R284">
-        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 283 - 1), NA())</f>
+        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 283 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="285">
       <c r="P285" s="2">
-        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 284 - 1), NA())</f>
+        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 284 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q285">
-        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 284 - 1), NA())</f>
+        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 284 - 1), NA())</f>
         <v/>
       </c>
       <c r="R285">
-        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 284 - 1), NA())</f>
+        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 284 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="286">
       <c r="P286" s="2">
-        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 285 - 1), NA())</f>
+        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 285 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q286">
-        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 285 - 1), NA())</f>
+        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 285 - 1), NA())</f>
         <v/>
       </c>
       <c r="R286">
-        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 285 - 1), NA())</f>
+        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 285 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="287">
       <c r="P287" s="2">
-        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 286 - 1), NA())</f>
+        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 286 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q287">
-        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 286 - 1), NA())</f>
+        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 286 - 1), NA())</f>
         <v/>
       </c>
       <c r="R287">
-        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 286 - 1), NA())</f>
+        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 286 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="288">
       <c r="P288" s="2">
-        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 287 - 1), NA())</f>
+        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 287 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q288">
-        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 287 - 1), NA())</f>
+        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 287 - 1), NA())</f>
         <v/>
       </c>
       <c r="R288">
-        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 287 - 1), NA())</f>
+        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 287 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="289">
       <c r="P289" s="2">
-        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 288 - 1), NA())</f>
+        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 288 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q289">
-        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 288 - 1), NA())</f>
+        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 288 - 1), NA())</f>
         <v/>
       </c>
       <c r="R289">
-        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 288 - 1), NA())</f>
+        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 288 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="290">
       <c r="P290" s="2">
-        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 289 - 1), NA())</f>
+        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 289 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q290">
-        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 289 - 1), NA())</f>
+        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 289 - 1), NA())</f>
         <v/>
       </c>
       <c r="R290">
-        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 289 - 1), NA())</f>
+        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 289 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="291">
       <c r="P291" s="2">
-        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 290 - 1), NA())</f>
+        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 290 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q291">
-        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 290 - 1), NA())</f>
+        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 290 - 1), NA())</f>
         <v/>
       </c>
       <c r="R291">
-        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 290 - 1), NA())</f>
+        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 290 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="292">
       <c r="P292" s="2">
-        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 291 - 1), NA())</f>
+        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 291 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q292">
-        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 291 - 1), NA())</f>
+        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 291 - 1), NA())</f>
         <v/>
       </c>
       <c r="R292">
-        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 291 - 1), NA())</f>
+        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 291 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="293">
       <c r="P293" s="2">
-        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 292 - 1), NA())</f>
+        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 292 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q293">
-        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 292 - 1), NA())</f>
+        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 292 - 1), NA())</f>
         <v/>
       </c>
       <c r="R293">
-        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 292 - 1), NA())</f>
+        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 292 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="294">
       <c r="P294" s="2">
-        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 293 - 1), NA())</f>
+        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 293 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q294">
-        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 293 - 1), NA())</f>
+        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 293 - 1), NA())</f>
         <v/>
       </c>
       <c r="R294">
-        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 293 - 1), NA())</f>
+        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 293 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="295">
       <c r="P295" s="2">
-        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 294 - 1), NA())</f>
+        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 294 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q295">
-        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 294 - 1), NA())</f>
+        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 294 - 1), NA())</f>
         <v/>
       </c>
       <c r="R295">
-        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 294 - 1), NA())</f>
+        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 294 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="296">
       <c r="P296" s="2">
-        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 295 - 1), NA())</f>
+        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 295 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q296">
-        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 295 - 1), NA())</f>
+        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 295 - 1), NA())</f>
         <v/>
       </c>
       <c r="R296">
-        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 295 - 1), NA())</f>
+        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 295 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="297">
       <c r="P297" s="2">
-        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 296 - 1), NA())</f>
+        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 296 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q297">
-        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 296 - 1), NA())</f>
+        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 296 - 1), NA())</f>
         <v/>
       </c>
       <c r="R297">
-        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 296 - 1), NA())</f>
+        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 296 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="298">
       <c r="P298" s="2">
-        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 297 - 1), NA())</f>
+        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 297 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q298">
-        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 297 - 1), NA())</f>
+        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 297 - 1), NA())</f>
         <v/>
       </c>
       <c r="R298">
-        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 297 - 1), NA())</f>
+        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 297 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="299">
       <c r="P299" s="2">
-        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 298 - 1), NA())</f>
+        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 298 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q299">
-        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 298 - 1), NA())</f>
+        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 298 - 1), NA())</f>
         <v/>
       </c>
       <c r="R299">
-        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 298 - 1), NA())</f>
+        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 298 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="300">
       <c r="P300" s="2">
-        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 299 - 1), NA())</f>
+        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 299 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q300">
-        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 299 - 1), NA())</f>
+        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 299 - 1), NA())</f>
         <v/>
       </c>
       <c r="R300">
-        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 299 - 1), NA())</f>
+        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 299 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="301">
       <c r="P301" s="2">
-        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 300 - 1), NA())</f>
+        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 300 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q301">
-        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 300 - 1), NA())</f>
+        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 300 - 1), NA())</f>
         <v/>
       </c>
       <c r="R301">
-        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 300 - 1), NA())</f>
+        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 300 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="302">
       <c r="P302" s="2">
-        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 301 - 1), NA())</f>
+        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 301 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q302">
-        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 301 - 1), NA())</f>
+        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 301 - 1), NA())</f>
         <v/>
       </c>
       <c r="R302">
-        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 301 - 1), NA())</f>
+        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 301 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="303">
       <c r="P303" s="2">
-        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 302 - 1), NA())</f>
+        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 302 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q303">
-        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 302 - 1), NA())</f>
+        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 302 - 1), NA())</f>
         <v/>
       </c>
       <c r="R303">
-        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 302 - 1), NA())</f>
+        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 302 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="304">
       <c r="P304" s="2">
-        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 303 - 1), NA())</f>
+        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 303 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q304">
-        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 303 - 1), NA())</f>
+        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 303 - 1), NA())</f>
         <v/>
       </c>
       <c r="R304">
-        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 303 - 1), NA())</f>
+        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 303 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="305">
       <c r="P305" s="2">
-        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 304 - 1), NA())</f>
+        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 304 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q305">
-        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 304 - 1), NA())</f>
+        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 304 - 1), NA())</f>
         <v/>
       </c>
       <c r="R305">
-        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 304 - 1), NA())</f>
+        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 304 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="306">
       <c r="P306" s="2">
-        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 305 - 1), NA())</f>
+        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 305 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q306">
-        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 305 - 1), NA())</f>
+        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 305 - 1), NA())</f>
         <v/>
       </c>
       <c r="R306">
-        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 305 - 1), NA())</f>
+        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 305 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="307">
       <c r="P307" s="2">
-        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 306 - 1), NA())</f>
+        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 306 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q307">
-        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 306 - 1), NA())</f>
+        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 306 - 1), NA())</f>
         <v/>
       </c>
       <c r="R307">
-        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 306 - 1), NA())</f>
+        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 306 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="308">
       <c r="P308" s="2">
-        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 307 - 1), NA())</f>
+        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 307 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q308">
-        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 307 - 1), NA())</f>
+        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 307 - 1), NA())</f>
         <v/>
       </c>
       <c r="R308">
-        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 307 - 1), NA())</f>
+        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 307 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="309">
       <c r="P309" s="2">
-        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 308 - 1), NA())</f>
+        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 308 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q309">
-        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 308 - 1), NA())</f>
+        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 308 - 1), NA())</f>
         <v/>
       </c>
       <c r="R309">
-        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 308 - 1), NA())</f>
+        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 308 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="310">
       <c r="P310" s="2">
-        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 309 - 1), NA())</f>
+        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 309 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q310">
-        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 309 - 1), NA())</f>
+        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 309 - 1), NA())</f>
         <v/>
       </c>
       <c r="R310">
-        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 309 - 1), NA())</f>
+        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 309 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="311">
       <c r="P311" s="2">
-        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 310 - 1), NA())</f>
+        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 310 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q311">
-        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 310 - 1), NA())</f>
+        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 310 - 1), NA())</f>
         <v/>
       </c>
       <c r="R311">
-        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 310 - 1), NA())</f>
+        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 310 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="312">
       <c r="P312" s="2">
-        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 311 - 1), NA())</f>
+        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 311 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q312">
-        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 311 - 1), NA())</f>
+        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 311 - 1), NA())</f>
         <v/>
       </c>
       <c r="R312">
-        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 311 - 1), NA())</f>
+        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 311 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="313">
       <c r="P313" s="2">
-        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 312 - 1), NA())</f>
+        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 312 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q313">
-        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 312 - 1), NA())</f>
+        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 312 - 1), NA())</f>
         <v/>
       </c>
       <c r="R313">
-        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 312 - 1), NA())</f>
+        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 312 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="314">
       <c r="P314" s="2">
-        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 313 - 1), NA())</f>
+        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 313 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q314">
-        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 313 - 1), NA())</f>
+        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 313 - 1), NA())</f>
         <v/>
       </c>
       <c r="R314">
-        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 313 - 1), NA())</f>
+        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 313 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="315">
       <c r="P315" s="2">
-        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 314 - 1), NA())</f>
+        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 314 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q315">
-        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 314 - 1), NA())</f>
+        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 314 - 1), NA())</f>
         <v/>
       </c>
       <c r="R315">
-        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 314 - 1), NA())</f>
+        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 314 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="316">
       <c r="P316" s="2">
-        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 315 - 1), NA())</f>
+        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 315 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q316">
-        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 315 - 1), NA())</f>
+        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 315 - 1), NA())</f>
         <v/>
       </c>
       <c r="R316">
-        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 315 - 1), NA())</f>
+        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 315 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="317">
       <c r="P317" s="2">
-        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 316 - 1), NA())</f>
+        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 316 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q317">
-        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 316 - 1), NA())</f>
+        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 316 - 1), NA())</f>
         <v/>
       </c>
       <c r="R317">
-        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 316 - 1), NA())</f>
+        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 316 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="318">
       <c r="P318" s="2">
-        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 317 - 1), NA())</f>
+        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 317 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q318">
-        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 317 - 1), NA())</f>
+        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 317 - 1), NA())</f>
         <v/>
       </c>
       <c r="R318">
-        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 317 - 1), NA())</f>
+        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 317 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="319">
       <c r="P319" s="2">
-        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 318 - 1), NA())</f>
+        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 318 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q319">
-        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 318 - 1), NA())</f>
+        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 318 - 1), NA())</f>
         <v/>
       </c>
       <c r="R319">
-        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 318 - 1), NA())</f>
+        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 318 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="320">
       <c r="P320" s="2">
-        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 319 - 1), NA())</f>
+        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 319 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q320">
-        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 319 - 1), NA())</f>
+        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 319 - 1), NA())</f>
         <v/>
       </c>
       <c r="R320">
-        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 319 - 1), NA())</f>
+        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 319 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="321">
       <c r="P321" s="2">
-        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 320 - 1), NA())</f>
+        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 320 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q321">
-        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 320 - 1), NA())</f>
+        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 320 - 1), NA())</f>
         <v/>
       </c>
       <c r="R321">
-        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 320 - 1), NA())</f>
+        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 320 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="322">
       <c r="P322" s="2">
-        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 321 - 1), NA())</f>
+        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 321 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q322">
-        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 321 - 1), NA())</f>
+        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 321 - 1), NA())</f>
         <v/>
       </c>
       <c r="R322">
-        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 321 - 1), NA())</f>
+        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 321 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="323">
       <c r="P323" s="2">
-        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 322 - 1), NA())</f>
+        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 322 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q323">
-        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 322 - 1), NA())</f>
+        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 322 - 1), NA())</f>
         <v/>
       </c>
       <c r="R323">
-        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 322 - 1), NA())</f>
+        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 322 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="324">
       <c r="P324" s="2">
-        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 323 - 1), NA())</f>
+        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 323 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q324">
-        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 323 - 1), NA())</f>
+        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 323 - 1), NA())</f>
         <v/>
       </c>
       <c r="R324">
-        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 323 - 1), NA())</f>
+        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 323 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="325">
       <c r="P325" s="2">
-        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 324 - 1), NA())</f>
+        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 324 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q325">
-        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 324 - 1), NA())</f>
+        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 324 - 1), NA())</f>
         <v/>
       </c>
       <c r="R325">
-        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 324 - 1), NA())</f>
+        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 324 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="326">
       <c r="P326" s="2">
-        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 325 - 1), NA())</f>
+        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 325 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q326">
-        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 325 - 1), NA())</f>
+        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 325 - 1), NA())</f>
         <v/>
       </c>
       <c r="R326">
-        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 325 - 1), NA())</f>
+        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 325 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="327">
       <c r="P327" s="2">
-        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 326 - 1), NA())</f>
+        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 326 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q327">
-        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 326 - 1), NA())</f>
+        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 326 - 1), NA())</f>
         <v/>
       </c>
       <c r="R327">
-        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 326 - 1), NA())</f>
+        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 326 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="328">
       <c r="P328" s="2">
-        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 327 - 1), NA())</f>
+        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 327 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q328">
-        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 327 - 1), NA())</f>
+        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 327 - 1), NA())</f>
         <v/>
       </c>
       <c r="R328">
-        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 327 - 1), NA())</f>
+        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 327 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="329">
       <c r="P329" s="2">
-        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 328 - 1), NA())</f>
+        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 328 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q329">
-        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 328 - 1), NA())</f>
+        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 328 - 1), NA())</f>
         <v/>
       </c>
       <c r="R329">
-        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 328 - 1), NA())</f>
+        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 328 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="330">
       <c r="P330" s="2">
-        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 329 - 1), NA())</f>
+        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 329 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q330">
-        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 329 - 1), NA())</f>
+        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 329 - 1), NA())</f>
         <v/>
       </c>
       <c r="R330">
-        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 329 - 1), NA())</f>
+        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 329 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="331">
       <c r="P331" s="2">
-        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 330 - 1), NA())</f>
+        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 330 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q331">
-        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 330 - 1), NA())</f>
+        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 330 - 1), NA())</f>
         <v/>
       </c>
       <c r="R331">
-        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 330 - 1), NA())</f>
+        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 330 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="332">
       <c r="P332" s="2">
-        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 331 - 1), NA())</f>
+        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 331 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q332">
-        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 331 - 1), NA())</f>
+        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 331 - 1), NA())</f>
         <v/>
       </c>
       <c r="R332">
-        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 331 - 1), NA())</f>
+        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 331 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="333">
       <c r="P333" s="2">
-        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 332 - 1), NA())</f>
+        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 332 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q333">
-        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 332 - 1), NA())</f>
+        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 332 - 1), NA())</f>
         <v/>
       </c>
       <c r="R333">
-        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 332 - 1), NA())</f>
+        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 332 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="334">
       <c r="P334" s="2">
-        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 333 - 1), NA())</f>
+        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 333 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q334">
-        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 333 - 1), NA())</f>
+        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 333 - 1), NA())</f>
         <v/>
       </c>
       <c r="R334">
-        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 333 - 1), NA())</f>
+        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 333 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="335">
       <c r="P335" s="2">
-        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 334 - 1), NA())</f>
+        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 334 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q335">
-        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 334 - 1), NA())</f>
+        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 334 - 1), NA())</f>
         <v/>
       </c>
       <c r="R335">
-        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 334 - 1), NA())</f>
+        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 334 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="336">
       <c r="P336" s="2">
-        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 335 - 1), NA())</f>
+        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 335 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q336">
-        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 335 - 1), NA())</f>
+        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 335 - 1), NA())</f>
         <v/>
       </c>
       <c r="R336">
-        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 335 - 1), NA())</f>
+        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 335 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="337">
       <c r="P337" s="2">
-        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 336 - 1), NA())</f>
+        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 336 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q337">
-        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 336 - 1), NA())</f>
+        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 336 - 1), NA())</f>
         <v/>
       </c>
       <c r="R337">
-        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 336 - 1), NA())</f>
+        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 336 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="338">
       <c r="P338" s="2">
-        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 337 - 1), NA())</f>
+        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 337 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q338">
-        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 337 - 1), NA())</f>
+        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 337 - 1), NA())</f>
         <v/>
       </c>
       <c r="R338">
-        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 337 - 1), NA())</f>
+        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 337 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="339">
       <c r="P339" s="2">
-        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 338 - 1), NA())</f>
+        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 338 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q339">
-        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 338 - 1), NA())</f>
+        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 338 - 1), NA())</f>
         <v/>
       </c>
       <c r="R339">
-        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 338 - 1), NA())</f>
+        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 338 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="340">
       <c r="P340" s="2">
-        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 339 - 1), NA())</f>
+        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 339 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q340">
-        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 339 - 1), NA())</f>
+        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 339 - 1), NA())</f>
         <v/>
       </c>
       <c r="R340">
-        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 339 - 1), NA())</f>
+        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 339 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="341">
       <c r="P341" s="2">
-        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 340 - 1), NA())</f>
+        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 340 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q341">
-        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 340 - 1), NA())</f>
+        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 340 - 1), NA())</f>
         <v/>
       </c>
       <c r="R341">
-        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 340 - 1), NA())</f>
+        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 340 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="342">
       <c r="P342" s="2">
-        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 341 - 1), NA())</f>
+        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 341 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q342">
-        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 341 - 1), NA())</f>
+        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 341 - 1), NA())</f>
         <v/>
       </c>
       <c r="R342">
-        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 341 - 1), NA())</f>
+        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 341 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="343">
       <c r="P343" s="2">
-        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 342 - 1), NA())</f>
+        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 342 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q343">
-        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 342 - 1), NA())</f>
+        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 342 - 1), NA())</f>
         <v/>
       </c>
       <c r="R343">
-        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 342 - 1), NA())</f>
+        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 342 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="344">
       <c r="P344" s="2">
-        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 343 - 1), NA())</f>
+        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 343 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q344">
-        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 343 - 1), NA())</f>
+        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 343 - 1), NA())</f>
         <v/>
       </c>
       <c r="R344">
-        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 343 - 1), NA())</f>
+        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 343 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="345">
       <c r="P345" s="2">
-        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 344 - 1), NA())</f>
+        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 344 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q345">
-        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 344 - 1), NA())</f>
+        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 344 - 1), NA())</f>
         <v/>
       </c>
       <c r="R345">
-        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 344 - 1), NA())</f>
+        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 344 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="346">
       <c r="P346" s="2">
-        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 345 - 1), NA())</f>
+        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 345 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q346">
-        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 345 - 1), NA())</f>
+        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 345 - 1), NA())</f>
         <v/>
       </c>
       <c r="R346">
-        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 345 - 1), NA())</f>
+        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 345 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="347">
       <c r="P347" s="2">
-        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 346 - 1), NA())</f>
+        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 346 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q347">
-        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 346 - 1), NA())</f>
+        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 346 - 1), NA())</f>
         <v/>
       </c>
       <c r="R347">
-        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 346 - 1), NA())</f>
+        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 346 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="348">
       <c r="P348" s="2">
-        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 347 - 1), NA())</f>
+        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 347 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q348">
-        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 347 - 1), NA())</f>
+        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 347 - 1), NA())</f>
         <v/>
       </c>
       <c r="R348">
-        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 347 - 1), NA())</f>
+        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 347 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="349">
       <c r="P349" s="2">
-        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 348 - 1), NA())</f>
+        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 348 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q349">
-        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 348 - 1), NA())</f>
+        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 348 - 1), NA())</f>
         <v/>
       </c>
       <c r="R349">
-        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 348 - 1), NA())</f>
+        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 348 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="350">
       <c r="P350" s="2">
-        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 349 - 1), NA())</f>
+        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 349 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q350">
-        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 349 - 1), NA())</f>
+        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 349 - 1), NA())</f>
         <v/>
       </c>
       <c r="R350">
-        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 349 - 1), NA())</f>
+        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 349 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="351">
       <c r="P351" s="2">
-        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 350 - 1), NA())</f>
+        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 350 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q351">
-        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 350 - 1), NA())</f>
+        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 350 - 1), NA())</f>
         <v/>
       </c>
       <c r="R351">
-        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 350 - 1), NA())</f>
+        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 350 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="352">
       <c r="P352" s="2">
-        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 351 - 1), NA())</f>
+        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 351 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q352">
-        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 351 - 1), NA())</f>
+        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 351 - 1), NA())</f>
         <v/>
       </c>
       <c r="R352">
-        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 351 - 1), NA())</f>
+        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 351 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="353">
       <c r="P353" s="2">
-        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 352 - 1), NA())</f>
+        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 352 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q353">
-        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 352 - 1), NA())</f>
+        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 352 - 1), NA())</f>
         <v/>
       </c>
       <c r="R353">
-        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 352 - 1), NA())</f>
+        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 352 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="354">
       <c r="P354" s="2">
-        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 353 - 1), NA())</f>
+        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 353 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q354">
-        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 353 - 1), NA())</f>
+        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 353 - 1), NA())</f>
         <v/>
       </c>
       <c r="R354">
-        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 353 - 1), NA())</f>
+        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 353 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="355">
       <c r="P355" s="2">
-        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 354 - 1), NA())</f>
+        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 354 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q355">
-        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 354 - 1), NA())</f>
+        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 354 - 1), NA())</f>
         <v/>
       </c>
       <c r="R355">
-        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 354 - 1), NA())</f>
+        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 354 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="356">
       <c r="P356" s="2">
-        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 355 - 1), NA())</f>
+        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 355 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q356">
-        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 355 - 1), NA())</f>
+        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 355 - 1), NA())</f>
         <v/>
       </c>
       <c r="R356">
-        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 355 - 1), NA())</f>
+        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 355 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="357">
       <c r="P357" s="2">
-        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 356 - 1), NA())</f>
+        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 356 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q357">
-        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 356 - 1), NA())</f>
+        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 356 - 1), NA())</f>
         <v/>
       </c>
       <c r="R357">
-        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 356 - 1), NA())</f>
+        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 356 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="358">
       <c r="P358" s="2">
-        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 357 - 1), NA())</f>
+        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 357 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q358">
-        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 357 - 1), NA())</f>
+        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 357 - 1), NA())</f>
         <v/>
       </c>
       <c r="R358">
-        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 357 - 1), NA())</f>
+        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 357 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="359">
       <c r="P359" s="2">
-        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 358 - 1), NA())</f>
+        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 358 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q359">
-        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 358 - 1), NA())</f>
+        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 358 - 1), NA())</f>
         <v/>
       </c>
       <c r="R359">
-        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 358 - 1), NA())</f>
+        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 358 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="360">
       <c r="P360" s="2">
-        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 359 - 1), NA())</f>
+        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 359 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q360">
-        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 359 - 1), NA())</f>
+        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 359 - 1), NA())</f>
         <v/>
       </c>
       <c r="R360">
-        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 359 - 1), NA())</f>
+        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 359 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="361">
       <c r="P361" s="2">
-        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 360 - 1), NA())</f>
+        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 360 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q361">
-        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 360 - 1), NA())</f>
+        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 360 - 1), NA())</f>
         <v/>
       </c>
       <c r="R361">
-        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 360 - 1), NA())</f>
+        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 360 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="362">
       <c r="P362" s="2">
-        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 361 - 1), NA())</f>
+        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 361 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q362">
-        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 361 - 1), NA())</f>
+        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 361 - 1), NA())</f>
         <v/>
       </c>
       <c r="R362">
-        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 361 - 1), NA())</f>
+        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 361 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="363">
       <c r="P363" s="2">
-        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 362 - 1), NA())</f>
+        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 362 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q363">
-        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 362 - 1), NA())</f>
+        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 362 - 1), NA())</f>
         <v/>
       </c>
       <c r="R363">
-        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 362 - 1), NA())</f>
+        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 362 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="364">
       <c r="P364" s="2">
-        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 363 - 1), NA())</f>
+        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 363 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q364">
-        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 363 - 1), NA())</f>
+        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 363 - 1), NA())</f>
         <v/>
       </c>
       <c r="R364">
-        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 363 - 1), NA())</f>
+        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 363 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="365">
       <c r="P365" s="2">
-        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 364 - 1), NA())</f>
+        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 364 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q365">
-        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 364 - 1), NA())</f>
+        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 364 - 1), NA())</f>
         <v/>
       </c>
       <c r="R365">
-        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 364 - 1), NA())</f>
+        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 364 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="366">
       <c r="P366" s="2">
-        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 365 - 1), NA())</f>
+        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 365 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q366">
-        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 365 - 1), NA())</f>
+        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 365 - 1), NA())</f>
         <v/>
       </c>
       <c r="R366">
-        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 365 - 1), NA())</f>
+        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 365 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="367">
       <c r="P367" s="2">
-        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 366 - 1), NA())</f>
+        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 366 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q367">
-        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 366 - 1), NA())</f>
+        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 366 - 1), NA())</f>
         <v/>
       </c>
       <c r="R367">
-        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 366 - 1), NA())</f>
+        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 366 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="368">
       <c r="P368" s="2">
-        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 367 - 1), NA())</f>
+        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 367 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q368">
-        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 367 - 1), NA())</f>
+        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 367 - 1), NA())</f>
         <v/>
       </c>
       <c r="R368">
-        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 367 - 1), NA())</f>
+        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 367 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="369">
       <c r="P369" s="2">
-        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 368 - 1), NA())</f>
+        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 368 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q369">
-        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 368 - 1), NA())</f>
+        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 368 - 1), NA())</f>
         <v/>
       </c>
       <c r="R369">
-        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 368 - 1), NA())</f>
+        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 368 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="370">
       <c r="P370" s="2">
-        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 369 - 1), NA())</f>
+        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 369 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q370">
-        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 369 - 1), NA())</f>
+        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 369 - 1), NA())</f>
         <v/>
       </c>
       <c r="R370">
-        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 369 - 1), NA())</f>
+        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 369 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="371">
       <c r="P371" s="2">
-        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 370 - 1), NA())</f>
+        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 370 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q371">
-        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 370 - 1), NA())</f>
+        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 370 - 1), NA())</f>
         <v/>
       </c>
       <c r="R371">
-        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 370 - 1), NA())</f>
+        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 370 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="372">
       <c r="P372" s="2">
-        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 371 - 1), NA())</f>
+        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 371 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q372">
-        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 371 - 1), NA())</f>
+        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 371 - 1), NA())</f>
         <v/>
       </c>
       <c r="R372">
-        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 371 - 1), NA())</f>
+        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 371 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="373">
       <c r="P373" s="2">
-        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 372 - 1), NA())</f>
+        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 372 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q373">
-        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 372 - 1), NA())</f>
+        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 372 - 1), NA())</f>
         <v/>
       </c>
       <c r="R373">
-        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 372 - 1), NA())</f>
+        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 372 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="374">
       <c r="P374" s="2">
-        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 373 - 1), NA())</f>
+        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 373 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q374">
-        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 373 - 1), NA())</f>
+        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 373 - 1), NA())</f>
         <v/>
       </c>
       <c r="R374">
-        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 373 - 1), NA())</f>
+        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 373 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="375">
       <c r="P375" s="2">
-        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 374 - 1), NA())</f>
+        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 374 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q375">
-        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 374 - 1), NA())</f>
+        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 374 - 1), NA())</f>
         <v/>
       </c>
       <c r="R375">
-        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 374 - 1), NA())</f>
+        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 374 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="376">
       <c r="P376" s="2">
-        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 375 - 1), NA())</f>
+        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 375 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q376">
-        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 375 - 1), NA())</f>
+        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 375 - 1), NA())</f>
         <v/>
       </c>
       <c r="R376">
-        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 375 - 1), NA())</f>
+        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 375 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="377">
       <c r="P377" s="2">
-        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 376 - 1), NA())</f>
+        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 376 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q377">
-        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 376 - 1), NA())</f>
+        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 376 - 1), NA())</f>
         <v/>
       </c>
       <c r="R377">
-        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 376 - 1), NA())</f>
+        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 376 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="378">
       <c r="P378" s="2">
-        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 377 - 1), NA())</f>
+        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 377 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q378">
-        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 377 - 1), NA())</f>
+        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 377 - 1), NA())</f>
         <v/>
       </c>
       <c r="R378">
-        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 377 - 1), NA())</f>
+        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 377 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="379">
       <c r="P379" s="2">
-        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 378 - 1), NA())</f>
+        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 378 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q379">
-        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 378 - 1), NA())</f>
+        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 378 - 1), NA())</f>
         <v/>
       </c>
       <c r="R379">
-        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 378 - 1), NA())</f>
+        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 378 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="380">
       <c r="P380" s="2">
-        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 379 - 1), NA())</f>
+        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 379 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q380">
-        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 379 - 1), NA())</f>
+        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 379 - 1), NA())</f>
         <v/>
       </c>
       <c r="R380">
-        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 379 - 1), NA())</f>
+        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 379 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="381">
       <c r="P381" s="2">
-        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 380 - 1), NA())</f>
+        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 380 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q381">
-        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 380 - 1), NA())</f>
+        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 380 - 1), NA())</f>
         <v/>
       </c>
       <c r="R381">
-        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 380 - 1), NA())</f>
+        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 380 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="382">
       <c r="P382" s="2">
-        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 381 - 1), NA())</f>
+        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 381 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q382">
-        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 381 - 1), NA())</f>
+        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 381 - 1), NA())</f>
         <v/>
       </c>
       <c r="R382">
-        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 381 - 1), NA())</f>
+        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 381 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="383">
       <c r="P383" s="2">
-        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 382 - 1), NA())</f>
+        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 382 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q383">
-        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 382 - 1), NA())</f>
+        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 382 - 1), NA())</f>
         <v/>
       </c>
       <c r="R383">
-        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 382 - 1), NA())</f>
+        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 382 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="384">
       <c r="P384" s="2">
-        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 383 - 1), NA())</f>
+        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 383 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q384">
-        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 383 - 1), NA())</f>
+        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 383 - 1), NA())</f>
         <v/>
       </c>
       <c r="R384">
-        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 383 - 1), NA())</f>
+        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 383 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="385">
       <c r="P385" s="2">
-        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 384 - 1), NA())</f>
+        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 384 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q385">
-        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 384 - 1), NA())</f>
+        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 384 - 1), NA())</f>
         <v/>
       </c>
       <c r="R385">
-        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 384 - 1), NA())</f>
+        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 384 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="386">
       <c r="P386" s="2">
-        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 385 - 1), NA())</f>
+        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 385 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q386">
-        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 385 - 1), NA())</f>
+        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 385 - 1), NA())</f>
         <v/>
       </c>
       <c r="R386">
-        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 385 - 1), NA())</f>
+        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 385 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="387">
       <c r="P387" s="2">
-        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 386 - 1), NA())</f>
+        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 386 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q387">
-        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 386 - 1), NA())</f>
+        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 386 - 1), NA())</f>
         <v/>
       </c>
       <c r="R387">
-        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 386 - 1), NA())</f>
+        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 386 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="388">
       <c r="P388" s="2">
-        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 387 - 1), NA())</f>
+        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 387 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q388">
-        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 387 - 1), NA())</f>
+        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 387 - 1), NA())</f>
         <v/>
       </c>
       <c r="R388">
-        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 387 - 1), NA())</f>
+        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 387 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="389">
       <c r="P389" s="2">
-        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 388 - 1), NA())</f>
+        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 388 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q389">
-        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 388 - 1), NA())</f>
+        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 388 - 1), NA())</f>
         <v/>
       </c>
       <c r="R389">
-        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 388 - 1), NA())</f>
+        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 388 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="390">
       <c r="P390" s="2">
-        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 389 - 1), NA())</f>
+        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 389 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q390">
-        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 389 - 1), NA())</f>
+        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 389 - 1), NA())</f>
         <v/>
       </c>
       <c r="R390">
-        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 389 - 1), NA())</f>
+        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 389 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="391">
       <c r="P391" s="2">
-        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 390 - 1), NA())</f>
+        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 390 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q391">
-        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 390 - 1), NA())</f>
+        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 390 - 1), NA())</f>
         <v/>
       </c>
       <c r="R391">
-        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 390 - 1), NA())</f>
+        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 390 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="392">
       <c r="P392" s="2">
-        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 391 - 1), NA())</f>
+        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 391 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q392">
-        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 391 - 1), NA())</f>
+        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 391 - 1), NA())</f>
         <v/>
       </c>
       <c r="R392">
-        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 391 - 1), NA())</f>
+        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 391 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="393">
       <c r="P393" s="2">
-        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 392 - 1), NA())</f>
+        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 392 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q393">
-        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 392 - 1), NA())</f>
+        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 392 - 1), NA())</f>
         <v/>
       </c>
       <c r="R393">
-        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 392 - 1), NA())</f>
+        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 392 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="394">
       <c r="P394" s="2">
-        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 393 - 1), NA())</f>
+        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 393 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q394">
-        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 393 - 1), NA())</f>
+        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 393 - 1), NA())</f>
         <v/>
       </c>
       <c r="R394">
-        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 393 - 1), NA())</f>
+        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 393 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="395">
       <c r="P395" s="2">
-        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 394 - 1), NA())</f>
+        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 394 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q395">
-        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 394 - 1), NA())</f>
+        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 394 - 1), NA())</f>
         <v/>
       </c>
       <c r="R395">
-        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 394 - 1), NA())</f>
+        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 394 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="396">
       <c r="P396" s="2">
-        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 395 - 1), NA())</f>
+        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 395 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q396">
-        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 395 - 1), NA())</f>
+        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 395 - 1), NA())</f>
         <v/>
       </c>
       <c r="R396">
-        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 395 - 1), NA())</f>
+        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 395 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="397">
       <c r="P397" s="2">
-        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 396 - 1), NA())</f>
+        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 396 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q397">
-        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 396 - 1), NA())</f>
+        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 396 - 1), NA())</f>
         <v/>
       </c>
       <c r="R397">
-        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 396 - 1), NA())</f>
+        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 396 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="398">
       <c r="P398" s="2">
-        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 397 - 1), NA())</f>
+        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 397 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q398">
-        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 397 - 1), NA())</f>
+        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 397 - 1), NA())</f>
         <v/>
       </c>
       <c r="R398">
-        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 397 - 1), NA())</f>
+        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 397 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="399">
       <c r="P399" s="2">
-        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 398 - 1), NA())</f>
+        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 398 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q399">
-        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 398 - 1), NA())</f>
+        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 398 - 1), NA())</f>
         <v/>
       </c>
       <c r="R399">
-        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 398 - 1), NA())</f>
+        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 398 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="400">
       <c r="P400" s="2">
-        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 399 - 1), NA())</f>
+        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 399 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q400">
-        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 399 - 1), NA())</f>
+        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 399 - 1), NA())</f>
         <v/>
       </c>
       <c r="R400">
-        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 399 - 1), NA())</f>
+        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 399 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="401">
       <c r="P401" s="2">
-        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 400 - 1), NA())</f>
+        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 400 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q401">
-        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 400 - 1), NA())</f>
+        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 400 - 1), NA())</f>
         <v/>
       </c>
       <c r="R401">
-        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 400 - 1), NA())</f>
+        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 400 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="402">
       <c r="P402" s="2">
-        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 401 - 1), NA())</f>
+        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 401 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q402">
-        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 401 - 1), NA())</f>
+        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 401 - 1), NA())</f>
         <v/>
       </c>
       <c r="R402">
-        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 401 - 1), NA())</f>
+        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 401 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="403">
       <c r="P403" s="2">
-        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 402 - 1), NA())</f>
+        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 402 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q403">
-        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 402 - 1), NA())</f>
+        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 402 - 1), NA())</f>
         <v/>
       </c>
       <c r="R403">
-        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 402 - 1), NA())</f>
+        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 402 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="404">
       <c r="P404" s="2">
-        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 403 - 1), NA())</f>
+        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 403 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q404">
-        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 403 - 1), NA())</f>
+        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 403 - 1), NA())</f>
         <v/>
       </c>
       <c r="R404">
-        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 403 - 1), NA())</f>
+        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 403 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="405">
       <c r="P405" s="2">
-        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 404 - 1), NA())</f>
+        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 404 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q405">
-        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 404 - 1), NA())</f>
+        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 404 - 1), NA())</f>
         <v/>
       </c>
       <c r="R405">
-        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 404 - 1), NA())</f>
+        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 404 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="406">
       <c r="P406" s="2">
-        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 405 - 1), NA())</f>
+        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 405 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q406">
-        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 405 - 1), NA())</f>
+        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 405 - 1), NA())</f>
         <v/>
       </c>
       <c r="R406">
-        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 405 - 1), NA())</f>
+        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 405 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="407">
       <c r="P407" s="2">
-        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 406 - 1), NA())</f>
+        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 406 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q407">
-        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 406 - 1), NA())</f>
+        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 406 - 1), NA())</f>
         <v/>
       </c>
       <c r="R407">
-        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 406 - 1), NA())</f>
+        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 406 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="408">
       <c r="P408" s="2">
-        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 407 - 1), NA())</f>
+        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 407 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q408">
-        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 407 - 1), NA())</f>
+        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 407 - 1), NA())</f>
         <v/>
       </c>
       <c r="R408">
-        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 407 - 1), NA())</f>
+        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 407 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="409">
       <c r="P409" s="2">
-        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 408 - 1), NA())</f>
+        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 408 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q409">
-        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 408 - 1), NA())</f>
+        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 408 - 1), NA())</f>
         <v/>
       </c>
       <c r="R409">
-        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 408 - 1), NA())</f>
+        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 408 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="410">
       <c r="P410" s="2">
-        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 409 - 1), NA())</f>
+        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 409 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q410">
-        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 409 - 1), NA())</f>
+        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 409 - 1), NA())</f>
         <v/>
       </c>
       <c r="R410">
-        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 409 - 1), NA())</f>
+        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 409 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="411">
       <c r="P411" s="2">
-        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 410 - 1), NA())</f>
+        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 410 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q411">
-        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 410 - 1), NA())</f>
+        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 410 - 1), NA())</f>
         <v/>
       </c>
       <c r="R411">
-        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 410 - 1), NA())</f>
+        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 410 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="412">
       <c r="P412" s="2">
-        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 411 - 1), NA())</f>
+        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 411 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q412">
-        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 411 - 1), NA())</f>
+        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 411 - 1), NA())</f>
         <v/>
       </c>
       <c r="R412">
-        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 411 - 1), NA())</f>
+        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 411 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="413">
       <c r="P413" s="2">
-        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 412 - 1), NA())</f>
+        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 412 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q413">
-        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 412 - 1), NA())</f>
+        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 412 - 1), NA())</f>
         <v/>
       </c>
       <c r="R413">
-        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 412 - 1), NA())</f>
+        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 412 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="414">
       <c r="P414" s="2">
-        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 413 - 1), NA())</f>
+        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 413 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q414">
-        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 413 - 1), NA())</f>
+        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 413 - 1), NA())</f>
         <v/>
       </c>
       <c r="R414">
-        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 413 - 1), NA())</f>
+        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 413 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="415">
       <c r="P415" s="2">
-        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 414 - 1), NA())</f>
+        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 414 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q415">
-        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 414 - 1), NA())</f>
+        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 414 - 1), NA())</f>
         <v/>
       </c>
       <c r="R415">
-        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 414 - 1), NA())</f>
+        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 414 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="416">
       <c r="P416" s="2">
-        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 415 - 1), NA())</f>
+        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 415 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q416">
-        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 415 - 1), NA())</f>
+        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 415 - 1), NA())</f>
         <v/>
       </c>
       <c r="R416">
-        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 415 - 1), NA())</f>
+        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 415 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="417">
       <c r="P417" s="2">
-        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 416 - 1), NA())</f>
+        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 416 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q417">
-        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 416 - 1), NA())</f>
+        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 416 - 1), NA())</f>
         <v/>
       </c>
       <c r="R417">
-        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 416 - 1), NA())</f>
+        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 416 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="418">
       <c r="P418" s="2">
-        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 417 - 1), NA())</f>
+        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 417 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q418">
-        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 417 - 1), NA())</f>
+        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 417 - 1), NA())</f>
         <v/>
       </c>
       <c r="R418">
-        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 417 - 1), NA())</f>
+        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 417 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="419">
       <c r="P419" s="2">
-        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 418 - 1), NA())</f>
+        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 418 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q419">
-        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 418 - 1), NA())</f>
+        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 418 - 1), NA())</f>
         <v/>
       </c>
       <c r="R419">
-        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 418 - 1), NA())</f>
+        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 418 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="420">
       <c r="P420" s="2">
-        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 419 - 1), NA())</f>
+        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 419 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q420">
-        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 419 - 1), NA())</f>
+        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 419 - 1), NA())</f>
         <v/>
       </c>
       <c r="R420">
-        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 419 - 1), NA())</f>
+        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 419 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="421">
       <c r="P421" s="2">
-        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 420 - 1), NA())</f>
+        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 420 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q421">
-        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 420 - 1), NA())</f>
+        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 420 - 1), NA())</f>
         <v/>
       </c>
       <c r="R421">
-        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 420 - 1), NA())</f>
+        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 420 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="422">
       <c r="P422" s="2">
-        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 421 - 1), NA())</f>
+        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 421 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q422">
-        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 421 - 1), NA())</f>
+        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 421 - 1), NA())</f>
         <v/>
       </c>
       <c r="R422">
-        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 421 - 1), NA())</f>
+        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 421 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="423">
       <c r="P423" s="2">
-        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 422 - 1), NA())</f>
+        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 422 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q423">
-        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 422 - 1), NA())</f>
+        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 422 - 1), NA())</f>
         <v/>
       </c>
       <c r="R423">
-        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 422 - 1), NA())</f>
+        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 422 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="424">
       <c r="P424" s="2">
-        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 423 - 1), NA())</f>
+        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 423 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q424">
-        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 423 - 1), NA())</f>
+        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 423 - 1), NA())</f>
         <v/>
       </c>
       <c r="R424">
-        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 423 - 1), NA())</f>
+        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 423 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="425">
       <c r="P425" s="2">
-        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 424 - 1), NA())</f>
+        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 424 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q425">
-        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 424 - 1), NA())</f>
+        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 424 - 1), NA())</f>
         <v/>
       </c>
       <c r="R425">
-        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 424 - 1), NA())</f>
+        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 424 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="426">
       <c r="P426" s="2">
-        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 425 - 1), NA())</f>
+        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 425 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q426">
-        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 425 - 1), NA())</f>
+        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 425 - 1), NA())</f>
         <v/>
       </c>
       <c r="R426">
-        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 425 - 1), NA())</f>
+        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 425 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="427">
       <c r="P427" s="2">
-        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 426 - 1), NA())</f>
+        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 426 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q427">
-        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 426 - 1), NA())</f>
+        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 426 - 1), NA())</f>
         <v/>
       </c>
       <c r="R427">
-        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 426 - 1), NA())</f>
+        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 426 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="428">
       <c r="P428" s="2">
-        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 427 - 1), NA())</f>
+        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 427 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q428">
-        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 427 - 1), NA())</f>
+        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 427 - 1), NA())</f>
         <v/>
       </c>
       <c r="R428">
-        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 427 - 1), NA())</f>
+        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 427 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="429">
       <c r="P429" s="2">
-        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 428 - 1), NA())</f>
+        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 428 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q429">
-        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 428 - 1), NA())</f>
+        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 428 - 1), NA())</f>
         <v/>
       </c>
       <c r="R429">
-        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 428 - 1), NA())</f>
+        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 428 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="430">
       <c r="P430" s="2">
-        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 429 - 1), NA())</f>
+        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 429 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q430">
-        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 429 - 1), NA())</f>
+        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 429 - 1), NA())</f>
         <v/>
       </c>
       <c r="R430">
-        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 429 - 1), NA())</f>
+        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 429 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="431">
       <c r="P431" s="2">
-        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 430 - 1), NA())</f>
+        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 430 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q431">
-        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 430 - 1), NA())</f>
+        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 430 - 1), NA())</f>
         <v/>
       </c>
       <c r="R431">
-        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 430 - 1), NA())</f>
+        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 430 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="432">
       <c r="P432" s="2">
-        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 431 - 1), NA())</f>
+        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 431 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q432">
-        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 431 - 1), NA())</f>
+        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 431 - 1), NA())</f>
         <v/>
       </c>
       <c r="R432">
-        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 431 - 1), NA())</f>
+        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 431 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="433">
       <c r="P433" s="2">
-        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 432 - 1), NA())</f>
+        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 432 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q433">
-        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 432 - 1), NA())</f>
+        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 432 - 1), NA())</f>
         <v/>
       </c>
       <c r="R433">
-        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 432 - 1), NA())</f>
+        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 432 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="434">
       <c r="P434" s="2">
-        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 433 - 1), NA())</f>
+        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 433 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q434">
-        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 433 - 1), NA())</f>
+        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 433 - 1), NA())</f>
         <v/>
       </c>
       <c r="R434">
-        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 433 - 1), NA())</f>
+        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 433 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="435">
       <c r="P435" s="2">
-        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 434 - 1), NA())</f>
+        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 434 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q435">
-        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 434 - 1), NA())</f>
+        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 434 - 1), NA())</f>
         <v/>
       </c>
       <c r="R435">
-        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 434 - 1), NA())</f>
+        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 434 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="436">
       <c r="P436" s="2">
-        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 435 - 1), NA())</f>
+        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 435 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q436">
-        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 435 - 1), NA())</f>
+        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 435 - 1), NA())</f>
         <v/>
       </c>
       <c r="R436">
-        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 435 - 1), NA())</f>
+        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 435 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="437">
       <c r="P437" s="2">
-        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 436 - 1), NA())</f>
+        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 436 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q437">
-        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 436 - 1), NA())</f>
+        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 436 - 1), NA())</f>
         <v/>
       </c>
       <c r="R437">
-        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 436 - 1), NA())</f>
+        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 436 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="438">
       <c r="P438" s="2">
-        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 437 - 1), NA())</f>
+        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 437 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q438">
-        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 437 - 1), NA())</f>
+        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 437 - 1), NA())</f>
         <v/>
       </c>
       <c r="R438">
-        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 437 - 1), NA())</f>
+        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 437 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="439">
       <c r="P439" s="2">
-        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 438 - 1), NA())</f>
+        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 438 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q439">
-        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 438 - 1), NA())</f>
+        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 438 - 1), NA())</f>
         <v/>
       </c>
       <c r="R439">
-        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 438 - 1), NA())</f>
+        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 438 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="440">
       <c r="P440" s="2">
-        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 439 - 1), NA())</f>
+        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 439 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q440">
-        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 439 - 1), NA())</f>
+        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 439 - 1), NA())</f>
         <v/>
       </c>
       <c r="R440">
-        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 439 - 1), NA())</f>
+        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 439 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="441">
       <c r="P441" s="2">
-        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 440 - 1), NA())</f>
+        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 440 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q441">
-        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 440 - 1), NA())</f>
+        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 440 - 1), NA())</f>
         <v/>
       </c>
       <c r="R441">
-        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 440 - 1), NA())</f>
+        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 440 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="442">
       <c r="P442" s="2">
-        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 441 - 1), NA())</f>
+        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 441 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q442">
-        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 441 - 1), NA())</f>
+        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 441 - 1), NA())</f>
         <v/>
       </c>
       <c r="R442">
-        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 441 - 1), NA())</f>
+        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 441 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="443">
       <c r="P443" s="2">
-        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 442 - 1), NA())</f>
+        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 442 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q443">
-        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 442 - 1), NA())</f>
+        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 442 - 1), NA())</f>
         <v/>
       </c>
       <c r="R443">
-        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 442 - 1), NA())</f>
+        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 442 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="444">
       <c r="P444" s="2">
-        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 443 - 1), NA())</f>
+        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 443 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q444">
-        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 443 - 1), NA())</f>
+        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 443 - 1), NA())</f>
         <v/>
       </c>
       <c r="R444">
-        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 443 - 1), NA())</f>
+        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 443 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="445">
       <c r="P445" s="2">
-        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 444 - 1), NA())</f>
+        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 444 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q445">
-        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 444 - 1), NA())</f>
+        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 444 - 1), NA())</f>
         <v/>
       </c>
       <c r="R445">
-        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 444 - 1), NA())</f>
+        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 444 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="446">
       <c r="P446" s="2">
-        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 445 - 1), NA())</f>
+        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 445 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q446">
-        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 445 - 1), NA())</f>
+        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 445 - 1), NA())</f>
         <v/>
       </c>
       <c r="R446">
-        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 445 - 1), NA())</f>
+        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 445 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="447">
       <c r="P447" s="2">
-        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 446 - 1), NA())</f>
+        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 446 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q447">
-        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 446 - 1), NA())</f>
+        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 446 - 1), NA())</f>
         <v/>
       </c>
       <c r="R447">
-        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 446 - 1), NA())</f>
+        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 446 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="448">
       <c r="P448" s="2">
-        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 447 - 1), NA())</f>
+        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 447 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q448">
-        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 447 - 1), NA())</f>
+        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 447 - 1), NA())</f>
         <v/>
       </c>
       <c r="R448">
-        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 447 - 1), NA())</f>
+        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 447 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="449">
       <c r="P449" s="2">
-        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 448 - 1), NA())</f>
+        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 448 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q449">
-        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 448 - 1), NA())</f>
+        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 448 - 1), NA())</f>
         <v/>
       </c>
       <c r="R449">
-        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 448 - 1), NA())</f>
+        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 448 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="450">
       <c r="P450" s="2">
-        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 449 - 1), NA())</f>
+        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 449 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q450">
-        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 449 - 1), NA())</f>
+        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 449 - 1), NA())</f>
         <v/>
       </c>
       <c r="R450">
-        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 449 - 1), NA())</f>
+        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 449 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="451">
       <c r="P451" s="2">
-        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 450 - 1), NA())</f>
+        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 450 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q451">
-        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 450 - 1), NA())</f>
+        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 450 - 1), NA())</f>
         <v/>
       </c>
       <c r="R451">
-        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 450 - 1), NA())</f>
+        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 450 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="452">
       <c r="P452" s="2">
-        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 451 - 1), NA())</f>
+        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 451 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q452">
-        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 451 - 1), NA())</f>
+        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 451 - 1), NA())</f>
         <v/>
       </c>
       <c r="R452">
-        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 451 - 1), NA())</f>
+        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 451 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="453">
       <c r="P453" s="2">
-        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 452 - 1), NA())</f>
+        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 452 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q453">
-        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 452 - 1), NA())</f>
+        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 452 - 1), NA())</f>
         <v/>
       </c>
       <c r="R453">
-        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 452 - 1), NA())</f>
+        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 452 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="454">
       <c r="P454" s="2">
-        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 453 - 1), NA())</f>
+        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 453 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q454">
-        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 453 - 1), NA())</f>
+        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 453 - 1), NA())</f>
         <v/>
       </c>
       <c r="R454">
-        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 453 - 1), NA())</f>
+        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 453 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="455">
       <c r="P455" s="2">
-        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 454 - 1), NA())</f>
+        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 454 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q455">
-        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 454 - 1), NA())</f>
+        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 454 - 1), NA())</f>
         <v/>
       </c>
       <c r="R455">
-        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 454 - 1), NA())</f>
+        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 454 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="456">
       <c r="P456" s="2">
-        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 455 - 1), NA())</f>
+        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 455 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q456">
-        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 455 - 1), NA())</f>
+        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 455 - 1), NA())</f>
         <v/>
       </c>
       <c r="R456">
-        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 455 - 1), NA())</f>
+        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 455 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="457">
       <c r="P457" s="2">
-        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 456 - 1), NA())</f>
+        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 456 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q457">
-        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 456 - 1), NA())</f>
+        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 456 - 1), NA())</f>
         <v/>
       </c>
       <c r="R457">
-        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 456 - 1), NA())</f>
+        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 456 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="458">
       <c r="P458" s="2">
-        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 457 - 1), NA())</f>
+        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 457 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q458">
-        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 457 - 1), NA())</f>
+        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 457 - 1), NA())</f>
         <v/>
       </c>
       <c r="R458">
-        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 457 - 1), NA())</f>
+        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 457 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="459">
       <c r="P459" s="2">
-        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 458 - 1), NA())</f>
+        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 458 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q459">
-        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 458 - 1), NA())</f>
+        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 458 - 1), NA())</f>
         <v/>
       </c>
       <c r="R459">
-        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 458 - 1), NA())</f>
+        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 458 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="460">
       <c r="P460" s="2">
-        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 459 - 1), NA())</f>
+        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 459 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q460">
-        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 459 - 1), NA())</f>
+        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 459 - 1), NA())</f>
         <v/>
       </c>
       <c r="R460">
-        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 459 - 1), NA())</f>
+        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 459 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="461">
       <c r="P461" s="2">
-        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 460 - 1), NA())</f>
+        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 460 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q461">
-        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 460 - 1), NA())</f>
+        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 460 - 1), NA())</f>
         <v/>
       </c>
       <c r="R461">
-        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 460 - 1), NA())</f>
+        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 460 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="462">
       <c r="P462" s="2">
-        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 461 - 1), NA())</f>
+        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 461 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q462">
-        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 461 - 1), NA())</f>
+        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 461 - 1), NA())</f>
         <v/>
       </c>
       <c r="R462">
-        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 461 - 1), NA())</f>
+        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 461 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="463">
       <c r="P463" s="2">
-        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 462 - 1), NA())</f>
+        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 462 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q463">
-        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 462 - 1), NA())</f>
+        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 462 - 1), NA())</f>
         <v/>
       </c>
       <c r="R463">
-        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 462 - 1), NA())</f>
+        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 462 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="464">
       <c r="P464" s="2">
-        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 463 - 1), NA())</f>
+        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 463 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q464">
-        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 463 - 1), NA())</f>
+        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 463 - 1), NA())</f>
         <v/>
       </c>
       <c r="R464">
-        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 463 - 1), NA())</f>
+        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 463 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="465">
       <c r="P465" s="2">
-        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 464 - 1), NA())</f>
+        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 464 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q465">
-        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 464 - 1), NA())</f>
+        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 464 - 1), NA())</f>
         <v/>
       </c>
       <c r="R465">
-        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 464 - 1), NA())</f>
+        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 464 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="466">
       <c r="P466" s="2">
-        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 465 - 1), NA())</f>
+        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 465 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q466">
-        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 465 - 1), NA())</f>
+        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 465 - 1), NA())</f>
         <v/>
       </c>
       <c r="R466">
-        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 465 - 1), NA())</f>
+        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 465 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="467">
       <c r="P467" s="2">
-        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 466 - 1), NA())</f>
+        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 466 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q467">
-        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 466 - 1), NA())</f>
+        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 466 - 1), NA())</f>
         <v/>
       </c>
       <c r="R467">
-        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 466 - 1), NA())</f>
+        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 466 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="468">
       <c r="P468" s="2">
-        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 467 - 1), NA())</f>
+        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 467 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q468">
-        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 467 - 1), NA())</f>
+        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 467 - 1), NA())</f>
         <v/>
       </c>
       <c r="R468">
-        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 467 - 1), NA())</f>
+        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 467 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="469">
       <c r="P469" s="2">
-        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 468 - 1), NA())</f>
+        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 468 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q469">
-        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 468 - 1), NA())</f>
+        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 468 - 1), NA())</f>
         <v/>
       </c>
       <c r="R469">
-        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 468 - 1), NA())</f>
+        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 468 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="470">
       <c r="P470" s="2">
-        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 469 - 1), NA())</f>
+        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 469 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q470">
-        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 469 - 1), NA())</f>
+        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 469 - 1), NA())</f>
         <v/>
       </c>
       <c r="R470">
-        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 469 - 1), NA())</f>
+        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 469 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="471">
       <c r="P471" s="2">
-        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 470 - 1), NA())</f>
+        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 470 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q471">
-        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 470 - 1), NA())</f>
+        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 470 - 1), NA())</f>
         <v/>
       </c>
       <c r="R471">
-        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 470 - 1), NA())</f>
+        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 470 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="472">
       <c r="P472" s="2">
-        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 471 - 1), NA())</f>
+        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 471 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q472">
-        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 471 - 1), NA())</f>
+        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 471 - 1), NA())</f>
         <v/>
       </c>
       <c r="R472">
-        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 471 - 1), NA())</f>
+        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 471 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="473">
       <c r="P473" s="2">
-        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 472 - 1), NA())</f>
+        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 472 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q473">
-        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 472 - 1), NA())</f>
+        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 472 - 1), NA())</f>
         <v/>
       </c>
       <c r="R473">
-        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 472 - 1), NA())</f>
+        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 472 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="474">
       <c r="P474" s="2">
-        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 473 - 1), NA())</f>
+        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 473 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q474">
-        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 473 - 1), NA())</f>
+        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 473 - 1), NA())</f>
         <v/>
       </c>
       <c r="R474">
-        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 473 - 1), NA())</f>
+        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 473 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="475">
       <c r="P475" s="2">
-        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 474 - 1), NA())</f>
+        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 474 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q475">
-        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 474 - 1), NA())</f>
+        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 474 - 1), NA())</f>
         <v/>
       </c>
       <c r="R475">
-        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 474 - 1), NA())</f>
+        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 474 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="476">
       <c r="P476" s="2">
-        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 475 - 1), NA())</f>
+        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 475 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q476">
-        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 475 - 1), NA())</f>
+        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 475 - 1), NA())</f>
         <v/>
       </c>
       <c r="R476">
-        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 475 - 1), NA())</f>
+        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 475 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="477">
       <c r="P477" s="2">
-        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 476 - 1), NA())</f>
+        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 476 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q477">
-        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 476 - 1), NA())</f>
+        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 476 - 1), NA())</f>
         <v/>
       </c>
       <c r="R477">
-        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 476 - 1), NA())</f>
+        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 476 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="478">
       <c r="P478" s="2">
-        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 477 - 1), NA())</f>
+        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 477 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q478">
-        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 477 - 1), NA())</f>
+        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 477 - 1), NA())</f>
         <v/>
       </c>
       <c r="R478">
-        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 477 - 1), NA())</f>
+        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 477 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="479">
       <c r="P479" s="2">
-        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 478 - 1), NA())</f>
+        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 478 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q479">
-        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 478 - 1), NA())</f>
+        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 478 - 1), NA())</f>
         <v/>
       </c>
       <c r="R479">
-        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 478 - 1), NA())</f>
+        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 478 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="480">
       <c r="P480" s="2">
-        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 479 - 1), NA())</f>
+        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 479 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q480">
-        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 479 - 1), NA())</f>
+        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 479 - 1), NA())</f>
         <v/>
       </c>
       <c r="R480">
-        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 479 - 1), NA())</f>
+        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 479 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="481">
       <c r="P481" s="2">
-        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 480 - 1), NA())</f>
+        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 480 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q481">
-        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 480 - 1), NA())</f>
+        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 480 - 1), NA())</f>
         <v/>
       </c>
       <c r="R481">
-        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 480 - 1), NA())</f>
+        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 480 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="482">
       <c r="P482" s="2">
-        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 481 - 1), NA())</f>
+        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 481 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q482">
-        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 481 - 1), NA())</f>
+        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 481 - 1), NA())</f>
         <v/>
       </c>
       <c r="R482">
-        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 481 - 1), NA())</f>
+        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 481 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="483">
       <c r="P483" s="2">
-        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 482 - 1), NA())</f>
+        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 482 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q483">
-        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 482 - 1), NA())</f>
+        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 482 - 1), NA())</f>
         <v/>
       </c>
       <c r="R483">
-        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 482 - 1), NA())</f>
+        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 482 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="484">
       <c r="P484" s="2">
-        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 483 - 1), NA())</f>
+        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 483 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q484">
-        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 483 - 1), NA())</f>
+        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 483 - 1), NA())</f>
         <v/>
       </c>
       <c r="R484">
-        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 483 - 1), NA())</f>
+        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 483 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="485">
       <c r="P485" s="2">
-        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 484 - 1), NA())</f>
+        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 484 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q485">
-        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 484 - 1), NA())</f>
+        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 484 - 1), NA())</f>
         <v/>
       </c>
       <c r="R485">
-        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 484 - 1), NA())</f>
+        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 484 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="486">
       <c r="P486" s="2">
-        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 485 - 1), NA())</f>
+        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 485 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q486">
-        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 485 - 1), NA())</f>
+        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 485 - 1), NA())</f>
         <v/>
       </c>
       <c r="R486">
-        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 485 - 1), NA())</f>
+        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 485 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="487">
       <c r="P487" s="2">
-        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 486 - 1), NA())</f>
+        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 486 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q487">
-        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 486 - 1), NA())</f>
+        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 486 - 1), NA())</f>
         <v/>
       </c>
       <c r="R487">
-        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 486 - 1), NA())</f>
+        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 486 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="488">
       <c r="P488" s="2">
-        <f>IF(487&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 487 - 1), NA())</f>
+        <f>IF(487&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 487 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q488">
-        <f>IF(487&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 487 - 1), NA())</f>
+        <f>IF(487&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 487 - 1), NA())</f>
         <v/>
       </c>
       <c r="R488">
-        <f>IF(487&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 487 - 1), NA())</f>
+        <f>IF(487&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 487 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="489">
       <c r="P489" s="2">
-        <f>IF(488&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$489, $G$8 - 1 + 488 - 1), NA())</f>
+        <f>IF(488&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 488 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q489">
-        <f>IF(488&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$489, $G$8 - 1 + 488 - 1), NA())</f>
+        <f>IF(488&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 488 - 1), NA())</f>
         <v/>
       </c>
       <c r="R489">
-        <f>IF(488&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$489, $G$8 - 1 + 488 - 1), NA())</f>
+        <f>IF(488&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 488 - 1), NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="490">
+      <c r="P490" s="2">
+        <f>IF(489&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 489 - 1), NA())</f>
+        <v/>
+      </c>
+      <c r="Q490">
+        <f>IF(489&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 489 - 1), NA())</f>
+        <v/>
+      </c>
+      <c r="R490">
+        <f>IF(489&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 489 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -8092,7 +8106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H489"/>
+  <dimension ref="A1:H490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22730,13 +22744,13 @@
         <v>46274</v>
       </c>
       <c r="B488" s="15" t="n">
-        <v>4393.89990234375</v>
+        <v>4416</v>
       </c>
       <c r="C488" s="15" t="n">
-        <v>66.2969970703125</v>
+        <v>67.94200134277344</v>
       </c>
       <c r="D488" s="15" t="n">
-        <v>3099.47998046875</v>
+        <v>3109.510009765625</v>
       </c>
       <c r="E488" s="16">
         <f>ROUND((B488/31.1034768)*D488, 2)</f>
@@ -22760,13 +22774,13 @@
         <v>46275</v>
       </c>
       <c r="B489" s="19" t="n">
-        <v>4436.39990234375</v>
+        <v>4416</v>
       </c>
       <c r="C489" s="19" t="n">
-        <v>67.91999816894531</v>
+        <v>67.94200134277344</v>
       </c>
       <c r="D489" s="19" t="n">
-        <v>3099.47998046875</v>
+        <v>3087.64990234375</v>
       </c>
       <c r="E489" s="20">
         <f>ROUND((B489/31.1034768)*D489, 2)</f>
@@ -22785,8 +22799,38 @@
         <v/>
       </c>
     </row>
+    <row r="490" ht="20" customHeight="1">
+      <c r="A490" s="14" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B490" s="15" t="n">
+        <v>4364.2001953125</v>
+      </c>
+      <c r="C490" s="15" t="n">
+        <v>64.125</v>
+      </c>
+      <c r="D490" s="15" t="n">
+        <v>3087.64990234375</v>
+      </c>
+      <c r="E490" s="16">
+        <f>ROUND((B490/31.1034768)*D490, 2)</f>
+        <v/>
+      </c>
+      <c r="F490" s="16">
+        <f>ROUND((C490/31.1034768)*D490, 2)</f>
+        <v/>
+      </c>
+      <c r="G490" s="17">
+        <f>IFERROR((E490-E489)/E489, 0)</f>
+        <v/>
+      </c>
+      <c r="H490" s="17">
+        <f>IFERROR((F490-F489)/F489, 0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H489"/>
+  <autoFilter ref="A1:H490"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Precios_Metales_COP.xlsx
+++ b/Precios_Metales_COP.xlsx
@@ -22774,13 +22774,13 @@
         <v>46275</v>
       </c>
       <c r="B489" s="19" t="n">
-        <v>4416</v>
+        <v>4364.5</v>
       </c>
       <c r="C489" s="19" t="n">
-        <v>67.94200134277344</v>
+        <v>64.28399658203125</v>
       </c>
       <c r="D489" s="19" t="n">
-        <v>3087.64990234375</v>
+        <v>3101.550048828125</v>
       </c>
       <c r="E489" s="20">
         <f>ROUND((B489/31.1034768)*D489, 2)</f>
@@ -22804,13 +22804,13 @@
         <v>46276</v>
       </c>
       <c r="B490" s="15" t="n">
-        <v>4364.2001953125</v>
+        <v>4390</v>
       </c>
       <c r="C490" s="15" t="n">
-        <v>64.125</v>
+        <v>65.01999664306641</v>
       </c>
       <c r="D490" s="15" t="n">
-        <v>3087.64990234375</v>
+        <v>3082.739990234375</v>
       </c>
       <c r="E490" s="16">
         <f>ROUND((B490/31.1034768)*D490, 2)</f>

--- a/Precios_Metales_COP.xlsx
+++ b/Precios_Metales_COP.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Precios Diarios" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Precios Diarios'!$A$1:$H$490</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Precios Diarios'!$A$1:$H$493</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -321,12 +321,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard y Gráficos'!$P$2:$P$490</f>
+              <f>'Dashboard y Gráficos'!$P$2:$P$493</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$Q$2:$Q$490</f>
+              <f>'Dashboard y Gráficos'!$Q$2:$Q$493</f>
             </numRef>
           </val>
         </ser>
@@ -446,12 +446,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard y Gráficos'!$P$2:$P$490</f>
+              <f>'Dashboard y Gráficos'!$P$2:$P$493</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$R$2:$R$490</f>
+              <f>'Dashboard y Gráficos'!$R$2:$R$493</f>
             </numRef>
           </val>
         </ser>
@@ -570,12 +570,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard y Gráficos'!$P$2:$P$490</f>
+              <f>'Dashboard y Gráficos'!$P$2:$P$493</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$Q$2:$Q$490</f>
+              <f>'Dashboard y Gráficos'!$Q$2:$Q$493</f>
             </numRef>
           </val>
         </ser>
@@ -610,7 +610,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$R$2:$R$490</f>
+              <f>'Dashboard y Gráficos'!$R$2:$R$493</f>
             </numRef>
           </val>
         </ser>
@@ -1074,7 +1074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R490"/>
+  <dimension ref="A1:R493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1118,15 +1118,15 @@
     </row>
     <row r="2">
       <c r="P2" s="2">
-        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 1 - 1), NA())</f>
+        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 1 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q2">
-        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 1 - 1), NA())</f>
+        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 1 - 1), NA())</f>
         <v/>
       </c>
       <c r="R2">
-        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 1 - 1), NA())</f>
+        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 1 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1166,58 +1166,58 @@
       </c>
       <c r="N3" s="4" t="n"/>
       <c r="P3" s="2">
-        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 2 - 1), NA())</f>
+        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 2 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q3">
-        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 2 - 1), NA())</f>
+        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 2 - 1), NA())</f>
         <v/>
       </c>
       <c r="R3">
-        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 2 - 1), NA())</f>
+        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 2 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5">
-        <f>'Precios Diarios'!A490</f>
+        <f>'Precios Diarios'!A493</f>
         <v/>
       </c>
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="6">
-        <f>'Precios Diarios'!E490</f>
+        <f>'Precios Diarios'!E493</f>
         <v/>
       </c>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="6">
-        <f>'Precios Diarios'!F490</f>
+        <f>'Precios Diarios'!F493</f>
         <v/>
       </c>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="6">
-        <f>'Precios Diarios'!D490</f>
+        <f>'Precios Diarios'!D493</f>
         <v/>
       </c>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="7">
-        <f>'Precios Diarios'!G490</f>
+        <f>'Precios Diarios'!G493</f>
         <v/>
       </c>
       <c r="N4" s="4" t="n"/>
       <c r="P4" s="2">
-        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 3 - 1), NA())</f>
+        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 3 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q4">
-        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 3 - 1), NA())</f>
+        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 3 - 1), NA())</f>
         <v/>
       </c>
       <c r="R4">
-        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 3 - 1), NA())</f>
+        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 3 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1237,29 +1237,29 @@
       <c r="M5" s="4" t="n"/>
       <c r="N5" s="4" t="n"/>
       <c r="P5" s="2">
-        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 4 - 1), NA())</f>
+        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 4 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q5">
-        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 4 - 1), NA())</f>
+        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 4 - 1), NA())</f>
         <v/>
       </c>
       <c r="R5">
-        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 4 - 1), NA())</f>
+        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 4 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="P6" s="2">
-        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 5 - 1), NA())</f>
+        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 5 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q6">
-        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 5 - 1), NA())</f>
+        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 5 - 1), NA())</f>
         <v/>
       </c>
       <c r="R6">
-        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 5 - 1), NA())</f>
+        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 5 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1270,15 +1270,15 @@
         </is>
       </c>
       <c r="P7" s="2">
-        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 6 - 1), NA())</f>
+        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 6 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q7">
-        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 6 - 1), NA())</f>
+        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 6 - 1), NA())</f>
         <v/>
       </c>
       <c r="R7">
-        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 6 - 1), NA())</f>
+        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 6 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1297,11 +1297,11 @@
         <v/>
       </c>
       <c r="G8" s="11">
-        <f>IFERROR(MATCH(E8, 'Precios Diarios'!$A$2:$A$490, 1), 1) + 1</f>
+        <f>IFERROR(MATCH(E8, 'Precios Diarios'!$A$2:$A$493, 1), 1) + 1</f>
         <v/>
       </c>
       <c r="H8" s="11">
-        <f>IFERROR(MATCH(F8, 'Precios Diarios'!$A$2:$A$490, 1), 489) + 1</f>
+        <f>IFERROR(MATCH(F8, 'Precios Diarios'!$A$2:$A$493, 1), 492) + 1</f>
         <v/>
       </c>
       <c r="I8" s="11">
@@ -1309,15 +1309,15 @@
         <v/>
       </c>
       <c r="P8" s="2">
-        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 7 - 1), NA())</f>
+        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 7 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q8">
-        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 7 - 1), NA())</f>
+        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 7 - 1), NA())</f>
         <v/>
       </c>
       <c r="R8">
-        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 7 - 1), NA())</f>
+        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 7 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1328,6749 +1328,6791 @@
         </is>
       </c>
       <c r="P9" s="2">
-        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 8 - 1), NA())</f>
+        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 8 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q9">
-        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 8 - 1), NA())</f>
+        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 8 - 1), NA())</f>
         <v/>
       </c>
       <c r="R9">
-        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 8 - 1), NA())</f>
+        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 8 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="P10" s="2">
-        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 9 - 1), NA())</f>
+        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 9 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q10">
-        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 9 - 1), NA())</f>
+        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 9 - 1), NA())</f>
         <v/>
       </c>
       <c r="R10">
-        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 9 - 1), NA())</f>
+        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 9 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="P11" s="2">
-        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 10 - 1), NA())</f>
+        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 10 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q11">
-        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 10 - 1), NA())</f>
+        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 10 - 1), NA())</f>
         <v/>
       </c>
       <c r="R11">
-        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 10 - 1), NA())</f>
+        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 10 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="P12" s="2">
-        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 11 - 1), NA())</f>
+        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 11 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q12">
-        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 11 - 1), NA())</f>
+        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 11 - 1), NA())</f>
         <v/>
       </c>
       <c r="R12">
-        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 11 - 1), NA())</f>
+        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 11 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="P13" s="2">
-        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 12 - 1), NA())</f>
+        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 12 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q13">
-        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 12 - 1), NA())</f>
+        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 12 - 1), NA())</f>
         <v/>
       </c>
       <c r="R13">
-        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 12 - 1), NA())</f>
+        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 12 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="P14" s="2">
-        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 13 - 1), NA())</f>
+        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 13 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q14">
-        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 13 - 1), NA())</f>
+        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 13 - 1), NA())</f>
         <v/>
       </c>
       <c r="R14">
-        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 13 - 1), NA())</f>
+        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 13 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="P15" s="2">
-        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 14 - 1), NA())</f>
+        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 14 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q15">
-        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 14 - 1), NA())</f>
+        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 14 - 1), NA())</f>
         <v/>
       </c>
       <c r="R15">
-        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 14 - 1), NA())</f>
+        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 14 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="P16" s="2">
-        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 15 - 1), NA())</f>
+        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 15 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q16">
-        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 15 - 1), NA())</f>
+        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 15 - 1), NA())</f>
         <v/>
       </c>
       <c r="R16">
-        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 15 - 1), NA())</f>
+        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 15 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="P17" s="2">
-        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 16 - 1), NA())</f>
+        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 16 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q17">
-        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 16 - 1), NA())</f>
+        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 16 - 1), NA())</f>
         <v/>
       </c>
       <c r="R17">
-        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 16 - 1), NA())</f>
+        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 16 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="P18" s="2">
-        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 17 - 1), NA())</f>
+        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 17 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q18">
-        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 17 - 1), NA())</f>
+        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 17 - 1), NA())</f>
         <v/>
       </c>
       <c r="R18">
-        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 17 - 1), NA())</f>
+        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 17 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="P19" s="2">
-        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 18 - 1), NA())</f>
+        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 18 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q19">
-        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 18 - 1), NA())</f>
+        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 18 - 1), NA())</f>
         <v/>
       </c>
       <c r="R19">
-        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 18 - 1), NA())</f>
+        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 18 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="P20" s="2">
-        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 19 - 1), NA())</f>
+        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 19 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q20">
-        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 19 - 1), NA())</f>
+        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 19 - 1), NA())</f>
         <v/>
       </c>
       <c r="R20">
-        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 19 - 1), NA())</f>
+        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 19 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="P21" s="2">
-        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 20 - 1), NA())</f>
+        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 20 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q21">
-        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 20 - 1), NA())</f>
+        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 20 - 1), NA())</f>
         <v/>
       </c>
       <c r="R21">
-        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 20 - 1), NA())</f>
+        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 20 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="P22" s="2">
-        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 21 - 1), NA())</f>
+        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 21 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q22">
-        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 21 - 1), NA())</f>
+        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 21 - 1), NA())</f>
         <v/>
       </c>
       <c r="R22">
-        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 21 - 1), NA())</f>
+        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 21 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="P23" s="2">
-        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 22 - 1), NA())</f>
+        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 22 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q23">
-        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 22 - 1), NA())</f>
+        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 22 - 1), NA())</f>
         <v/>
       </c>
       <c r="R23">
-        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 22 - 1), NA())</f>
+        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 22 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="P24" s="2">
-        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 23 - 1), NA())</f>
+        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 23 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q24">
-        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 23 - 1), NA())</f>
+        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 23 - 1), NA())</f>
         <v/>
       </c>
       <c r="R24">
-        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 23 - 1), NA())</f>
+        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 23 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="P25" s="2">
-        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 24 - 1), NA())</f>
+        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 24 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q25">
-        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 24 - 1), NA())</f>
+        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 24 - 1), NA())</f>
         <v/>
       </c>
       <c r="R25">
-        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 24 - 1), NA())</f>
+        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 24 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="P26" s="2">
-        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 25 - 1), NA())</f>
+        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 25 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q26">
-        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 25 - 1), NA())</f>
+        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 25 - 1), NA())</f>
         <v/>
       </c>
       <c r="R26">
-        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 25 - 1), NA())</f>
+        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 25 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="P27" s="2">
-        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 26 - 1), NA())</f>
+        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 26 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q27">
-        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 26 - 1), NA())</f>
+        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 26 - 1), NA())</f>
         <v/>
       </c>
       <c r="R27">
-        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 26 - 1), NA())</f>
+        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 26 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="P28" s="2">
-        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 27 - 1), NA())</f>
+        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 27 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q28">
-        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 27 - 1), NA())</f>
+        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 27 - 1), NA())</f>
         <v/>
       </c>
       <c r="R28">
-        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 27 - 1), NA())</f>
+        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 27 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="P29" s="2">
-        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 28 - 1), NA())</f>
+        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 28 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q29">
-        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 28 - 1), NA())</f>
+        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 28 - 1), NA())</f>
         <v/>
       </c>
       <c r="R29">
-        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 28 - 1), NA())</f>
+        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 28 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="P30" s="2">
-        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 29 - 1), NA())</f>
+        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 29 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q30">
-        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 29 - 1), NA())</f>
+        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 29 - 1), NA())</f>
         <v/>
       </c>
       <c r="R30">
-        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 29 - 1), NA())</f>
+        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 29 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="P31" s="2">
-        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 30 - 1), NA())</f>
+        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 30 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q31">
-        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 30 - 1), NA())</f>
+        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 30 - 1), NA())</f>
         <v/>
       </c>
       <c r="R31">
-        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 30 - 1), NA())</f>
+        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 30 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="P32" s="2">
-        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 31 - 1), NA())</f>
+        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 31 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q32">
-        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 31 - 1), NA())</f>
+        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 31 - 1), NA())</f>
         <v/>
       </c>
       <c r="R32">
-        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 31 - 1), NA())</f>
+        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 31 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="P33" s="2">
-        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 32 - 1), NA())</f>
+        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 32 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q33">
-        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 32 - 1), NA())</f>
+        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 32 - 1), NA())</f>
         <v/>
       </c>
       <c r="R33">
-        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 32 - 1), NA())</f>
+        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 32 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="P34" s="2">
-        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 33 - 1), NA())</f>
+        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 33 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q34">
-        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 33 - 1), NA())</f>
+        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 33 - 1), NA())</f>
         <v/>
       </c>
       <c r="R34">
-        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 33 - 1), NA())</f>
+        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 33 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="P35" s="2">
-        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 34 - 1), NA())</f>
+        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 34 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q35">
-        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 34 - 1), NA())</f>
+        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 34 - 1), NA())</f>
         <v/>
       </c>
       <c r="R35">
-        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 34 - 1), NA())</f>
+        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 34 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="P36" s="2">
-        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 35 - 1), NA())</f>
+        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 35 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q36">
-        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 35 - 1), NA())</f>
+        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 35 - 1), NA())</f>
         <v/>
       </c>
       <c r="R36">
-        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 35 - 1), NA())</f>
+        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 35 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="P37" s="2">
-        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 36 - 1), NA())</f>
+        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 36 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q37">
-        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 36 - 1), NA())</f>
+        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 36 - 1), NA())</f>
         <v/>
       </c>
       <c r="R37">
-        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 36 - 1), NA())</f>
+        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 36 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="P38" s="2">
-        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 37 - 1), NA())</f>
+        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 37 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q38">
-        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 37 - 1), NA())</f>
+        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 37 - 1), NA())</f>
         <v/>
       </c>
       <c r="R38">
-        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 37 - 1), NA())</f>
+        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 37 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="P39" s="2">
-        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 38 - 1), NA())</f>
+        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 38 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q39">
-        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 38 - 1), NA())</f>
+        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 38 - 1), NA())</f>
         <v/>
       </c>
       <c r="R39">
-        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 38 - 1), NA())</f>
+        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 38 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="P40" s="2">
-        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 39 - 1), NA())</f>
+        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 39 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q40">
-        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 39 - 1), NA())</f>
+        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 39 - 1), NA())</f>
         <v/>
       </c>
       <c r="R40">
-        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 39 - 1), NA())</f>
+        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 39 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="P41" s="2">
-        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 40 - 1), NA())</f>
+        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 40 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q41">
-        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 40 - 1), NA())</f>
+        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 40 - 1), NA())</f>
         <v/>
       </c>
       <c r="R41">
-        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 40 - 1), NA())</f>
+        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 40 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="P42" s="2">
-        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 41 - 1), NA())</f>
+        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 41 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q42">
-        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 41 - 1), NA())</f>
+        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 41 - 1), NA())</f>
         <v/>
       </c>
       <c r="R42">
-        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 41 - 1), NA())</f>
+        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 41 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="P43" s="2">
-        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 42 - 1), NA())</f>
+        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 42 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q43">
-        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 42 - 1), NA())</f>
+        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 42 - 1), NA())</f>
         <v/>
       </c>
       <c r="R43">
-        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 42 - 1), NA())</f>
+        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 42 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="P44" s="2">
-        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 43 - 1), NA())</f>
+        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 43 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q44">
-        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 43 - 1), NA())</f>
+        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 43 - 1), NA())</f>
         <v/>
       </c>
       <c r="R44">
-        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 43 - 1), NA())</f>
+        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 43 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="P45" s="2">
-        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 44 - 1), NA())</f>
+        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 44 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q45">
-        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 44 - 1), NA())</f>
+        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 44 - 1), NA())</f>
         <v/>
       </c>
       <c r="R45">
-        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 44 - 1), NA())</f>
+        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 44 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="P46" s="2">
-        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 45 - 1), NA())</f>
+        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 45 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q46">
-        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 45 - 1), NA())</f>
+        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 45 - 1), NA())</f>
         <v/>
       </c>
       <c r="R46">
-        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 45 - 1), NA())</f>
+        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 45 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="P47" s="2">
-        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 46 - 1), NA())</f>
+        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 46 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q47">
-        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 46 - 1), NA())</f>
+        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 46 - 1), NA())</f>
         <v/>
       </c>
       <c r="R47">
-        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 46 - 1), NA())</f>
+        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 46 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="P48" s="2">
-        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 47 - 1), NA())</f>
+        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 47 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q48">
-        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 47 - 1), NA())</f>
+        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 47 - 1), NA())</f>
         <v/>
       </c>
       <c r="R48">
-        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 47 - 1), NA())</f>
+        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 47 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="P49" s="2">
-        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 48 - 1), NA())</f>
+        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 48 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q49">
-        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 48 - 1), NA())</f>
+        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 48 - 1), NA())</f>
         <v/>
       </c>
       <c r="R49">
-        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 48 - 1), NA())</f>
+        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 48 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="P50" s="2">
-        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 49 - 1), NA())</f>
+        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 49 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q50">
-        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 49 - 1), NA())</f>
+        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 49 - 1), NA())</f>
         <v/>
       </c>
       <c r="R50">
-        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 49 - 1), NA())</f>
+        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 49 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="P51" s="2">
-        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 50 - 1), NA())</f>
+        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 50 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q51">
-        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 50 - 1), NA())</f>
+        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 50 - 1), NA())</f>
         <v/>
       </c>
       <c r="R51">
-        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 50 - 1), NA())</f>
+        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 50 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="P52" s="2">
-        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 51 - 1), NA())</f>
+        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 51 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q52">
-        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 51 - 1), NA())</f>
+        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 51 - 1), NA())</f>
         <v/>
       </c>
       <c r="R52">
-        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 51 - 1), NA())</f>
+        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 51 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="P53" s="2">
-        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 52 - 1), NA())</f>
+        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 52 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q53">
-        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 52 - 1), NA())</f>
+        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 52 - 1), NA())</f>
         <v/>
       </c>
       <c r="R53">
-        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 52 - 1), NA())</f>
+        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 52 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="P54" s="2">
-        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 53 - 1), NA())</f>
+        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 53 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q54">
-        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 53 - 1), NA())</f>
+        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 53 - 1), NA())</f>
         <v/>
       </c>
       <c r="R54">
-        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 53 - 1), NA())</f>
+        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 53 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="P55" s="2">
-        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 54 - 1), NA())</f>
+        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 54 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q55">
-        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 54 - 1), NA())</f>
+        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 54 - 1), NA())</f>
         <v/>
       </c>
       <c r="R55">
-        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 54 - 1), NA())</f>
+        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 54 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="P56" s="2">
-        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 55 - 1), NA())</f>
+        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 55 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q56">
-        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 55 - 1), NA())</f>
+        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 55 - 1), NA())</f>
         <v/>
       </c>
       <c r="R56">
-        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 55 - 1), NA())</f>
+        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 55 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="P57" s="2">
-        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 56 - 1), NA())</f>
+        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 56 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q57">
-        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 56 - 1), NA())</f>
+        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 56 - 1), NA())</f>
         <v/>
       </c>
       <c r="R57">
-        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 56 - 1), NA())</f>
+        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 56 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="P58" s="2">
-        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 57 - 1), NA())</f>
+        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 57 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q58">
-        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 57 - 1), NA())</f>
+        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 57 - 1), NA())</f>
         <v/>
       </c>
       <c r="R58">
-        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 57 - 1), NA())</f>
+        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 57 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="P59" s="2">
-        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 58 - 1), NA())</f>
+        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 58 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q59">
-        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 58 - 1), NA())</f>
+        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 58 - 1), NA())</f>
         <v/>
       </c>
       <c r="R59">
-        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 58 - 1), NA())</f>
+        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 58 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="P60" s="2">
-        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 59 - 1), NA())</f>
+        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 59 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q60">
-        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 59 - 1), NA())</f>
+        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 59 - 1), NA())</f>
         <v/>
       </c>
       <c r="R60">
-        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 59 - 1), NA())</f>
+        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 59 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="P61" s="2">
-        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 60 - 1), NA())</f>
+        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 60 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q61">
-        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 60 - 1), NA())</f>
+        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 60 - 1), NA())</f>
         <v/>
       </c>
       <c r="R61">
-        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 60 - 1), NA())</f>
+        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 60 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="P62" s="2">
-        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 61 - 1), NA())</f>
+        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 61 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q62">
-        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 61 - 1), NA())</f>
+        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 61 - 1), NA())</f>
         <v/>
       </c>
       <c r="R62">
-        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 61 - 1), NA())</f>
+        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 61 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="P63" s="2">
-        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 62 - 1), NA())</f>
+        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 62 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q63">
-        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 62 - 1), NA())</f>
+        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 62 - 1), NA())</f>
         <v/>
       </c>
       <c r="R63">
-        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 62 - 1), NA())</f>
+        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 62 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="P64" s="2">
-        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 63 - 1), NA())</f>
+        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 63 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q64">
-        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 63 - 1), NA())</f>
+        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 63 - 1), NA())</f>
         <v/>
       </c>
       <c r="R64">
-        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 63 - 1), NA())</f>
+        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 63 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="P65" s="2">
-        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 64 - 1), NA())</f>
+        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 64 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q65">
-        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 64 - 1), NA())</f>
+        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 64 - 1), NA())</f>
         <v/>
       </c>
       <c r="R65">
-        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 64 - 1), NA())</f>
+        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 64 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="P66" s="2">
-        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 65 - 1), NA())</f>
+        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 65 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q66">
-        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 65 - 1), NA())</f>
+        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 65 - 1), NA())</f>
         <v/>
       </c>
       <c r="R66">
-        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 65 - 1), NA())</f>
+        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 65 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="P67" s="2">
-        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 66 - 1), NA())</f>
+        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 66 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q67">
-        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 66 - 1), NA())</f>
+        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 66 - 1), NA())</f>
         <v/>
       </c>
       <c r="R67">
-        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 66 - 1), NA())</f>
+        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 66 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="P68" s="2">
-        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 67 - 1), NA())</f>
+        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 67 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q68">
-        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 67 - 1), NA())</f>
+        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 67 - 1), NA())</f>
         <v/>
       </c>
       <c r="R68">
-        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 67 - 1), NA())</f>
+        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 67 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="P69" s="2">
-        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 68 - 1), NA())</f>
+        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 68 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q69">
-        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 68 - 1), NA())</f>
+        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 68 - 1), NA())</f>
         <v/>
       </c>
       <c r="R69">
-        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 68 - 1), NA())</f>
+        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 68 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="P70" s="2">
-        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 69 - 1), NA())</f>
+        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 69 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q70">
-        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 69 - 1), NA())</f>
+        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 69 - 1), NA())</f>
         <v/>
       </c>
       <c r="R70">
-        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 69 - 1), NA())</f>
+        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 69 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="P71" s="2">
-        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 70 - 1), NA())</f>
+        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 70 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q71">
-        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 70 - 1), NA())</f>
+        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 70 - 1), NA())</f>
         <v/>
       </c>
       <c r="R71">
-        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 70 - 1), NA())</f>
+        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 70 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="P72" s="2">
-        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 71 - 1), NA())</f>
+        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 71 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q72">
-        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 71 - 1), NA())</f>
+        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 71 - 1), NA())</f>
         <v/>
       </c>
       <c r="R72">
-        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 71 - 1), NA())</f>
+        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 71 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="P73" s="2">
-        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 72 - 1), NA())</f>
+        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 72 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q73">
-        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 72 - 1), NA())</f>
+        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 72 - 1), NA())</f>
         <v/>
       </c>
       <c r="R73">
-        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 72 - 1), NA())</f>
+        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 72 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="P74" s="2">
-        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 73 - 1), NA())</f>
+        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 73 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q74">
-        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 73 - 1), NA())</f>
+        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 73 - 1), NA())</f>
         <v/>
       </c>
       <c r="R74">
-        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 73 - 1), NA())</f>
+        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 73 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="P75" s="2">
-        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 74 - 1), NA())</f>
+        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 74 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q75">
-        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 74 - 1), NA())</f>
+        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 74 - 1), NA())</f>
         <v/>
       </c>
       <c r="R75">
-        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 74 - 1), NA())</f>
+        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 74 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="P76" s="2">
-        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 75 - 1), NA())</f>
+        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 75 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q76">
-        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 75 - 1), NA())</f>
+        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 75 - 1), NA())</f>
         <v/>
       </c>
       <c r="R76">
-        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 75 - 1), NA())</f>
+        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 75 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="P77" s="2">
-        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 76 - 1), NA())</f>
+        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 76 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q77">
-        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 76 - 1), NA())</f>
+        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 76 - 1), NA())</f>
         <v/>
       </c>
       <c r="R77">
-        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 76 - 1), NA())</f>
+        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 76 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="P78" s="2">
-        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 77 - 1), NA())</f>
+        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 77 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q78">
-        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 77 - 1), NA())</f>
+        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 77 - 1), NA())</f>
         <v/>
       </c>
       <c r="R78">
-        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 77 - 1), NA())</f>
+        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 77 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="P79" s="2">
-        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 78 - 1), NA())</f>
+        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 78 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q79">
-        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 78 - 1), NA())</f>
+        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 78 - 1), NA())</f>
         <v/>
       </c>
       <c r="R79">
-        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 78 - 1), NA())</f>
+        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 78 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="P80" s="2">
-        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 79 - 1), NA())</f>
+        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 79 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q80">
-        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 79 - 1), NA())</f>
+        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 79 - 1), NA())</f>
         <v/>
       </c>
       <c r="R80">
-        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 79 - 1), NA())</f>
+        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 79 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="P81" s="2">
-        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 80 - 1), NA())</f>
+        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 80 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q81">
-        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 80 - 1), NA())</f>
+        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 80 - 1), NA())</f>
         <v/>
       </c>
       <c r="R81">
-        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 80 - 1), NA())</f>
+        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 80 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="P82" s="2">
-        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 81 - 1), NA())</f>
+        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 81 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q82">
-        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 81 - 1), NA())</f>
+        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 81 - 1), NA())</f>
         <v/>
       </c>
       <c r="R82">
-        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 81 - 1), NA())</f>
+        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 81 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="P83" s="2">
-        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 82 - 1), NA())</f>
+        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 82 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q83">
-        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 82 - 1), NA())</f>
+        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 82 - 1), NA())</f>
         <v/>
       </c>
       <c r="R83">
-        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 82 - 1), NA())</f>
+        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 82 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="P84" s="2">
-        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 83 - 1), NA())</f>
+        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 83 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q84">
-        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 83 - 1), NA())</f>
+        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 83 - 1), NA())</f>
         <v/>
       </c>
       <c r="R84">
-        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 83 - 1), NA())</f>
+        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 83 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="P85" s="2">
-        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 84 - 1), NA())</f>
+        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 84 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q85">
-        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 84 - 1), NA())</f>
+        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 84 - 1), NA())</f>
         <v/>
       </c>
       <c r="R85">
-        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 84 - 1), NA())</f>
+        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 84 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="P86" s="2">
-        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 85 - 1), NA())</f>
+        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 85 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q86">
-        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 85 - 1), NA())</f>
+        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 85 - 1), NA())</f>
         <v/>
       </c>
       <c r="R86">
-        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 85 - 1), NA())</f>
+        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 85 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="P87" s="2">
-        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 86 - 1), NA())</f>
+        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 86 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q87">
-        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 86 - 1), NA())</f>
+        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 86 - 1), NA())</f>
         <v/>
       </c>
       <c r="R87">
-        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 86 - 1), NA())</f>
+        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 86 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="P88" s="2">
-        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 87 - 1), NA())</f>
+        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 87 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q88">
-        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 87 - 1), NA())</f>
+        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 87 - 1), NA())</f>
         <v/>
       </c>
       <c r="R88">
-        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 87 - 1), NA())</f>
+        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 87 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="P89" s="2">
-        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 88 - 1), NA())</f>
+        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 88 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q89">
-        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 88 - 1), NA())</f>
+        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 88 - 1), NA())</f>
         <v/>
       </c>
       <c r="R89">
-        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 88 - 1), NA())</f>
+        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 88 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="P90" s="2">
-        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 89 - 1), NA())</f>
+        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 89 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q90">
-        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 89 - 1), NA())</f>
+        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 89 - 1), NA())</f>
         <v/>
       </c>
       <c r="R90">
-        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 89 - 1), NA())</f>
+        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 89 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="P91" s="2">
-        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 90 - 1), NA())</f>
+        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 90 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q91">
-        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 90 - 1), NA())</f>
+        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 90 - 1), NA())</f>
         <v/>
       </c>
       <c r="R91">
-        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 90 - 1), NA())</f>
+        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 90 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="P92" s="2">
-        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 91 - 1), NA())</f>
+        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 91 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q92">
-        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 91 - 1), NA())</f>
+        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 91 - 1), NA())</f>
         <v/>
       </c>
       <c r="R92">
-        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 91 - 1), NA())</f>
+        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 91 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="P93" s="2">
-        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 92 - 1), NA())</f>
+        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 92 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q93">
-        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 92 - 1), NA())</f>
+        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 92 - 1), NA())</f>
         <v/>
       </c>
       <c r="R93">
-        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 92 - 1), NA())</f>
+        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 92 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="P94" s="2">
-        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 93 - 1), NA())</f>
+        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 93 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q94">
-        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 93 - 1), NA())</f>
+        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 93 - 1), NA())</f>
         <v/>
       </c>
       <c r="R94">
-        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 93 - 1), NA())</f>
+        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 93 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="P95" s="2">
-        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 94 - 1), NA())</f>
+        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 94 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q95">
-        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 94 - 1), NA())</f>
+        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 94 - 1), NA())</f>
         <v/>
       </c>
       <c r="R95">
-        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 94 - 1), NA())</f>
+        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 94 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="P96" s="2">
-        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 95 - 1), NA())</f>
+        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 95 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q96">
-        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 95 - 1), NA())</f>
+        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 95 - 1), NA())</f>
         <v/>
       </c>
       <c r="R96">
-        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 95 - 1), NA())</f>
+        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 95 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="P97" s="2">
-        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 96 - 1), NA())</f>
+        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 96 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q97">
-        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 96 - 1), NA())</f>
+        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 96 - 1), NA())</f>
         <v/>
       </c>
       <c r="R97">
-        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 96 - 1), NA())</f>
+        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 96 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="P98" s="2">
-        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 97 - 1), NA())</f>
+        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 97 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q98">
-        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 97 - 1), NA())</f>
+        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 97 - 1), NA())</f>
         <v/>
       </c>
       <c r="R98">
-        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 97 - 1), NA())</f>
+        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 97 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="P99" s="2">
-        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 98 - 1), NA())</f>
+        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 98 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q99">
-        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 98 - 1), NA())</f>
+        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 98 - 1), NA())</f>
         <v/>
       </c>
       <c r="R99">
-        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 98 - 1), NA())</f>
+        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 98 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="P100" s="2">
-        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 99 - 1), NA())</f>
+        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 99 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q100">
-        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 99 - 1), NA())</f>
+        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 99 - 1), NA())</f>
         <v/>
       </c>
       <c r="R100">
-        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 99 - 1), NA())</f>
+        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 99 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="P101" s="2">
-        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 100 - 1), NA())</f>
+        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 100 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q101">
-        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 100 - 1), NA())</f>
+        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 100 - 1), NA())</f>
         <v/>
       </c>
       <c r="R101">
-        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 100 - 1), NA())</f>
+        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 100 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="P102" s="2">
-        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 101 - 1), NA())</f>
+        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 101 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q102">
-        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 101 - 1), NA())</f>
+        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 101 - 1), NA())</f>
         <v/>
       </c>
       <c r="R102">
-        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 101 - 1), NA())</f>
+        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 101 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="P103" s="2">
-        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 102 - 1), NA())</f>
+        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 102 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q103">
-        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 102 - 1), NA())</f>
+        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 102 - 1), NA())</f>
         <v/>
       </c>
       <c r="R103">
-        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 102 - 1), NA())</f>
+        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 102 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="P104" s="2">
-        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 103 - 1), NA())</f>
+        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 103 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q104">
-        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 103 - 1), NA())</f>
+        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 103 - 1), NA())</f>
         <v/>
       </c>
       <c r="R104">
-        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 103 - 1), NA())</f>
+        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 103 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="P105" s="2">
-        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 104 - 1), NA())</f>
+        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 104 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q105">
-        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 104 - 1), NA())</f>
+        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 104 - 1), NA())</f>
         <v/>
       </c>
       <c r="R105">
-        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 104 - 1), NA())</f>
+        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 104 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="P106" s="2">
-        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 105 - 1), NA())</f>
+        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 105 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q106">
-        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 105 - 1), NA())</f>
+        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 105 - 1), NA())</f>
         <v/>
       </c>
       <c r="R106">
-        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 105 - 1), NA())</f>
+        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 105 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="P107" s="2">
-        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 106 - 1), NA())</f>
+        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 106 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q107">
-        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 106 - 1), NA())</f>
+        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 106 - 1), NA())</f>
         <v/>
       </c>
       <c r="R107">
-        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 106 - 1), NA())</f>
+        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 106 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="P108" s="2">
-        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 107 - 1), NA())</f>
+        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 107 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q108">
-        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 107 - 1), NA())</f>
+        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 107 - 1), NA())</f>
         <v/>
       </c>
       <c r="R108">
-        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 107 - 1), NA())</f>
+        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 107 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="P109" s="2">
-        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 108 - 1), NA())</f>
+        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 108 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q109">
-        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 108 - 1), NA())</f>
+        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 108 - 1), NA())</f>
         <v/>
       </c>
       <c r="R109">
-        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 108 - 1), NA())</f>
+        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 108 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="P110" s="2">
-        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 109 - 1), NA())</f>
+        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 109 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q110">
-        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 109 - 1), NA())</f>
+        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 109 - 1), NA())</f>
         <v/>
       </c>
       <c r="R110">
-        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 109 - 1), NA())</f>
+        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 109 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="P111" s="2">
-        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 110 - 1), NA())</f>
+        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 110 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q111">
-        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 110 - 1), NA())</f>
+        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 110 - 1), NA())</f>
         <v/>
       </c>
       <c r="R111">
-        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 110 - 1), NA())</f>
+        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 110 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="P112" s="2">
-        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 111 - 1), NA())</f>
+        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 111 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q112">
-        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 111 - 1), NA())</f>
+        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 111 - 1), NA())</f>
         <v/>
       </c>
       <c r="R112">
-        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 111 - 1), NA())</f>
+        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 111 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="P113" s="2">
-        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 112 - 1), NA())</f>
+        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 112 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q113">
-        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 112 - 1), NA())</f>
+        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 112 - 1), NA())</f>
         <v/>
       </c>
       <c r="R113">
-        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 112 - 1), NA())</f>
+        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 112 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="P114" s="2">
-        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 113 - 1), NA())</f>
+        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 113 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q114">
-        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 113 - 1), NA())</f>
+        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 113 - 1), NA())</f>
         <v/>
       </c>
       <c r="R114">
-        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 113 - 1), NA())</f>
+        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 113 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="P115" s="2">
-        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 114 - 1), NA())</f>
+        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 114 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q115">
-        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 114 - 1), NA())</f>
+        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 114 - 1), NA())</f>
         <v/>
       </c>
       <c r="R115">
-        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 114 - 1), NA())</f>
+        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 114 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="P116" s="2">
-        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 115 - 1), NA())</f>
+        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 115 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q116">
-        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 115 - 1), NA())</f>
+        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 115 - 1), NA())</f>
         <v/>
       </c>
       <c r="R116">
-        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 115 - 1), NA())</f>
+        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 115 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="P117" s="2">
-        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 116 - 1), NA())</f>
+        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 116 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q117">
-        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 116 - 1), NA())</f>
+        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 116 - 1), NA())</f>
         <v/>
       </c>
       <c r="R117">
-        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 116 - 1), NA())</f>
+        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 116 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="P118" s="2">
-        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 117 - 1), NA())</f>
+        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 117 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q118">
-        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 117 - 1), NA())</f>
+        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 117 - 1), NA())</f>
         <v/>
       </c>
       <c r="R118">
-        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 117 - 1), NA())</f>
+        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 117 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="P119" s="2">
-        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 118 - 1), NA())</f>
+        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 118 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q119">
-        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 118 - 1), NA())</f>
+        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 118 - 1), NA())</f>
         <v/>
       </c>
       <c r="R119">
-        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 118 - 1), NA())</f>
+        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 118 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="P120" s="2">
-        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 119 - 1), NA())</f>
+        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 119 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q120">
-        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 119 - 1), NA())</f>
+        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 119 - 1), NA())</f>
         <v/>
       </c>
       <c r="R120">
-        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 119 - 1), NA())</f>
+        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 119 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="P121" s="2">
-        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 120 - 1), NA())</f>
+        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 120 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q121">
-        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 120 - 1), NA())</f>
+        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 120 - 1), NA())</f>
         <v/>
       </c>
       <c r="R121">
-        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 120 - 1), NA())</f>
+        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 120 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="P122" s="2">
-        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 121 - 1), NA())</f>
+        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 121 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q122">
-        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 121 - 1), NA())</f>
+        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 121 - 1), NA())</f>
         <v/>
       </c>
       <c r="R122">
-        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 121 - 1), NA())</f>
+        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 121 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="123">
       <c r="P123" s="2">
-        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 122 - 1), NA())</f>
+        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 122 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q123">
-        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 122 - 1), NA())</f>
+        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 122 - 1), NA())</f>
         <v/>
       </c>
       <c r="R123">
-        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 122 - 1), NA())</f>
+        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 122 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="124">
       <c r="P124" s="2">
-        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 123 - 1), NA())</f>
+        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 123 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q124">
-        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 123 - 1), NA())</f>
+        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 123 - 1), NA())</f>
         <v/>
       </c>
       <c r="R124">
-        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 123 - 1), NA())</f>
+        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 123 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="125">
       <c r="P125" s="2">
-        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 124 - 1), NA())</f>
+        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 124 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q125">
-        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 124 - 1), NA())</f>
+        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 124 - 1), NA())</f>
         <v/>
       </c>
       <c r="R125">
-        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 124 - 1), NA())</f>
+        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 124 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="126">
       <c r="P126" s="2">
-        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 125 - 1), NA())</f>
+        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 125 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q126">
-        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 125 - 1), NA())</f>
+        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 125 - 1), NA())</f>
         <v/>
       </c>
       <c r="R126">
-        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 125 - 1), NA())</f>
+        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 125 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="127">
       <c r="P127" s="2">
-        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 126 - 1), NA())</f>
+        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 126 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q127">
-        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 126 - 1), NA())</f>
+        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 126 - 1), NA())</f>
         <v/>
       </c>
       <c r="R127">
-        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 126 - 1), NA())</f>
+        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 126 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="P128" s="2">
-        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 127 - 1), NA())</f>
+        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 127 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q128">
-        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 127 - 1), NA())</f>
+        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 127 - 1), NA())</f>
         <v/>
       </c>
       <c r="R128">
-        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 127 - 1), NA())</f>
+        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 127 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="129">
       <c r="P129" s="2">
-        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 128 - 1), NA())</f>
+        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 128 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q129">
-        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 128 - 1), NA())</f>
+        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 128 - 1), NA())</f>
         <v/>
       </c>
       <c r="R129">
-        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 128 - 1), NA())</f>
+        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 128 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="130">
       <c r="P130" s="2">
-        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 129 - 1), NA())</f>
+        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 129 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q130">
-        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 129 - 1), NA())</f>
+        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 129 - 1), NA())</f>
         <v/>
       </c>
       <c r="R130">
-        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 129 - 1), NA())</f>
+        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 129 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="131">
       <c r="P131" s="2">
-        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 130 - 1), NA())</f>
+        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 130 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q131">
-        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 130 - 1), NA())</f>
+        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 130 - 1), NA())</f>
         <v/>
       </c>
       <c r="R131">
-        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 130 - 1), NA())</f>
+        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 130 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="132">
       <c r="P132" s="2">
-        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 131 - 1), NA())</f>
+        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 131 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q132">
-        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 131 - 1), NA())</f>
+        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 131 - 1), NA())</f>
         <v/>
       </c>
       <c r="R132">
-        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 131 - 1), NA())</f>
+        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 131 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="133">
       <c r="P133" s="2">
-        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 132 - 1), NA())</f>
+        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 132 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q133">
-        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 132 - 1), NA())</f>
+        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 132 - 1), NA())</f>
         <v/>
       </c>
       <c r="R133">
-        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 132 - 1), NA())</f>
+        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 132 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="134">
       <c r="P134" s="2">
-        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 133 - 1), NA())</f>
+        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 133 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q134">
-        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 133 - 1), NA())</f>
+        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 133 - 1), NA())</f>
         <v/>
       </c>
       <c r="R134">
-        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 133 - 1), NA())</f>
+        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 133 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="135">
       <c r="P135" s="2">
-        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 134 - 1), NA())</f>
+        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 134 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q135">
-        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 134 - 1), NA())</f>
+        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 134 - 1), NA())</f>
         <v/>
       </c>
       <c r="R135">
-        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 134 - 1), NA())</f>
+        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 134 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="136">
       <c r="P136" s="2">
-        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 135 - 1), NA())</f>
+        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 135 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q136">
-        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 135 - 1), NA())</f>
+        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 135 - 1), NA())</f>
         <v/>
       </c>
       <c r="R136">
-        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 135 - 1), NA())</f>
+        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 135 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="137">
       <c r="P137" s="2">
-        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 136 - 1), NA())</f>
+        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 136 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q137">
-        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 136 - 1), NA())</f>
+        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 136 - 1), NA())</f>
         <v/>
       </c>
       <c r="R137">
-        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 136 - 1), NA())</f>
+        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 136 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="138">
       <c r="P138" s="2">
-        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 137 - 1), NA())</f>
+        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 137 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q138">
-        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 137 - 1), NA())</f>
+        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 137 - 1), NA())</f>
         <v/>
       </c>
       <c r="R138">
-        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 137 - 1), NA())</f>
+        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 137 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="139">
       <c r="P139" s="2">
-        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 138 - 1), NA())</f>
+        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 138 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q139">
-        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 138 - 1), NA())</f>
+        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 138 - 1), NA())</f>
         <v/>
       </c>
       <c r="R139">
-        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 138 - 1), NA())</f>
+        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 138 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="140">
       <c r="P140" s="2">
-        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 139 - 1), NA())</f>
+        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 139 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q140">
-        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 139 - 1), NA())</f>
+        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 139 - 1), NA())</f>
         <v/>
       </c>
       <c r="R140">
-        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 139 - 1), NA())</f>
+        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 139 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="141">
       <c r="P141" s="2">
-        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 140 - 1), NA())</f>
+        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 140 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q141">
-        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 140 - 1), NA())</f>
+        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 140 - 1), NA())</f>
         <v/>
       </c>
       <c r="R141">
-        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 140 - 1), NA())</f>
+        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 140 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="142">
       <c r="P142" s="2">
-        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 141 - 1), NA())</f>
+        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 141 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q142">
-        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 141 - 1), NA())</f>
+        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 141 - 1), NA())</f>
         <v/>
       </c>
       <c r="R142">
-        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 141 - 1), NA())</f>
+        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 141 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="143">
       <c r="P143" s="2">
-        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 142 - 1), NA())</f>
+        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 142 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q143">
-        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 142 - 1), NA())</f>
+        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 142 - 1), NA())</f>
         <v/>
       </c>
       <c r="R143">
-        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 142 - 1), NA())</f>
+        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 142 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="144">
       <c r="P144" s="2">
-        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 143 - 1), NA())</f>
+        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 143 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q144">
-        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 143 - 1), NA())</f>
+        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 143 - 1), NA())</f>
         <v/>
       </c>
       <c r="R144">
-        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 143 - 1), NA())</f>
+        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 143 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="145">
       <c r="P145" s="2">
-        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 144 - 1), NA())</f>
+        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 144 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q145">
-        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 144 - 1), NA())</f>
+        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 144 - 1), NA())</f>
         <v/>
       </c>
       <c r="R145">
-        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 144 - 1), NA())</f>
+        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 144 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="146">
       <c r="P146" s="2">
-        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 145 - 1), NA())</f>
+        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 145 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q146">
-        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 145 - 1), NA())</f>
+        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 145 - 1), NA())</f>
         <v/>
       </c>
       <c r="R146">
-        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 145 - 1), NA())</f>
+        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 145 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="147">
       <c r="P147" s="2">
-        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 146 - 1), NA())</f>
+        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 146 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q147">
-        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 146 - 1), NA())</f>
+        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 146 - 1), NA())</f>
         <v/>
       </c>
       <c r="R147">
-        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 146 - 1), NA())</f>
+        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 146 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="148">
       <c r="P148" s="2">
-        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 147 - 1), NA())</f>
+        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 147 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q148">
-        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 147 - 1), NA())</f>
+        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 147 - 1), NA())</f>
         <v/>
       </c>
       <c r="R148">
-        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 147 - 1), NA())</f>
+        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 147 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="149">
       <c r="P149" s="2">
-        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 148 - 1), NA())</f>
+        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 148 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q149">
-        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 148 - 1), NA())</f>
+        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 148 - 1), NA())</f>
         <v/>
       </c>
       <c r="R149">
-        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 148 - 1), NA())</f>
+        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 148 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="150">
       <c r="P150" s="2">
-        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 149 - 1), NA())</f>
+        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 149 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q150">
-        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 149 - 1), NA())</f>
+        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 149 - 1), NA())</f>
         <v/>
       </c>
       <c r="R150">
-        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 149 - 1), NA())</f>
+        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 149 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="151">
       <c r="P151" s="2">
-        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 150 - 1), NA())</f>
+        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 150 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q151">
-        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 150 - 1), NA())</f>
+        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 150 - 1), NA())</f>
         <v/>
       </c>
       <c r="R151">
-        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 150 - 1), NA())</f>
+        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 150 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="152">
       <c r="P152" s="2">
-        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 151 - 1), NA())</f>
+        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 151 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q152">
-        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 151 - 1), NA())</f>
+        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 151 - 1), NA())</f>
         <v/>
       </c>
       <c r="R152">
-        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 151 - 1), NA())</f>
+        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 151 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="153">
       <c r="P153" s="2">
-        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 152 - 1), NA())</f>
+        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 152 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q153">
-        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 152 - 1), NA())</f>
+        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 152 - 1), NA())</f>
         <v/>
       </c>
       <c r="R153">
-        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 152 - 1), NA())</f>
+        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 152 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="154">
       <c r="P154" s="2">
-        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 153 - 1), NA())</f>
+        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 153 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q154">
-        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 153 - 1), NA())</f>
+        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 153 - 1), NA())</f>
         <v/>
       </c>
       <c r="R154">
-        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 153 - 1), NA())</f>
+        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 153 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="155">
       <c r="P155" s="2">
-        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 154 - 1), NA())</f>
+        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 154 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q155">
-        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 154 - 1), NA())</f>
+        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 154 - 1), NA())</f>
         <v/>
       </c>
       <c r="R155">
-        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 154 - 1), NA())</f>
+        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 154 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="156">
       <c r="P156" s="2">
-        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 155 - 1), NA())</f>
+        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 155 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q156">
-        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 155 - 1), NA())</f>
+        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 155 - 1), NA())</f>
         <v/>
       </c>
       <c r="R156">
-        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 155 - 1), NA())</f>
+        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 155 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="157">
       <c r="P157" s="2">
-        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 156 - 1), NA())</f>
+        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 156 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q157">
-        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 156 - 1), NA())</f>
+        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 156 - 1), NA())</f>
         <v/>
       </c>
       <c r="R157">
-        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 156 - 1), NA())</f>
+        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 156 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="158">
       <c r="P158" s="2">
-        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 157 - 1), NA())</f>
+        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 157 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q158">
-        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 157 - 1), NA())</f>
+        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 157 - 1), NA())</f>
         <v/>
       </c>
       <c r="R158">
-        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 157 - 1), NA())</f>
+        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 157 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="159">
       <c r="P159" s="2">
-        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 158 - 1), NA())</f>
+        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 158 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q159">
-        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 158 - 1), NA())</f>
+        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 158 - 1), NA())</f>
         <v/>
       </c>
       <c r="R159">
-        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 158 - 1), NA())</f>
+        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 158 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="160">
       <c r="P160" s="2">
-        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 159 - 1), NA())</f>
+        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 159 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q160">
-        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 159 - 1), NA())</f>
+        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 159 - 1), NA())</f>
         <v/>
       </c>
       <c r="R160">
-        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 159 - 1), NA())</f>
+        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 159 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="161">
       <c r="P161" s="2">
-        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 160 - 1), NA())</f>
+        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 160 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q161">
-        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 160 - 1), NA())</f>
+        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 160 - 1), NA())</f>
         <v/>
       </c>
       <c r="R161">
-        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 160 - 1), NA())</f>
+        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 160 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="162">
       <c r="P162" s="2">
-        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 161 - 1), NA())</f>
+        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 161 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q162">
-        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 161 - 1), NA())</f>
+        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 161 - 1), NA())</f>
         <v/>
       </c>
       <c r="R162">
-        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 161 - 1), NA())</f>
+        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 161 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="163">
       <c r="P163" s="2">
-        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 162 - 1), NA())</f>
+        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 162 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q163">
-        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 162 - 1), NA())</f>
+        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 162 - 1), NA())</f>
         <v/>
       </c>
       <c r="R163">
-        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 162 - 1), NA())</f>
+        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 162 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="164">
       <c r="P164" s="2">
-        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 163 - 1), NA())</f>
+        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 163 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q164">
-        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 163 - 1), NA())</f>
+        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 163 - 1), NA())</f>
         <v/>
       </c>
       <c r="R164">
-        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 163 - 1), NA())</f>
+        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 163 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="165">
       <c r="P165" s="2">
-        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 164 - 1), NA())</f>
+        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 164 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q165">
-        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 164 - 1), NA())</f>
+        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 164 - 1), NA())</f>
         <v/>
       </c>
       <c r="R165">
-        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 164 - 1), NA())</f>
+        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 164 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="166">
       <c r="P166" s="2">
-        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 165 - 1), NA())</f>
+        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 165 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q166">
-        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 165 - 1), NA())</f>
+        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 165 - 1), NA())</f>
         <v/>
       </c>
       <c r="R166">
-        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 165 - 1), NA())</f>
+        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 165 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="167">
       <c r="P167" s="2">
-        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 166 - 1), NA())</f>
+        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 166 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q167">
-        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 166 - 1), NA())</f>
+        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 166 - 1), NA())</f>
         <v/>
       </c>
       <c r="R167">
-        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 166 - 1), NA())</f>
+        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 166 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="168">
       <c r="P168" s="2">
-        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 167 - 1), NA())</f>
+        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 167 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q168">
-        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 167 - 1), NA())</f>
+        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 167 - 1), NA())</f>
         <v/>
       </c>
       <c r="R168">
-        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 167 - 1), NA())</f>
+        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 167 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="169">
       <c r="P169" s="2">
-        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 168 - 1), NA())</f>
+        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 168 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q169">
-        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 168 - 1), NA())</f>
+        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 168 - 1), NA())</f>
         <v/>
       </c>
       <c r="R169">
-        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 168 - 1), NA())</f>
+        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 168 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="170">
       <c r="P170" s="2">
-        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 169 - 1), NA())</f>
+        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 169 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q170">
-        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 169 - 1), NA())</f>
+        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 169 - 1), NA())</f>
         <v/>
       </c>
       <c r="R170">
-        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 169 - 1), NA())</f>
+        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 169 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="171">
       <c r="P171" s="2">
-        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 170 - 1), NA())</f>
+        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 170 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q171">
-        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 170 - 1), NA())</f>
+        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 170 - 1), NA())</f>
         <v/>
       </c>
       <c r="R171">
-        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 170 - 1), NA())</f>
+        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 170 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="172">
       <c r="P172" s="2">
-        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 171 - 1), NA())</f>
+        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 171 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q172">
-        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 171 - 1), NA())</f>
+        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 171 - 1), NA())</f>
         <v/>
       </c>
       <c r="R172">
-        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 171 - 1), NA())</f>
+        <f>IF(171&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 171 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="173">
       <c r="P173" s="2">
-        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 172 - 1), NA())</f>
+        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 172 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q173">
-        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 172 - 1), NA())</f>
+        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 172 - 1), NA())</f>
         <v/>
       </c>
       <c r="R173">
-        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 172 - 1), NA())</f>
+        <f>IF(172&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 172 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="174">
       <c r="P174" s="2">
-        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 173 - 1), NA())</f>
+        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 173 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q174">
-        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 173 - 1), NA())</f>
+        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 173 - 1), NA())</f>
         <v/>
       </c>
       <c r="R174">
-        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 173 - 1), NA())</f>
+        <f>IF(173&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 173 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="175">
       <c r="P175" s="2">
-        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 174 - 1), NA())</f>
+        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 174 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q175">
-        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 174 - 1), NA())</f>
+        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 174 - 1), NA())</f>
         <v/>
       </c>
       <c r="R175">
-        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 174 - 1), NA())</f>
+        <f>IF(174&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 174 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="176">
       <c r="P176" s="2">
-        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 175 - 1), NA())</f>
+        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 175 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q176">
-        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 175 - 1), NA())</f>
+        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 175 - 1), NA())</f>
         <v/>
       </c>
       <c r="R176">
-        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 175 - 1), NA())</f>
+        <f>IF(175&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 175 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="177">
       <c r="P177" s="2">
-        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 176 - 1), NA())</f>
+        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 176 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q177">
-        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 176 - 1), NA())</f>
+        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 176 - 1), NA())</f>
         <v/>
       </c>
       <c r="R177">
-        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 176 - 1), NA())</f>
+        <f>IF(176&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 176 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="178">
       <c r="P178" s="2">
-        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 177 - 1), NA())</f>
+        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 177 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q178">
-        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 177 - 1), NA())</f>
+        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 177 - 1), NA())</f>
         <v/>
       </c>
       <c r="R178">
-        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 177 - 1), NA())</f>
+        <f>IF(177&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 177 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="179">
       <c r="P179" s="2">
-        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 178 - 1), NA())</f>
+        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 178 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q179">
-        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 178 - 1), NA())</f>
+        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 178 - 1), NA())</f>
         <v/>
       </c>
       <c r="R179">
-        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 178 - 1), NA())</f>
+        <f>IF(178&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 178 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="180">
       <c r="P180" s="2">
-        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 179 - 1), NA())</f>
+        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 179 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q180">
-        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 179 - 1), NA())</f>
+        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 179 - 1), NA())</f>
         <v/>
       </c>
       <c r="R180">
-        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 179 - 1), NA())</f>
+        <f>IF(179&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 179 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="181">
       <c r="P181" s="2">
-        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 180 - 1), NA())</f>
+        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 180 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q181">
-        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 180 - 1), NA())</f>
+        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 180 - 1), NA())</f>
         <v/>
       </c>
       <c r="R181">
-        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 180 - 1), NA())</f>
+        <f>IF(180&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 180 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="182">
       <c r="P182" s="2">
-        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 181 - 1), NA())</f>
+        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 181 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q182">
-        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 181 - 1), NA())</f>
+        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 181 - 1), NA())</f>
         <v/>
       </c>
       <c r="R182">
-        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 181 - 1), NA())</f>
+        <f>IF(181&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 181 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="183">
       <c r="P183" s="2">
-        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 182 - 1), NA())</f>
+        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 182 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q183">
-        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 182 - 1), NA())</f>
+        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 182 - 1), NA())</f>
         <v/>
       </c>
       <c r="R183">
-        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 182 - 1), NA())</f>
+        <f>IF(182&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 182 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="184">
       <c r="P184" s="2">
-        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 183 - 1), NA())</f>
+        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 183 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q184">
-        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 183 - 1), NA())</f>
+        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 183 - 1), NA())</f>
         <v/>
       </c>
       <c r="R184">
-        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 183 - 1), NA())</f>
+        <f>IF(183&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 183 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="185">
       <c r="P185" s="2">
-        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 184 - 1), NA())</f>
+        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 184 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q185">
-        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 184 - 1), NA())</f>
+        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 184 - 1), NA())</f>
         <v/>
       </c>
       <c r="R185">
-        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 184 - 1), NA())</f>
+        <f>IF(184&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 184 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="186">
       <c r="P186" s="2">
-        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 185 - 1), NA())</f>
+        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 185 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q186">
-        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 185 - 1), NA())</f>
+        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 185 - 1), NA())</f>
         <v/>
       </c>
       <c r="R186">
-        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 185 - 1), NA())</f>
+        <f>IF(185&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 185 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="187">
       <c r="P187" s="2">
-        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 186 - 1), NA())</f>
+        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 186 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q187">
-        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 186 - 1), NA())</f>
+        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 186 - 1), NA())</f>
         <v/>
       </c>
       <c r="R187">
-        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 186 - 1), NA())</f>
+        <f>IF(186&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 186 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="188">
       <c r="P188" s="2">
-        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 187 - 1), NA())</f>
+        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 187 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q188">
-        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 187 - 1), NA())</f>
+        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 187 - 1), NA())</f>
         <v/>
       </c>
       <c r="R188">
-        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 187 - 1), NA())</f>
+        <f>IF(187&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 187 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="189">
       <c r="P189" s="2">
-        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 188 - 1), NA())</f>
+        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 188 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q189">
-        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 188 - 1), NA())</f>
+        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 188 - 1), NA())</f>
         <v/>
       </c>
       <c r="R189">
-        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 188 - 1), NA())</f>
+        <f>IF(188&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 188 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="190">
       <c r="P190" s="2">
-        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 189 - 1), NA())</f>
+        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 189 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q190">
-        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 189 - 1), NA())</f>
+        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 189 - 1), NA())</f>
         <v/>
       </c>
       <c r="R190">
-        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 189 - 1), NA())</f>
+        <f>IF(189&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 189 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="191">
       <c r="P191" s="2">
-        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 190 - 1), NA())</f>
+        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 190 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q191">
-        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 190 - 1), NA())</f>
+        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 190 - 1), NA())</f>
         <v/>
       </c>
       <c r="R191">
-        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 190 - 1), NA())</f>
+        <f>IF(190&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 190 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="192">
       <c r="P192" s="2">
-        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 191 - 1), NA())</f>
+        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 191 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q192">
-        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 191 - 1), NA())</f>
+        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 191 - 1), NA())</f>
         <v/>
       </c>
       <c r="R192">
-        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 191 - 1), NA())</f>
+        <f>IF(191&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 191 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="193">
       <c r="P193" s="2">
-        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 192 - 1), NA())</f>
+        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 192 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q193">
-        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 192 - 1), NA())</f>
+        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 192 - 1), NA())</f>
         <v/>
       </c>
       <c r="R193">
-        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 192 - 1), NA())</f>
+        <f>IF(192&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 192 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="194">
       <c r="P194" s="2">
-        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 193 - 1), NA())</f>
+        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 193 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q194">
-        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 193 - 1), NA())</f>
+        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 193 - 1), NA())</f>
         <v/>
       </c>
       <c r="R194">
-        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 193 - 1), NA())</f>
+        <f>IF(193&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 193 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="195">
       <c r="P195" s="2">
-        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 194 - 1), NA())</f>
+        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 194 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q195">
-        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 194 - 1), NA())</f>
+        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 194 - 1), NA())</f>
         <v/>
       </c>
       <c r="R195">
-        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 194 - 1), NA())</f>
+        <f>IF(194&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 194 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="196">
       <c r="P196" s="2">
-        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 195 - 1), NA())</f>
+        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 195 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q196">
-        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 195 - 1), NA())</f>
+        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 195 - 1), NA())</f>
         <v/>
       </c>
       <c r="R196">
-        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 195 - 1), NA())</f>
+        <f>IF(195&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 195 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="197">
       <c r="P197" s="2">
-        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 196 - 1), NA())</f>
+        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 196 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q197">
-        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 196 - 1), NA())</f>
+        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 196 - 1), NA())</f>
         <v/>
       </c>
       <c r="R197">
-        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 196 - 1), NA())</f>
+        <f>IF(196&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 196 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="198">
       <c r="P198" s="2">
-        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 197 - 1), NA())</f>
+        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 197 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q198">
-        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 197 - 1), NA())</f>
+        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 197 - 1), NA())</f>
         <v/>
       </c>
       <c r="R198">
-        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 197 - 1), NA())</f>
+        <f>IF(197&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 197 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="199">
       <c r="P199" s="2">
-        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 198 - 1), NA())</f>
+        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 198 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q199">
-        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 198 - 1), NA())</f>
+        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 198 - 1), NA())</f>
         <v/>
       </c>
       <c r="R199">
-        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 198 - 1), NA())</f>
+        <f>IF(198&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 198 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="200">
       <c r="P200" s="2">
-        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 199 - 1), NA())</f>
+        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 199 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q200">
-        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 199 - 1), NA())</f>
+        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 199 - 1), NA())</f>
         <v/>
       </c>
       <c r="R200">
-        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 199 - 1), NA())</f>
+        <f>IF(199&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 199 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="201">
       <c r="P201" s="2">
-        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 200 - 1), NA())</f>
+        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 200 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q201">
-        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 200 - 1), NA())</f>
+        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 200 - 1), NA())</f>
         <v/>
       </c>
       <c r="R201">
-        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 200 - 1), NA())</f>
+        <f>IF(200&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 200 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="202">
       <c r="P202" s="2">
-        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 201 - 1), NA())</f>
+        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 201 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q202">
-        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 201 - 1), NA())</f>
+        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 201 - 1), NA())</f>
         <v/>
       </c>
       <c r="R202">
-        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 201 - 1), NA())</f>
+        <f>IF(201&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 201 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="203">
       <c r="P203" s="2">
-        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 202 - 1), NA())</f>
+        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 202 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q203">
-        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 202 - 1), NA())</f>
+        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 202 - 1), NA())</f>
         <v/>
       </c>
       <c r="R203">
-        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 202 - 1), NA())</f>
+        <f>IF(202&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 202 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="204">
       <c r="P204" s="2">
-        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 203 - 1), NA())</f>
+        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 203 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q204">
-        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 203 - 1), NA())</f>
+        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 203 - 1), NA())</f>
         <v/>
       </c>
       <c r="R204">
-        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 203 - 1), NA())</f>
+        <f>IF(203&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 203 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="205">
       <c r="P205" s="2">
-        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 204 - 1), NA())</f>
+        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 204 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q205">
-        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 204 - 1), NA())</f>
+        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 204 - 1), NA())</f>
         <v/>
       </c>
       <c r="R205">
-        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 204 - 1), NA())</f>
+        <f>IF(204&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 204 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="206">
       <c r="P206" s="2">
-        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 205 - 1), NA())</f>
+        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 205 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q206">
-        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 205 - 1), NA())</f>
+        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 205 - 1), NA())</f>
         <v/>
       </c>
       <c r="R206">
-        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 205 - 1), NA())</f>
+        <f>IF(205&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 205 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="207">
       <c r="P207" s="2">
-        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 206 - 1), NA())</f>
+        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 206 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q207">
-        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 206 - 1), NA())</f>
+        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 206 - 1), NA())</f>
         <v/>
       </c>
       <c r="R207">
-        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 206 - 1), NA())</f>
+        <f>IF(206&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 206 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="208">
       <c r="P208" s="2">
-        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 207 - 1), NA())</f>
+        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 207 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q208">
-        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 207 - 1), NA())</f>
+        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 207 - 1), NA())</f>
         <v/>
       </c>
       <c r="R208">
-        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 207 - 1), NA())</f>
+        <f>IF(207&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 207 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="209">
       <c r="P209" s="2">
-        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 208 - 1), NA())</f>
+        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 208 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q209">
-        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 208 - 1), NA())</f>
+        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 208 - 1), NA())</f>
         <v/>
       </c>
       <c r="R209">
-        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 208 - 1), NA())</f>
+        <f>IF(208&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 208 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="210">
       <c r="P210" s="2">
-        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 209 - 1), NA())</f>
+        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 209 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q210">
-        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 209 - 1), NA())</f>
+        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 209 - 1), NA())</f>
         <v/>
       </c>
       <c r="R210">
-        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 209 - 1), NA())</f>
+        <f>IF(209&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 209 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="211">
       <c r="P211" s="2">
-        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 210 - 1), NA())</f>
+        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 210 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q211">
-        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 210 - 1), NA())</f>
+        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 210 - 1), NA())</f>
         <v/>
       </c>
       <c r="R211">
-        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 210 - 1), NA())</f>
+        <f>IF(210&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 210 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="212">
       <c r="P212" s="2">
-        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 211 - 1), NA())</f>
+        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 211 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q212">
-        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 211 - 1), NA())</f>
+        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 211 - 1), NA())</f>
         <v/>
       </c>
       <c r="R212">
-        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 211 - 1), NA())</f>
+        <f>IF(211&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 211 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="213">
       <c r="P213" s="2">
-        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 212 - 1), NA())</f>
+        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 212 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q213">
-        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 212 - 1), NA())</f>
+        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 212 - 1), NA())</f>
         <v/>
       </c>
       <c r="R213">
-        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 212 - 1), NA())</f>
+        <f>IF(212&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 212 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="214">
       <c r="P214" s="2">
-        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 213 - 1), NA())</f>
+        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 213 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q214">
-        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 213 - 1), NA())</f>
+        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 213 - 1), NA())</f>
         <v/>
       </c>
       <c r="R214">
-        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 213 - 1), NA())</f>
+        <f>IF(213&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 213 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="215">
       <c r="P215" s="2">
-        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 214 - 1), NA())</f>
+        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 214 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q215">
-        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 214 - 1), NA())</f>
+        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 214 - 1), NA())</f>
         <v/>
       </c>
       <c r="R215">
-        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 214 - 1), NA())</f>
+        <f>IF(214&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 214 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="216">
       <c r="P216" s="2">
-        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 215 - 1), NA())</f>
+        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 215 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q216">
-        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 215 - 1), NA())</f>
+        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 215 - 1), NA())</f>
         <v/>
       </c>
       <c r="R216">
-        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 215 - 1), NA())</f>
+        <f>IF(215&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 215 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="217">
       <c r="P217" s="2">
-        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 216 - 1), NA())</f>
+        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 216 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q217">
-        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 216 - 1), NA())</f>
+        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 216 - 1), NA())</f>
         <v/>
       </c>
       <c r="R217">
-        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 216 - 1), NA())</f>
+        <f>IF(216&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 216 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="218">
       <c r="P218" s="2">
-        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 217 - 1), NA())</f>
+        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 217 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q218">
-        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 217 - 1), NA())</f>
+        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 217 - 1), NA())</f>
         <v/>
       </c>
       <c r="R218">
-        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 217 - 1), NA())</f>
+        <f>IF(217&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 217 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="219">
       <c r="P219" s="2">
-        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 218 - 1), NA())</f>
+        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 218 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q219">
-        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 218 - 1), NA())</f>
+        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 218 - 1), NA())</f>
         <v/>
       </c>
       <c r="R219">
-        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 218 - 1), NA())</f>
+        <f>IF(218&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 218 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="220">
       <c r="P220" s="2">
-        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 219 - 1), NA())</f>
+        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 219 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q220">
-        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 219 - 1), NA())</f>
+        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 219 - 1), NA())</f>
         <v/>
       </c>
       <c r="R220">
-        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 219 - 1), NA())</f>
+        <f>IF(219&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 219 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="221">
       <c r="P221" s="2">
-        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 220 - 1), NA())</f>
+        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 220 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q221">
-        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 220 - 1), NA())</f>
+        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 220 - 1), NA())</f>
         <v/>
       </c>
       <c r="R221">
-        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 220 - 1), NA())</f>
+        <f>IF(220&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 220 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="222">
       <c r="P222" s="2">
-        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 221 - 1), NA())</f>
+        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 221 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q222">
-        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 221 - 1), NA())</f>
+        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 221 - 1), NA())</f>
         <v/>
       </c>
       <c r="R222">
-        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 221 - 1), NA())</f>
+        <f>IF(221&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 221 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="223">
       <c r="P223" s="2">
-        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 222 - 1), NA())</f>
+        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 222 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q223">
-        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 222 - 1), NA())</f>
+        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 222 - 1), NA())</f>
         <v/>
       </c>
       <c r="R223">
-        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 222 - 1), NA())</f>
+        <f>IF(222&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 222 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="224">
       <c r="P224" s="2">
-        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 223 - 1), NA())</f>
+        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 223 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q224">
-        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 223 - 1), NA())</f>
+        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 223 - 1), NA())</f>
         <v/>
       </c>
       <c r="R224">
-        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 223 - 1), NA())</f>
+        <f>IF(223&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 223 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="225">
       <c r="P225" s="2">
-        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 224 - 1), NA())</f>
+        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 224 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q225">
-        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 224 - 1), NA())</f>
+        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 224 - 1), NA())</f>
         <v/>
       </c>
       <c r="R225">
-        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 224 - 1), NA())</f>
+        <f>IF(224&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 224 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="226">
       <c r="P226" s="2">
-        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 225 - 1), NA())</f>
+        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 225 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q226">
-        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 225 - 1), NA())</f>
+        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 225 - 1), NA())</f>
         <v/>
       </c>
       <c r="R226">
-        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 225 - 1), NA())</f>
+        <f>IF(225&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 225 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="227">
       <c r="P227" s="2">
-        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 226 - 1), NA())</f>
+        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 226 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q227">
-        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 226 - 1), NA())</f>
+        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 226 - 1), NA())</f>
         <v/>
       </c>
       <c r="R227">
-        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 226 - 1), NA())</f>
+        <f>IF(226&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 226 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="228">
       <c r="P228" s="2">
-        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 227 - 1), NA())</f>
+        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 227 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q228">
-        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 227 - 1), NA())</f>
+        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 227 - 1), NA())</f>
         <v/>
       </c>
       <c r="R228">
-        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 227 - 1), NA())</f>
+        <f>IF(227&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 227 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="229">
       <c r="P229" s="2">
-        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 228 - 1), NA())</f>
+        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 228 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q229">
-        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 228 - 1), NA())</f>
+        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 228 - 1), NA())</f>
         <v/>
       </c>
       <c r="R229">
-        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 228 - 1), NA())</f>
+        <f>IF(228&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 228 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="230">
       <c r="P230" s="2">
-        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 229 - 1), NA())</f>
+        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 229 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q230">
-        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 229 - 1), NA())</f>
+        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 229 - 1), NA())</f>
         <v/>
       </c>
       <c r="R230">
-        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 229 - 1), NA())</f>
+        <f>IF(229&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 229 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="231">
       <c r="P231" s="2">
-        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 230 - 1), NA())</f>
+        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 230 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q231">
-        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 230 - 1), NA())</f>
+        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 230 - 1), NA())</f>
         <v/>
       </c>
       <c r="R231">
-        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 230 - 1), NA())</f>
+        <f>IF(230&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 230 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="232">
       <c r="P232" s="2">
-        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 231 - 1), NA())</f>
+        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 231 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q232">
-        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 231 - 1), NA())</f>
+        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 231 - 1), NA())</f>
         <v/>
       </c>
       <c r="R232">
-        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 231 - 1), NA())</f>
+        <f>IF(231&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 231 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="233">
       <c r="P233" s="2">
-        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 232 - 1), NA())</f>
+        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 232 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q233">
-        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 232 - 1), NA())</f>
+        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 232 - 1), NA())</f>
         <v/>
       </c>
       <c r="R233">
-        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 232 - 1), NA())</f>
+        <f>IF(232&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 232 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="234">
       <c r="P234" s="2">
-        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 233 - 1), NA())</f>
+        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 233 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q234">
-        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 233 - 1), NA())</f>
+        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 233 - 1), NA())</f>
         <v/>
       </c>
       <c r="R234">
-        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 233 - 1), NA())</f>
+        <f>IF(233&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 233 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="235">
       <c r="P235" s="2">
-        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 234 - 1), NA())</f>
+        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 234 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q235">
-        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 234 - 1), NA())</f>
+        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 234 - 1), NA())</f>
         <v/>
       </c>
       <c r="R235">
-        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 234 - 1), NA())</f>
+        <f>IF(234&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 234 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="236">
       <c r="P236" s="2">
-        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 235 - 1), NA())</f>
+        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 235 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q236">
-        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 235 - 1), NA())</f>
+        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 235 - 1), NA())</f>
         <v/>
       </c>
       <c r="R236">
-        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 235 - 1), NA())</f>
+        <f>IF(235&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 235 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="237">
       <c r="P237" s="2">
-        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 236 - 1), NA())</f>
+        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 236 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q237">
-        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 236 - 1), NA())</f>
+        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 236 - 1), NA())</f>
         <v/>
       </c>
       <c r="R237">
-        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 236 - 1), NA())</f>
+        <f>IF(236&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 236 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="238">
       <c r="P238" s="2">
-        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 237 - 1), NA())</f>
+        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 237 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q238">
-        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 237 - 1), NA())</f>
+        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 237 - 1), NA())</f>
         <v/>
       </c>
       <c r="R238">
-        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 237 - 1), NA())</f>
+        <f>IF(237&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 237 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="239">
       <c r="P239" s="2">
-        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 238 - 1), NA())</f>
+        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 238 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q239">
-        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 238 - 1), NA())</f>
+        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 238 - 1), NA())</f>
         <v/>
       </c>
       <c r="R239">
-        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 238 - 1), NA())</f>
+        <f>IF(238&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 238 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="240">
       <c r="P240" s="2">
-        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 239 - 1), NA())</f>
+        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 239 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q240">
-        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 239 - 1), NA())</f>
+        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 239 - 1), NA())</f>
         <v/>
       </c>
       <c r="R240">
-        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 239 - 1), NA())</f>
+        <f>IF(239&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 239 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="241">
       <c r="P241" s="2">
-        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 240 - 1), NA())</f>
+        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 240 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q241">
-        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 240 - 1), NA())</f>
+        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 240 - 1), NA())</f>
         <v/>
       </c>
       <c r="R241">
-        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 240 - 1), NA())</f>
+        <f>IF(240&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 240 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="242">
       <c r="P242" s="2">
-        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 241 - 1), NA())</f>
+        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 241 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q242">
-        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 241 - 1), NA())</f>
+        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 241 - 1), NA())</f>
         <v/>
       </c>
       <c r="R242">
-        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 241 - 1), NA())</f>
+        <f>IF(241&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 241 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="243">
       <c r="P243" s="2">
-        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 242 - 1), NA())</f>
+        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 242 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q243">
-        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 242 - 1), NA())</f>
+        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 242 - 1), NA())</f>
         <v/>
       </c>
       <c r="R243">
-        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 242 - 1), NA())</f>
+        <f>IF(242&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 242 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="244">
       <c r="P244" s="2">
-        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 243 - 1), NA())</f>
+        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 243 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q244">
-        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 243 - 1), NA())</f>
+        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 243 - 1), NA())</f>
         <v/>
       </c>
       <c r="R244">
-        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 243 - 1), NA())</f>
+        <f>IF(243&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 243 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="245">
       <c r="P245" s="2">
-        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 244 - 1), NA())</f>
+        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 244 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q245">
-        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 244 - 1), NA())</f>
+        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 244 - 1), NA())</f>
         <v/>
       </c>
       <c r="R245">
-        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 244 - 1), NA())</f>
+        <f>IF(244&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 244 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="246">
       <c r="P246" s="2">
-        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 245 - 1), NA())</f>
+        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 245 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q246">
-        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 245 - 1), NA())</f>
+        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 245 - 1), NA())</f>
         <v/>
       </c>
       <c r="R246">
-        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 245 - 1), NA())</f>
+        <f>IF(245&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 245 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="247">
       <c r="P247" s="2">
-        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 246 - 1), NA())</f>
+        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 246 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q247">
-        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 246 - 1), NA())</f>
+        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 246 - 1), NA())</f>
         <v/>
       </c>
       <c r="R247">
-        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 246 - 1), NA())</f>
+        <f>IF(246&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 246 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="248">
       <c r="P248" s="2">
-        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 247 - 1), NA())</f>
+        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 247 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q248">
-        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 247 - 1), NA())</f>
+        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 247 - 1), NA())</f>
         <v/>
       </c>
       <c r="R248">
-        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 247 - 1), NA())</f>
+        <f>IF(247&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 247 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="249">
       <c r="P249" s="2">
-        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 248 - 1), NA())</f>
+        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 248 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q249">
-        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 248 - 1), NA())</f>
+        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 248 - 1), NA())</f>
         <v/>
       </c>
       <c r="R249">
-        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 248 - 1), NA())</f>
+        <f>IF(248&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 248 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="250">
       <c r="P250" s="2">
-        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 249 - 1), NA())</f>
+        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 249 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q250">
-        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 249 - 1), NA())</f>
+        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 249 - 1), NA())</f>
         <v/>
       </c>
       <c r="R250">
-        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 249 - 1), NA())</f>
+        <f>IF(249&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 249 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="251">
       <c r="P251" s="2">
-        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 250 - 1), NA())</f>
+        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 250 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q251">
-        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 250 - 1), NA())</f>
+        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 250 - 1), NA())</f>
         <v/>
       </c>
       <c r="R251">
-        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 250 - 1), NA())</f>
+        <f>IF(250&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 250 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="252">
       <c r="P252" s="2">
-        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 251 - 1), NA())</f>
+        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 251 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q252">
-        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 251 - 1), NA())</f>
+        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 251 - 1), NA())</f>
         <v/>
       </c>
       <c r="R252">
-        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 251 - 1), NA())</f>
+        <f>IF(251&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 251 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="253">
       <c r="P253" s="2">
-        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 252 - 1), NA())</f>
+        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 252 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q253">
-        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 252 - 1), NA())</f>
+        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 252 - 1), NA())</f>
         <v/>
       </c>
       <c r="R253">
-        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 252 - 1), NA())</f>
+        <f>IF(252&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 252 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="254">
       <c r="P254" s="2">
-        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 253 - 1), NA())</f>
+        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 253 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q254">
-        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 253 - 1), NA())</f>
+        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 253 - 1), NA())</f>
         <v/>
       </c>
       <c r="R254">
-        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 253 - 1), NA())</f>
+        <f>IF(253&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 253 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="255">
       <c r="P255" s="2">
-        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 254 - 1), NA())</f>
+        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 254 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q255">
-        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 254 - 1), NA())</f>
+        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 254 - 1), NA())</f>
         <v/>
       </c>
       <c r="R255">
-        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 254 - 1), NA())</f>
+        <f>IF(254&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 254 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="256">
       <c r="P256" s="2">
-        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 255 - 1), NA())</f>
+        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 255 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q256">
-        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 255 - 1), NA())</f>
+        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 255 - 1), NA())</f>
         <v/>
       </c>
       <c r="R256">
-        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 255 - 1), NA())</f>
+        <f>IF(255&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 255 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="257">
       <c r="P257" s="2">
-        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 256 - 1), NA())</f>
+        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 256 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q257">
-        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 256 - 1), NA())</f>
+        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 256 - 1), NA())</f>
         <v/>
       </c>
       <c r="R257">
-        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 256 - 1), NA())</f>
+        <f>IF(256&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 256 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="258">
       <c r="P258" s="2">
-        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 257 - 1), NA())</f>
+        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 257 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q258">
-        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 257 - 1), NA())</f>
+        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 257 - 1), NA())</f>
         <v/>
       </c>
       <c r="R258">
-        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 257 - 1), NA())</f>
+        <f>IF(257&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 257 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="259">
       <c r="P259" s="2">
-        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 258 - 1), NA())</f>
+        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 258 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q259">
-        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 258 - 1), NA())</f>
+        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 258 - 1), NA())</f>
         <v/>
       </c>
       <c r="R259">
-        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 258 - 1), NA())</f>
+        <f>IF(258&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 258 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="260">
       <c r="P260" s="2">
-        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 259 - 1), NA())</f>
+        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 259 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q260">
-        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 259 - 1), NA())</f>
+        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 259 - 1), NA())</f>
         <v/>
       </c>
       <c r="R260">
-        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 259 - 1), NA())</f>
+        <f>IF(259&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 259 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="261">
       <c r="P261" s="2">
-        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 260 - 1), NA())</f>
+        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 260 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q261">
-        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 260 - 1), NA())</f>
+        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 260 - 1), NA())</f>
         <v/>
       </c>
       <c r="R261">
-        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 260 - 1), NA())</f>
+        <f>IF(260&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 260 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="262">
       <c r="P262" s="2">
-        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 261 - 1), NA())</f>
+        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 261 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q262">
-        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 261 - 1), NA())</f>
+        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 261 - 1), NA())</f>
         <v/>
       </c>
       <c r="R262">
-        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 261 - 1), NA())</f>
+        <f>IF(261&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 261 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="263">
       <c r="P263" s="2">
-        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 262 - 1), NA())</f>
+        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 262 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q263">
-        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 262 - 1), NA())</f>
+        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 262 - 1), NA())</f>
         <v/>
       </c>
       <c r="R263">
-        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 262 - 1), NA())</f>
+        <f>IF(262&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 262 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="264">
       <c r="P264" s="2">
-        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 263 - 1), NA())</f>
+        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 263 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q264">
-        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 263 - 1), NA())</f>
+        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 263 - 1), NA())</f>
         <v/>
       </c>
       <c r="R264">
-        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 263 - 1), NA())</f>
+        <f>IF(263&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 263 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="265">
       <c r="P265" s="2">
-        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 264 - 1), NA())</f>
+        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 264 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q265">
-        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 264 - 1), NA())</f>
+        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 264 - 1), NA())</f>
         <v/>
       </c>
       <c r="R265">
-        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 264 - 1), NA())</f>
+        <f>IF(264&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 264 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="266">
       <c r="P266" s="2">
-        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 265 - 1), NA())</f>
+        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 265 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q266">
-        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 265 - 1), NA())</f>
+        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 265 - 1), NA())</f>
         <v/>
       </c>
       <c r="R266">
-        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 265 - 1), NA())</f>
+        <f>IF(265&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 265 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="267">
       <c r="P267" s="2">
-        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 266 - 1), NA())</f>
+        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 266 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q267">
-        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 266 - 1), NA())</f>
+        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 266 - 1), NA())</f>
         <v/>
       </c>
       <c r="R267">
-        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 266 - 1), NA())</f>
+        <f>IF(266&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 266 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="268">
       <c r="P268" s="2">
-        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 267 - 1), NA())</f>
+        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 267 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q268">
-        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 267 - 1), NA())</f>
+        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 267 - 1), NA())</f>
         <v/>
       </c>
       <c r="R268">
-        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 267 - 1), NA())</f>
+        <f>IF(267&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 267 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="269">
       <c r="P269" s="2">
-        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 268 - 1), NA())</f>
+        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 268 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q269">
-        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 268 - 1), NA())</f>
+        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 268 - 1), NA())</f>
         <v/>
       </c>
       <c r="R269">
-        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 268 - 1), NA())</f>
+        <f>IF(268&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 268 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="270">
       <c r="P270" s="2">
-        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 269 - 1), NA())</f>
+        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 269 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q270">
-        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 269 - 1), NA())</f>
+        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 269 - 1), NA())</f>
         <v/>
       </c>
       <c r="R270">
-        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 269 - 1), NA())</f>
+        <f>IF(269&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 269 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="271">
       <c r="P271" s="2">
-        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 270 - 1), NA())</f>
+        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 270 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q271">
-        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 270 - 1), NA())</f>
+        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 270 - 1), NA())</f>
         <v/>
       </c>
       <c r="R271">
-        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 270 - 1), NA())</f>
+        <f>IF(270&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 270 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="272">
       <c r="P272" s="2">
-        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 271 - 1), NA())</f>
+        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 271 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q272">
-        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 271 - 1), NA())</f>
+        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 271 - 1), NA())</f>
         <v/>
       </c>
       <c r="R272">
-        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 271 - 1), NA())</f>
+        <f>IF(271&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 271 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="273">
       <c r="P273" s="2">
-        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 272 - 1), NA())</f>
+        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 272 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q273">
-        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 272 - 1), NA())</f>
+        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 272 - 1), NA())</f>
         <v/>
       </c>
       <c r="R273">
-        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 272 - 1), NA())</f>
+        <f>IF(272&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 272 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="274">
       <c r="P274" s="2">
-        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 273 - 1), NA())</f>
+        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 273 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q274">
-        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 273 - 1), NA())</f>
+        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 273 - 1), NA())</f>
         <v/>
       </c>
       <c r="R274">
-        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 273 - 1), NA())</f>
+        <f>IF(273&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 273 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="275">
       <c r="P275" s="2">
-        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 274 - 1), NA())</f>
+        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 274 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q275">
-        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 274 - 1), NA())</f>
+        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 274 - 1), NA())</f>
         <v/>
       </c>
       <c r="R275">
-        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 274 - 1), NA())</f>
+        <f>IF(274&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 274 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="276">
       <c r="P276" s="2">
-        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 275 - 1), NA())</f>
+        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 275 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q276">
-        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 275 - 1), NA())</f>
+        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 275 - 1), NA())</f>
         <v/>
       </c>
       <c r="R276">
-        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 275 - 1), NA())</f>
+        <f>IF(275&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 275 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="277">
       <c r="P277" s="2">
-        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 276 - 1), NA())</f>
+        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 276 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q277">
-        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 276 - 1), NA())</f>
+        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 276 - 1), NA())</f>
         <v/>
       </c>
       <c r="R277">
-        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 276 - 1), NA())</f>
+        <f>IF(276&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 276 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="278">
       <c r="P278" s="2">
-        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 277 - 1), NA())</f>
+        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 277 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q278">
-        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 277 - 1), NA())</f>
+        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 277 - 1), NA())</f>
         <v/>
       </c>
       <c r="R278">
-        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 277 - 1), NA())</f>
+        <f>IF(277&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 277 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="279">
       <c r="P279" s="2">
-        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 278 - 1), NA())</f>
+        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 278 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q279">
-        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 278 - 1), NA())</f>
+        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 278 - 1), NA())</f>
         <v/>
       </c>
       <c r="R279">
-        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 278 - 1), NA())</f>
+        <f>IF(278&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 278 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="280">
       <c r="P280" s="2">
-        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 279 - 1), NA())</f>
+        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 279 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q280">
-        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 279 - 1), NA())</f>
+        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 279 - 1), NA())</f>
         <v/>
       </c>
       <c r="R280">
-        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 279 - 1), NA())</f>
+        <f>IF(279&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 279 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="281">
       <c r="P281" s="2">
-        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 280 - 1), NA())</f>
+        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 280 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q281">
-        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 280 - 1), NA())</f>
+        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 280 - 1), NA())</f>
         <v/>
       </c>
       <c r="R281">
-        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 280 - 1), NA())</f>
+        <f>IF(280&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 280 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="282">
       <c r="P282" s="2">
-        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 281 - 1), NA())</f>
+        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 281 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q282">
-        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 281 - 1), NA())</f>
+        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 281 - 1), NA())</f>
         <v/>
       </c>
       <c r="R282">
-        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 281 - 1), NA())</f>
+        <f>IF(281&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 281 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="283">
       <c r="P283" s="2">
-        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 282 - 1), NA())</f>
+        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 282 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q283">
-        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 282 - 1), NA())</f>
+        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 282 - 1), NA())</f>
         <v/>
       </c>
       <c r="R283">
-        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 282 - 1), NA())</f>
+        <f>IF(282&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 282 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="284">
       <c r="P284" s="2">
-        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 283 - 1), NA())</f>
+        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 283 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q284">
-        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 283 - 1), NA())</f>
+        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 283 - 1), NA())</f>
         <v/>
       </c>
       <c r="R284">
-        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 283 - 1), NA())</f>
+        <f>IF(283&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 283 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="285">
       <c r="P285" s="2">
-        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 284 - 1), NA())</f>
+        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 284 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q285">
-        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 284 - 1), NA())</f>
+        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 284 - 1), NA())</f>
         <v/>
       </c>
       <c r="R285">
-        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 284 - 1), NA())</f>
+        <f>IF(284&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 284 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="286">
       <c r="P286" s="2">
-        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 285 - 1), NA())</f>
+        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 285 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q286">
-        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 285 - 1), NA())</f>
+        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 285 - 1), NA())</f>
         <v/>
       </c>
       <c r="R286">
-        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 285 - 1), NA())</f>
+        <f>IF(285&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 285 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="287">
       <c r="P287" s="2">
-        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 286 - 1), NA())</f>
+        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 286 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q287">
-        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 286 - 1), NA())</f>
+        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 286 - 1), NA())</f>
         <v/>
       </c>
       <c r="R287">
-        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 286 - 1), NA())</f>
+        <f>IF(286&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 286 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="288">
       <c r="P288" s="2">
-        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 287 - 1), NA())</f>
+        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 287 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q288">
-        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 287 - 1), NA())</f>
+        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 287 - 1), NA())</f>
         <v/>
       </c>
       <c r="R288">
-        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 287 - 1), NA())</f>
+        <f>IF(287&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 287 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="289">
       <c r="P289" s="2">
-        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 288 - 1), NA())</f>
+        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 288 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q289">
-        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 288 - 1), NA())</f>
+        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 288 - 1), NA())</f>
         <v/>
       </c>
       <c r="R289">
-        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 288 - 1), NA())</f>
+        <f>IF(288&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 288 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="290">
       <c r="P290" s="2">
-        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 289 - 1), NA())</f>
+        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 289 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q290">
-        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 289 - 1), NA())</f>
+        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 289 - 1), NA())</f>
         <v/>
       </c>
       <c r="R290">
-        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 289 - 1), NA())</f>
+        <f>IF(289&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 289 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="291">
       <c r="P291" s="2">
-        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 290 - 1), NA())</f>
+        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 290 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q291">
-        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 290 - 1), NA())</f>
+        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 290 - 1), NA())</f>
         <v/>
       </c>
       <c r="R291">
-        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 290 - 1), NA())</f>
+        <f>IF(290&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 290 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="292">
       <c r="P292" s="2">
-        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 291 - 1), NA())</f>
+        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 291 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q292">
-        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 291 - 1), NA())</f>
+        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 291 - 1), NA())</f>
         <v/>
       </c>
       <c r="R292">
-        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 291 - 1), NA())</f>
+        <f>IF(291&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 291 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="293">
       <c r="P293" s="2">
-        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 292 - 1), NA())</f>
+        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 292 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q293">
-        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 292 - 1), NA())</f>
+        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 292 - 1), NA())</f>
         <v/>
       </c>
       <c r="R293">
-        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 292 - 1), NA())</f>
+        <f>IF(292&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 292 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="294">
       <c r="P294" s="2">
-        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 293 - 1), NA())</f>
+        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 293 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q294">
-        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 293 - 1), NA())</f>
+        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 293 - 1), NA())</f>
         <v/>
       </c>
       <c r="R294">
-        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 293 - 1), NA())</f>
+        <f>IF(293&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 293 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="295">
       <c r="P295" s="2">
-        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 294 - 1), NA())</f>
+        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 294 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q295">
-        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 294 - 1), NA())</f>
+        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 294 - 1), NA())</f>
         <v/>
       </c>
       <c r="R295">
-        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 294 - 1), NA())</f>
+        <f>IF(294&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 294 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="296">
       <c r="P296" s="2">
-        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 295 - 1), NA())</f>
+        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 295 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q296">
-        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 295 - 1), NA())</f>
+        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 295 - 1), NA())</f>
         <v/>
       </c>
       <c r="R296">
-        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 295 - 1), NA())</f>
+        <f>IF(295&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 295 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="297">
       <c r="P297" s="2">
-        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 296 - 1), NA())</f>
+        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 296 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q297">
-        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 296 - 1), NA())</f>
+        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 296 - 1), NA())</f>
         <v/>
       </c>
       <c r="R297">
-        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 296 - 1), NA())</f>
+        <f>IF(296&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 296 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="298">
       <c r="P298" s="2">
-        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 297 - 1), NA())</f>
+        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 297 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q298">
-        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 297 - 1), NA())</f>
+        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 297 - 1), NA())</f>
         <v/>
       </c>
       <c r="R298">
-        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 297 - 1), NA())</f>
+        <f>IF(297&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 297 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="299">
       <c r="P299" s="2">
-        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 298 - 1), NA())</f>
+        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 298 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q299">
-        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 298 - 1), NA())</f>
+        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 298 - 1), NA())</f>
         <v/>
       </c>
       <c r="R299">
-        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 298 - 1), NA())</f>
+        <f>IF(298&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 298 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="300">
       <c r="P300" s="2">
-        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 299 - 1), NA())</f>
+        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 299 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q300">
-        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 299 - 1), NA())</f>
+        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 299 - 1), NA())</f>
         <v/>
       </c>
       <c r="R300">
-        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 299 - 1), NA())</f>
+        <f>IF(299&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 299 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="301">
       <c r="P301" s="2">
-        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 300 - 1), NA())</f>
+        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 300 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q301">
-        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 300 - 1), NA())</f>
+        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 300 - 1), NA())</f>
         <v/>
       </c>
       <c r="R301">
-        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 300 - 1), NA())</f>
+        <f>IF(300&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 300 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="302">
       <c r="P302" s="2">
-        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 301 - 1), NA())</f>
+        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 301 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q302">
-        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 301 - 1), NA())</f>
+        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 301 - 1), NA())</f>
         <v/>
       </c>
       <c r="R302">
-        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 301 - 1), NA())</f>
+        <f>IF(301&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 301 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="303">
       <c r="P303" s="2">
-        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 302 - 1), NA())</f>
+        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 302 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q303">
-        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 302 - 1), NA())</f>
+        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 302 - 1), NA())</f>
         <v/>
       </c>
       <c r="R303">
-        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 302 - 1), NA())</f>
+        <f>IF(302&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 302 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="304">
       <c r="P304" s="2">
-        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 303 - 1), NA())</f>
+        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 303 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q304">
-        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 303 - 1), NA())</f>
+        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 303 - 1), NA())</f>
         <v/>
       </c>
       <c r="R304">
-        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 303 - 1), NA())</f>
+        <f>IF(303&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 303 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="305">
       <c r="P305" s="2">
-        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 304 - 1), NA())</f>
+        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 304 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q305">
-        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 304 - 1), NA())</f>
+        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 304 - 1), NA())</f>
         <v/>
       </c>
       <c r="R305">
-        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 304 - 1), NA())</f>
+        <f>IF(304&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 304 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="306">
       <c r="P306" s="2">
-        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 305 - 1), NA())</f>
+        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 305 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q306">
-        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 305 - 1), NA())</f>
+        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 305 - 1), NA())</f>
         <v/>
       </c>
       <c r="R306">
-        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 305 - 1), NA())</f>
+        <f>IF(305&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 305 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="307">
       <c r="P307" s="2">
-        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 306 - 1), NA())</f>
+        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 306 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q307">
-        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 306 - 1), NA())</f>
+        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 306 - 1), NA())</f>
         <v/>
       </c>
       <c r="R307">
-        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 306 - 1), NA())</f>
+        <f>IF(306&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 306 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="308">
       <c r="P308" s="2">
-        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 307 - 1), NA())</f>
+        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 307 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q308">
-        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 307 - 1), NA())</f>
+        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 307 - 1), NA())</f>
         <v/>
       </c>
       <c r="R308">
-        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 307 - 1), NA())</f>
+        <f>IF(307&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 307 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="309">
       <c r="P309" s="2">
-        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 308 - 1), NA())</f>
+        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 308 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q309">
-        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 308 - 1), NA())</f>
+        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 308 - 1), NA())</f>
         <v/>
       </c>
       <c r="R309">
-        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 308 - 1), NA())</f>
+        <f>IF(308&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 308 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="310">
       <c r="P310" s="2">
-        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 309 - 1), NA())</f>
+        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 309 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q310">
-        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 309 - 1), NA())</f>
+        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 309 - 1), NA())</f>
         <v/>
       </c>
       <c r="R310">
-        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 309 - 1), NA())</f>
+        <f>IF(309&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 309 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="311">
       <c r="P311" s="2">
-        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 310 - 1), NA())</f>
+        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 310 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q311">
-        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 310 - 1), NA())</f>
+        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 310 - 1), NA())</f>
         <v/>
       </c>
       <c r="R311">
-        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 310 - 1), NA())</f>
+        <f>IF(310&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 310 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="312">
       <c r="P312" s="2">
-        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 311 - 1), NA())</f>
+        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 311 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q312">
-        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 311 - 1), NA())</f>
+        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 311 - 1), NA())</f>
         <v/>
       </c>
       <c r="R312">
-        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 311 - 1), NA())</f>
+        <f>IF(311&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 311 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="313">
       <c r="P313" s="2">
-        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 312 - 1), NA())</f>
+        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 312 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q313">
-        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 312 - 1), NA())</f>
+        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 312 - 1), NA())</f>
         <v/>
       </c>
       <c r="R313">
-        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 312 - 1), NA())</f>
+        <f>IF(312&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 312 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="314">
       <c r="P314" s="2">
-        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 313 - 1), NA())</f>
+        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 313 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q314">
-        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 313 - 1), NA())</f>
+        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 313 - 1), NA())</f>
         <v/>
       </c>
       <c r="R314">
-        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 313 - 1), NA())</f>
+        <f>IF(313&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 313 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="315">
       <c r="P315" s="2">
-        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 314 - 1), NA())</f>
+        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 314 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q315">
-        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 314 - 1), NA())</f>
+        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 314 - 1), NA())</f>
         <v/>
       </c>
       <c r="R315">
-        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 314 - 1), NA())</f>
+        <f>IF(314&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 314 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="316">
       <c r="P316" s="2">
-        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 315 - 1), NA())</f>
+        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 315 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q316">
-        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 315 - 1), NA())</f>
+        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 315 - 1), NA())</f>
         <v/>
       </c>
       <c r="R316">
-        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 315 - 1), NA())</f>
+        <f>IF(315&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 315 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="317">
       <c r="P317" s="2">
-        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 316 - 1), NA())</f>
+        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 316 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q317">
-        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 316 - 1), NA())</f>
+        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 316 - 1), NA())</f>
         <v/>
       </c>
       <c r="R317">
-        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 316 - 1), NA())</f>
+        <f>IF(316&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 316 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="318">
       <c r="P318" s="2">
-        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 317 - 1), NA())</f>
+        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 317 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q318">
-        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 317 - 1), NA())</f>
+        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 317 - 1), NA())</f>
         <v/>
       </c>
       <c r="R318">
-        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 317 - 1), NA())</f>
+        <f>IF(317&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 317 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="319">
       <c r="P319" s="2">
-        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 318 - 1), NA())</f>
+        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 318 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q319">
-        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 318 - 1), NA())</f>
+        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 318 - 1), NA())</f>
         <v/>
       </c>
       <c r="R319">
-        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 318 - 1), NA())</f>
+        <f>IF(318&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 318 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="320">
       <c r="P320" s="2">
-        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 319 - 1), NA())</f>
+        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 319 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q320">
-        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 319 - 1), NA())</f>
+        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 319 - 1), NA())</f>
         <v/>
       </c>
       <c r="R320">
-        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 319 - 1), NA())</f>
+        <f>IF(319&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 319 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="321">
       <c r="P321" s="2">
-        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 320 - 1), NA())</f>
+        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 320 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q321">
-        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 320 - 1), NA())</f>
+        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 320 - 1), NA())</f>
         <v/>
       </c>
       <c r="R321">
-        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 320 - 1), NA())</f>
+        <f>IF(320&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 320 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="322">
       <c r="P322" s="2">
-        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 321 - 1), NA())</f>
+        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 321 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q322">
-        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 321 - 1), NA())</f>
+        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 321 - 1), NA())</f>
         <v/>
       </c>
       <c r="R322">
-        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 321 - 1), NA())</f>
+        <f>IF(321&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 321 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="323">
       <c r="P323" s="2">
-        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 322 - 1), NA())</f>
+        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 322 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q323">
-        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 322 - 1), NA())</f>
+        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 322 - 1), NA())</f>
         <v/>
       </c>
       <c r="R323">
-        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 322 - 1), NA())</f>
+        <f>IF(322&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 322 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="324">
       <c r="P324" s="2">
-        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 323 - 1), NA())</f>
+        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 323 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q324">
-        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 323 - 1), NA())</f>
+        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 323 - 1), NA())</f>
         <v/>
       </c>
       <c r="R324">
-        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 323 - 1), NA())</f>
+        <f>IF(323&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 323 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="325">
       <c r="P325" s="2">
-        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 324 - 1), NA())</f>
+        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 324 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q325">
-        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 324 - 1), NA())</f>
+        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 324 - 1), NA())</f>
         <v/>
       </c>
       <c r="R325">
-        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 324 - 1), NA())</f>
+        <f>IF(324&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 324 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="326">
       <c r="P326" s="2">
-        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 325 - 1), NA())</f>
+        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 325 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q326">
-        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 325 - 1), NA())</f>
+        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 325 - 1), NA())</f>
         <v/>
       </c>
       <c r="R326">
-        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 325 - 1), NA())</f>
+        <f>IF(325&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 325 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="327">
       <c r="P327" s="2">
-        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 326 - 1), NA())</f>
+        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 326 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q327">
-        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 326 - 1), NA())</f>
+        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 326 - 1), NA())</f>
         <v/>
       </c>
       <c r="R327">
-        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 326 - 1), NA())</f>
+        <f>IF(326&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 326 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="328">
       <c r="P328" s="2">
-        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 327 - 1), NA())</f>
+        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 327 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q328">
-        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 327 - 1), NA())</f>
+        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 327 - 1), NA())</f>
         <v/>
       </c>
       <c r="R328">
-        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 327 - 1), NA())</f>
+        <f>IF(327&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 327 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="329">
       <c r="P329" s="2">
-        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 328 - 1), NA())</f>
+        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 328 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q329">
-        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 328 - 1), NA())</f>
+        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 328 - 1), NA())</f>
         <v/>
       </c>
       <c r="R329">
-        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 328 - 1), NA())</f>
+        <f>IF(328&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 328 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="330">
       <c r="P330" s="2">
-        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 329 - 1), NA())</f>
+        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 329 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q330">
-        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 329 - 1), NA())</f>
+        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 329 - 1), NA())</f>
         <v/>
       </c>
       <c r="R330">
-        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 329 - 1), NA())</f>
+        <f>IF(329&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 329 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="331">
       <c r="P331" s="2">
-        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 330 - 1), NA())</f>
+        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 330 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q331">
-        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 330 - 1), NA())</f>
+        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 330 - 1), NA())</f>
         <v/>
       </c>
       <c r="R331">
-        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 330 - 1), NA())</f>
+        <f>IF(330&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 330 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="332">
       <c r="P332" s="2">
-        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 331 - 1), NA())</f>
+        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 331 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q332">
-        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 331 - 1), NA())</f>
+        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 331 - 1), NA())</f>
         <v/>
       </c>
       <c r="R332">
-        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 331 - 1), NA())</f>
+        <f>IF(331&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 331 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="333">
       <c r="P333" s="2">
-        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 332 - 1), NA())</f>
+        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 332 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q333">
-        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 332 - 1), NA())</f>
+        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 332 - 1), NA())</f>
         <v/>
       </c>
       <c r="R333">
-        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 332 - 1), NA())</f>
+        <f>IF(332&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 332 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="334">
       <c r="P334" s="2">
-        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 333 - 1), NA())</f>
+        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 333 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q334">
-        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 333 - 1), NA())</f>
+        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 333 - 1), NA())</f>
         <v/>
       </c>
       <c r="R334">
-        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 333 - 1), NA())</f>
+        <f>IF(333&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 333 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="335">
       <c r="P335" s="2">
-        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 334 - 1), NA())</f>
+        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 334 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q335">
-        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 334 - 1), NA())</f>
+        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 334 - 1), NA())</f>
         <v/>
       </c>
       <c r="R335">
-        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 334 - 1), NA())</f>
+        <f>IF(334&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 334 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="336">
       <c r="P336" s="2">
-        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 335 - 1), NA())</f>
+        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 335 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q336">
-        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 335 - 1), NA())</f>
+        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 335 - 1), NA())</f>
         <v/>
       </c>
       <c r="R336">
-        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 335 - 1), NA())</f>
+        <f>IF(335&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 335 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="337">
       <c r="P337" s="2">
-        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 336 - 1), NA())</f>
+        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 336 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q337">
-        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 336 - 1), NA())</f>
+        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 336 - 1), NA())</f>
         <v/>
       </c>
       <c r="R337">
-        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 336 - 1), NA())</f>
+        <f>IF(336&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 336 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="338">
       <c r="P338" s="2">
-        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 337 - 1), NA())</f>
+        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 337 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q338">
-        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 337 - 1), NA())</f>
+        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 337 - 1), NA())</f>
         <v/>
       </c>
       <c r="R338">
-        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 337 - 1), NA())</f>
+        <f>IF(337&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 337 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="339">
       <c r="P339" s="2">
-        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 338 - 1), NA())</f>
+        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 338 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q339">
-        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 338 - 1), NA())</f>
+        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 338 - 1), NA())</f>
         <v/>
       </c>
       <c r="R339">
-        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 338 - 1), NA())</f>
+        <f>IF(338&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 338 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="340">
       <c r="P340" s="2">
-        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 339 - 1), NA())</f>
+        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 339 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q340">
-        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 339 - 1), NA())</f>
+        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 339 - 1), NA())</f>
         <v/>
       </c>
       <c r="R340">
-        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 339 - 1), NA())</f>
+        <f>IF(339&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 339 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="341">
       <c r="P341" s="2">
-        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 340 - 1), NA())</f>
+        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 340 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q341">
-        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 340 - 1), NA())</f>
+        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 340 - 1), NA())</f>
         <v/>
       </c>
       <c r="R341">
-        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 340 - 1), NA())</f>
+        <f>IF(340&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 340 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="342">
       <c r="P342" s="2">
-        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 341 - 1), NA())</f>
+        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 341 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q342">
-        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 341 - 1), NA())</f>
+        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 341 - 1), NA())</f>
         <v/>
       </c>
       <c r="R342">
-        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 341 - 1), NA())</f>
+        <f>IF(341&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 341 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="343">
       <c r="P343" s="2">
-        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 342 - 1), NA())</f>
+        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 342 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q343">
-        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 342 - 1), NA())</f>
+        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 342 - 1), NA())</f>
         <v/>
       </c>
       <c r="R343">
-        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 342 - 1), NA())</f>
+        <f>IF(342&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 342 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="344">
       <c r="P344" s="2">
-        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 343 - 1), NA())</f>
+        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 343 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q344">
-        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 343 - 1), NA())</f>
+        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 343 - 1), NA())</f>
         <v/>
       </c>
       <c r="R344">
-        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 343 - 1), NA())</f>
+        <f>IF(343&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 343 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="345">
       <c r="P345" s="2">
-        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 344 - 1), NA())</f>
+        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 344 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q345">
-        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 344 - 1), NA())</f>
+        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 344 - 1), NA())</f>
         <v/>
       </c>
       <c r="R345">
-        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 344 - 1), NA())</f>
+        <f>IF(344&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 344 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="346">
       <c r="P346" s="2">
-        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 345 - 1), NA())</f>
+        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 345 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q346">
-        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 345 - 1), NA())</f>
+        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 345 - 1), NA())</f>
         <v/>
       </c>
       <c r="R346">
-        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 345 - 1), NA())</f>
+        <f>IF(345&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 345 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="347">
       <c r="P347" s="2">
-        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 346 - 1), NA())</f>
+        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 346 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q347">
-        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 346 - 1), NA())</f>
+        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 346 - 1), NA())</f>
         <v/>
       </c>
       <c r="R347">
-        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 346 - 1), NA())</f>
+        <f>IF(346&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 346 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="348">
       <c r="P348" s="2">
-        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 347 - 1), NA())</f>
+        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 347 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q348">
-        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 347 - 1), NA())</f>
+        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 347 - 1), NA())</f>
         <v/>
       </c>
       <c r="R348">
-        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 347 - 1), NA())</f>
+        <f>IF(347&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 347 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="349">
       <c r="P349" s="2">
-        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 348 - 1), NA())</f>
+        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 348 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q349">
-        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 348 - 1), NA())</f>
+        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 348 - 1), NA())</f>
         <v/>
       </c>
       <c r="R349">
-        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 348 - 1), NA())</f>
+        <f>IF(348&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 348 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="350">
       <c r="P350" s="2">
-        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 349 - 1), NA())</f>
+        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 349 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q350">
-        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 349 - 1), NA())</f>
+        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 349 - 1), NA())</f>
         <v/>
       </c>
       <c r="R350">
-        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 349 - 1), NA())</f>
+        <f>IF(349&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 349 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="351">
       <c r="P351" s="2">
-        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 350 - 1), NA())</f>
+        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 350 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q351">
-        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 350 - 1), NA())</f>
+        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 350 - 1), NA())</f>
         <v/>
       </c>
       <c r="R351">
-        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 350 - 1), NA())</f>
+        <f>IF(350&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 350 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="352">
       <c r="P352" s="2">
-        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 351 - 1), NA())</f>
+        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 351 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q352">
-        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 351 - 1), NA())</f>
+        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 351 - 1), NA())</f>
         <v/>
       </c>
       <c r="R352">
-        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 351 - 1), NA())</f>
+        <f>IF(351&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 351 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="353">
       <c r="P353" s="2">
-        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 352 - 1), NA())</f>
+        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 352 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q353">
-        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 352 - 1), NA())</f>
+        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 352 - 1), NA())</f>
         <v/>
       </c>
       <c r="R353">
-        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 352 - 1), NA())</f>
+        <f>IF(352&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 352 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="354">
       <c r="P354" s="2">
-        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 353 - 1), NA())</f>
+        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 353 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q354">
-        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 353 - 1), NA())</f>
+        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 353 - 1), NA())</f>
         <v/>
       </c>
       <c r="R354">
-        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 353 - 1), NA())</f>
+        <f>IF(353&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 353 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="355">
       <c r="P355" s="2">
-        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 354 - 1), NA())</f>
+        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 354 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q355">
-        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 354 - 1), NA())</f>
+        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 354 - 1), NA())</f>
         <v/>
       </c>
       <c r="R355">
-        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 354 - 1), NA())</f>
+        <f>IF(354&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 354 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="356">
       <c r="P356" s="2">
-        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 355 - 1), NA())</f>
+        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 355 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q356">
-        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 355 - 1), NA())</f>
+        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 355 - 1), NA())</f>
         <v/>
       </c>
       <c r="R356">
-        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 355 - 1), NA())</f>
+        <f>IF(355&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 355 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="357">
       <c r="P357" s="2">
-        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 356 - 1), NA())</f>
+        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 356 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q357">
-        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 356 - 1), NA())</f>
+        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 356 - 1), NA())</f>
         <v/>
       </c>
       <c r="R357">
-        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 356 - 1), NA())</f>
+        <f>IF(356&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 356 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="358">
       <c r="P358" s="2">
-        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 357 - 1), NA())</f>
+        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 357 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q358">
-        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 357 - 1), NA())</f>
+        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 357 - 1), NA())</f>
         <v/>
       </c>
       <c r="R358">
-        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 357 - 1), NA())</f>
+        <f>IF(357&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 357 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="359">
       <c r="P359" s="2">
-        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 358 - 1), NA())</f>
+        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 358 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q359">
-        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 358 - 1), NA())</f>
+        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 358 - 1), NA())</f>
         <v/>
       </c>
       <c r="R359">
-        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 358 - 1), NA())</f>
+        <f>IF(358&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 358 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="360">
       <c r="P360" s="2">
-        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 359 - 1), NA())</f>
+        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 359 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q360">
-        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 359 - 1), NA())</f>
+        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 359 - 1), NA())</f>
         <v/>
       </c>
       <c r="R360">
-        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 359 - 1), NA())</f>
+        <f>IF(359&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 359 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="361">
       <c r="P361" s="2">
-        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 360 - 1), NA())</f>
+        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 360 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q361">
-        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 360 - 1), NA())</f>
+        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 360 - 1), NA())</f>
         <v/>
       </c>
       <c r="R361">
-        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 360 - 1), NA())</f>
+        <f>IF(360&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 360 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="362">
       <c r="P362" s="2">
-        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 361 - 1), NA())</f>
+        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 361 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q362">
-        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 361 - 1), NA())</f>
+        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 361 - 1), NA())</f>
         <v/>
       </c>
       <c r="R362">
-        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 361 - 1), NA())</f>
+        <f>IF(361&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 361 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="363">
       <c r="P363" s="2">
-        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 362 - 1), NA())</f>
+        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 362 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q363">
-        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 362 - 1), NA())</f>
+        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 362 - 1), NA())</f>
         <v/>
       </c>
       <c r="R363">
-        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 362 - 1), NA())</f>
+        <f>IF(362&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 362 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="364">
       <c r="P364" s="2">
-        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 363 - 1), NA())</f>
+        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 363 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q364">
-        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 363 - 1), NA())</f>
+        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 363 - 1), NA())</f>
         <v/>
       </c>
       <c r="R364">
-        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 363 - 1), NA())</f>
+        <f>IF(363&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 363 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="365">
       <c r="P365" s="2">
-        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 364 - 1), NA())</f>
+        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 364 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q365">
-        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 364 - 1), NA())</f>
+        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 364 - 1), NA())</f>
         <v/>
       </c>
       <c r="R365">
-        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 364 - 1), NA())</f>
+        <f>IF(364&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 364 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="366">
       <c r="P366" s="2">
-        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 365 - 1), NA())</f>
+        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 365 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q366">
-        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 365 - 1), NA())</f>
+        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 365 - 1), NA())</f>
         <v/>
       </c>
       <c r="R366">
-        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 365 - 1), NA())</f>
+        <f>IF(365&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 365 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="367">
       <c r="P367" s="2">
-        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 366 - 1), NA())</f>
+        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 366 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q367">
-        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 366 - 1), NA())</f>
+        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 366 - 1), NA())</f>
         <v/>
       </c>
       <c r="R367">
-        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 366 - 1), NA())</f>
+        <f>IF(366&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 366 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="368">
       <c r="P368" s="2">
-        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 367 - 1), NA())</f>
+        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 367 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q368">
-        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 367 - 1), NA())</f>
+        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 367 - 1), NA())</f>
         <v/>
       </c>
       <c r="R368">
-        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 367 - 1), NA())</f>
+        <f>IF(367&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 367 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="369">
       <c r="P369" s="2">
-        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 368 - 1), NA())</f>
+        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 368 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q369">
-        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 368 - 1), NA())</f>
+        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 368 - 1), NA())</f>
         <v/>
       </c>
       <c r="R369">
-        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 368 - 1), NA())</f>
+        <f>IF(368&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 368 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="370">
       <c r="P370" s="2">
-        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 369 - 1), NA())</f>
+        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 369 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q370">
-        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 369 - 1), NA())</f>
+        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 369 - 1), NA())</f>
         <v/>
       </c>
       <c r="R370">
-        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 369 - 1), NA())</f>
+        <f>IF(369&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 369 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="371">
       <c r="P371" s="2">
-        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 370 - 1), NA())</f>
+        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 370 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q371">
-        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 370 - 1), NA())</f>
+        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 370 - 1), NA())</f>
         <v/>
       </c>
       <c r="R371">
-        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 370 - 1), NA())</f>
+        <f>IF(370&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 370 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="372">
       <c r="P372" s="2">
-        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 371 - 1), NA())</f>
+        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 371 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q372">
-        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 371 - 1), NA())</f>
+        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 371 - 1), NA())</f>
         <v/>
       </c>
       <c r="R372">
-        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 371 - 1), NA())</f>
+        <f>IF(371&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 371 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="373">
       <c r="P373" s="2">
-        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 372 - 1), NA())</f>
+        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 372 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q373">
-        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 372 - 1), NA())</f>
+        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 372 - 1), NA())</f>
         <v/>
       </c>
       <c r="R373">
-        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 372 - 1), NA())</f>
+        <f>IF(372&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 372 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="374">
       <c r="P374" s="2">
-        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 373 - 1), NA())</f>
+        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 373 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q374">
-        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 373 - 1), NA())</f>
+        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 373 - 1), NA())</f>
         <v/>
       </c>
       <c r="R374">
-        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 373 - 1), NA())</f>
+        <f>IF(373&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 373 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="375">
       <c r="P375" s="2">
-        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 374 - 1), NA())</f>
+        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 374 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q375">
-        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 374 - 1), NA())</f>
+        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 374 - 1), NA())</f>
         <v/>
       </c>
       <c r="R375">
-        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 374 - 1), NA())</f>
+        <f>IF(374&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 374 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="376">
       <c r="P376" s="2">
-        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 375 - 1), NA())</f>
+        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 375 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q376">
-        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 375 - 1), NA())</f>
+        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 375 - 1), NA())</f>
         <v/>
       </c>
       <c r="R376">
-        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 375 - 1), NA())</f>
+        <f>IF(375&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 375 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="377">
       <c r="P377" s="2">
-        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 376 - 1), NA())</f>
+        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 376 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q377">
-        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 376 - 1), NA())</f>
+        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 376 - 1), NA())</f>
         <v/>
       </c>
       <c r="R377">
-        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 376 - 1), NA())</f>
+        <f>IF(376&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 376 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="378">
       <c r="P378" s="2">
-        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 377 - 1), NA())</f>
+        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 377 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q378">
-        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 377 - 1), NA())</f>
+        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 377 - 1), NA())</f>
         <v/>
       </c>
       <c r="R378">
-        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 377 - 1), NA())</f>
+        <f>IF(377&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 377 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="379">
       <c r="P379" s="2">
-        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 378 - 1), NA())</f>
+        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 378 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q379">
-        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 378 - 1), NA())</f>
+        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 378 - 1), NA())</f>
         <v/>
       </c>
       <c r="R379">
-        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 378 - 1), NA())</f>
+        <f>IF(378&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 378 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="380">
       <c r="P380" s="2">
-        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 379 - 1), NA())</f>
+        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 379 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q380">
-        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 379 - 1), NA())</f>
+        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 379 - 1), NA())</f>
         <v/>
       </c>
       <c r="R380">
-        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 379 - 1), NA())</f>
+        <f>IF(379&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 379 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="381">
       <c r="P381" s="2">
-        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 380 - 1), NA())</f>
+        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 380 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q381">
-        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 380 - 1), NA())</f>
+        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 380 - 1), NA())</f>
         <v/>
       </c>
       <c r="R381">
-        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 380 - 1), NA())</f>
+        <f>IF(380&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 380 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="382">
       <c r="P382" s="2">
-        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 381 - 1), NA())</f>
+        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 381 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q382">
-        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 381 - 1), NA())</f>
+        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 381 - 1), NA())</f>
         <v/>
       </c>
       <c r="R382">
-        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 381 - 1), NA())</f>
+        <f>IF(381&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 381 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="383">
       <c r="P383" s="2">
-        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 382 - 1), NA())</f>
+        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 382 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q383">
-        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 382 - 1), NA())</f>
+        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 382 - 1), NA())</f>
         <v/>
       </c>
       <c r="R383">
-        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 382 - 1), NA())</f>
+        <f>IF(382&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 382 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="384">
       <c r="P384" s="2">
-        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 383 - 1), NA())</f>
+        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 383 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q384">
-        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 383 - 1), NA())</f>
+        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 383 - 1), NA())</f>
         <v/>
       </c>
       <c r="R384">
-        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 383 - 1), NA())</f>
+        <f>IF(383&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 383 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="385">
       <c r="P385" s="2">
-        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 384 - 1), NA())</f>
+        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 384 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q385">
-        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 384 - 1), NA())</f>
+        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 384 - 1), NA())</f>
         <v/>
       </c>
       <c r="R385">
-        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 384 - 1), NA())</f>
+        <f>IF(384&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 384 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="386">
       <c r="P386" s="2">
-        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 385 - 1), NA())</f>
+        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 385 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q386">
-        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 385 - 1), NA())</f>
+        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 385 - 1), NA())</f>
         <v/>
       </c>
       <c r="R386">
-        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 385 - 1), NA())</f>
+        <f>IF(385&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 385 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="387">
       <c r="P387" s="2">
-        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 386 - 1), NA())</f>
+        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 386 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q387">
-        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 386 - 1), NA())</f>
+        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 386 - 1), NA())</f>
         <v/>
       </c>
       <c r="R387">
-        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 386 - 1), NA())</f>
+        <f>IF(386&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 386 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="388">
       <c r="P388" s="2">
-        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 387 - 1), NA())</f>
+        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 387 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q388">
-        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 387 - 1), NA())</f>
+        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 387 - 1), NA())</f>
         <v/>
       </c>
       <c r="R388">
-        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 387 - 1), NA())</f>
+        <f>IF(387&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 387 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="389">
       <c r="P389" s="2">
-        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 388 - 1), NA())</f>
+        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 388 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q389">
-        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 388 - 1), NA())</f>
+        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 388 - 1), NA())</f>
         <v/>
       </c>
       <c r="R389">
-        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 388 - 1), NA())</f>
+        <f>IF(388&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 388 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="390">
       <c r="P390" s="2">
-        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 389 - 1), NA())</f>
+        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 389 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q390">
-        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 389 - 1), NA())</f>
+        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 389 - 1), NA())</f>
         <v/>
       </c>
       <c r="R390">
-        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 389 - 1), NA())</f>
+        <f>IF(389&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 389 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="391">
       <c r="P391" s="2">
-        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 390 - 1), NA())</f>
+        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 390 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q391">
-        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 390 - 1), NA())</f>
+        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 390 - 1), NA())</f>
         <v/>
       </c>
       <c r="R391">
-        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 390 - 1), NA())</f>
+        <f>IF(390&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 390 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="392">
       <c r="P392" s="2">
-        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 391 - 1), NA())</f>
+        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 391 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q392">
-        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 391 - 1), NA())</f>
+        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 391 - 1), NA())</f>
         <v/>
       </c>
       <c r="R392">
-        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 391 - 1), NA())</f>
+        <f>IF(391&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 391 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="393">
       <c r="P393" s="2">
-        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 392 - 1), NA())</f>
+        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 392 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q393">
-        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 392 - 1), NA())</f>
+        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 392 - 1), NA())</f>
         <v/>
       </c>
       <c r="R393">
-        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 392 - 1), NA())</f>
+        <f>IF(392&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 392 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="394">
       <c r="P394" s="2">
-        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 393 - 1), NA())</f>
+        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 393 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q394">
-        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 393 - 1), NA())</f>
+        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 393 - 1), NA())</f>
         <v/>
       </c>
       <c r="R394">
-        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 393 - 1), NA())</f>
+        <f>IF(393&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 393 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="395">
       <c r="P395" s="2">
-        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 394 - 1), NA())</f>
+        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 394 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q395">
-        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 394 - 1), NA())</f>
+        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 394 - 1), NA())</f>
         <v/>
       </c>
       <c r="R395">
-        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 394 - 1), NA())</f>
+        <f>IF(394&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 394 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="396">
       <c r="P396" s="2">
-        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 395 - 1), NA())</f>
+        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 395 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q396">
-        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 395 - 1), NA())</f>
+        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 395 - 1), NA())</f>
         <v/>
       </c>
       <c r="R396">
-        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 395 - 1), NA())</f>
+        <f>IF(395&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 395 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="397">
       <c r="P397" s="2">
-        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 396 - 1), NA())</f>
+        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 396 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q397">
-        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 396 - 1), NA())</f>
+        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 396 - 1), NA())</f>
         <v/>
       </c>
       <c r="R397">
-        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 396 - 1), NA())</f>
+        <f>IF(396&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 396 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="398">
       <c r="P398" s="2">
-        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 397 - 1), NA())</f>
+        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 397 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q398">
-        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 397 - 1), NA())</f>
+        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 397 - 1), NA())</f>
         <v/>
       </c>
       <c r="R398">
-        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 397 - 1), NA())</f>
+        <f>IF(397&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 397 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="399">
       <c r="P399" s="2">
-        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 398 - 1), NA())</f>
+        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 398 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q399">
-        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 398 - 1), NA())</f>
+        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 398 - 1), NA())</f>
         <v/>
       </c>
       <c r="R399">
-        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 398 - 1), NA())</f>
+        <f>IF(398&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 398 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="400">
       <c r="P400" s="2">
-        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 399 - 1), NA())</f>
+        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 399 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q400">
-        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 399 - 1), NA())</f>
+        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 399 - 1), NA())</f>
         <v/>
       </c>
       <c r="R400">
-        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 399 - 1), NA())</f>
+        <f>IF(399&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 399 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="401">
       <c r="P401" s="2">
-        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 400 - 1), NA())</f>
+        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 400 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q401">
-        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 400 - 1), NA())</f>
+        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 400 - 1), NA())</f>
         <v/>
       </c>
       <c r="R401">
-        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 400 - 1), NA())</f>
+        <f>IF(400&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 400 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="402">
       <c r="P402" s="2">
-        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 401 - 1), NA())</f>
+        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 401 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q402">
-        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 401 - 1), NA())</f>
+        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 401 - 1), NA())</f>
         <v/>
       </c>
       <c r="R402">
-        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 401 - 1), NA())</f>
+        <f>IF(401&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 401 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="403">
       <c r="P403" s="2">
-        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 402 - 1), NA())</f>
+        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 402 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q403">
-        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 402 - 1), NA())</f>
+        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 402 - 1), NA())</f>
         <v/>
       </c>
       <c r="R403">
-        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 402 - 1), NA())</f>
+        <f>IF(402&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 402 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="404">
       <c r="P404" s="2">
-        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 403 - 1), NA())</f>
+        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 403 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q404">
-        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 403 - 1), NA())</f>
+        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 403 - 1), NA())</f>
         <v/>
       </c>
       <c r="R404">
-        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 403 - 1), NA())</f>
+        <f>IF(403&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 403 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="405">
       <c r="P405" s="2">
-        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 404 - 1), NA())</f>
+        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 404 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q405">
-        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 404 - 1), NA())</f>
+        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 404 - 1), NA())</f>
         <v/>
       </c>
       <c r="R405">
-        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 404 - 1), NA())</f>
+        <f>IF(404&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 404 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="406">
       <c r="P406" s="2">
-        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 405 - 1), NA())</f>
+        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 405 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q406">
-        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 405 - 1), NA())</f>
+        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 405 - 1), NA())</f>
         <v/>
       </c>
       <c r="R406">
-        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 405 - 1), NA())</f>
+        <f>IF(405&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 405 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="407">
       <c r="P407" s="2">
-        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 406 - 1), NA())</f>
+        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 406 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q407">
-        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 406 - 1), NA())</f>
+        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 406 - 1), NA())</f>
         <v/>
       </c>
       <c r="R407">
-        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 406 - 1), NA())</f>
+        <f>IF(406&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 406 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="408">
       <c r="P408" s="2">
-        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 407 - 1), NA())</f>
+        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 407 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q408">
-        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 407 - 1), NA())</f>
+        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 407 - 1), NA())</f>
         <v/>
       </c>
       <c r="R408">
-        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 407 - 1), NA())</f>
+        <f>IF(407&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 407 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="409">
       <c r="P409" s="2">
-        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 408 - 1), NA())</f>
+        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 408 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q409">
-        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 408 - 1), NA())</f>
+        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 408 - 1), NA())</f>
         <v/>
       </c>
       <c r="R409">
-        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 408 - 1), NA())</f>
+        <f>IF(408&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 408 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="410">
       <c r="P410" s="2">
-        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 409 - 1), NA())</f>
+        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 409 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q410">
-        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 409 - 1), NA())</f>
+        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 409 - 1), NA())</f>
         <v/>
       </c>
       <c r="R410">
-        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 409 - 1), NA())</f>
+        <f>IF(409&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 409 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="411">
       <c r="P411" s="2">
-        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 410 - 1), NA())</f>
+        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 410 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q411">
-        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 410 - 1), NA())</f>
+        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 410 - 1), NA())</f>
         <v/>
       </c>
       <c r="R411">
-        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 410 - 1), NA())</f>
+        <f>IF(410&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 410 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="412">
       <c r="P412" s="2">
-        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 411 - 1), NA())</f>
+        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 411 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q412">
-        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 411 - 1), NA())</f>
+        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 411 - 1), NA())</f>
         <v/>
       </c>
       <c r="R412">
-        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 411 - 1), NA())</f>
+        <f>IF(411&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 411 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="413">
       <c r="P413" s="2">
-        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 412 - 1), NA())</f>
+        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 412 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q413">
-        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 412 - 1), NA())</f>
+        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 412 - 1), NA())</f>
         <v/>
       </c>
       <c r="R413">
-        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 412 - 1), NA())</f>
+        <f>IF(412&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 412 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="414">
       <c r="P414" s="2">
-        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 413 - 1), NA())</f>
+        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 413 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q414">
-        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 413 - 1), NA())</f>
+        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 413 - 1), NA())</f>
         <v/>
       </c>
       <c r="R414">
-        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 413 - 1), NA())</f>
+        <f>IF(413&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 413 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="415">
       <c r="P415" s="2">
-        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 414 - 1), NA())</f>
+        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 414 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q415">
-        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 414 - 1), NA())</f>
+        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 414 - 1), NA())</f>
         <v/>
       </c>
       <c r="R415">
-        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 414 - 1), NA())</f>
+        <f>IF(414&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 414 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="416">
       <c r="P416" s="2">
-        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 415 - 1), NA())</f>
+        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 415 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q416">
-        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 415 - 1), NA())</f>
+        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 415 - 1), NA())</f>
         <v/>
       </c>
       <c r="R416">
-        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 415 - 1), NA())</f>
+        <f>IF(415&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 415 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="417">
       <c r="P417" s="2">
-        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 416 - 1), NA())</f>
+        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 416 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q417">
-        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 416 - 1), NA())</f>
+        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 416 - 1), NA())</f>
         <v/>
       </c>
       <c r="R417">
-        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 416 - 1), NA())</f>
+        <f>IF(416&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 416 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="418">
       <c r="P418" s="2">
-        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 417 - 1), NA())</f>
+        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 417 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q418">
-        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 417 - 1), NA())</f>
+        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 417 - 1), NA())</f>
         <v/>
       </c>
       <c r="R418">
-        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 417 - 1), NA())</f>
+        <f>IF(417&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 417 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="419">
       <c r="P419" s="2">
-        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 418 - 1), NA())</f>
+        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 418 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q419">
-        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 418 - 1), NA())</f>
+        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 418 - 1), NA())</f>
         <v/>
       </c>
       <c r="R419">
-        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 418 - 1), NA())</f>
+        <f>IF(418&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 418 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="420">
       <c r="P420" s="2">
-        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 419 - 1), NA())</f>
+        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 419 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q420">
-        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 419 - 1), NA())</f>
+        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 419 - 1), NA())</f>
         <v/>
       </c>
       <c r="R420">
-        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 419 - 1), NA())</f>
+        <f>IF(419&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 419 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="421">
       <c r="P421" s="2">
-        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 420 - 1), NA())</f>
+        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 420 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q421">
-        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 420 - 1), NA())</f>
+        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 420 - 1), NA())</f>
         <v/>
       </c>
       <c r="R421">
-        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 420 - 1), NA())</f>
+        <f>IF(420&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 420 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="422">
       <c r="P422" s="2">
-        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 421 - 1), NA())</f>
+        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 421 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q422">
-        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 421 - 1), NA())</f>
+        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 421 - 1), NA())</f>
         <v/>
       </c>
       <c r="R422">
-        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 421 - 1), NA())</f>
+        <f>IF(421&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 421 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="423">
       <c r="P423" s="2">
-        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 422 - 1), NA())</f>
+        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 422 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q423">
-        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 422 - 1), NA())</f>
+        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 422 - 1), NA())</f>
         <v/>
       </c>
       <c r="R423">
-        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 422 - 1), NA())</f>
+        <f>IF(422&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 422 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="424">
       <c r="P424" s="2">
-        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 423 - 1), NA())</f>
+        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 423 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q424">
-        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 423 - 1), NA())</f>
+        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 423 - 1), NA())</f>
         <v/>
       </c>
       <c r="R424">
-        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 423 - 1), NA())</f>
+        <f>IF(423&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 423 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="425">
       <c r="P425" s="2">
-        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 424 - 1), NA())</f>
+        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 424 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q425">
-        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 424 - 1), NA())</f>
+        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 424 - 1), NA())</f>
         <v/>
       </c>
       <c r="R425">
-        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 424 - 1), NA())</f>
+        <f>IF(424&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 424 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="426">
       <c r="P426" s="2">
-        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 425 - 1), NA())</f>
+        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 425 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q426">
-        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 425 - 1), NA())</f>
+        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 425 - 1), NA())</f>
         <v/>
       </c>
       <c r="R426">
-        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 425 - 1), NA())</f>
+        <f>IF(425&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 425 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="427">
       <c r="P427" s="2">
-        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 426 - 1), NA())</f>
+        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 426 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q427">
-        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 426 - 1), NA())</f>
+        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 426 - 1), NA())</f>
         <v/>
       </c>
       <c r="R427">
-        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 426 - 1), NA())</f>
+        <f>IF(426&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 426 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="428">
       <c r="P428" s="2">
-        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 427 - 1), NA())</f>
+        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 427 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q428">
-        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 427 - 1), NA())</f>
+        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 427 - 1), NA())</f>
         <v/>
       </c>
       <c r="R428">
-        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 427 - 1), NA())</f>
+        <f>IF(427&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 427 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="429">
       <c r="P429" s="2">
-        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 428 - 1), NA())</f>
+        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 428 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q429">
-        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 428 - 1), NA())</f>
+        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 428 - 1), NA())</f>
         <v/>
       </c>
       <c r="R429">
-        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 428 - 1), NA())</f>
+        <f>IF(428&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 428 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="430">
       <c r="P430" s="2">
-        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 429 - 1), NA())</f>
+        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 429 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q430">
-        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 429 - 1), NA())</f>
+        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 429 - 1), NA())</f>
         <v/>
       </c>
       <c r="R430">
-        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 429 - 1), NA())</f>
+        <f>IF(429&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 429 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="431">
       <c r="P431" s="2">
-        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 430 - 1), NA())</f>
+        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 430 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q431">
-        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 430 - 1), NA())</f>
+        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 430 - 1), NA())</f>
         <v/>
       </c>
       <c r="R431">
-        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 430 - 1), NA())</f>
+        <f>IF(430&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 430 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="432">
       <c r="P432" s="2">
-        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 431 - 1), NA())</f>
+        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 431 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q432">
-        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 431 - 1), NA())</f>
+        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 431 - 1), NA())</f>
         <v/>
       </c>
       <c r="R432">
-        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 431 - 1), NA())</f>
+        <f>IF(431&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 431 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="433">
       <c r="P433" s="2">
-        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 432 - 1), NA())</f>
+        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 432 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q433">
-        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 432 - 1), NA())</f>
+        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 432 - 1), NA())</f>
         <v/>
       </c>
       <c r="R433">
-        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 432 - 1), NA())</f>
+        <f>IF(432&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 432 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="434">
       <c r="P434" s="2">
-        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 433 - 1), NA())</f>
+        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 433 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q434">
-        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 433 - 1), NA())</f>
+        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 433 - 1), NA())</f>
         <v/>
       </c>
       <c r="R434">
-        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 433 - 1), NA())</f>
+        <f>IF(433&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 433 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="435">
       <c r="P435" s="2">
-        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 434 - 1), NA())</f>
+        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 434 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q435">
-        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 434 - 1), NA())</f>
+        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 434 - 1), NA())</f>
         <v/>
       </c>
       <c r="R435">
-        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 434 - 1), NA())</f>
+        <f>IF(434&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 434 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="436">
       <c r="P436" s="2">
-        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 435 - 1), NA())</f>
+        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 435 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q436">
-        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 435 - 1), NA())</f>
+        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 435 - 1), NA())</f>
         <v/>
       </c>
       <c r="R436">
-        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 435 - 1), NA())</f>
+        <f>IF(435&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 435 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="437">
       <c r="P437" s="2">
-        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 436 - 1), NA())</f>
+        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 436 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q437">
-        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 436 - 1), NA())</f>
+        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 436 - 1), NA())</f>
         <v/>
       </c>
       <c r="R437">
-        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 436 - 1), NA())</f>
+        <f>IF(436&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 436 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="438">
       <c r="P438" s="2">
-        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 437 - 1), NA())</f>
+        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 437 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q438">
-        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 437 - 1), NA())</f>
+        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 437 - 1), NA())</f>
         <v/>
       </c>
       <c r="R438">
-        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 437 - 1), NA())</f>
+        <f>IF(437&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 437 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="439">
       <c r="P439" s="2">
-        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 438 - 1), NA())</f>
+        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 438 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q439">
-        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 438 - 1), NA())</f>
+        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 438 - 1), NA())</f>
         <v/>
       </c>
       <c r="R439">
-        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 438 - 1), NA())</f>
+        <f>IF(438&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 438 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="440">
       <c r="P440" s="2">
-        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 439 - 1), NA())</f>
+        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 439 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q440">
-        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 439 - 1), NA())</f>
+        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 439 - 1), NA())</f>
         <v/>
       </c>
       <c r="R440">
-        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 439 - 1), NA())</f>
+        <f>IF(439&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 439 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="441">
       <c r="P441" s="2">
-        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 440 - 1), NA())</f>
+        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 440 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q441">
-        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 440 - 1), NA())</f>
+        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 440 - 1), NA())</f>
         <v/>
       </c>
       <c r="R441">
-        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 440 - 1), NA())</f>
+        <f>IF(440&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 440 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="442">
       <c r="P442" s="2">
-        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 441 - 1), NA())</f>
+        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 441 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q442">
-        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 441 - 1), NA())</f>
+        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 441 - 1), NA())</f>
         <v/>
       </c>
       <c r="R442">
-        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 441 - 1), NA())</f>
+        <f>IF(441&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 441 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="443">
       <c r="P443" s="2">
-        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 442 - 1), NA())</f>
+        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 442 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q443">
-        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 442 - 1), NA())</f>
+        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 442 - 1), NA())</f>
         <v/>
       </c>
       <c r="R443">
-        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 442 - 1), NA())</f>
+        <f>IF(442&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 442 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="444">
       <c r="P444" s="2">
-        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 443 - 1), NA())</f>
+        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 443 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q444">
-        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 443 - 1), NA())</f>
+        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 443 - 1), NA())</f>
         <v/>
       </c>
       <c r="R444">
-        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 443 - 1), NA())</f>
+        <f>IF(443&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 443 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="445">
       <c r="P445" s="2">
-        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 444 - 1), NA())</f>
+        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 444 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q445">
-        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 444 - 1), NA())</f>
+        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 444 - 1), NA())</f>
         <v/>
       </c>
       <c r="R445">
-        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 444 - 1), NA())</f>
+        <f>IF(444&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 444 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="446">
       <c r="P446" s="2">
-        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 445 - 1), NA())</f>
+        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 445 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q446">
-        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 445 - 1), NA())</f>
+        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 445 - 1), NA())</f>
         <v/>
       </c>
       <c r="R446">
-        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 445 - 1), NA())</f>
+        <f>IF(445&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 445 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="447">
       <c r="P447" s="2">
-        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 446 - 1), NA())</f>
+        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 446 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q447">
-        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 446 - 1), NA())</f>
+        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 446 - 1), NA())</f>
         <v/>
       </c>
       <c r="R447">
-        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 446 - 1), NA())</f>
+        <f>IF(446&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 446 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="448">
       <c r="P448" s="2">
-        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 447 - 1), NA())</f>
+        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 447 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q448">
-        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 447 - 1), NA())</f>
+        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 447 - 1), NA())</f>
         <v/>
       </c>
       <c r="R448">
-        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 447 - 1), NA())</f>
+        <f>IF(447&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 447 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="449">
       <c r="P449" s="2">
-        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 448 - 1), NA())</f>
+        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 448 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q449">
-        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 448 - 1), NA())</f>
+        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 448 - 1), NA())</f>
         <v/>
       </c>
       <c r="R449">
-        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 448 - 1), NA())</f>
+        <f>IF(448&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 448 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="450">
       <c r="P450" s="2">
-        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 449 - 1), NA())</f>
+        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 449 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q450">
-        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 449 - 1), NA())</f>
+        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 449 - 1), NA())</f>
         <v/>
       </c>
       <c r="R450">
-        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 449 - 1), NA())</f>
+        <f>IF(449&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 449 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="451">
       <c r="P451" s="2">
-        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 450 - 1), NA())</f>
+        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 450 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q451">
-        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 450 - 1), NA())</f>
+        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 450 - 1), NA())</f>
         <v/>
       </c>
       <c r="R451">
-        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 450 - 1), NA())</f>
+        <f>IF(450&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 450 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="452">
       <c r="P452" s="2">
-        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 451 - 1), NA())</f>
+        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 451 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q452">
-        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 451 - 1), NA())</f>
+        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 451 - 1), NA())</f>
         <v/>
       </c>
       <c r="R452">
-        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 451 - 1), NA())</f>
+        <f>IF(451&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 451 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="453">
       <c r="P453" s="2">
-        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 452 - 1), NA())</f>
+        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 452 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q453">
-        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 452 - 1), NA())</f>
+        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 452 - 1), NA())</f>
         <v/>
       </c>
       <c r="R453">
-        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 452 - 1), NA())</f>
+        <f>IF(452&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 452 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="454">
       <c r="P454" s="2">
-        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 453 - 1), NA())</f>
+        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 453 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q454">
-        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 453 - 1), NA())</f>
+        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 453 - 1), NA())</f>
         <v/>
       </c>
       <c r="R454">
-        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 453 - 1), NA())</f>
+        <f>IF(453&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 453 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="455">
       <c r="P455" s="2">
-        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 454 - 1), NA())</f>
+        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 454 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q455">
-        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 454 - 1), NA())</f>
+        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 454 - 1), NA())</f>
         <v/>
       </c>
       <c r="R455">
-        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 454 - 1), NA())</f>
+        <f>IF(454&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 454 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="456">
       <c r="P456" s="2">
-        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 455 - 1), NA())</f>
+        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 455 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q456">
-        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 455 - 1), NA())</f>
+        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 455 - 1), NA())</f>
         <v/>
       </c>
       <c r="R456">
-        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 455 - 1), NA())</f>
+        <f>IF(455&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 455 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="457">
       <c r="P457" s="2">
-        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 456 - 1), NA())</f>
+        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 456 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q457">
-        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 456 - 1), NA())</f>
+        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 456 - 1), NA())</f>
         <v/>
       </c>
       <c r="R457">
-        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 456 - 1), NA())</f>
+        <f>IF(456&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 456 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="458">
       <c r="P458" s="2">
-        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 457 - 1), NA())</f>
+        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 457 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q458">
-        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 457 - 1), NA())</f>
+        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 457 - 1), NA())</f>
         <v/>
       </c>
       <c r="R458">
-        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 457 - 1), NA())</f>
+        <f>IF(457&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 457 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="459">
       <c r="P459" s="2">
-        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 458 - 1), NA())</f>
+        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 458 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q459">
-        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 458 - 1), NA())</f>
+        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 458 - 1), NA())</f>
         <v/>
       </c>
       <c r="R459">
-        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 458 - 1), NA())</f>
+        <f>IF(458&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 458 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="460">
       <c r="P460" s="2">
-        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 459 - 1), NA())</f>
+        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 459 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q460">
-        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 459 - 1), NA())</f>
+        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 459 - 1), NA())</f>
         <v/>
       </c>
       <c r="R460">
-        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 459 - 1), NA())</f>
+        <f>IF(459&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 459 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="461">
       <c r="P461" s="2">
-        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 460 - 1), NA())</f>
+        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 460 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q461">
-        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 460 - 1), NA())</f>
+        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 460 - 1), NA())</f>
         <v/>
       </c>
       <c r="R461">
-        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 460 - 1), NA())</f>
+        <f>IF(460&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 460 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="462">
       <c r="P462" s="2">
-        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 461 - 1), NA())</f>
+        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 461 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q462">
-        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 461 - 1), NA())</f>
+        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 461 - 1), NA())</f>
         <v/>
       </c>
       <c r="R462">
-        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 461 - 1), NA())</f>
+        <f>IF(461&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 461 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="463">
       <c r="P463" s="2">
-        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 462 - 1), NA())</f>
+        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 462 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q463">
-        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 462 - 1), NA())</f>
+        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 462 - 1), NA())</f>
         <v/>
       </c>
       <c r="R463">
-        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 462 - 1), NA())</f>
+        <f>IF(462&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 462 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="464">
       <c r="P464" s="2">
-        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 463 - 1), NA())</f>
+        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 463 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q464">
-        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 463 - 1), NA())</f>
+        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 463 - 1), NA())</f>
         <v/>
       </c>
       <c r="R464">
-        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 463 - 1), NA())</f>
+        <f>IF(463&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 463 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="465">
       <c r="P465" s="2">
-        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 464 - 1), NA())</f>
+        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 464 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q465">
-        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 464 - 1), NA())</f>
+        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 464 - 1), NA())</f>
         <v/>
       </c>
       <c r="R465">
-        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 464 - 1), NA())</f>
+        <f>IF(464&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 464 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="466">
       <c r="P466" s="2">
-        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 465 - 1), NA())</f>
+        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 465 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q466">
-        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 465 - 1), NA())</f>
+        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 465 - 1), NA())</f>
         <v/>
       </c>
       <c r="R466">
-        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 465 - 1), NA())</f>
+        <f>IF(465&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 465 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="467">
       <c r="P467" s="2">
-        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 466 - 1), NA())</f>
+        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 466 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q467">
-        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 466 - 1), NA())</f>
+        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 466 - 1), NA())</f>
         <v/>
       </c>
       <c r="R467">
-        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 466 - 1), NA())</f>
+        <f>IF(466&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 466 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="468">
       <c r="P468" s="2">
-        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 467 - 1), NA())</f>
+        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 467 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q468">
-        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 467 - 1), NA())</f>
+        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 467 - 1), NA())</f>
         <v/>
       </c>
       <c r="R468">
-        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 467 - 1), NA())</f>
+        <f>IF(467&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 467 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="469">
       <c r="P469" s="2">
-        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 468 - 1), NA())</f>
+        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 468 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q469">
-        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 468 - 1), NA())</f>
+        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 468 - 1), NA())</f>
         <v/>
       </c>
       <c r="R469">
-        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 468 - 1), NA())</f>
+        <f>IF(468&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 468 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="470">
       <c r="P470" s="2">
-        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 469 - 1), NA())</f>
+        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 469 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q470">
-        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 469 - 1), NA())</f>
+        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 469 - 1), NA())</f>
         <v/>
       </c>
       <c r="R470">
-        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 469 - 1), NA())</f>
+        <f>IF(469&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 469 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="471">
       <c r="P471" s="2">
-        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 470 - 1), NA())</f>
+        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 470 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q471">
-        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 470 - 1), NA())</f>
+        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 470 - 1), NA())</f>
         <v/>
       </c>
       <c r="R471">
-        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 470 - 1), NA())</f>
+        <f>IF(470&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 470 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="472">
       <c r="P472" s="2">
-        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 471 - 1), NA())</f>
+        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 471 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q472">
-        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 471 - 1), NA())</f>
+        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 471 - 1), NA())</f>
         <v/>
       </c>
       <c r="R472">
-        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 471 - 1), NA())</f>
+        <f>IF(471&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 471 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="473">
       <c r="P473" s="2">
-        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 472 - 1), NA())</f>
+        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 472 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q473">
-        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 472 - 1), NA())</f>
+        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 472 - 1), NA())</f>
         <v/>
       </c>
       <c r="R473">
-        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 472 - 1), NA())</f>
+        <f>IF(472&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 472 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="474">
       <c r="P474" s="2">
-        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 473 - 1), NA())</f>
+        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 473 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q474">
-        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 473 - 1), NA())</f>
+        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 473 - 1), NA())</f>
         <v/>
       </c>
       <c r="R474">
-        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 473 - 1), NA())</f>
+        <f>IF(473&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 473 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="475">
       <c r="P475" s="2">
-        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 474 - 1), NA())</f>
+        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 474 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q475">
-        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 474 - 1), NA())</f>
+        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 474 - 1), NA())</f>
         <v/>
       </c>
       <c r="R475">
-        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 474 - 1), NA())</f>
+        <f>IF(474&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 474 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="476">
       <c r="P476" s="2">
-        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 475 - 1), NA())</f>
+        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 475 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q476">
-        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 475 - 1), NA())</f>
+        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 475 - 1), NA())</f>
         <v/>
       </c>
       <c r="R476">
-        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 475 - 1), NA())</f>
+        <f>IF(475&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 475 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="477">
       <c r="P477" s="2">
-        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 476 - 1), NA())</f>
+        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 476 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q477">
-        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 476 - 1), NA())</f>
+        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 476 - 1), NA())</f>
         <v/>
       </c>
       <c r="R477">
-        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 476 - 1), NA())</f>
+        <f>IF(476&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 476 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="478">
       <c r="P478" s="2">
-        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 477 - 1), NA())</f>
+        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 477 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q478">
-        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 477 - 1), NA())</f>
+        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 477 - 1), NA())</f>
         <v/>
       </c>
       <c r="R478">
-        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 477 - 1), NA())</f>
+        <f>IF(477&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 477 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="479">
       <c r="P479" s="2">
-        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 478 - 1), NA())</f>
+        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 478 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q479">
-        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 478 - 1), NA())</f>
+        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 478 - 1), NA())</f>
         <v/>
       </c>
       <c r="R479">
-        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 478 - 1), NA())</f>
+        <f>IF(478&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 478 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="480">
       <c r="P480" s="2">
-        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 479 - 1), NA())</f>
+        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 479 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q480">
-        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 479 - 1), NA())</f>
+        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 479 - 1), NA())</f>
         <v/>
       </c>
       <c r="R480">
-        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 479 - 1), NA())</f>
+        <f>IF(479&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 479 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="481">
       <c r="P481" s="2">
-        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 480 - 1), NA())</f>
+        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 480 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q481">
-        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 480 - 1), NA())</f>
+        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 480 - 1), NA())</f>
         <v/>
       </c>
       <c r="R481">
-        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 480 - 1), NA())</f>
+        <f>IF(480&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 480 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="482">
       <c r="P482" s="2">
-        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 481 - 1), NA())</f>
+        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 481 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q482">
-        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 481 - 1), NA())</f>
+        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 481 - 1), NA())</f>
         <v/>
       </c>
       <c r="R482">
-        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 481 - 1), NA())</f>
+        <f>IF(481&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 481 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="483">
       <c r="P483" s="2">
-        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 482 - 1), NA())</f>
+        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 482 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q483">
-        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 482 - 1), NA())</f>
+        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 482 - 1), NA())</f>
         <v/>
       </c>
       <c r="R483">
-        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 482 - 1), NA())</f>
+        <f>IF(482&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 482 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="484">
       <c r="P484" s="2">
-        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 483 - 1), NA())</f>
+        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 483 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q484">
-        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 483 - 1), NA())</f>
+        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 483 - 1), NA())</f>
         <v/>
       </c>
       <c r="R484">
-        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 483 - 1), NA())</f>
+        <f>IF(483&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 483 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="485">
       <c r="P485" s="2">
-        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 484 - 1), NA())</f>
+        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 484 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q485">
-        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 484 - 1), NA())</f>
+        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 484 - 1), NA())</f>
         <v/>
       </c>
       <c r="R485">
-        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 484 - 1), NA())</f>
+        <f>IF(484&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 484 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="486">
       <c r="P486" s="2">
-        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 485 - 1), NA())</f>
+        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 485 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q486">
-        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 485 - 1), NA())</f>
+        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 485 - 1), NA())</f>
         <v/>
       </c>
       <c r="R486">
-        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 485 - 1), NA())</f>
+        <f>IF(485&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 485 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="487">
       <c r="P487" s="2">
-        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 486 - 1), NA())</f>
+        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 486 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q487">
-        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 486 - 1), NA())</f>
+        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 486 - 1), NA())</f>
         <v/>
       </c>
       <c r="R487">
-        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 486 - 1), NA())</f>
+        <f>IF(486&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 486 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="488">
       <c r="P488" s="2">
-        <f>IF(487&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 487 - 1), NA())</f>
+        <f>IF(487&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 487 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q488">
-        <f>IF(487&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 487 - 1), NA())</f>
+        <f>IF(487&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 487 - 1), NA())</f>
         <v/>
       </c>
       <c r="R488">
-        <f>IF(487&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 487 - 1), NA())</f>
+        <f>IF(487&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 487 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="489">
       <c r="P489" s="2">
-        <f>IF(488&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 488 - 1), NA())</f>
+        <f>IF(488&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 488 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q489">
-        <f>IF(488&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 488 - 1), NA())</f>
+        <f>IF(488&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 488 - 1), NA())</f>
         <v/>
       </c>
       <c r="R489">
-        <f>IF(488&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 488 - 1), NA())</f>
+        <f>IF(488&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 488 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="490">
       <c r="P490" s="2">
-        <f>IF(489&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$490, $G$8 - 1 + 489 - 1), NA())</f>
+        <f>IF(489&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 489 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q490">
-        <f>IF(489&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$490, $G$8 - 1 + 489 - 1), NA())</f>
+        <f>IF(489&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 489 - 1), NA())</f>
         <v/>
       </c>
       <c r="R490">
-        <f>IF(489&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$490, $G$8 - 1 + 489 - 1), NA())</f>
+        <f>IF(489&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 489 - 1), NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="491">
+      <c r="P491" s="2">
+        <f>IF(490&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 490 - 1), NA())</f>
+        <v/>
+      </c>
+      <c r="Q491">
+        <f>IF(490&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 490 - 1), NA())</f>
+        <v/>
+      </c>
+      <c r="R491">
+        <f>IF(490&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 490 - 1), NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="492">
+      <c r="P492" s="2">
+        <f>IF(491&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 491 - 1), NA())</f>
+        <v/>
+      </c>
+      <c r="Q492">
+        <f>IF(491&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 491 - 1), NA())</f>
+        <v/>
+      </c>
+      <c r="R492">
+        <f>IF(491&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 491 - 1), NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="493">
+      <c r="P493" s="2">
+        <f>IF(492&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$493, $G$8 - 1 + 492 - 1), NA())</f>
+        <v/>
+      </c>
+      <c r="Q493">
+        <f>IF(492&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$493, $G$8 - 1 + 492 - 1), NA())</f>
+        <v/>
+      </c>
+      <c r="R493">
+        <f>IF(492&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$493, $G$8 - 1 + 492 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -8106,7 +8148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H490"/>
+  <dimension ref="A1:H493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22804,13 +22846,13 @@
         <v>46276</v>
       </c>
       <c r="B490" s="15" t="n">
-        <v>4390</v>
+        <v>4408.89990234375</v>
       </c>
       <c r="C490" s="15" t="n">
-        <v>65.01999664306641</v>
+        <v>64.55400085449219</v>
       </c>
       <c r="D490" s="15" t="n">
-        <v>3082.739990234375</v>
+        <v>3101.550048828125</v>
       </c>
       <c r="E490" s="16">
         <f>ROUND((B490/31.1034768)*D490, 2)</f>
@@ -22829,8 +22871,98 @@
         <v/>
       </c>
     </row>
+    <row r="491" ht="20" customHeight="1">
+      <c r="A491" s="18" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B491" s="19" t="n">
+        <v>4408.89990234375</v>
+      </c>
+      <c r="C491" s="19" t="n">
+        <v>64.55400085449219</v>
+      </c>
+      <c r="D491" s="19" t="n">
+        <v>3091.659912109375</v>
+      </c>
+      <c r="E491" s="20">
+        <f>ROUND((B491/31.1034768)*D491, 2)</f>
+        <v/>
+      </c>
+      <c r="F491" s="20">
+        <f>ROUND((C491/31.1034768)*D491, 2)</f>
+        <v/>
+      </c>
+      <c r="G491" s="21">
+        <f>IFERROR((E491-E490)/E490, 0)</f>
+        <v/>
+      </c>
+      <c r="H491" s="21">
+        <f>IFERROR((F491-F490)/F490, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="492" ht="20" customHeight="1">
+      <c r="A492" s="14" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B492" s="15" t="n">
+        <v>4408.89990234375</v>
+      </c>
+      <c r="C492" s="15" t="n">
+        <v>64.55400085449219</v>
+      </c>
+      <c r="D492" s="15" t="n">
+        <v>3107.169921875</v>
+      </c>
+      <c r="E492" s="16">
+        <f>ROUND((B492/31.1034768)*D492, 2)</f>
+        <v/>
+      </c>
+      <c r="F492" s="16">
+        <f>ROUND((C492/31.1034768)*D492, 2)</f>
+        <v/>
+      </c>
+      <c r="G492" s="17">
+        <f>IFERROR((E492-E491)/E491, 0)</f>
+        <v/>
+      </c>
+      <c r="H492" s="17">
+        <f>IFERROR((F492-F491)/F491, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="493" ht="20" customHeight="1">
+      <c r="A493" s="18" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B493" s="19" t="n">
+        <v>4336.2001953125</v>
+      </c>
+      <c r="C493" s="19" t="n">
+        <v>63.66500091552734</v>
+      </c>
+      <c r="D493" s="19" t="n">
+        <v>3107.169921875</v>
+      </c>
+      <c r="E493" s="20">
+        <f>ROUND((B493/31.1034768)*D493, 2)</f>
+        <v/>
+      </c>
+      <c r="F493" s="20">
+        <f>ROUND((C493/31.1034768)*D493, 2)</f>
+        <v/>
+      </c>
+      <c r="G493" s="21">
+        <f>IFERROR((E493-E492)/E492, 0)</f>
+        <v/>
+      </c>
+      <c r="H493" s="21">
+        <f>IFERROR((F493-F492)/F492, 0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H490"/>
+  <autoFilter ref="A1:H493"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Precios_Metales_COP.xlsx
+++ b/Precios_Metales_COP.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Precios Diarios" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Precios Diarios'!$A$1:$H$494</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Precios Diarios'!$A$1:$H$495</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -321,12 +321,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard y Gráficos'!$P$2:$P$494</f>
+              <f>'Dashboard y Gráficos'!$P$2:$P$495</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$Q$2:$Q$494</f>
+              <f>'Dashboard y Gráficos'!$Q$2:$Q$495</f>
             </numRef>
           </val>
         </ser>
@@ -446,12 +446,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard y Gráficos'!$P$2:$P$494</f>
+              <f>'Dashboard y Gráficos'!$P$2:$P$495</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$R$2:$R$494</f>
+              <f>'Dashboard y Gráficos'!$R$2:$R$495</f>
             </numRef>
           </val>
         </ser>
@@ -570,12 +570,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard y Gráficos'!$P$2:$P$494</f>
+              <f>'Dashboard y Gráficos'!$P$2:$P$495</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$Q$2:$Q$494</f>
+              <f>'Dashboard y Gráficos'!$Q$2:$Q$495</f>
             </numRef>
           </val>
         </ser>
@@ -610,7 +610,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Dashboard y Gráficos'!$R$2:$R$494</f>
+              <f>'Dashboard y Gráficos'!$R$2:$R$495</f>
             </numRef>
           </val>
         </ser>
@@ -1074,7 +1074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R494"/>
+  <dimension ref="A1:R495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1118,15 +1118,15 @@
     </row>
     <row r="2">
       <c r="P2" s="2">
-        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 1 - 1), NA())</f>
+        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 1 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q2">
-        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 1 - 1), NA())</f>
+        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 1 - 1), NA())</f>
         <v/>
       </c>
       <c r="R2">
-        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 1 - 1), NA())</f>
+        <f>IF(1&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 1 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1166,58 +1166,58 @@
       </c>
       <c r="N3" s="4" t="n"/>
       <c r="P3" s="2">
-        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 2 - 1), NA())</f>
+        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 2 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q3">
-        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 2 - 1), NA())</f>
+        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 2 - 1), NA())</f>
         <v/>
       </c>
       <c r="R3">
-        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 2 - 1), NA())</f>
+        <f>IF(2&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 2 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5">
-        <f>'Precios Diarios'!A494</f>
+        <f>'Precios Diarios'!A495</f>
         <v/>
       </c>
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="6">
-        <f>'Precios Diarios'!E494</f>
+        <f>'Precios Diarios'!E495</f>
         <v/>
       </c>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="6">
-        <f>'Precios Diarios'!F494</f>
+        <f>'Precios Diarios'!F495</f>
         <v/>
       </c>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="6">
-        <f>'Precios Diarios'!D494</f>
+        <f>'Precios Diarios'!D495</f>
         <v/>
       </c>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="7">
-        <f>'Precios Diarios'!G494</f>
+        <f>'Precios Diarios'!G495</f>
         <v/>
       </c>
       <c r="N4" s="4" t="n"/>
       <c r="P4" s="2">
-        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 3 - 1), NA())</f>
+        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 3 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q4">
-        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 3 - 1), NA())</f>
+        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 3 - 1), NA())</f>
         <v/>
       </c>
       <c r="R4">
-        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 3 - 1), NA())</f>
+        <f>IF(3&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 3 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1237,29 +1237,29 @@
       <c r="M5" s="4" t="n"/>
       <c r="N5" s="4" t="n"/>
       <c r="P5" s="2">
-        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 4 - 1), NA())</f>
+        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 4 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q5">
-        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 4 - 1), NA())</f>
+        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 4 - 1), NA())</f>
         <v/>
       </c>
       <c r="R5">
-        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 4 - 1), NA())</f>
+        <f>IF(4&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 4 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="P6" s="2">
-        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 5 - 1), NA())</f>
+        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 5 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q6">
-        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 5 - 1), NA())</f>
+        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 5 - 1), NA())</f>
         <v/>
       </c>
       <c r="R6">
-        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 5 - 1), NA())</f>
+        <f>IF(5&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 5 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1270,15 +1270,15 @@
         </is>
       </c>
       <c r="P7" s="2">
-        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 6 - 1), NA())</f>
+        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 6 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q7">
-        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 6 - 1), NA())</f>
+        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 6 - 1), NA())</f>
         <v/>
       </c>
       <c r="R7">
-        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 6 - 1), NA())</f>
+        <f>IF(6&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 6 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1297,11 +1297,11 @@
         <v/>
       </c>
       <c r="G8" s="11">
-        <f>IFERROR(MATCH(E8, 'Precios Diarios'!$A$2:$A$494, 1), 1) + 1</f>
+        <f>IFERROR(MATCH(E8, 'Precios Diarios'!$A$2:$A$495, 1), 1) + 1</f>
         <v/>
       </c>
       <c r="H8" s="11">
-        <f>IFERROR(MATCH(F8, 'Precios Diarios'!$A$2:$A$494, 1), 493) + 1</f>
+        <f>IFERROR(MATCH(F8, 'Precios Diarios'!$A$2:$A$495, 1), 494) + 1</f>
         <v/>
       </c>
       <c r="I8" s="11">
@@ -1309,15 +1309,15 @@
         <v/>
       </c>
       <c r="P8" s="2">
-        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 7 - 1), NA())</f>
+        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 7 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q8">
-        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 7 - 1), NA())</f>
+        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 7 - 1), NA())</f>
         <v/>
       </c>
       <c r="R8">
-        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 7 - 1), NA())</f>
+        <f>IF(7&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 7 - 1), NA())</f>
         <v/>
       </c>
     </row>
@@ -1328,6805 +1328,6819 @@
         </is>
       </c>
       <c r="P9" s="2">
-        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 8 - 1), NA())</f>
+        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 8 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q9">
-        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 8 - 1), NA())</f>
+        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 8 - 1), NA())</f>
         <v/>
       </c>
       <c r="R9">
-        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 8 - 1), NA())</f>
+        <f>IF(8&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 8 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="P10" s="2">
-        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 9 - 1), NA())</f>
+        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 9 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q10">
-        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 9 - 1), NA())</f>
+        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 9 - 1), NA())</f>
         <v/>
       </c>
       <c r="R10">
-        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 9 - 1), NA())</f>
+        <f>IF(9&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 9 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="P11" s="2">
-        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 10 - 1), NA())</f>
+        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 10 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q11">
-        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 10 - 1), NA())</f>
+        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 10 - 1), NA())</f>
         <v/>
       </c>
       <c r="R11">
-        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 10 - 1), NA())</f>
+        <f>IF(10&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 10 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="P12" s="2">
-        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 11 - 1), NA())</f>
+        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 11 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q12">
-        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 11 - 1), NA())</f>
+        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 11 - 1), NA())</f>
         <v/>
       </c>
       <c r="R12">
-        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 11 - 1), NA())</f>
+        <f>IF(11&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 11 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="P13" s="2">
-        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 12 - 1), NA())</f>
+        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 12 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q13">
-        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 12 - 1), NA())</f>
+        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 12 - 1), NA())</f>
         <v/>
       </c>
       <c r="R13">
-        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 12 - 1), NA())</f>
+        <f>IF(12&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 12 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="P14" s="2">
-        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 13 - 1), NA())</f>
+        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 13 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q14">
-        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 13 - 1), NA())</f>
+        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 13 - 1), NA())</f>
         <v/>
       </c>
       <c r="R14">
-        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 13 - 1), NA())</f>
+        <f>IF(13&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 13 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="P15" s="2">
-        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 14 - 1), NA())</f>
+        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 14 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q15">
-        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 14 - 1), NA())</f>
+        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 14 - 1), NA())</f>
         <v/>
       </c>
       <c r="R15">
-        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 14 - 1), NA())</f>
+        <f>IF(14&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 14 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="P16" s="2">
-        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 15 - 1), NA())</f>
+        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 15 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q16">
-        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 15 - 1), NA())</f>
+        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 15 - 1), NA())</f>
         <v/>
       </c>
       <c r="R16">
-        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 15 - 1), NA())</f>
+        <f>IF(15&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 15 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="P17" s="2">
-        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 16 - 1), NA())</f>
+        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 16 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q17">
-        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 16 - 1), NA())</f>
+        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 16 - 1), NA())</f>
         <v/>
       </c>
       <c r="R17">
-        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 16 - 1), NA())</f>
+        <f>IF(16&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 16 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="P18" s="2">
-        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 17 - 1), NA())</f>
+        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 17 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q18">
-        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 17 - 1), NA())</f>
+        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 17 - 1), NA())</f>
         <v/>
       </c>
       <c r="R18">
-        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 17 - 1), NA())</f>
+        <f>IF(17&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 17 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="P19" s="2">
-        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 18 - 1), NA())</f>
+        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 18 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q19">
-        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 18 - 1), NA())</f>
+        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 18 - 1), NA())</f>
         <v/>
       </c>
       <c r="R19">
-        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 18 - 1), NA())</f>
+        <f>IF(18&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 18 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="P20" s="2">
-        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 19 - 1), NA())</f>
+        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 19 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q20">
-        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 19 - 1), NA())</f>
+        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 19 - 1), NA())</f>
         <v/>
       </c>
       <c r="R20">
-        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 19 - 1), NA())</f>
+        <f>IF(19&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 19 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="P21" s="2">
-        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 20 - 1), NA())</f>
+        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 20 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q21">
-        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 20 - 1), NA())</f>
+        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 20 - 1), NA())</f>
         <v/>
       </c>
       <c r="R21">
-        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 20 - 1), NA())</f>
+        <f>IF(20&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 20 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="P22" s="2">
-        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 21 - 1), NA())</f>
+        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 21 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q22">
-        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 21 - 1), NA())</f>
+        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 21 - 1), NA())</f>
         <v/>
       </c>
       <c r="R22">
-        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 21 - 1), NA())</f>
+        <f>IF(21&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 21 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="P23" s="2">
-        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 22 - 1), NA())</f>
+        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 22 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q23">
-        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 22 - 1), NA())</f>
+        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 22 - 1), NA())</f>
         <v/>
       </c>
       <c r="R23">
-        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 22 - 1), NA())</f>
+        <f>IF(22&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 22 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="P24" s="2">
-        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 23 - 1), NA())</f>
+        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 23 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q24">
-        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 23 - 1), NA())</f>
+        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 23 - 1), NA())</f>
         <v/>
       </c>
       <c r="R24">
-        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 23 - 1), NA())</f>
+        <f>IF(23&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 23 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="P25" s="2">
-        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 24 - 1), NA())</f>
+        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 24 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q25">
-        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 24 - 1), NA())</f>
+        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 24 - 1), NA())</f>
         <v/>
       </c>
       <c r="R25">
-        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 24 - 1), NA())</f>
+        <f>IF(24&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 24 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="P26" s="2">
-        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 25 - 1), NA())</f>
+        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 25 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q26">
-        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 25 - 1), NA())</f>
+        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 25 - 1), NA())</f>
         <v/>
       </c>
       <c r="R26">
-        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 25 - 1), NA())</f>
+        <f>IF(25&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 25 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="P27" s="2">
-        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 26 - 1), NA())</f>
+        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 26 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q27">
-        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 26 - 1), NA())</f>
+        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 26 - 1), NA())</f>
         <v/>
       </c>
       <c r="R27">
-        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 26 - 1), NA())</f>
+        <f>IF(26&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 26 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="P28" s="2">
-        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 27 - 1), NA())</f>
+        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 27 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q28">
-        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 27 - 1), NA())</f>
+        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 27 - 1), NA())</f>
         <v/>
       </c>
       <c r="R28">
-        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 27 - 1), NA())</f>
+        <f>IF(27&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 27 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="P29" s="2">
-        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 28 - 1), NA())</f>
+        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 28 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q29">
-        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 28 - 1), NA())</f>
+        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 28 - 1), NA())</f>
         <v/>
       </c>
       <c r="R29">
-        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 28 - 1), NA())</f>
+        <f>IF(28&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 28 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="P30" s="2">
-        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 29 - 1), NA())</f>
+        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 29 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q30">
-        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 29 - 1), NA())</f>
+        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 29 - 1), NA())</f>
         <v/>
       </c>
       <c r="R30">
-        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 29 - 1), NA())</f>
+        <f>IF(29&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 29 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="P31" s="2">
-        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 30 - 1), NA())</f>
+        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 30 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q31">
-        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 30 - 1), NA())</f>
+        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 30 - 1), NA())</f>
         <v/>
       </c>
       <c r="R31">
-        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 30 - 1), NA())</f>
+        <f>IF(30&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 30 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="P32" s="2">
-        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 31 - 1), NA())</f>
+        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 31 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q32">
-        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 31 - 1), NA())</f>
+        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 31 - 1), NA())</f>
         <v/>
       </c>
       <c r="R32">
-        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 31 - 1), NA())</f>
+        <f>IF(31&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 31 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="P33" s="2">
-        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 32 - 1), NA())</f>
+        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 32 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q33">
-        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 32 - 1), NA())</f>
+        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 32 - 1), NA())</f>
         <v/>
       </c>
       <c r="R33">
-        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 32 - 1), NA())</f>
+        <f>IF(32&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 32 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="P34" s="2">
-        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 33 - 1), NA())</f>
+        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 33 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q34">
-        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 33 - 1), NA())</f>
+        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 33 - 1), NA())</f>
         <v/>
       </c>
       <c r="R34">
-        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 33 - 1), NA())</f>
+        <f>IF(33&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 33 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="P35" s="2">
-        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 34 - 1), NA())</f>
+        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 34 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q35">
-        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 34 - 1), NA())</f>
+        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 34 - 1), NA())</f>
         <v/>
       </c>
       <c r="R35">
-        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 34 - 1), NA())</f>
+        <f>IF(34&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 34 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="P36" s="2">
-        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 35 - 1), NA())</f>
+        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 35 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q36">
-        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 35 - 1), NA())</f>
+        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 35 - 1), NA())</f>
         <v/>
       </c>
       <c r="R36">
-        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 35 - 1), NA())</f>
+        <f>IF(35&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 35 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="P37" s="2">
-        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 36 - 1), NA())</f>
+        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 36 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q37">
-        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 36 - 1), NA())</f>
+        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 36 - 1), NA())</f>
         <v/>
       </c>
       <c r="R37">
-        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 36 - 1), NA())</f>
+        <f>IF(36&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 36 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="P38" s="2">
-        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 37 - 1), NA())</f>
+        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 37 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q38">
-        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 37 - 1), NA())</f>
+        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 37 - 1), NA())</f>
         <v/>
       </c>
       <c r="R38">
-        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 37 - 1), NA())</f>
+        <f>IF(37&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 37 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="P39" s="2">
-        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 38 - 1), NA())</f>
+        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 38 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q39">
-        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 38 - 1), NA())</f>
+        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 38 - 1), NA())</f>
         <v/>
       </c>
       <c r="R39">
-        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 38 - 1), NA())</f>
+        <f>IF(38&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 38 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="P40" s="2">
-        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 39 - 1), NA())</f>
+        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 39 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q40">
-        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 39 - 1), NA())</f>
+        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 39 - 1), NA())</f>
         <v/>
       </c>
       <c r="R40">
-        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 39 - 1), NA())</f>
+        <f>IF(39&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 39 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="P41" s="2">
-        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 40 - 1), NA())</f>
+        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 40 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q41">
-        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 40 - 1), NA())</f>
+        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 40 - 1), NA())</f>
         <v/>
       </c>
       <c r="R41">
-        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 40 - 1), NA())</f>
+        <f>IF(40&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 40 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="P42" s="2">
-        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 41 - 1), NA())</f>
+        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 41 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q42">
-        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 41 - 1), NA())</f>
+        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 41 - 1), NA())</f>
         <v/>
       </c>
       <c r="R42">
-        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 41 - 1), NA())</f>
+        <f>IF(41&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 41 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="P43" s="2">
-        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 42 - 1), NA())</f>
+        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 42 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q43">
-        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 42 - 1), NA())</f>
+        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 42 - 1), NA())</f>
         <v/>
       </c>
       <c r="R43">
-        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 42 - 1), NA())</f>
+        <f>IF(42&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 42 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="P44" s="2">
-        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 43 - 1), NA())</f>
+        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 43 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q44">
-        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 43 - 1), NA())</f>
+        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 43 - 1), NA())</f>
         <v/>
       </c>
       <c r="R44">
-        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 43 - 1), NA())</f>
+        <f>IF(43&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 43 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="P45" s="2">
-        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 44 - 1), NA())</f>
+        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 44 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q45">
-        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 44 - 1), NA())</f>
+        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 44 - 1), NA())</f>
         <v/>
       </c>
       <c r="R45">
-        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 44 - 1), NA())</f>
+        <f>IF(44&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 44 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="P46" s="2">
-        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 45 - 1), NA())</f>
+        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 45 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q46">
-        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 45 - 1), NA())</f>
+        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 45 - 1), NA())</f>
         <v/>
       </c>
       <c r="R46">
-        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 45 - 1), NA())</f>
+        <f>IF(45&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 45 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="P47" s="2">
-        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 46 - 1), NA())</f>
+        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 46 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q47">
-        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 46 - 1), NA())</f>
+        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 46 - 1), NA())</f>
         <v/>
       </c>
       <c r="R47">
-        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 46 - 1), NA())</f>
+        <f>IF(46&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 46 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="P48" s="2">
-        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 47 - 1), NA())</f>
+        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 47 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q48">
-        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 47 - 1), NA())</f>
+        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 47 - 1), NA())</f>
         <v/>
       </c>
       <c r="R48">
-        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 47 - 1), NA())</f>
+        <f>IF(47&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 47 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="P49" s="2">
-        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 48 - 1), NA())</f>
+        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 48 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q49">
-        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 48 - 1), NA())</f>
+        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 48 - 1), NA())</f>
         <v/>
       </c>
       <c r="R49">
-        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 48 - 1), NA())</f>
+        <f>IF(48&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 48 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="P50" s="2">
-        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 49 - 1), NA())</f>
+        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 49 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q50">
-        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 49 - 1), NA())</f>
+        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 49 - 1), NA())</f>
         <v/>
       </c>
       <c r="R50">
-        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 49 - 1), NA())</f>
+        <f>IF(49&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 49 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="P51" s="2">
-        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 50 - 1), NA())</f>
+        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 50 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q51">
-        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 50 - 1), NA())</f>
+        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 50 - 1), NA())</f>
         <v/>
       </c>
       <c r="R51">
-        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 50 - 1), NA())</f>
+        <f>IF(50&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 50 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="P52" s="2">
-        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 51 - 1), NA())</f>
+        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 51 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q52">
-        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 51 - 1), NA())</f>
+        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 51 - 1), NA())</f>
         <v/>
       </c>
       <c r="R52">
-        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 51 - 1), NA())</f>
+        <f>IF(51&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 51 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="P53" s="2">
-        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 52 - 1), NA())</f>
+        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 52 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q53">
-        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 52 - 1), NA())</f>
+        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 52 - 1), NA())</f>
         <v/>
       </c>
       <c r="R53">
-        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 52 - 1), NA())</f>
+        <f>IF(52&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 52 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="P54" s="2">
-        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 53 - 1), NA())</f>
+        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 53 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q54">
-        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 53 - 1), NA())</f>
+        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 53 - 1), NA())</f>
         <v/>
       </c>
       <c r="R54">
-        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 53 - 1), NA())</f>
+        <f>IF(53&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 53 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="P55" s="2">
-        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 54 - 1), NA())</f>
+        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 54 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q55">
-        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 54 - 1), NA())</f>
+        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 54 - 1), NA())</f>
         <v/>
       </c>
       <c r="R55">
-        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 54 - 1), NA())</f>
+        <f>IF(54&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 54 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="P56" s="2">
-        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 55 - 1), NA())</f>
+        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 55 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q56">
-        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 55 - 1), NA())</f>
+        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 55 - 1), NA())</f>
         <v/>
       </c>
       <c r="R56">
-        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 55 - 1), NA())</f>
+        <f>IF(55&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 55 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="P57" s="2">
-        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 56 - 1), NA())</f>
+        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 56 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q57">
-        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 56 - 1), NA())</f>
+        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 56 - 1), NA())</f>
         <v/>
       </c>
       <c r="R57">
-        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 56 - 1), NA())</f>
+        <f>IF(56&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 56 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="P58" s="2">
-        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 57 - 1), NA())</f>
+        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 57 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q58">
-        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 57 - 1), NA())</f>
+        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 57 - 1), NA())</f>
         <v/>
       </c>
       <c r="R58">
-        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 57 - 1), NA())</f>
+        <f>IF(57&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 57 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="P59" s="2">
-        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 58 - 1), NA())</f>
+        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 58 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q59">
-        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 58 - 1), NA())</f>
+        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 58 - 1), NA())</f>
         <v/>
       </c>
       <c r="R59">
-        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 58 - 1), NA())</f>
+        <f>IF(58&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 58 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="P60" s="2">
-        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 59 - 1), NA())</f>
+        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 59 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q60">
-        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 59 - 1), NA())</f>
+        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 59 - 1), NA())</f>
         <v/>
       </c>
       <c r="R60">
-        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 59 - 1), NA())</f>
+        <f>IF(59&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 59 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="P61" s="2">
-        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 60 - 1), NA())</f>
+        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 60 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q61">
-        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 60 - 1), NA())</f>
+        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 60 - 1), NA())</f>
         <v/>
       </c>
       <c r="R61">
-        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 60 - 1), NA())</f>
+        <f>IF(60&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 60 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="P62" s="2">
-        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 61 - 1), NA())</f>
+        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 61 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q62">
-        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 61 - 1), NA())</f>
+        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 61 - 1), NA())</f>
         <v/>
       </c>
       <c r="R62">
-        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 61 - 1), NA())</f>
+        <f>IF(61&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 61 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="P63" s="2">
-        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 62 - 1), NA())</f>
+        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 62 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q63">
-        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 62 - 1), NA())</f>
+        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 62 - 1), NA())</f>
         <v/>
       </c>
       <c r="R63">
-        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 62 - 1), NA())</f>
+        <f>IF(62&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 62 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="P64" s="2">
-        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 63 - 1), NA())</f>
+        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 63 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q64">
-        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 63 - 1), NA())</f>
+        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 63 - 1), NA())</f>
         <v/>
       </c>
       <c r="R64">
-        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 63 - 1), NA())</f>
+        <f>IF(63&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 63 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="P65" s="2">
-        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 64 - 1), NA())</f>
+        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 64 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q65">
-        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 64 - 1), NA())</f>
+        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 64 - 1), NA())</f>
         <v/>
       </c>
       <c r="R65">
-        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 64 - 1), NA())</f>
+        <f>IF(64&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 64 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="P66" s="2">
-        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 65 - 1), NA())</f>
+        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 65 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q66">
-        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 65 - 1), NA())</f>
+        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 65 - 1), NA())</f>
         <v/>
       </c>
       <c r="R66">
-        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 65 - 1), NA())</f>
+        <f>IF(65&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 65 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="P67" s="2">
-        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 66 - 1), NA())</f>
+        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 66 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q67">
-        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 66 - 1), NA())</f>
+        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 66 - 1), NA())</f>
         <v/>
       </c>
       <c r="R67">
-        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 66 - 1), NA())</f>
+        <f>IF(66&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 66 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="P68" s="2">
-        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 67 - 1), NA())</f>
+        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 67 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q68">
-        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 67 - 1), NA())</f>
+        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 67 - 1), NA())</f>
         <v/>
       </c>
       <c r="R68">
-        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 67 - 1), NA())</f>
+        <f>IF(67&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 67 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="P69" s="2">
-        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 68 - 1), NA())</f>
+        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 68 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q69">
-        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 68 - 1), NA())</f>
+        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 68 - 1), NA())</f>
         <v/>
       </c>
       <c r="R69">
-        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 68 - 1), NA())</f>
+        <f>IF(68&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 68 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="P70" s="2">
-        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 69 - 1), NA())</f>
+        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 69 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q70">
-        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 69 - 1), NA())</f>
+        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 69 - 1), NA())</f>
         <v/>
       </c>
       <c r="R70">
-        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 69 - 1), NA())</f>
+        <f>IF(69&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 69 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="P71" s="2">
-        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 70 - 1), NA())</f>
+        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 70 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q71">
-        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 70 - 1), NA())</f>
+        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 70 - 1), NA())</f>
         <v/>
       </c>
       <c r="R71">
-        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 70 - 1), NA())</f>
+        <f>IF(70&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 70 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="P72" s="2">
-        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 71 - 1), NA())</f>
+        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 71 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q72">
-        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 71 - 1), NA())</f>
+        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 71 - 1), NA())</f>
         <v/>
       </c>
       <c r="R72">
-        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 71 - 1), NA())</f>
+        <f>IF(71&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 71 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="P73" s="2">
-        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 72 - 1), NA())</f>
+        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 72 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q73">
-        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 72 - 1), NA())</f>
+        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 72 - 1), NA())</f>
         <v/>
       </c>
       <c r="R73">
-        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 72 - 1), NA())</f>
+        <f>IF(72&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 72 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="P74" s="2">
-        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 73 - 1), NA())</f>
+        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 73 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q74">
-        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 73 - 1), NA())</f>
+        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 73 - 1), NA())</f>
         <v/>
       </c>
       <c r="R74">
-        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 73 - 1), NA())</f>
+        <f>IF(73&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 73 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="P75" s="2">
-        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 74 - 1), NA())</f>
+        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 74 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q75">
-        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 74 - 1), NA())</f>
+        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 74 - 1), NA())</f>
         <v/>
       </c>
       <c r="R75">
-        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 74 - 1), NA())</f>
+        <f>IF(74&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 74 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="P76" s="2">
-        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 75 - 1), NA())</f>
+        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 75 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q76">
-        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 75 - 1), NA())</f>
+        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 75 - 1), NA())</f>
         <v/>
       </c>
       <c r="R76">
-        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 75 - 1), NA())</f>
+        <f>IF(75&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 75 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="P77" s="2">
-        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 76 - 1), NA())</f>
+        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 76 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q77">
-        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 76 - 1), NA())</f>
+        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 76 - 1), NA())</f>
         <v/>
       </c>
       <c r="R77">
-        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 76 - 1), NA())</f>
+        <f>IF(76&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 76 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="P78" s="2">
-        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 77 - 1), NA())</f>
+        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 77 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q78">
-        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 77 - 1), NA())</f>
+        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 77 - 1), NA())</f>
         <v/>
       </c>
       <c r="R78">
-        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 77 - 1), NA())</f>
+        <f>IF(77&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 77 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="P79" s="2">
-        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 78 - 1), NA())</f>
+        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 78 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q79">
-        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 78 - 1), NA())</f>
+        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 78 - 1), NA())</f>
         <v/>
       </c>
       <c r="R79">
-        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 78 - 1), NA())</f>
+        <f>IF(78&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 78 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="P80" s="2">
-        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 79 - 1), NA())</f>
+        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 79 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q80">
-        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 79 - 1), NA())</f>
+        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 79 - 1), NA())</f>
         <v/>
       </c>
       <c r="R80">
-        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 79 - 1), NA())</f>
+        <f>IF(79&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 79 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="P81" s="2">
-        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 80 - 1), NA())</f>
+        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 80 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q81">
-        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 80 - 1), NA())</f>
+        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 80 - 1), NA())</f>
         <v/>
       </c>
       <c r="R81">
-        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 80 - 1), NA())</f>
+        <f>IF(80&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 80 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="P82" s="2">
-        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 81 - 1), NA())</f>
+        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 81 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q82">
-        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 81 - 1), NA())</f>
+        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 81 - 1), NA())</f>
         <v/>
       </c>
       <c r="R82">
-        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 81 - 1), NA())</f>
+        <f>IF(81&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 81 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="P83" s="2">
-        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 82 - 1), NA())</f>
+        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 82 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q83">
-        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 82 - 1), NA())</f>
+        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 82 - 1), NA())</f>
         <v/>
       </c>
       <c r="R83">
-        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 82 - 1), NA())</f>
+        <f>IF(82&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 82 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="P84" s="2">
-        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 83 - 1), NA())</f>
+        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 83 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q84">
-        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 83 - 1), NA())</f>
+        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 83 - 1), NA())</f>
         <v/>
       </c>
       <c r="R84">
-        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 83 - 1), NA())</f>
+        <f>IF(83&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 83 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="P85" s="2">
-        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 84 - 1), NA())</f>
+        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 84 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q85">
-        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 84 - 1), NA())</f>
+        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 84 - 1), NA())</f>
         <v/>
       </c>
       <c r="R85">
-        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 84 - 1), NA())</f>
+        <f>IF(84&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 84 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="P86" s="2">
-        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 85 - 1), NA())</f>
+        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 85 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q86">
-        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 85 - 1), NA())</f>
+        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 85 - 1), NA())</f>
         <v/>
       </c>
       <c r="R86">
-        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 85 - 1), NA())</f>
+        <f>IF(85&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 85 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="P87" s="2">
-        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 86 - 1), NA())</f>
+        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 86 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q87">
-        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 86 - 1), NA())</f>
+        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 86 - 1), NA())</f>
         <v/>
       </c>
       <c r="R87">
-        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 86 - 1), NA())</f>
+        <f>IF(86&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 86 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="P88" s="2">
-        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 87 - 1), NA())</f>
+        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 87 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q88">
-        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 87 - 1), NA())</f>
+        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 87 - 1), NA())</f>
         <v/>
       </c>
       <c r="R88">
-        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 87 - 1), NA())</f>
+        <f>IF(87&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 87 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="P89" s="2">
-        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 88 - 1), NA())</f>
+        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 88 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q89">
-        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 88 - 1), NA())</f>
+        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 88 - 1), NA())</f>
         <v/>
       </c>
       <c r="R89">
-        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 88 - 1), NA())</f>
+        <f>IF(88&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 88 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="P90" s="2">
-        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 89 - 1), NA())</f>
+        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 89 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q90">
-        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 89 - 1), NA())</f>
+        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 89 - 1), NA())</f>
         <v/>
       </c>
       <c r="R90">
-        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 89 - 1), NA())</f>
+        <f>IF(89&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 89 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="P91" s="2">
-        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 90 - 1), NA())</f>
+        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 90 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q91">
-        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 90 - 1), NA())</f>
+        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 90 - 1), NA())</f>
         <v/>
       </c>
       <c r="R91">
-        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 90 - 1), NA())</f>
+        <f>IF(90&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 90 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="P92" s="2">
-        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 91 - 1), NA())</f>
+        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 91 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q92">
-        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 91 - 1), NA())</f>
+        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 91 - 1), NA())</f>
         <v/>
       </c>
       <c r="R92">
-        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 91 - 1), NA())</f>
+        <f>IF(91&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 91 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="P93" s="2">
-        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 92 - 1), NA())</f>
+        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 92 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q93">
-        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 92 - 1), NA())</f>
+        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 92 - 1), NA())</f>
         <v/>
       </c>
       <c r="R93">
-        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 92 - 1), NA())</f>
+        <f>IF(92&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 92 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="P94" s="2">
-        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 93 - 1), NA())</f>
+        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 93 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q94">
-        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 93 - 1), NA())</f>
+        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 93 - 1), NA())</f>
         <v/>
       </c>
       <c r="R94">
-        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 93 - 1), NA())</f>
+        <f>IF(93&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 93 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="P95" s="2">
-        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 94 - 1), NA())</f>
+        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 94 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q95">
-        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 94 - 1), NA())</f>
+        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 94 - 1), NA())</f>
         <v/>
       </c>
       <c r="R95">
-        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 94 - 1), NA())</f>
+        <f>IF(94&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 94 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="P96" s="2">
-        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 95 - 1), NA())</f>
+        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 95 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q96">
-        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 95 - 1), NA())</f>
+        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 95 - 1), NA())</f>
         <v/>
       </c>
       <c r="R96">
-        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 95 - 1), NA())</f>
+        <f>IF(95&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 95 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="P97" s="2">
-        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 96 - 1), NA())</f>
+        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 96 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q97">
-        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 96 - 1), NA())</f>
+        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 96 - 1), NA())</f>
         <v/>
       </c>
       <c r="R97">
-        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 96 - 1), NA())</f>
+        <f>IF(96&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 96 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="P98" s="2">
-        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 97 - 1), NA())</f>
+        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 97 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q98">
-        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 97 - 1), NA())</f>
+        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 97 - 1), NA())</f>
         <v/>
       </c>
       <c r="R98">
-        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 97 - 1), NA())</f>
+        <f>IF(97&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 97 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="P99" s="2">
-        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 98 - 1), NA())</f>
+        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 98 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q99">
-        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 98 - 1), NA())</f>
+        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 98 - 1), NA())</f>
         <v/>
       </c>
       <c r="R99">
-        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 98 - 1), NA())</f>
+        <f>IF(98&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 98 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="P100" s="2">
-        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 99 - 1), NA())</f>
+        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 99 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q100">
-        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 99 - 1), NA())</f>
+        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 99 - 1), NA())</f>
         <v/>
       </c>
       <c r="R100">
-        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 99 - 1), NA())</f>
+        <f>IF(99&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 99 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="P101" s="2">
-        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 100 - 1), NA())</f>
+        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 100 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q101">
-        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 100 - 1), NA())</f>
+        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 100 - 1), NA())</f>
         <v/>
       </c>
       <c r="R101">
-        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 100 - 1), NA())</f>
+        <f>IF(100&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 100 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="P102" s="2">
-        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 101 - 1), NA())</f>
+        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 101 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q102">
-        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 101 - 1), NA())</f>
+        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 101 - 1), NA())</f>
         <v/>
       </c>
       <c r="R102">
-        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 101 - 1), NA())</f>
+        <f>IF(101&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 101 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="P103" s="2">
-        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 102 - 1), NA())</f>
+        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 102 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q103">
-        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 102 - 1), NA())</f>
+        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 102 - 1), NA())</f>
         <v/>
       </c>
       <c r="R103">
-        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 102 - 1), NA())</f>
+        <f>IF(102&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 102 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="P104" s="2">
-        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 103 - 1), NA())</f>
+        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 103 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q104">
-        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 103 - 1), NA())</f>
+        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 103 - 1), NA())</f>
         <v/>
       </c>
       <c r="R104">
-        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 103 - 1), NA())</f>
+        <f>IF(103&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 103 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="P105" s="2">
-        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 104 - 1), NA())</f>
+        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 104 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q105">
-        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 104 - 1), NA())</f>
+        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 104 - 1), NA())</f>
         <v/>
       </c>
       <c r="R105">
-        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 104 - 1), NA())</f>
+        <f>IF(104&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 104 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="P106" s="2">
-        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 105 - 1), NA())</f>
+        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 105 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q106">
-        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 105 - 1), NA())</f>
+        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 105 - 1), NA())</f>
         <v/>
       </c>
       <c r="R106">
-        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 105 - 1), NA())</f>
+        <f>IF(105&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 105 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="P107" s="2">
-        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 106 - 1), NA())</f>
+        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 106 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q107">
-        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 106 - 1), NA())</f>
+        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 106 - 1), NA())</f>
         <v/>
       </c>
       <c r="R107">
-        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 106 - 1), NA())</f>
+        <f>IF(106&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 106 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="P108" s="2">
-        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 107 - 1), NA())</f>
+        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 107 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q108">
-        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 107 - 1), NA())</f>
+        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 107 - 1), NA())</f>
         <v/>
       </c>
       <c r="R108">
-        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 107 - 1), NA())</f>
+        <f>IF(107&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 107 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="P109" s="2">
-        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 108 - 1), NA())</f>
+        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 108 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q109">
-        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 108 - 1), NA())</f>
+        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 108 - 1), NA())</f>
         <v/>
       </c>
       <c r="R109">
-        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 108 - 1), NA())</f>
+        <f>IF(108&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 108 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="P110" s="2">
-        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 109 - 1), NA())</f>
+        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 109 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q110">
-        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 109 - 1), NA())</f>
+        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 109 - 1), NA())</f>
         <v/>
       </c>
       <c r="R110">
-        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 109 - 1), NA())</f>
+        <f>IF(109&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 109 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="P111" s="2">
-        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 110 - 1), NA())</f>
+        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 110 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q111">
-        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 110 - 1), NA())</f>
+        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 110 - 1), NA())</f>
         <v/>
       </c>
       <c r="R111">
-        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 110 - 1), NA())</f>
+        <f>IF(110&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 110 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="P112" s="2">
-        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 111 - 1), NA())</f>
+        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 111 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q112">
-        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 111 - 1), NA())</f>
+        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 111 - 1), NA())</f>
         <v/>
       </c>
       <c r="R112">
-        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 111 - 1), NA())</f>
+        <f>IF(111&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 111 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="P113" s="2">
-        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 112 - 1), NA())</f>
+        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 112 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q113">
-        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 112 - 1), NA())</f>
+        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 112 - 1), NA())</f>
         <v/>
       </c>
       <c r="R113">
-        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 112 - 1), NA())</f>
+        <f>IF(112&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 112 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="P114" s="2">
-        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 113 - 1), NA())</f>
+        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 113 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q114">
-        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 113 - 1), NA())</f>
+        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 113 - 1), NA())</f>
         <v/>
       </c>
       <c r="R114">
-        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 113 - 1), NA())</f>
+        <f>IF(113&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 113 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="P115" s="2">
-        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 114 - 1), NA())</f>
+        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 114 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q115">
-        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 114 - 1), NA())</f>
+        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 114 - 1), NA())</f>
         <v/>
       </c>
       <c r="R115">
-        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 114 - 1), NA())</f>
+        <f>IF(114&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 114 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="P116" s="2">
-        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 115 - 1), NA())</f>
+        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 115 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q116">
-        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 115 - 1), NA())</f>
+        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 115 - 1), NA())</f>
         <v/>
       </c>
       <c r="R116">
-        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 115 - 1), NA())</f>
+        <f>IF(115&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 115 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="P117" s="2">
-        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 116 - 1), NA())</f>
+        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 116 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q117">
-        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 116 - 1), NA())</f>
+        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 116 - 1), NA())</f>
         <v/>
       </c>
       <c r="R117">
-        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 116 - 1), NA())</f>
+        <f>IF(116&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 116 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="P118" s="2">
-        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 117 - 1), NA())</f>
+        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 117 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q118">
-        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 117 - 1), NA())</f>
+        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 117 - 1), NA())</f>
         <v/>
       </c>
       <c r="R118">
-        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 117 - 1), NA())</f>
+        <f>IF(117&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 117 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="P119" s="2">
-        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 118 - 1), NA())</f>
+        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 118 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q119">
-        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 118 - 1), NA())</f>
+        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 118 - 1), NA())</f>
         <v/>
       </c>
       <c r="R119">
-        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 118 - 1), NA())</f>
+        <f>IF(118&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 118 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="P120" s="2">
-        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 119 - 1), NA())</f>
+        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 119 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q120">
-        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 119 - 1), NA())</f>
+        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 119 - 1), NA())</f>
         <v/>
       </c>
       <c r="R120">
-        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 119 - 1), NA())</f>
+        <f>IF(119&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 119 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="P121" s="2">
-        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 120 - 1), NA())</f>
+        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 120 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q121">
-        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 120 - 1), NA())</f>
+        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 120 - 1), NA())</f>
         <v/>
       </c>
       <c r="R121">
-        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 120 - 1), NA())</f>
+        <f>IF(120&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 120 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="P122" s="2">
-        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 121 - 1), NA())</f>
+        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 121 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q122">
-        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 121 - 1), NA())</f>
+        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 121 - 1), NA())</f>
         <v/>
       </c>
       <c r="R122">
-        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 121 - 1), NA())</f>
+        <f>IF(121&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 121 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="123">
       <c r="P123" s="2">
-        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 122 - 1), NA())</f>
+        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 122 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q123">
-        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 122 - 1), NA())</f>
+        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 122 - 1), NA())</f>
         <v/>
       </c>
       <c r="R123">
-        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 122 - 1), NA())</f>
+        <f>IF(122&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 122 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="124">
       <c r="P124" s="2">
-        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 123 - 1), NA())</f>
+        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 123 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q124">
-        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 123 - 1), NA())</f>
+        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 123 - 1), NA())</f>
         <v/>
       </c>
       <c r="R124">
-        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 123 - 1), NA())</f>
+        <f>IF(123&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 123 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="125">
       <c r="P125" s="2">
-        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 124 - 1), NA())</f>
+        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 124 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q125">
-        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 124 - 1), NA())</f>
+        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 124 - 1), NA())</f>
         <v/>
       </c>
       <c r="R125">
-        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 124 - 1), NA())</f>
+        <f>IF(124&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 124 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="126">
       <c r="P126" s="2">
-        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 125 - 1), NA())</f>
+        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 125 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q126">
-        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 125 - 1), NA())</f>
+        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 125 - 1), NA())</f>
         <v/>
       </c>
       <c r="R126">
-        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 125 - 1), NA())</f>
+        <f>IF(125&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 125 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="127">
       <c r="P127" s="2">
-        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 126 - 1), NA())</f>
+        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 126 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q127">
-        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 126 - 1), NA())</f>
+        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 126 - 1), NA())</f>
         <v/>
       </c>
       <c r="R127">
-        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 126 - 1), NA())</f>
+        <f>IF(126&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 126 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="P128" s="2">
-        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 127 - 1), NA())</f>
+        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 127 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q128">
-        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 127 - 1), NA())</f>
+        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 127 - 1), NA())</f>
         <v/>
       </c>
       <c r="R128">
-        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 127 - 1), NA())</f>
+        <f>IF(127&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 127 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="129">
       <c r="P129" s="2">
-        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 128 - 1), NA())</f>
+        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 128 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q129">
-        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 128 - 1), NA())</f>
+        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 128 - 1), NA())</f>
         <v/>
       </c>
       <c r="R129">
-        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 128 - 1), NA())</f>
+        <f>IF(128&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 128 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="130">
       <c r="P130" s="2">
-        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 129 - 1), NA())</f>
+        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 129 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q130">
-        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 129 - 1), NA())</f>
+        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 129 - 1), NA())</f>
         <v/>
       </c>
       <c r="R130">
-        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 129 - 1), NA())</f>
+        <f>IF(129&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 129 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="131">
       <c r="P131" s="2">
-        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 130 - 1), NA())</f>
+        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 130 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q131">
-        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 130 - 1), NA())</f>
+        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 130 - 1), NA())</f>
         <v/>
       </c>
       <c r="R131">
-        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 130 - 1), NA())</f>
+        <f>IF(130&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 130 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="132">
       <c r="P132" s="2">
-        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 131 - 1), NA())</f>
+        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 131 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q132">
-        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 131 - 1), NA())</f>
+        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 131 - 1), NA())</f>
         <v/>
       </c>
       <c r="R132">
-        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 131 - 1), NA())</f>
+        <f>IF(131&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 131 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="133">
       <c r="P133" s="2">
-        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 132 - 1), NA())</f>
+        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 132 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q133">
-        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 132 - 1), NA())</f>
+        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 132 - 1), NA())</f>
         <v/>
       </c>
       <c r="R133">
-        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 132 - 1), NA())</f>
+        <f>IF(132&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 132 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="134">
       <c r="P134" s="2">
-        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 133 - 1), NA())</f>
+        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 133 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q134">
-        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 133 - 1), NA())</f>
+        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 133 - 1), NA())</f>
         <v/>
       </c>
       <c r="R134">
-        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 133 - 1), NA())</f>
+        <f>IF(133&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 133 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="135">
       <c r="P135" s="2">
-        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 134 - 1), NA())</f>
+        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 134 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q135">
-        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 134 - 1), NA())</f>
+        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 134 - 1), NA())</f>
         <v/>
       </c>
       <c r="R135">
-        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 134 - 1), NA())</f>
+        <f>IF(134&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 134 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="136">
       <c r="P136" s="2">
-        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 135 - 1), NA())</f>
+        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 135 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q136">
-        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 135 - 1), NA())</f>
+        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 135 - 1), NA())</f>
         <v/>
       </c>
       <c r="R136">
-        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 135 - 1), NA())</f>
+        <f>IF(135&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 135 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="137">
       <c r="P137" s="2">
-        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 136 - 1), NA())</f>
+        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 136 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q137">
-        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 136 - 1), NA())</f>
+        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 136 - 1), NA())</f>
         <v/>
       </c>
       <c r="R137">
-        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 136 - 1), NA())</f>
+        <f>IF(136&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 136 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="138">
       <c r="P138" s="2">
-        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 137 - 1), NA())</f>
+        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 137 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q138">
-        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 137 - 1), NA())</f>
+        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 137 - 1), NA())</f>
         <v/>
       </c>
       <c r="R138">
-        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 137 - 1), NA())</f>
+        <f>IF(137&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 137 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="139">
       <c r="P139" s="2">
-        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 138 - 1), NA())</f>
+        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 138 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q139">
-        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 138 - 1), NA())</f>
+        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 138 - 1), NA())</f>
         <v/>
       </c>
       <c r="R139">
-        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 138 - 1), NA())</f>
+        <f>IF(138&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 138 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="140">
       <c r="P140" s="2">
-        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 139 - 1), NA())</f>
+        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 139 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q140">
-        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 139 - 1), NA())</f>
+        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 139 - 1), NA())</f>
         <v/>
       </c>
       <c r="R140">
-        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 139 - 1), NA())</f>
+        <f>IF(139&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 139 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="141">
       <c r="P141" s="2">
-        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 140 - 1), NA())</f>
+        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 140 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q141">
-        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 140 - 1), NA())</f>
+        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 140 - 1), NA())</f>
         <v/>
       </c>
       <c r="R141">
-        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 140 - 1), NA())</f>
+        <f>IF(140&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 140 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="142">
       <c r="P142" s="2">
-        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 141 - 1), NA())</f>
+        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 141 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q142">
-        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 141 - 1), NA())</f>
+        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 141 - 1), NA())</f>
         <v/>
       </c>
       <c r="R142">
-        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 141 - 1), NA())</f>
+        <f>IF(141&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 141 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="143">
       <c r="P143" s="2">
-        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 142 - 1), NA())</f>
+        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 142 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q143">
-        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 142 - 1), NA())</f>
+        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 142 - 1), NA())</f>
         <v/>
       </c>
       <c r="R143">
-        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 142 - 1), NA())</f>
+        <f>IF(142&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 142 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="144">
       <c r="P144" s="2">
-        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 143 - 1), NA())</f>
+        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 143 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q144">
-        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 143 - 1), NA())</f>
+        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 143 - 1), NA())</f>
         <v/>
       </c>
       <c r="R144">
-        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 143 - 1), NA())</f>
+        <f>IF(143&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 143 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="145">
       <c r="P145" s="2">
-        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 144 - 1), NA())</f>
+        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 144 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q145">
-        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 144 - 1), NA())</f>
+        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 144 - 1), NA())</f>
         <v/>
       </c>
       <c r="R145">
-        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 144 - 1), NA())</f>
+        <f>IF(144&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 144 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="146">
       <c r="P146" s="2">
-        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 145 - 1), NA())</f>
+        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 145 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q146">
-        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 145 - 1), NA())</f>
+        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 145 - 1), NA())</f>
         <v/>
       </c>
       <c r="R146">
-        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 145 - 1), NA())</f>
+        <f>IF(145&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 145 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="147">
       <c r="P147" s="2">
-        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 146 - 1), NA())</f>
+        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 146 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q147">
-        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 146 - 1), NA())</f>
+        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 146 - 1), NA())</f>
         <v/>
       </c>
       <c r="R147">
-        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 146 - 1), NA())</f>
+        <f>IF(146&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 146 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="148">
       <c r="P148" s="2">
-        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 147 - 1), NA())</f>
+        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 147 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q148">
-        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 147 - 1), NA())</f>
+        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 147 - 1), NA())</f>
         <v/>
       </c>
       <c r="R148">
-        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 147 - 1), NA())</f>
+        <f>IF(147&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 147 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="149">
       <c r="P149" s="2">
-        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 148 - 1), NA())</f>
+        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 148 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q149">
-        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 148 - 1), NA())</f>
+        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 148 - 1), NA())</f>
         <v/>
       </c>
       <c r="R149">
-        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 148 - 1), NA())</f>
+        <f>IF(148&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 148 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="150">
       <c r="P150" s="2">
-        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 149 - 1), NA())</f>
+        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 149 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q150">
-        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 149 - 1), NA())</f>
+        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 149 - 1), NA())</f>
         <v/>
       </c>
       <c r="R150">
-        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 149 - 1), NA())</f>
+        <f>IF(149&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 149 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="151">
       <c r="P151" s="2">
-        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 150 - 1), NA())</f>
+        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 150 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q151">
-        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 150 - 1), NA())</f>
+        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 150 - 1), NA())</f>
         <v/>
       </c>
       <c r="R151">
-        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 150 - 1), NA())</f>
+        <f>IF(150&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 150 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="152">
       <c r="P152" s="2">
-        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 151 - 1), NA())</f>
+        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 151 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q152">
-        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 151 - 1), NA())</f>
+        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 151 - 1), NA())</f>
         <v/>
       </c>
       <c r="R152">
-        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 151 - 1), NA())</f>
+        <f>IF(151&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 151 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="153">
       <c r="P153" s="2">
-        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 152 - 1), NA())</f>
+        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 152 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q153">
-        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 152 - 1), NA())</f>
+        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 152 - 1), NA())</f>
         <v/>
       </c>
       <c r="R153">
-        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 152 - 1), NA())</f>
+        <f>IF(152&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 152 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="154">
       <c r="P154" s="2">
-        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 153 - 1), NA())</f>
+        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 153 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q154">
-        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 153 - 1), NA())</f>
+        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 153 - 1), NA())</f>
         <v/>
       </c>
       <c r="R154">
-        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 153 - 1), NA())</f>
+        <f>IF(153&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 153 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="155">
       <c r="P155" s="2">
-        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 154 - 1), NA())</f>
+        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 154 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q155">
-        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 154 - 1), NA())</f>
+        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 154 - 1), NA())</f>
         <v/>
       </c>
       <c r="R155">
-        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 154 - 1), NA())</f>
+        <f>IF(154&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 154 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="156">
       <c r="P156" s="2">
-        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 155 - 1), NA())</f>
+        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 155 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q156">
-        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 155 - 1), NA())</f>
+        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 155 - 1), NA())</f>
         <v/>
       </c>
       <c r="R156">
-        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 155 - 1), NA())</f>
+        <f>IF(155&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 155 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="157">
       <c r="P157" s="2">
-        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 156 - 1), NA())</f>
+        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 156 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q157">
-        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 156 - 1), NA())</f>
+        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 156 - 1), NA())</f>
         <v/>
       </c>
       <c r="R157">
-        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 156 - 1), NA())</f>
+        <f>IF(156&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 156 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="158">
       <c r="P158" s="2">
-        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 157 - 1), NA())</f>
+        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 157 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q158">
-        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 157 - 1), NA())</f>
+        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 157 - 1), NA())</f>
         <v/>
       </c>
       <c r="R158">
-        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 157 - 1), NA())</f>
+        <f>IF(157&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 157 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="159">
       <c r="P159" s="2">
-        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 158 - 1), NA())</f>
+        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 158 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q159">
-        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 158 - 1), NA())</f>
+        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 158 - 1), NA())</f>
         <v/>
       </c>
       <c r="R159">
-        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 158 - 1), NA())</f>
+        <f>IF(158&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 158 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="160">
       <c r="P160" s="2">
-        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 159 - 1), NA())</f>
+        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 159 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q160">
-        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 159 - 1), NA())</f>
+        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 159 - 1), NA())</f>
         <v/>
       </c>
       <c r="R160">
-        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 159 - 1), NA())</f>
+        <f>IF(159&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 159 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="161">
       <c r="P161" s="2">
-        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 160 - 1), NA())</f>
+        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 160 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q161">
-        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 160 - 1), NA())</f>
+        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 160 - 1), NA())</f>
         <v/>
       </c>
       <c r="R161">
-        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 160 - 1), NA())</f>
+        <f>IF(160&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 160 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="162">
       <c r="P162" s="2">
-        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 161 - 1), NA())</f>
+        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 161 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q162">
-        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 161 - 1), NA())</f>
+        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 161 - 1), NA())</f>
         <v/>
       </c>
       <c r="R162">
-        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 161 - 1), NA())</f>
+        <f>IF(161&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 161 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="163">
       <c r="P163" s="2">
-        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 162 - 1), NA())</f>
+        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 162 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q163">
-        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 162 - 1), NA())</f>
+        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 162 - 1), NA())</f>
         <v/>
       </c>
       <c r="R163">
-        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 162 - 1), NA())</f>
+        <f>IF(162&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 162 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="164">
       <c r="P164" s="2">
-        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 163 - 1), NA())</f>
+        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 163 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q164">
-        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 163 - 1), NA())</f>
+        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 163 - 1), NA())</f>
         <v/>
       </c>
       <c r="R164">
-        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 163 - 1), NA())</f>
+        <f>IF(163&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 163 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="165">
       <c r="P165" s="2">
-        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 164 - 1), NA())</f>
+        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 164 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q165">
-        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 164 - 1), NA())</f>
+        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 164 - 1), NA())</f>
         <v/>
       </c>
       <c r="R165">
-        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 164 - 1), NA())</f>
+        <f>IF(164&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 164 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="166">
       <c r="P166" s="2">
-        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 165 - 1), NA())</f>
+        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 165 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q166">
-        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 165 - 1), NA())</f>
+        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 165 - 1), NA())</f>
         <v/>
       </c>
       <c r="R166">
-        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 165 - 1), NA())</f>
+        <f>IF(165&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 165 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="167">
       <c r="P167" s="2">
-        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 166 - 1), NA())</f>
+        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 166 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q167">
-        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 166 - 1), NA())</f>
+        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 166 - 1), NA())</f>
         <v/>
       </c>
       <c r="R167">
-        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 166 - 1), NA())</f>
+        <f>IF(166&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 166 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="168">
       <c r="P168" s="2">
-        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 167 - 1), NA())</f>
+        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 167 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q168">
-        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 167 - 1), NA())</f>
+        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 167 - 1), NA())</f>
         <v/>
       </c>
       <c r="R168">
-        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 167 - 1), NA())</f>
+        <f>IF(167&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 167 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="169">
       <c r="P169" s="2">
-        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 168 - 1), NA())</f>
+        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 168 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q169">
-        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 168 - 1), NA())</f>
+        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 168 - 1), NA())</f>
         <v/>
       </c>
       <c r="R169">
-        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 168 - 1), NA())</f>
+        <f>IF(168&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 168 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="170">
       <c r="P170" s="2">
-        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$8 - 1 + 169 - 1), NA())</f>
+        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$495, $G$8 - 1 + 169 - 1), NA())</f>
         <v/>
       </c>
       <c r="Q170">
-        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$494, $G$8 - 1 + 169 - 1), NA())</f>
+        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$E$2:$E$495, $G$8 - 1 + 169 - 1), NA())</f>
         <v/>
       </c>
       <c r="R170">
-        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$494, $G$8 - 1 + 169 - 1), NA())</f>
+        <f>IF(169&lt;=$I$8, INDEX('Precios Diarios'!$F$2:$F$495, $G$8 - 1 + 169 - 1), NA())</f>
         <v/>
       </c>
     </row>
     <row r="171">
       <c r="P171" s="2">
-        <f>IF(170&lt;=$I$8, INDEX('Precios Diarios'!$A$2:$A$494, $G$